--- a/docs/plan/dit-annual-plan.xlsx
+++ b/docs/plan/dit-annual-plan.xlsx
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 26 недель не входят и идут до них.</t>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 13 недель не входят и идут до них.</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -635,209 +635,254 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>46451</v>
+        <v>46360</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Дата начала + 26 недель, последний рабочий день</t>
+          <t>Дата начала + 13 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Трудозатраты, ч-д</t>
+          <t>Трудозатраты всего, ч-д</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>26 недель × 5 рабочих дней. План предполагает одного инженера на полной занятости.</t>
+          <t>Сумма по этапам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>11515</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Этапы 1–7. Помещается в 13 недель × 5 дней = 65 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>B8*B9</f>
-        <v>1496950</v>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>29</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Этапы 8–9 (консолидация мелких АТС и перенумерация) — работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером 85 ч-д за 13 недель не выполняются, это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
+          <t>Внутренняя ставка, ₽/ч-д</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>11515</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Оборудование (4 сервера) проходит закупкой, в себестоимость работ не входит — как и во всех строках исходного плана ДИТ.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>1255</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B12" s="6">
+        <f>B8*B11</f>
+        <v>978775</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>12</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Сервер под московский узел проходит закупкой, в себестоимость работ не входит — как и во всех строках исходного плана ДИТ.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
+          <t>Абонентов в периметре</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>8</v>
+        <v>1255</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>7 региональных узлов + резервный мастер</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>8 узлов + арбитр без данных</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Новогодние каникулы</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>неделя 18</t>
-        </is>
+          <t>Узлов кластера после внедрения</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. При старте 07.09.2026 неделя 18 приходится на 04–08.01.2027, то есть на нерабочие дни. Сроки в плане календарные и этого не учитывают. Либо сдвиньте дату начала, либо считайте план 27-недельным: этапы 8 и 9 (консолидация и перенумерация) в эту неделю не ведутся.</t>
+          <t>Ростов (мастер) 426, Воронеж 445, Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80. Сумма 1255 сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Голосов в кворуме</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Пять узлов, число нечётное — отдельный арбитр не нужен. Кластер переживает потерю двух узлов из пяти.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Серверов нужно докупить</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>ДОПУЩЕНИЕ: «у нас 5 серверов» прочитано как пять узлов кластера. Четыре площадки уже имеют свои машины, новый сервер нужен только под Москву. Ставрополь (74 абонента) остаётся на ростовском сервере, как сейчас.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Резервный мастер отдельной машиной</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Пятый сервер занят московским узлом. Отдельная машина под тёплый резерв не требуется: каждый узел — клон мастера, FreePBX на нём уже установлен и только отключён, поэтому роль мастера передаётся на любой рабочий узел. Процедура отрабатывается на этапе 7 учебно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Исполнитель</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Инженер проекта и ответственные за стадии. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>IP-адреса Славянска-на-Кубани и локального PBX</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>В исходных данных аудита отсутствуют, запрашиваются в первую неделю.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -854,7 +899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO56"/>
+  <dimension ref="A1:AB50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7" customWidth="1" min="1" max="1"/>
@@ -885,19 +930,6 @@
     <col width="6.6" customWidth="1" min="26" max="26"/>
     <col width="6.6" customWidth="1" min="27" max="27"/>
     <col width="6.6" customWidth="1" min="28" max="28"/>
-    <col width="6.6" customWidth="1" min="29" max="29"/>
-    <col width="6.6" customWidth="1" min="30" max="30"/>
-    <col width="6.6" customWidth="1" min="31" max="31"/>
-    <col width="6.6" customWidth="1" min="32" max="32"/>
-    <col width="6.6" customWidth="1" min="33" max="33"/>
-    <col width="6.6" customWidth="1" min="34" max="34"/>
-    <col width="6.6" customWidth="1" min="35" max="35"/>
-    <col width="6.6" customWidth="1" min="36" max="36"/>
-    <col width="6.6" customWidth="1" min="37" max="37"/>
-    <col width="6.6" customWidth="1" min="38" max="38"/>
-    <col width="6.6" customWidth="1" min="39" max="39"/>
-    <col width="6.6" customWidth="1" min="40" max="40"/>
-    <col width="6.6" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -921,26 +953,6 @@
           <t>Ноябрь 2026</t>
         </is>
       </c>
-      <c r="AC1" s="12" t="inlineStr">
-        <is>
-          <t>Декабрь 2026</t>
-        </is>
-      </c>
-      <c r="AG1" s="12" t="inlineStr">
-        <is>
-          <t>Январь 2027</t>
-        </is>
-      </c>
-      <c r="AK1" s="12" t="inlineStr">
-        <is>
-          <t>Февраль 2027</t>
-        </is>
-      </c>
-      <c r="AO1" s="12" t="inlineStr">
-        <is>
-          <t>Март 2027</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -1081,71 +1093,6 @@
       <c r="AB2" s="14" t="inlineStr">
         <is>
           <t>30-06</t>
-        </is>
-      </c>
-      <c r="AC2" s="14" t="inlineStr">
-        <is>
-          <t>07-13</t>
-        </is>
-      </c>
-      <c r="AD2" s="14" t="inlineStr">
-        <is>
-          <t>14-20</t>
-        </is>
-      </c>
-      <c r="AE2" s="14" t="inlineStr">
-        <is>
-          <t>21-27</t>
-        </is>
-      </c>
-      <c r="AF2" s="14" t="inlineStr">
-        <is>
-          <t>28-03</t>
-        </is>
-      </c>
-      <c r="AG2" s="14" t="inlineStr">
-        <is>
-          <t>04-10</t>
-        </is>
-      </c>
-      <c r="AH2" s="14" t="inlineStr">
-        <is>
-          <t>11-17</t>
-        </is>
-      </c>
-      <c r="AI2" s="14" t="inlineStr">
-        <is>
-          <t>18-24</t>
-        </is>
-      </c>
-      <c r="AJ2" s="14" t="inlineStr">
-        <is>
-          <t>25-31</t>
-        </is>
-      </c>
-      <c r="AK2" s="14" t="inlineStr">
-        <is>
-          <t>01-07</t>
-        </is>
-      </c>
-      <c r="AL2" s="14" t="inlineStr">
-        <is>
-          <t>08-14</t>
-        </is>
-      </c>
-      <c r="AM2" s="14" t="inlineStr">
-        <is>
-          <t>15-21</t>
-        </is>
-      </c>
-      <c r="AN2" s="14" t="inlineStr">
-        <is>
-          <t>22-28</t>
-        </is>
-      </c>
-      <c r="AO2" s="14" t="inlineStr">
-        <is>
-          <t>01-07</t>
         </is>
       </c>
     </row>
@@ -1176,21 +1123,21 @@
         <v>46272</v>
       </c>
       <c r="G3" s="17">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H3" s="17">
         <f>G3</f>
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="I3" s="15" t="inlineStr">
         <is>
-          <t>Шесть регионов не связаны между собой сетью; у двух площадок нет собственной АТС; у операторов нет отдельных учётных записей на каждую площадку</t>
+          <t>Пять площадок не связаны между собой сетью; у операторов нет отдельных учётных записей на каждую площадку</t>
         </is>
       </c>
       <c r="J3" s="15" t="inlineStr">
         <is>
-          <t>VPN между шестью регионами поднят, RTT измерен и зафиксирован, серверы получены, у каждой площадки свой SIP-пользователь ВАТС</t>
+          <t>VPN между площадками поднят, RTT измерен и зафиксирован, пятый сервер под Москву получен, у каждой площадки свой SIP-пользователь ВАТС</t>
         </is>
       </c>
       <c r="K3" s="16" t="n"/>
@@ -1200,18 +1147,17 @@
         </is>
       </c>
       <c r="M3" s="15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N3" s="18">
-        <f>Параметры!$B$9*M3</f>
-        <v>115150</v>
+        <f>Параметры!$B$11*M3</f>
+        <v>92120</v>
       </c>
       <c r="O3" s="18" t="n">
         <v>0</v>
       </c>
       <c r="P3" s="19" t="n"/>
       <c r="Q3" s="19" t="n"/>
-      <c r="R3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -1263,7 +1209,7 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>Организовать site-to-site VPN между шестью регионами</t>
+          <t>Организовать site-to-site VPN между пятью площадками</t>
         </is>
       </c>
       <c r="C5" s="22" t="n"/>
@@ -1274,8 +1220,8 @@
         <v>46272</v>
       </c>
       <c r="G5" s="23">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="22" t="n"/>
@@ -1297,7 +1243,6 @@
       <c r="O5" s="22" t="n"/>
       <c r="P5" s="19" t="n"/>
       <c r="Q5" s="19" t="n"/>
-      <c r="R5" s="19" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -1307,25 +1252,25 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>Замерить RTT и потери между всеми парами регионов</t>
+          <t>Замерить RTT и потери между всеми парами площадок</t>
         </is>
       </c>
       <c r="C6" s="22" t="n"/>
       <c r="D6" s="22" t="n"/>
       <c r="E6" s="22" t="n"/>
       <c r="F6" s="23">
-        <f>Параметры!$B$5+14</f>
-        <v>46286</v>
+        <f>Параметры!$B$5+7</f>
+        <v>46279</v>
       </c>
       <c r="G6" s="23">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>Замеры выполнены; регионы с RTT выше 50 мс исключены из синхронной репликации</t>
+          <t>Замеры выполнены; площадки с RTT выше 50 мс исключены из синхронной репликации</t>
         </is>
       </c>
       <c r="K6" s="24" t="n"/>
@@ -1335,11 +1280,11 @@
         </is>
       </c>
       <c r="M6" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="22" t="n"/>
       <c r="O6" s="22" t="n"/>
-      <c r="R6" s="19" t="n"/>
+      <c r="Q6" s="19" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -1391,7 +1336,7 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Заказать серверы: Ставрополь, Москва, резервный мастер, арбитр</t>
+          <t>Подготовить сервер под московский узел</t>
         </is>
       </c>
       <c r="C8" s="22" t="n"/>
@@ -1402,14 +1347,14 @@
         <v>46272</v>
       </c>
       <c r="G8" s="23">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H8" s="22" t="n"/>
       <c r="I8" s="22" t="n"/>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>Четыре сервера получены и доступны по сети</t>
+          <t>Сервер получен и доступен по сети</t>
         </is>
       </c>
       <c r="K8" s="24" t="n"/>
@@ -1419,13 +1364,12 @@
         </is>
       </c>
       <c r="M8" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="19" t="n"/>
       <c r="Q8" s="19" t="n"/>
-      <c r="R8" s="19" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
@@ -1442,18 +1386,18 @@
       <c r="D9" s="22" t="n"/>
       <c r="E9" s="22" t="n"/>
       <c r="F9" s="23">
-        <f>Параметры!$B$5+7</f>
-        <v>46279</v>
+        <f>Параметры!$B$5+0</f>
+        <v>46272</v>
       </c>
       <c r="G9" s="23">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H9" s="22" t="n"/>
       <c r="I9" s="22" t="n"/>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>Учётные записи получены на все шесть площадок</t>
+          <t>Учётные записи получены на все пять площадок</t>
         </is>
       </c>
       <c r="K9" s="24" t="n"/>
@@ -1467,8 +1411,8 @@
       </c>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
+      <c r="P9" s="19" t="n"/>
       <c r="Q9" s="19" t="n"/>
-      <c r="R9" s="19" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -1493,16 +1437,16 @@
       </c>
       <c r="E10" s="16" t="n"/>
       <c r="F10" s="17">
-        <f>Параметры!$B$5+7</f>
-        <v>46279</v>
+        <f>Параметры!$B$5+0</f>
+        <v>46272</v>
       </c>
       <c r="G10" s="17">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H10" s="17">
         <f>G10</f>
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
@@ -1521,17 +1465,17 @@
         </is>
       </c>
       <c r="M10" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N10" s="18">
-        <f>Параметры!$B$9*M10</f>
-        <v>138180</v>
+        <f>Параметры!$B$11*M10</f>
+        <v>115150</v>
       </c>
       <c r="O10" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="P10" s="19" t="n"/>
       <c r="Q10" s="19" t="n"/>
-      <c r="R10" s="19" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
@@ -1548,12 +1492,12 @@
       <c r="D11" s="22" t="n"/>
       <c r="E11" s="22" t="n"/>
       <c r="F11" s="23">
-        <f>Параметры!$B$5+7</f>
-        <v>46279</v>
+        <f>Параметры!$B$5+0</f>
+        <v>46272</v>
       </c>
       <c r="G11" s="23">
-        <f>Параметры!$B$5+11</f>
-        <v>46283</v>
+        <f>Параметры!$B$5+4</f>
+        <v>46276</v>
       </c>
       <c r="H11" s="22" t="n"/>
       <c r="I11" s="22" t="n"/>
@@ -1573,7 +1517,7 @@
       </c>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
-      <c r="Q11" s="19" t="n"/>
+      <c r="P11" s="19" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
@@ -1590,12 +1534,12 @@
       <c r="D12" s="22" t="n"/>
       <c r="E12" s="22" t="n"/>
       <c r="F12" s="23">
-        <f>Параметры!$B$5+7</f>
-        <v>46279</v>
+        <f>Параметры!$B$5+0</f>
+        <v>46272</v>
       </c>
       <c r="G12" s="23">
-        <f>Параметры!$B$5+11</f>
-        <v>46283</v>
+        <f>Параметры!$B$5+4</f>
+        <v>46276</v>
       </c>
       <c r="H12" s="22" t="n"/>
       <c r="I12" s="22" t="n"/>
@@ -1615,7 +1559,7 @@
       </c>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
-      <c r="Q12" s="19" t="n"/>
+      <c r="P12" s="19" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
@@ -1632,12 +1576,12 @@
       <c r="D13" s="22" t="n"/>
       <c r="E13" s="22" t="n"/>
       <c r="F13" s="23">
-        <f>Параметры!$B$5+7</f>
-        <v>46279</v>
+        <f>Параметры!$B$5+0</f>
+        <v>46272</v>
       </c>
       <c r="G13" s="23">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H13" s="22" t="n"/>
       <c r="I13" s="22" t="n"/>
@@ -1653,12 +1597,12 @@
         </is>
       </c>
       <c r="M13" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
+      <c r="P13" s="19" t="n"/>
       <c r="Q13" s="19" t="n"/>
-      <c r="R13" s="19" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
@@ -1675,12 +1619,12 @@
       <c r="D14" s="22" t="n"/>
       <c r="E14" s="22" t="n"/>
       <c r="F14" s="23">
-        <f>Параметры!$B$5+14</f>
-        <v>46286</v>
+        <f>Параметры!$B$5+7</f>
+        <v>46279</v>
       </c>
       <c r="G14" s="23">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H14" s="22" t="n"/>
       <c r="I14" s="22" t="n"/>
@@ -1700,7 +1644,7 @@
       </c>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
-      <c r="R14" s="19" t="n"/>
+      <c r="Q14" s="19" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
@@ -1717,12 +1661,12 @@
       <c r="D15" s="22" t="n"/>
       <c r="E15" s="22" t="n"/>
       <c r="F15" s="23">
-        <f>Параметры!$B$5+14</f>
-        <v>46286</v>
+        <f>Параметры!$B$5+7</f>
+        <v>46279</v>
       </c>
       <c r="G15" s="23">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H15" s="22" t="n"/>
       <c r="I15" s="22" t="n"/>
@@ -1742,7 +1686,7 @@
       </c>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
-      <c r="R15" s="19" t="n"/>
+      <c r="Q15" s="19" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
@@ -1759,12 +1703,12 @@
       <c r="D16" s="22" t="n"/>
       <c r="E16" s="22" t="n"/>
       <c r="F16" s="23">
-        <f>Параметры!$B$5+14</f>
-        <v>46286</v>
+        <f>Параметры!$B$5+7</f>
+        <v>46279</v>
       </c>
       <c r="G16" s="23">
-        <f>Параметры!$B$5+18</f>
-        <v>46290</v>
+        <f>Параметры!$B$5+11</f>
+        <v>46283</v>
       </c>
       <c r="H16" s="22" t="n"/>
       <c r="I16" s="22" t="n"/>
@@ -1780,11 +1724,11 @@
         </is>
       </c>
       <c r="M16" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
-      <c r="R16" s="19" t="n"/>
+      <c r="Q16" s="19" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -1813,12 +1757,12 @@
         <v>46286</v>
       </c>
       <c r="G17" s="17">
-        <f>Параметры!$B$5+25</f>
-        <v>46297</v>
+        <f>Параметры!$B$5+18</f>
+        <v>46290</v>
       </c>
       <c r="H17" s="17">
         <f>G17</f>
-        <v>46297</v>
+        <v>46290</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1827,7 +1771,7 @@
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
-          <t>Стенд из двух машин прошёл чек-лист приёмки; восстановление кворума и переключение мастера выполнены руками</t>
+          <t>Стенд из двух машин прошёл чек-лист приёмки; восстановление кворума и передача роли мастера выполнены руками</t>
         </is>
       </c>
       <c r="K17" s="16" t="n"/>
@@ -1837,17 +1781,16 @@
         </is>
       </c>
       <c r="M17" s="15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N17" s="18">
-        <f>Параметры!$B$9*M17</f>
-        <v>115150</v>
+        <f>Параметры!$B$11*M17</f>
+        <v>69090</v>
       </c>
       <c r="O17" s="18" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="19" t="n"/>
-      <c r="S17" s="19" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
@@ -1857,7 +1800,7 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Развернуть тестовый мастер</t>
+          <t>Развернуть тестовый мастер и клонировать его в узел</t>
         </is>
       </c>
       <c r="C18" s="22" t="n"/>
@@ -1875,7 +1818,7 @@
       <c r="I18" s="22" t="n"/>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>Тестовый мастер работает</t>
+          <t>Клон вступил в кластер, конфликтов имён узлов нет</t>
         </is>
       </c>
       <c r="K18" s="24" t="n"/>
@@ -1885,7 +1828,7 @@
         </is>
       </c>
       <c r="M18" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
@@ -1899,7 +1842,7 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>Клонировать машину мастера и расшить клон в самостоятельный узел</t>
+          <t>Прогнать чек-лист приёмки</t>
         </is>
       </c>
       <c r="C19" s="22" t="n"/>
@@ -1917,7 +1860,7 @@
       <c r="I19" s="22" t="n"/>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>Клон вступил в кластер, конфликтов имён узлов нет</t>
+          <t>Чек-лист пройден</t>
         </is>
       </c>
       <c r="K19" s="24" t="n"/>
@@ -1927,7 +1870,7 @@
         </is>
       </c>
       <c r="M19" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
@@ -1941,25 +1884,25 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Прогнать чек-лист приёмки</t>
+          <t>Отработать восстановление кворума и передачу роли мастера</t>
         </is>
       </c>
       <c r="C20" s="22" t="n"/>
       <c r="D20" s="22" t="n"/>
       <c r="E20" s="22" t="n"/>
       <c r="F20" s="23">
-        <f>Параметры!$B$5+21</f>
-        <v>46293</v>
+        <f>Параметры!$B$5+14</f>
+        <v>46286</v>
       </c>
       <c r="G20" s="23">
-        <f>Параметры!$B$5+25</f>
-        <v>46297</v>
+        <f>Параметры!$B$5+18</f>
+        <v>46290</v>
       </c>
       <c r="H20" s="22" t="n"/>
       <c r="I20" s="22" t="n"/>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>Чек-лист пройден</t>
+          <t>Процедуры выполнены и задокументированы</t>
         </is>
       </c>
       <c r="K20" s="24" t="n"/>
@@ -1969,144 +1912,143 @@
         </is>
       </c>
       <c r="M20" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
-      <c r="S20" s="19" t="n"/>
+      <c r="R20" s="19" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>Отработать восстановление кворума и переключение на резервный мастер</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="23">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Перевод ростовской АТС в режим мастера кластера</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="17">
         <f>Параметры!$B$5+21</f>
         <v>46293</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="17">
         <f>Параметры!$B$5+25</f>
         <v>46297</v>
       </c>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="inlineStr">
-        <is>
-          <t>Процедуры выполнены и задокументированы</t>
-        </is>
-      </c>
-      <c r="K21" s="24" t="n"/>
-      <c r="L21" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M21" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="22" t="n"/>
+      <c r="H21" s="17">
+        <f>G21</f>
+        <v>46297</v>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>Существующая АТС работает как отдельная станция и не может обслуживать площадки</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>Ростовская АТС работает мастером кластера без переустановки; номера доступны площадкам через общую базу</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="n"/>
+      <c r="L21" s="15" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M21" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" s="18">
+        <f>Параметры!$B$11*M21</f>
+        <v>46060</v>
+      </c>
+      <c r="O21" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="S21" s="19" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Перевод ростовской АТС в режим мастера кластера</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="17">
-        <f>Параметры!$B$5+28</f>
-        <v>46300</v>
-      </c>
-      <c r="G22" s="17">
-        <f>Параметры!$B$5+39</f>
-        <v>46311</v>
-      </c>
-      <c r="H22" s="17">
-        <f>G22</f>
-        <v>46311</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Существующая АТС работает как отдельная станция и не может обслуживать площадки</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Ростовская АТС работает мастером кластера без переустановки; номера доступны площадкам через общую базу</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="15" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M22" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" s="18">
-        <f>Параметры!$B$9*M22</f>
-        <v>57575</v>
-      </c>
-      <c r="O22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="19" t="n"/>
-      <c r="U22" s="19" t="n"/>
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Снять резервную копию, перевести таблицы и запустить репликацию</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="23">
+        <f>Параметры!$B$5+21</f>
+        <v>46293</v>
+      </c>
+      <c r="G22" s="23">
+        <f>Параметры!$B$5+25</f>
+        <v>46297</v>
+      </c>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>База работает в режиме кластера, число добавочных сошлось</t>
+        </is>
+      </c>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22" t="n"/>
+      <c r="S22" s="19" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>Снять резервную копию, перевести таблицы и запустить репликацию</t>
+          <t>Выгрузить номера в общую базу и проверить</t>
         </is>
       </c>
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="22" t="n"/>
       <c r="E23" s="22" t="n"/>
       <c r="F23" s="23">
-        <f>Параметры!$B$5+28</f>
-        <v>46300</v>
+        <f>Параметры!$B$5+21</f>
+        <v>46293</v>
       </c>
       <c r="G23" s="23">
-        <f>Параметры!$B$5+32</f>
-        <v>46304</v>
+        <f>Параметры!$B$5+25</f>
+        <v>46297</v>
       </c>
       <c r="H23" s="22" t="n"/>
       <c r="I23" s="22" t="n"/>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>База работает в режиме кластера, число добавочных сошлось</t>
+          <t>Абоненты видны из общей базы</t>
         </is>
       </c>
       <c r="K23" s="24" t="n"/>
@@ -2116,39 +2058,39 @@
         </is>
       </c>
       <c r="M23" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23" s="22" t="n"/>
       <c r="O23" s="22" t="n"/>
-      <c r="T23" s="19" t="n"/>
+      <c r="S23" s="19" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>Выгрузить номера в общую базу и проверить</t>
+          <t>Наблюдение до ввода первой площадки</t>
         </is>
       </c>
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="22" t="n"/>
       <c r="E24" s="22" t="n"/>
       <c r="F24" s="23">
-        <f>Параметры!$B$5+28</f>
-        <v>46300</v>
+        <f>Параметры!$B$5+21</f>
+        <v>46293</v>
       </c>
       <c r="G24" s="23">
-        <f>Параметры!$B$5+32</f>
-        <v>46304</v>
+        <f>Параметры!$B$5+25</f>
+        <v>46297</v>
       </c>
       <c r="H24" s="22" t="n"/>
       <c r="I24" s="22" t="n"/>
       <c r="J24" s="22" t="inlineStr">
         <is>
-          <t>Абоненты видны из общей базы</t>
+          <t>Отклонений не выявлено</t>
         </is>
       </c>
       <c r="K24" s="24" t="n"/>
@@ -2162,141 +2104,140 @@
       </c>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
-      <c r="T24" s="19" t="n"/>
+      <c r="S24" s="19" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>Неделя наблюдения</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="23">
-        <f>Параметры!$B$5+35</f>
-        <v>46307</v>
-      </c>
-      <c r="G25" s="23">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Первая площадка — Воронеж</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="17">
+        <f>Параметры!$B$5+28</f>
+        <v>46300</v>
+      </c>
+      <c r="G25" s="17">
         <f>Параметры!$B$5+39</f>
         <v>46311</v>
       </c>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="22" t="n"/>
-      <c r="J25" s="22" t="inlineStr">
-        <is>
-          <t>Отклонений не выявлено</t>
-        </is>
-      </c>
-      <c r="K25" s="24" t="n"/>
-      <c r="L25" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M25" s="22" t="n">
+      <c r="H25" s="17">
+        <f>G25</f>
+        <v>46311</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>Схема не проверена на реальной нагрузке и реальном канале</t>
+        </is>
+      </c>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>Воронеж работает узлом кластера: локальная регистрация телефонов, свой выход в город, переключение на Ростов при отказе площадки</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M25" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="18">
+        <f>Параметры!$B$11*M25</f>
+        <v>115150</v>
+      </c>
+      <c r="O25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="19" t="n"/>
+      <c r="U25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Клонировать машину мастера и расшить клон в узел</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="23">
+        <f>Параметры!$B$5+28</f>
+        <v>46300</v>
+      </c>
+      <c r="G26" s="23">
+        <f>Параметры!$B$5+32</f>
+        <v>46304</v>
+      </c>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>Узел в кластере</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="n"/>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="22" t="n"/>
-      <c r="O25" s="22" t="n"/>
-      <c r="U25" s="19" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Первая площадка — Воронеж</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="17">
-        <f>Параметры!$B$5+35</f>
-        <v>46307</v>
-      </c>
-      <c r="G26" s="17">
-        <f>Параметры!$B$5+53</f>
-        <v>46325</v>
-      </c>
-      <c r="H26" s="17">
-        <f>G26</f>
-        <v>46325</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>Схема не проверена на реальной нагрузке и реальном канале</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="inlineStr">
-        <is>
-          <t>Воронеж работает узлом кластера: локальная регистрация телефонов, свой выход в город, переключение на Ростов при отказе площадки</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M26" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="N26" s="18">
-        <f>Параметры!$B$9*M26</f>
-        <v>172725</v>
-      </c>
-      <c r="O26" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="19" t="n"/>
-      <c r="V26" s="19" t="n"/>
-      <c r="W26" s="19" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="T26" s="19" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>Клонировать машину мастера и расшить клон в узел</t>
+          <t>Настроить межузловые транки и перенести диалплан</t>
         </is>
       </c>
       <c r="C27" s="22" t="n"/>
       <c r="D27" s="22" t="n"/>
       <c r="E27" s="22" t="n"/>
       <c r="F27" s="23">
-        <f>Параметры!$B$5+35</f>
-        <v>46307</v>
+        <f>Параметры!$B$5+28</f>
+        <v>46300</v>
       </c>
       <c r="G27" s="23">
-        <f>Параметры!$B$5+39</f>
-        <v>46311</v>
+        <f>Параметры!$B$5+32</f>
+        <v>46304</v>
       </c>
       <c r="H27" s="22" t="n"/>
       <c r="I27" s="22" t="n"/>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>Узел в кластере</t>
+          <t>Вызовы между Ростовом и Воронежем проходят</t>
         </is>
       </c>
       <c r="K27" s="24" t="n"/>
@@ -2306,39 +2247,39 @@
         </is>
       </c>
       <c r="M27" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
-      <c r="U27" s="19" t="n"/>
+      <c r="T27" s="19" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>Настроить межузловые транки и перенести диалплан</t>
+          <t>Подключить локальный транк оператора</t>
         </is>
       </c>
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="22" t="n"/>
       <c r="E28" s="22" t="n"/>
       <c r="F28" s="23">
-        <f>Параметры!$B$5+35</f>
-        <v>46307</v>
+        <f>Параметры!$B$5+28</f>
+        <v>46300</v>
       </c>
       <c r="G28" s="23">
-        <f>Параметры!$B$5+39</f>
-        <v>46311</v>
+        <f>Параметры!$B$5+32</f>
+        <v>46304</v>
       </c>
       <c r="H28" s="22" t="n"/>
       <c r="I28" s="22" t="n"/>
       <c r="J28" s="22" t="inlineStr">
         <is>
-          <t>Вызовы между Ростовом и Воронежем проходят</t>
+          <t>Свой выход в город работает</t>
         </is>
       </c>
       <c r="K28" s="24" t="n"/>
@@ -2348,39 +2289,39 @@
         </is>
       </c>
       <c r="M28" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" s="22" t="n"/>
       <c r="O28" s="22" t="n"/>
-      <c r="U28" s="19" t="n"/>
+      <c r="T28" s="19" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>Подключить локальный транк оператора</t>
+          <t>Перевести телефоны на узел через провижининг</t>
         </is>
       </c>
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="22" t="n"/>
       <c r="E29" s="22" t="n"/>
       <c r="F29" s="23">
-        <f>Параметры!$B$5+42</f>
-        <v>46314</v>
+        <f>Параметры!$B$5+28</f>
+        <v>46300</v>
       </c>
       <c r="G29" s="23">
-        <f>Параметры!$B$5+46</f>
-        <v>46318</v>
+        <f>Параметры!$B$5+32</f>
+        <v>46304</v>
       </c>
       <c r="H29" s="22" t="n"/>
       <c r="I29" s="22" t="n"/>
       <c r="J29" s="22" t="inlineStr">
         <is>
-          <t>Свой выход в город работает</t>
+          <t>Телефоны регистрируются на площадке, резервный сервер — Ростов</t>
         </is>
       </c>
       <c r="K29" s="24" t="n"/>
@@ -2394,35 +2335,35 @@
       </c>
       <c r="N29" s="22" t="n"/>
       <c r="O29" s="22" t="n"/>
-      <c r="V29" s="19" t="n"/>
+      <c r="T29" s="19" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Перевести телефоны на узел через провижининг</t>
+          <t>Неделя наблюдения под реальной нагрузкой</t>
         </is>
       </c>
       <c r="C30" s="22" t="n"/>
       <c r="D30" s="22" t="n"/>
       <c r="E30" s="22" t="n"/>
       <c r="F30" s="23">
-        <f>Параметры!$B$5+42</f>
-        <v>46314</v>
+        <f>Параметры!$B$5+35</f>
+        <v>46307</v>
       </c>
       <c r="G30" s="23">
-        <f>Параметры!$B$5+46</f>
-        <v>46318</v>
+        <f>Параметры!$B$5+39</f>
+        <v>46311</v>
       </c>
       <c r="H30" s="22" t="n"/>
       <c r="I30" s="22" t="n"/>
       <c r="J30" s="22" t="inlineStr">
         <is>
-          <t>Телефоны регистрируются на площадке, резервный сервер — Ростов</t>
+          <t>Отказ площадки и возврат отработаны, решение о тиражировании принято</t>
         </is>
       </c>
       <c r="K30" s="24" t="n"/>
@@ -2436,140 +2377,135 @@
       </c>
       <c r="N30" s="22" t="n"/>
       <c r="O30" s="22" t="n"/>
-      <c r="V30" s="19" t="n"/>
+      <c r="U30" s="19" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>Две недели наблюдения под реальной нагрузкой</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="23">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Тиражирование на три площадки</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="17">
         <f>Параметры!$B$5+42</f>
         <v>46314</v>
       </c>
-      <c r="G31" s="23">
-        <f>Параметры!$B$5+53</f>
-        <v>46325</v>
-      </c>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="22" t="n"/>
-      <c r="J31" s="22" t="inlineStr">
-        <is>
-          <t>Отказ площадки и возврат отработаны, решение о тиражировании принято</t>
-        </is>
-      </c>
-      <c r="K31" s="24" t="n"/>
-      <c r="L31" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M31" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" s="22" t="n"/>
-      <c r="O31" s="22" t="n"/>
+      <c r="G31" s="17">
+        <f>Параметры!$B$5+60</f>
+        <v>46332</v>
+      </c>
+      <c r="H31" s="17">
+        <f>G31</f>
+        <v>46332</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>Три площадки обслуживаются разрозненными станциями либо удалённо из Ростова</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="inlineStr">
+        <is>
+          <t>Все пять площадок работают узлами одного кластера, кворум нечётный</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="n"/>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M31" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="N31" s="18">
+        <f>Параметры!$B$11*M31</f>
+        <v>172725</v>
+      </c>
+      <c r="O31" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="V31" s="19" t="n"/>
       <c r="W31" s="19" t="n"/>
+      <c r="X31" s="19" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>Тиражирование на пять площадок</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="17">
-        <f>Параметры!$B$5+56</f>
-        <v>46328</v>
-      </c>
-      <c r="G32" s="17">
-        <f>Параметры!$B$5+102</f>
-        <v>46374</v>
-      </c>
-      <c r="H32" s="17">
-        <f>G32</f>
-        <v>46374</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Пять регионов обслуживаются разрозненными станциями либо удалённо из Ростова</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="inlineStr">
-        <is>
-          <t>Все шесть регионов работают узлами одного кластера, кворум нечётный</t>
-        </is>
-      </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M32" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="N32" s="18">
-        <f>Параметры!$B$9*M32</f>
-        <v>322420</v>
-      </c>
-      <c r="O32" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="19" t="n"/>
-      <c r="Y32" s="19" t="n"/>
-      <c r="Z32" s="19" t="n"/>
-      <c r="AA32" s="19" t="n"/>
-      <c r="AB32" s="19" t="n"/>
-      <c r="AC32" s="19" t="n"/>
-      <c r="AD32" s="19" t="n"/>
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Нижний Новгород — 164 абонента</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="23">
+        <f>Параметры!$B$5+42</f>
+        <v>46314</v>
+      </c>
+      <c r="G32" s="23">
+        <f>Параметры!$B$5+46</f>
+        <v>46318</v>
+      </c>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>Узел работает</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="n"/>
+      <c r="L32" s="22" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" s="22" t="n"/>
+      <c r="O32" s="22" t="n"/>
+      <c r="V32" s="19" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>Мясокомбинат — 187 абонентов</t>
+          <t>Славянск-на-Кубани (Краснодар) — 140 абонентов</t>
         </is>
       </c>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="22" t="n"/>
       <c r="E33" s="22" t="n"/>
       <c r="F33" s="23">
-        <f>Параметры!$B$5+56</f>
-        <v>46328</v>
+        <f>Параметры!$B$5+49</f>
+        <v>46321</v>
       </c>
       <c r="G33" s="23">
-        <f>Параметры!$B$5+60</f>
-        <v>46332</v>
+        <f>Параметры!$B$5+53</f>
+        <v>46325</v>
       </c>
       <c r="H33" s="22" t="n"/>
       <c r="I33" s="22" t="n"/>
@@ -2589,35 +2525,35 @@
       </c>
       <c r="N33" s="22" t="n"/>
       <c r="O33" s="22" t="n"/>
-      <c r="X33" s="19" t="n"/>
+      <c r="W33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>Арбитр кворума на отдельном хосте</t>
+          <t>Москва — 80 абонентов, новый узел вместо обслуживания из Ростова</t>
         </is>
       </c>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="22" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="23">
-        <f>Параметры!$B$5+63</f>
-        <v>46335</v>
+        <f>Параметры!$B$5+56</f>
+        <v>46328</v>
       </c>
       <c r="G34" s="23">
-        <f>Параметры!$B$5+67</f>
-        <v>46339</v>
+        <f>Параметры!$B$5+60</f>
+        <v>46332</v>
       </c>
       <c r="H34" s="22" t="n"/>
       <c r="I34" s="22" t="n"/>
       <c r="J34" s="22" t="inlineStr">
         <is>
-          <t>Кворум сохраняется при чётном числе узлов</t>
+          <t>Узел работает, абоненты переведены с Ростова и локального PBX</t>
         </is>
       </c>
       <c r="K34" s="24" t="n"/>
@@ -2627,81 +2563,101 @@
         </is>
       </c>
       <c r="M34" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N34" s="22" t="n"/>
       <c r="O34" s="22" t="n"/>
-      <c r="Y34" s="19" t="n"/>
+      <c r="X34" s="19" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>Славянск-на-Кубани (Краснодар) — 140 абонентов</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
-      <c r="F35" s="23">
-        <f>Параметры!$B$5+70</f>
-        <v>46342</v>
-      </c>
-      <c r="G35" s="23">
-        <f>Параметры!$B$5+74</f>
-        <v>46346</v>
-      </c>
-      <c r="H35" s="22" t="n"/>
-      <c r="I35" s="22" t="n"/>
-      <c r="J35" s="22" t="inlineStr">
-        <is>
-          <t>Узел работает</t>
-        </is>
-      </c>
-      <c r="K35" s="24" t="n"/>
-      <c r="L35" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M35" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N35" s="22" t="n"/>
-      <c r="O35" s="22" t="n"/>
-      <c r="Z35" s="19" t="n"/>
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Учебная передача роли мастера</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="17">
+        <f>Параметры!$B$5+63</f>
+        <v>46335</v>
+      </c>
+      <c r="G35" s="17">
+        <f>Параметры!$B$5+67</f>
+        <v>46339</v>
+      </c>
+      <c r="H35" s="17">
+        <f>G35</f>
+        <v>46339</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>Управление кластером сосредоточено на одном сервере, процедура замены не опробована</t>
+        </is>
+      </c>
+      <c r="J35" s="15" t="inlineStr">
+        <is>
+          <t>Роль мастера передана на другой узел и возвращена обратно в согласованное окно</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="n"/>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M35" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" s="18">
+        <f>Параметры!$B$11*M35</f>
+        <v>34545</v>
+      </c>
+      <c r="O35" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="19" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>Нижний Новгород — 164 абонента</t>
+          <t>Передать роль мастера на резервный узел</t>
         </is>
       </c>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="22" t="n"/>
       <c r="E36" s="22" t="n"/>
       <c r="F36" s="23">
-        <f>Параметры!$B$5+77</f>
-        <v>46349</v>
+        <f>Параметры!$B$5+63</f>
+        <v>46335</v>
       </c>
       <c r="G36" s="23">
-        <f>Параметры!$B$5+81</f>
-        <v>46353</v>
+        <f>Параметры!$B$5+67</f>
+        <v>46339</v>
       </c>
       <c r="H36" s="22" t="n"/>
       <c r="I36" s="22" t="n"/>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>Узел работает</t>
+          <t>Управление и звонки работают с нового мастера</t>
         </is>
       </c>
       <c r="K36" s="24" t="n"/>
@@ -2711,39 +2667,39 @@
         </is>
       </c>
       <c r="M36" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N36" s="22" t="n"/>
       <c r="O36" s="22" t="n"/>
-      <c r="AA36" s="19" t="n"/>
+      <c r="Y36" s="19" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>Ставрополь — 74 абонента, новый узел вместо обслуживания из Ростова</t>
+          <t>Вернуть роль обратно на Ростов</t>
         </is>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="22" t="n"/>
       <c r="E37" s="22" t="n"/>
       <c r="F37" s="23">
-        <f>Параметры!$B$5+84</f>
-        <v>46356</v>
+        <f>Параметры!$B$5+63</f>
+        <v>46335</v>
       </c>
       <c r="G37" s="23">
-        <f>Параметры!$B$5+95</f>
-        <v>46367</v>
+        <f>Параметры!$B$5+67</f>
+        <v>46339</v>
       </c>
       <c r="H37" s="22" t="n"/>
       <c r="I37" s="22" t="n"/>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>Узел работает, абоненты переведены с ростовского сервера</t>
+          <t>Схема возвращена в штатное состояние</t>
         </is>
       </c>
       <c r="K37" s="24" t="n"/>
@@ -2753,144 +2709,150 @@
         </is>
       </c>
       <c r="M37" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N37" s="22" t="n"/>
       <c r="O37" s="22" t="n"/>
-      <c r="AB37" s="19" t="n"/>
-      <c r="AC37" s="19" t="n"/>
+      <c r="Y37" s="19" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>Москва — 80 абонентов, новый узел</t>
-        </is>
-      </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="23">
-        <f>Параметры!$B$5+98</f>
-        <v>46370</v>
-      </c>
-      <c r="G38" s="23">
-        <f>Параметры!$B$5+102</f>
-        <v>46374</v>
-      </c>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="22" t="n"/>
-      <c r="J38" s="22" t="inlineStr">
-        <is>
-          <t>Узел работает, абоненты переведены с Ростова и локального PBX</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="n"/>
-      <c r="L38" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M38" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N38" s="22" t="n"/>
-      <c r="O38" s="22" t="n"/>
-      <c r="AD38" s="19" t="n"/>
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Консолидация мелких АТС</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="17">
+        <f>Параметры!$B$5+35</f>
+        <v>46307</v>
+      </c>
+      <c r="G38" s="17">
+        <f>Параметры!$B$5+81</f>
+        <v>46353</v>
+      </c>
+      <c r="H38" s="17">
+        <f>G38</f>
+        <v>46353</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>Семь станций на 156 абонентов дорого поддерживать и невыгодно включать в кластер отдельными узлами</t>
+        </is>
+      </c>
+      <c r="J38" s="15" t="inlineStr">
+        <is>
+          <t>Абоненты мелких станций переведены на узлы кластера, станции выведены из эксплуатации</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="n"/>
+      <c r="L38" s="15" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M38" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="N38" s="18">
+        <f>Параметры!$B$11*M38</f>
+        <v>161210</v>
+      </c>
+      <c r="O38" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="19" t="n"/>
+      <c r="V38" s="19" t="n"/>
+      <c r="W38" s="19" t="n"/>
+      <c r="X38" s="19" t="n"/>
+      <c r="Y38" s="19" t="n"/>
+      <c r="Z38" s="19" t="n"/>
+      <c r="AA38" s="19" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Резервный мастер</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="17">
-        <f>Параметры!$B$5+105</f>
-        <v>46377</v>
-      </c>
-      <c r="G39" s="17">
-        <f>Параметры!$B$5+109</f>
-        <v>46381</v>
-      </c>
-      <c r="H39" s="17">
-        <f>G39</f>
-        <v>46381</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Управление кластером сосредоточено на одном сервере</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="inlineStr">
-        <is>
-          <t>Резервный мастер развёрнут, переключение на него и возврат проверены учебно</t>
-        </is>
-      </c>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="15" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M39" s="15" t="n">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Мясокомбинат — 187 абонентов — в Воронеж</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="23">
+        <f>Параметры!$B$5+35</f>
+        <v>46307</v>
+      </c>
+      <c r="G39" s="23">
+        <f>Параметры!$B$5+46</f>
+        <v>46318</v>
+      </c>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="22" t="inlineStr">
+        <is>
+          <t>Станция выведена</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="n"/>
+      <c r="L39" s="22" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M39" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="N39" s="18">
-        <f>Параметры!$B$9*M39</f>
-        <v>46060</v>
-      </c>
-      <c r="O39" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="19" t="n"/>
+      <c r="N39" s="22" t="n"/>
+      <c r="O39" s="22" t="n"/>
+      <c r="U39" s="19" t="n"/>
+      <c r="V39" s="19" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>Развернуть резервный мастер</t>
+          <t>Калуга — 29 абонентов — в Воронеж</t>
         </is>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="22" t="n"/>
       <c r="E40" s="22" t="n"/>
       <c r="F40" s="23">
-        <f>Параметры!$B$5+105</f>
-        <v>46377</v>
+        <f>Параметры!$B$5+49</f>
+        <v>46321</v>
       </c>
       <c r="G40" s="23">
-        <f>Параметры!$B$5+109</f>
-        <v>46381</v>
+        <f>Параметры!$B$5+53</f>
+        <v>46325</v>
       </c>
       <c r="H40" s="22" t="n"/>
       <c r="I40" s="22" t="n"/>
       <c r="J40" s="22" t="inlineStr">
         <is>
-          <t>Резервный мастер в кластере</t>
+          <t>Станция выведена</t>
         </is>
       </c>
       <c r="K40" s="24" t="n"/>
@@ -2904,35 +2866,35 @@
       </c>
       <c r="N40" s="22" t="n"/>
       <c r="O40" s="22" t="n"/>
-      <c r="AE40" s="19" t="n"/>
+      <c r="W40" s="19" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>Провести учебное переключение и возврат</t>
+          <t>ССЗ — 39 абонентов — в Нижний Новгород</t>
         </is>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="22" t="n"/>
       <c r="E41" s="22" t="n"/>
       <c r="F41" s="23">
-        <f>Параметры!$B$5+105</f>
-        <v>46377</v>
+        <f>Параметры!$B$5+56</f>
+        <v>46328</v>
       </c>
       <c r="G41" s="23">
-        <f>Параметры!$B$5+109</f>
-        <v>46381</v>
+        <f>Параметры!$B$5+60</f>
+        <v>46332</v>
       </c>
       <c r="H41" s="22" t="n"/>
       <c r="I41" s="22" t="n"/>
       <c r="J41" s="22" t="inlineStr">
         <is>
-          <t>Процедура выполнена в согласованное окно</t>
+          <t>Станция выведена</t>
         </is>
       </c>
       <c r="K41" s="24" t="n"/>
@@ -2946,87 +2908,60 @@
       </c>
       <c r="N41" s="22" t="n"/>
       <c r="O41" s="22" t="n"/>
-      <c r="AE41" s="19" t="n"/>
+      <c r="X41" s="19" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>Консолидация семи мелких АТС</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="17">
-        <f>Параметры!$B$5+77</f>
-        <v>46349</v>
-      </c>
-      <c r="G42" s="17">
-        <f>Параметры!$B$5+137</f>
-        <v>46409</v>
-      </c>
-      <c r="H42" s="17">
-        <f>G42</f>
-        <v>46409</v>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>Семь станций на 156 абонентов дорого поддерживать и невыгодно включать в кластер отдельными узлами</t>
-        </is>
-      </c>
-      <c r="J42" s="15" t="inlineStr">
-        <is>
-          <t>Абоненты семи станций переведены на региональные узлы, станции выведены из эксплуатации</t>
-        </is>
-      </c>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="15" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M42" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="N42" s="18">
-        <f>Параметры!$B$9*M42</f>
-        <v>241815</v>
-      </c>
-      <c r="O42" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="19" t="n"/>
-      <c r="AB42" s="19" t="n"/>
-      <c r="AC42" s="19" t="n"/>
-      <c r="AD42" s="19" t="n"/>
-      <c r="AE42" s="19" t="n"/>
-      <c r="AF42" s="19" t="n"/>
-      <c r="AG42" s="19" t="n"/>
-      <c r="AH42" s="19" t="n"/>
-      <c r="AI42" s="19" t="n"/>
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Манитек, Семикаракорский, Цимлянский, Приманыческий — 73 абонента — в Ростов</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="23">
+        <f>Параметры!$B$5+63</f>
+        <v>46335</v>
+      </c>
+      <c r="G42" s="23">
+        <f>Параметры!$B$5+74</f>
+        <v>46346</v>
+      </c>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>Станции выведены</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="n"/>
+      <c r="L42" s="22" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M42" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" s="22" t="n"/>
+      <c r="O42" s="22" t="n"/>
+      <c r="Y42" s="19" t="n"/>
+      <c r="Z42" s="19" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>Калуга — 29 абонентов — в Воронеж</t>
+          <t>Локальный PBX — 15 абонентов — в Москву</t>
         </is>
       </c>
       <c r="C43" s="22" t="n"/>
@@ -3037,8 +2972,8 @@
         <v>46349</v>
       </c>
       <c r="G43" s="23">
-        <f>Параметры!$B$5+88</f>
-        <v>46360</v>
+        <f>Параметры!$B$5+81</f>
+        <v>46353</v>
       </c>
       <c r="H43" s="22" t="n"/>
       <c r="I43" s="22" t="n"/>
@@ -3054,83 +2989,109 @@
         </is>
       </c>
       <c r="M43" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" s="22" t="n"/>
       <c r="O43" s="22" t="n"/>
       <c r="AA43" s="19" t="n"/>
-      <c r="AB43" s="19" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B44" s="21" t="inlineStr">
-        <is>
-          <t>ССЗ — 39 абонентов — в Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="F44" s="23">
-        <f>Параметры!$B$5+91</f>
-        <v>46363</v>
-      </c>
-      <c r="G44" s="23">
-        <f>Параметры!$B$5+102</f>
-        <v>46374</v>
-      </c>
-      <c r="H44" s="22" t="n"/>
-      <c r="I44" s="22" t="n"/>
-      <c r="J44" s="22" t="inlineStr">
-        <is>
-          <t>Станция выведена</t>
-        </is>
-      </c>
-      <c r="K44" s="24" t="n"/>
-      <c r="L44" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M44" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" s="22" t="n"/>
-      <c r="O44" s="22" t="n"/>
-      <c r="AC44" s="19" t="n"/>
-      <c r="AD44" s="19" t="n"/>
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Перевод абонентов на единый план нумерации</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="17">
+        <f>Параметры!$B$5+28</f>
+        <v>46300</v>
+      </c>
+      <c r="G44" s="17">
+        <f>Параметры!$B$5+88</f>
+        <v>46360</v>
+      </c>
+      <c r="H44" s="17">
+        <f>G44</f>
+        <v>46360</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>Двенадцать станций используют пересекающиеся номера, единый план невозможен без разведения конфликтов</t>
+        </is>
+      </c>
+      <c r="J44" s="15" t="inlineStr">
+        <is>
+          <t>Все абоненты переведены на пятизначную нумерацию, переадресации со старых номеров сняты</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="n"/>
+      <c r="L44" s="15" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M44" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="N44" s="18">
+        <f>Параметры!$B$11*M44</f>
+        <v>172725</v>
+      </c>
+      <c r="O44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="19" t="n"/>
+      <c r="U44" s="19" t="n"/>
+      <c r="V44" s="19" t="n"/>
+      <c r="W44" s="19" t="n"/>
+      <c r="X44" s="19" t="n"/>
+      <c r="Y44" s="19" t="n"/>
+      <c r="Z44" s="19" t="n"/>
+      <c r="AA44" s="19" t="n"/>
+      <c r="AB44" s="19" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>Манитек, Семикаракорский, Цимлянский, Приманыческий — 73 абонента — в Ростов</t>
+          <t>Воронеж и Мясокомбинат — 416 абонентов</t>
         </is>
       </c>
       <c r="C45" s="22" t="n"/>
       <c r="D45" s="22" t="n"/>
       <c r="E45" s="22" t="n"/>
       <c r="F45" s="23">
-        <f>Параметры!$B$5+105</f>
-        <v>46377</v>
+        <f>Параметры!$B$5+28</f>
+        <v>46300</v>
       </c>
       <c r="G45" s="23">
-        <f>Параметры!$B$5+123</f>
-        <v>46395</v>
+        <f>Параметры!$B$5+53</f>
+        <v>46325</v>
       </c>
       <c r="H45" s="22" t="n"/>
       <c r="I45" s="22" t="n"/>
       <c r="J45" s="22" t="inlineStr">
         <is>
-          <t>Станции выведены</t>
+          <t>Площадки переведены</t>
         </is>
       </c>
       <c r="K45" s="24" t="n"/>
@@ -3140,41 +3101,42 @@
         </is>
       </c>
       <c r="M45" s="22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N45" s="22" t="n"/>
       <c r="O45" s="22" t="n"/>
-      <c r="AE45" s="19" t="n"/>
-      <c r="AF45" s="19" t="n"/>
-      <c r="AG45" s="19" t="n"/>
+      <c r="T45" s="19" t="n"/>
+      <c r="U45" s="19" t="n"/>
+      <c r="V45" s="19" t="n"/>
+      <c r="W45" s="19" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>Локальный PBX — 15 абонентов — в Москву</t>
+          <t>Нижний Новгород и ССЗ — 161 абонент</t>
         </is>
       </c>
       <c r="C46" s="22" t="n"/>
       <c r="D46" s="22" t="n"/>
       <c r="E46" s="22" t="n"/>
       <c r="F46" s="23">
-        <f>Параметры!$B$5+126</f>
-        <v>46398</v>
+        <f>Параметры!$B$5+42</f>
+        <v>46314</v>
       </c>
       <c r="G46" s="23">
-        <f>Параметры!$B$5+137</f>
-        <v>46409</v>
+        <f>Параметры!$B$5+60</f>
+        <v>46332</v>
       </c>
       <c r="H46" s="22" t="n"/>
       <c r="I46" s="22" t="n"/>
       <c r="J46" s="22" t="inlineStr">
         <is>
-          <t>Станция выведена</t>
+          <t>Площадки переведены</t>
         </is>
       </c>
       <c r="K46" s="24" t="n"/>
@@ -3184,122 +3146,85 @@
         </is>
       </c>
       <c r="M46" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N46" s="22" t="n"/>
       <c r="O46" s="22" t="n"/>
-      <c r="AH46" s="19" t="n"/>
-      <c r="AI46" s="19" t="n"/>
+      <c r="V46" s="19" t="n"/>
+      <c r="W46" s="19" t="n"/>
+      <c r="X46" s="19" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>Перевод абонентов на единый план нумерации</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="17">
-        <f>Параметры!$B$5+35</f>
-        <v>46307</v>
-      </c>
-      <c r="G47" s="17">
-        <f>Параметры!$B$5+179</f>
-        <v>46451</v>
-      </c>
-      <c r="H47" s="17">
-        <f>G47</f>
-        <v>46451</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>Двенадцать станций используют пересекающиеся номера, единый план невозможен без разведения конфликтов</t>
-        </is>
-      </c>
-      <c r="J47" s="15" t="inlineStr">
-        <is>
-          <t>Все абоненты переведены на пятизначную нумерацию, переадресации со старых номеров сняты</t>
-        </is>
-      </c>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="15" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M47" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="N47" s="18">
-        <f>Параметры!$B$9*M47</f>
-        <v>287875</v>
-      </c>
-      <c r="O47" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="19" t="n"/>
-      <c r="V47" s="19" t="n"/>
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>Славянск-на-Кубани — 136 абонентов</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="23">
+        <f>Параметры!$B$5+49</f>
+        <v>46321</v>
+      </c>
+      <c r="G47" s="23">
+        <f>Параметры!$B$5+67</f>
+        <v>46339</v>
+      </c>
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="22" t="n"/>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>Площадка переведена</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="n"/>
+      <c r="L47" s="22" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M47" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" s="22" t="n"/>
+      <c r="O47" s="22" t="n"/>
       <c r="W47" s="19" t="n"/>
       <c r="X47" s="19" t="n"/>
       <c r="Y47" s="19" t="n"/>
-      <c r="Z47" s="19" t="n"/>
-      <c r="AA47" s="19" t="n"/>
-      <c r="AB47" s="19" t="n"/>
-      <c r="AC47" s="19" t="n"/>
-      <c r="AD47" s="19" t="n"/>
-      <c r="AE47" s="19" t="n"/>
-      <c r="AF47" s="19" t="n"/>
-      <c r="AG47" s="19" t="n"/>
-      <c r="AH47" s="19" t="n"/>
-      <c r="AI47" s="19" t="n"/>
-      <c r="AJ47" s="19" t="n"/>
-      <c r="AK47" s="19" t="n"/>
-      <c r="AL47" s="19" t="n"/>
-      <c r="AM47" s="19" t="n"/>
-      <c r="AN47" s="19" t="n"/>
-      <c r="AO47" s="19" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>Воронеж — 229 абонентов</t>
+          <t>Ростов, его мелкие площадки и Ставрополь — 426 абонентов</t>
         </is>
       </c>
       <c r="C48" s="22" t="n"/>
       <c r="D48" s="22" t="n"/>
       <c r="E48" s="22" t="n"/>
       <c r="F48" s="23">
-        <f>Параметры!$B$5+35</f>
-        <v>46307</v>
+        <f>Параметры!$B$5+56</f>
+        <v>46328</v>
       </c>
       <c r="G48" s="23">
-        <f>Параметры!$B$5+67</f>
-        <v>46339</v>
+        <f>Параметры!$B$5+81</f>
+        <v>46353</v>
       </c>
       <c r="H48" s="22" t="n"/>
       <c r="I48" s="22" t="n"/>
       <c r="J48" s="22" t="inlineStr">
         <is>
-          <t>Площадка переведена</t>
+          <t>Площадки переведены</t>
         </is>
       </c>
       <c r="K48" s="24" t="n"/>
@@ -3313,39 +3238,38 @@
       </c>
       <c r="N48" s="22" t="n"/>
       <c r="O48" s="22" t="n"/>
-      <c r="U48" s="19" t="n"/>
-      <c r="V48" s="19" t="n"/>
-      <c r="W48" s="19" t="n"/>
       <c r="X48" s="19" t="n"/>
       <c r="Y48" s="19" t="n"/>
+      <c r="Z48" s="19" t="n"/>
+      <c r="AA48" s="19" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B49" s="21" t="inlineStr">
         <is>
-          <t>Мясокомбинат и Калуга — 216 абонентов</t>
+          <t>Москва — 80 абонентов, снятие переадресаций</t>
         </is>
       </c>
       <c r="C49" s="22" t="n"/>
       <c r="D49" s="22" t="n"/>
       <c r="E49" s="22" t="n"/>
       <c r="F49" s="23">
-        <f>Параметры!$B$5+63</f>
-        <v>46335</v>
+        <f>Параметры!$B$5+70</f>
+        <v>46342</v>
       </c>
       <c r="G49" s="23">
-        <f>Параметры!$B$5+95</f>
-        <v>46367</v>
+        <f>Параметры!$B$5+88</f>
+        <v>46360</v>
       </c>
       <c r="H49" s="22" t="n"/>
       <c r="I49" s="22" t="n"/>
       <c r="J49" s="22" t="inlineStr">
         <is>
-          <t>Площадки переведены</t>
+          <t>Площадка переведена, переадресации сняты</t>
         </is>
       </c>
       <c r="K49" s="24" t="n"/>
@@ -3355,326 +3279,47 @@
         </is>
       </c>
       <c r="M49" s="22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N49" s="22" t="n"/>
       <c r="O49" s="22" t="n"/>
-      <c r="Y49" s="19" t="n"/>
       <c r="Z49" s="19" t="n"/>
       <c r="AA49" s="19" t="n"/>
       <c r="AB49" s="19" t="n"/>
-      <c r="AC49" s="19" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>Славянск-на-Кубани — 136 абонентов</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="22" t="n"/>
-      <c r="F50" s="23">
-        <f>Параметры!$B$5+77</f>
-        <v>46349</v>
-      </c>
-      <c r="G50" s="23">
-        <f>Параметры!$B$5+109</f>
-        <v>46381</v>
-      </c>
-      <c r="H50" s="22" t="n"/>
-      <c r="I50" s="22" t="n"/>
-      <c r="J50" s="22" t="inlineStr">
-        <is>
-          <t>Площадка переведена</t>
-        </is>
-      </c>
-      <c r="K50" s="24" t="n"/>
-      <c r="L50" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M50" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" s="22" t="n"/>
-      <c r="O50" s="22" t="n"/>
-      <c r="AA50" s="19" t="n"/>
-      <c r="AB50" s="19" t="n"/>
-      <c r="AC50" s="19" t="n"/>
-      <c r="AD50" s="19" t="n"/>
-      <c r="AE50" s="19" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="B51" s="21" t="inlineStr">
-        <is>
-          <t>Нижний Новгород и ССЗ — 161 абонент</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
-      <c r="F51" s="23">
-        <f>Параметры!$B$5+91</f>
-        <v>46363</v>
-      </c>
-      <c r="G51" s="23">
-        <f>Параметры!$B$5+123</f>
-        <v>46395</v>
-      </c>
-      <c r="H51" s="22" t="n"/>
-      <c r="I51" s="22" t="n"/>
-      <c r="J51" s="22" t="inlineStr">
-        <is>
-          <t>Площадки переведены</t>
-        </is>
-      </c>
-      <c r="K51" s="24" t="n"/>
-      <c r="L51" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M51" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" s="22" t="n"/>
-      <c r="O51" s="22" t="n"/>
-      <c r="AC51" s="19" t="n"/>
-      <c r="AD51" s="19" t="n"/>
-      <c r="AE51" s="19" t="n"/>
-      <c r="AF51" s="19" t="n"/>
-      <c r="AG51" s="19" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="B52" s="21" t="inlineStr">
-        <is>
-          <t>Ростов и его мелкие площадки — 352 абонента</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="22" t="n"/>
-      <c r="F52" s="23">
-        <f>Параметры!$B$5+105</f>
-        <v>46377</v>
-      </c>
-      <c r="G52" s="23">
-        <f>Параметры!$B$5+137</f>
-        <v>46409</v>
-      </c>
-      <c r="H52" s="22" t="n"/>
-      <c r="I52" s="22" t="n"/>
-      <c r="J52" s="22" t="inlineStr">
-        <is>
-          <t>Площадки переведены</t>
-        </is>
-      </c>
-      <c r="K52" s="24" t="n"/>
-      <c r="L52" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M52" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="N52" s="22" t="n"/>
-      <c r="O52" s="22" t="n"/>
-      <c r="AE52" s="19" t="n"/>
-      <c r="AF52" s="19" t="n"/>
-      <c r="AG52" s="19" t="n"/>
-      <c r="AH52" s="19" t="n"/>
-      <c r="AI52" s="19" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="B53" s="21" t="inlineStr">
-        <is>
-          <t>Ставрополь — 74 абонента</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="22" t="n"/>
-      <c r="E53" s="22" t="n"/>
-      <c r="F53" s="23">
-        <f>Параметры!$B$5+119</f>
-        <v>46391</v>
-      </c>
-      <c r="G53" s="23">
-        <f>Параметры!$B$5+151</f>
-        <v>46423</v>
-      </c>
-      <c r="H53" s="22" t="n"/>
-      <c r="I53" s="22" t="n"/>
-      <c r="J53" s="22" t="inlineStr">
-        <is>
-          <t>Площадка переведена</t>
-        </is>
-      </c>
-      <c r="K53" s="24" t="n"/>
-      <c r="L53" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M53" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N53" s="22" t="n"/>
-      <c r="O53" s="22" t="n"/>
-      <c r="AG53" s="19" t="n"/>
-      <c r="AH53" s="19" t="n"/>
-      <c r="AI53" s="19" t="n"/>
-      <c r="AJ53" s="19" t="n"/>
-      <c r="AK53" s="19" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="inlineStr">
-        <is>
-          <t>Москва — 80 абонентов</t>
-        </is>
-      </c>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="22" t="n"/>
-      <c r="E54" s="22" t="n"/>
-      <c r="F54" s="23">
-        <f>Параметры!$B$5+133</f>
-        <v>46405</v>
-      </c>
-      <c r="G54" s="23">
-        <f>Параметры!$B$5+165</f>
-        <v>46437</v>
-      </c>
-      <c r="H54" s="22" t="n"/>
-      <c r="I54" s="22" t="n"/>
-      <c r="J54" s="22" t="inlineStr">
-        <is>
-          <t>Площадка переведена</t>
-        </is>
-      </c>
-      <c r="K54" s="24" t="n"/>
-      <c r="L54" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M54" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N54" s="22" t="n"/>
-      <c r="O54" s="22" t="n"/>
-      <c r="AI54" s="19" t="n"/>
-      <c r="AJ54" s="19" t="n"/>
-      <c r="AK54" s="19" t="n"/>
-      <c r="AL54" s="19" t="n"/>
-      <c r="AM54" s="19" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="B55" s="21" t="inlineStr">
-        <is>
-          <t>Снять переадресации со старых номеров</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="22" t="n"/>
-      <c r="E55" s="22" t="n"/>
-      <c r="F55" s="23">
-        <f>Параметры!$B$5+161</f>
-        <v>46433</v>
-      </c>
-      <c r="G55" s="23">
-        <f>Параметры!$B$5+179</f>
-        <v>46451</v>
-      </c>
-      <c r="H55" s="22" t="n"/>
-      <c r="I55" s="22" t="n"/>
-      <c r="J55" s="22" t="inlineStr">
-        <is>
-          <t>Переадресации сняты</t>
-        </is>
-      </c>
-      <c r="K55" s="24" t="n"/>
-      <c r="L55" s="22" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M55" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" s="22" t="n"/>
-      <c r="O55" s="22" t="n"/>
-      <c r="AM55" s="19" t="n"/>
-      <c r="AN55" s="19" t="n"/>
-      <c r="AO55" s="19" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="25" t="n"/>
-      <c r="B56" s="25" t="inlineStr">
+      <c r="A50" s="25" t="n"/>
+      <c r="B50" s="25" t="inlineStr">
         <is>
           <t>ИТОГО по проекту</t>
         </is>
       </c>
-      <c r="C56" s="25" t="n"/>
-      <c r="D56" s="25" t="n"/>
-      <c r="E56" s="25" t="n"/>
-      <c r="F56" s="25" t="n"/>
-      <c r="G56" s="25" t="n"/>
-      <c r="H56" s="25" t="n"/>
-      <c r="I56" s="25" t="n"/>
-      <c r="J56" s="25" t="n"/>
-      <c r="K56" s="25" t="n"/>
-      <c r="L56" s="25" t="n"/>
-      <c r="M56" s="25">
-        <f>M3+M10+M17+M22+M26+M32+M39+M42+M47</f>
-        <v>130</v>
-      </c>
-      <c r="N56" s="26">
-        <f>N3+N10+N17+N22+N26+N32+N39+N42+N47</f>
-        <v>1496950</v>
-      </c>
-      <c r="O56" s="26">
-        <f>O3+O10+O17+O22+O26+O32+O39+O42+O47</f>
+      <c r="C50" s="25" t="n"/>
+      <c r="D50" s="25" t="n"/>
+      <c r="E50" s="25" t="n"/>
+      <c r="F50" s="25" t="n"/>
+      <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="25" t="n"/>
+      <c r="L50" s="25" t="n"/>
+      <c r="M50" s="25">
+        <f>M3+M10+M17+M21+M25+M31+M35+M38+M44</f>
+        <v>85</v>
+      </c>
+      <c r="N50" s="26">
+        <f>N3+N10+N17+N21+N25+N31+N35+N38+N44</f>
+        <v>978775</v>
+      </c>
+      <c r="O50" s="26">
+        <f>O3+O10+O17+O21+O25+O31+O35+O38+O44</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="AG1:AJ1"/>
+  <mergeCells count="3">
     <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AK1:AN1"/>
-    <mergeCell ref="AC1:AF1"/>
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="T1:W1"/>
   </mergeCells>

--- a/docs/plan/dit-annual-plan.xlsx
+++ b/docs/plan/dit-annual-plan.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Сервер под московский узел проходит закупкой, в себестоимость работ не входит — как и во всех строках исходного плана ДИТ.</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
@@ -801,28 +801,62 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ: «у нас 5 серверов» прочитано как пять узлов кластера. Четыре площадки уже имеют свои машины, новый сервер нужен только под Москву. Ставрополь (74 абонента) остаётся на ростовском сервере, как сейчас.</t>
+          <t>Все узлы — свои виртуальные машины. Московский узел — ещё одна ВМ на существующих мощностях. ДОПУЩЕНИЕ: «у нас 5 серверов» прочитано как пять узлов кластера; Ставрополь (74 абонента) остаётся на ростовском, как сейчас.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Резервный мастер отдельной машиной</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Пятый сервер занят московским узлом. Отдельная машина под тёплый резерв не требуется: каждый узел — клон мастера, FreePBX на нём уже установлен и только отключён, поэтому роль мастера передаётся на любой рабочий узел. Процедура отрабатывается на этапе 7 учебно.</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Не требуется: каждый узел — клон мастера, FreePBX на нём уже установлен и только отключён, поэтому роль мастера передаётся на любой рабочий узел; процедура отрабатывается на этапе 7 учебно. На своих ВМ выделенный резерв возможен, но требует ДВУХ машин: шестой узел делает число чётным, и кворум приходится добирать арбитром garbd. Это правка одного этапа.</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1171,7 @@
       </c>
       <c r="J3" s="15" t="inlineStr">
         <is>
-          <t>VPN между площадками поднят, RTT измерен и зафиксирован, пятый сервер под Москву получен, у каждой площадки свой SIP-пользователь ВАТС</t>
+          <t>VPN между площадками поднят, RTT измерен и зафиксирован, ВМ под московский узел выделена и размещена на отдельном хосте, у каждой площадки свой SIP-пользователь ВАТС</t>
         </is>
       </c>
       <c r="K3" s="16" t="n"/>
@@ -1336,7 +1370,7 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Подготовить сервер под московский узел</t>
+          <t>Выделить ВМ под московский узел, проверить размещение узлов по хостам</t>
         </is>
       </c>
       <c r="C8" s="22" t="n"/>
@@ -1347,14 +1381,14 @@
         <v>46272</v>
       </c>
       <c r="G8" s="23">
-        <f>Параметры!$B$5+11</f>
-        <v>46283</v>
+        <f>Параметры!$B$5+4</f>
+        <v>46276</v>
       </c>
       <c r="H8" s="22" t="n"/>
       <c r="I8" s="22" t="n"/>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>Сервер получен и доступен по сети</t>
+          <t>ВМ выделена; узлы кластера стоят на разных физических хостах</t>
         </is>
       </c>
       <c r="K8" s="24" t="n"/>
@@ -1369,7 +1403,6 @@
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="19" t="n"/>
-      <c r="Q8" s="19" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">

--- a/docs/plan/dit-annual-plan.xlsx
+++ b/docs/plan/dit-annual-plan.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Централизованная телефония на Asterisk с выносами в кластерах</t>
+          <t>Централизованная телефония на Asterisk: центр в московском ЦОД, выносы по городам</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.»</t>
+          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.» Уточнение: центр размещается в московском ЦОД — мастер на первой площадке, копия на второй; остальные узлы по городам.</t>
         </is>
       </c>
     </row>
@@ -670,417 +670,502 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>централизованная, с выносами</t>
+          <t>центр в ЦОД + выносы</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Центральный узел — Ростов: мастер базы, FreePBX, управление. Выносы — Нижний Новгород, Славянск-на-Кубани, Москва, Воронеж — работают узлами одного кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят на центральный узел.</t>
+          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Дата начала работ</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>46272</v>
+          <t>Два зала ЦОД — независимы?</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ ДО СТАРТА</t>
+        </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+          <t>КРИТИЧНО. Копия во втором зале даёт резервирование только если залы не делят физический хост, ввод питания и аплинк. Две стойки одного зала за одним вводом — это не две площадки, и вся схема резервирования теряет смысл. Проверяется в задаче 1 до выделения ВМ.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Длительность, недель</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>15</v>
+          <t>Дата начала работ</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Длительность, недель</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>Дата завершения работ</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>46374</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="B12" s="6" t="n">
+        <v>46381</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Дата начала + 15 недель, последний рабочий день</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>ЭТАП 1 — все, кроме Воронежа</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>недели 1–11, 810 абонентов</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Ростов 426 (включая Ставрополь 74), Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>недели 1–12, 810 абонентов</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>ЦОД-1 (Москва) 80, ЦОД-2 копия, Ростов 426 (включая Ставрополь 74), Нижний Новгород 164, Славянск-на-Кубани 140.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>ЭТАП 2 — Воронеж</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>недели 12–15, 445 абонентов</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>недели 13–16, 445 абонентов</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Пилотная площадка</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Из оставшихся Нижний Новгород — самый крупный (164) и единственный со своей станцией и станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком. Москва проще: её абоненты уже в базе центрального узла.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>89</v>
+          <t>Порядок переноса центра</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
+        </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 426 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>59</v>
+          <t>Пилотный вынос</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
+          <t>Трудозатраты всего, ч-д</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>11515</v>
+        <v>65</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B19" s="7">
-        <f>B15*B18</f>
-        <v>1024835</v>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>0</v>
+          <t>Внутренняя ставка, ₽/ч-д</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>11515</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>1255</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B21" s="7">
+        <f>B17*B20</f>
+        <v>1093925</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>12</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
+          <t>Абонентов в периметре</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>5</v>
+        <v>1255</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Ростов (центральный) 426, Воронеж 445, Нижний Новгород 164, Славянск-на-Кубани 140, Москва 80. Сумма 1255 сходится с аудитом.</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Пять узлов, число нечётное — отдельный арбитр не нужен. Кластер переживает потерю двух узлов из пяти.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Пока Воронеж не введён, узлов четыре — число чётное. Кластер переживает потерю только одного узла, а при разрыве сети пополам ни одна половина не имеет большинства. Это состояние держится недели 8–11; если оно нежелательно, на этот период ставится арбитр garbd (1 vCPU, 512 МБ).</t>
+          <t>ЦОД-1 40, ЦОД-2 40 (оба живые), Ростов 426, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Абонентов 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Серверов нужно докупить</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Все узлы — свои виртуальные машины. Московский узел — ещё одна ВМ на существующих мощностях.</t>
+          <t>Шесть узлов — число ЧЁТНОЕ, поэтому нужен арбитр garbd: он даёт седьмой голос и не хранит данные. Кластер переживает потерю двух узлов и остаётся работоспособным при потере ЦОД целиком (четыре голоса из семи в городах).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
+          <t>Где стоит арбитр</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>Ростов, отдельная ВМ</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>НЕ в ЦОД. Если поставить арбитр в ЦОД, потеря дата-центра уносит три голоса из семи разом. В Ростове — самая крупная площадка после Воронежа и своя инфраструктура. Требования: 1 vCPU, 512 МБ.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>нельзя</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>Пять узлов — нечётное, арбитр на этапе 1 не нужен. Он ставится в задаче 11 вместе с вводом Воронежа, который делает число узлов чётным.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Резервный центральный узел отдельной машиной</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Не требуется: каждый вынос — клон центрального узла, FreePBX на нём уже установлен и только отключён, поэтому роль передаётся на любой рабочий вынос; процедура отрабатывается в задаче 7 учебно.</t>
+          <t>ЦОД-1, ЦОД-2 и ВМ под арбитр в Ростове. Все — свои мощности, закупки нет. У четырёх городских площадок машины уже есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Оба узла ЦОД — живые</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Панель управления FreePBX</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Неделя 16 — предновогодняя</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>21–25 декабря</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Исполнитель</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Дата протокола совещания</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Проставить дату документа, из которого взята этапность.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>IP-адреса Славянска-на-Кубани и локального PBX</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>В исходных данных аудита отсутствуют, запрашиваются в первую неделю.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1097,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD60"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7" customWidth="1" min="1" max="1"/>
@@ -1130,6 +1215,7 @@
     <col width="6.6" customWidth="1" min="28" max="28"/>
     <col width="6.6" customWidth="1" min="29" max="29"/>
     <col width="6.6" customWidth="1" min="30" max="30"/>
+    <col width="6.6" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1310,12 +1396,17 @@
           <t>14-20</t>
         </is>
       </c>
+      <c r="AE2" s="16" t="inlineStr">
+        <is>
+          <t>21-27</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="17" t="n"/>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>ЭТАП 1 — все площадки, кроме Воронежа (недели 1–11, 810 абонентов)</t>
+          <t>ЭТАП 1 — центр в московском ЦОД и все выносы, кроме Воронежа (недели 1–12, 810 абонентов)</t>
         </is>
       </c>
       <c r="C3" s="17" t="n"/>
@@ -1346,6 +1437,7 @@
       <c r="AB3" s="17" t="n"/>
       <c r="AC3" s="17" t="n"/>
       <c r="AD3" s="17" t="n"/>
+      <c r="AE3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
@@ -1355,7 +1447,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Подготовка: сеть, виртуальные машины, договорённости с операторами</t>
+          <t>Подготовка: ЦОД, сеть, виртуальные машины, договорённости с операторами</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
@@ -1370,11 +1462,11 @@
       </c>
       <c r="E4" s="20" t="n"/>
       <c r="F4" s="21">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G4" s="21">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H4" s="21">
@@ -1383,12 +1475,12 @@
       </c>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>Площадки не связаны между собой сетью; у операторов нет отдельных учётных записей на каждую площадку</t>
+          <t>Площадки не связаны между собой сетью; в ЦОД не выделены машины под центральные узлы; у операторов нет отдельных учётных записей на каждую площадку</t>
         </is>
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>VPN между площадками поднят, RTT измерен и зафиксирован, ВМ под московский узел выделена и размещена на отдельном хосте, у каждой площадки свой SIP-пользователь ВАТС</t>
+          <t>VPN между ЦОД и всеми городами поднят, RTT измерен, в ЦОД выделены две ВМ в разных залах, у каждой площадки свой SIP-пользователь ВАТС</t>
         </is>
       </c>
       <c r="K4" s="20" t="n"/>
@@ -1401,7 +1493,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="22">
-        <f>Параметры!$B$18*M4</f>
+        <f>Параметры!$B$20*M4</f>
         <v>92120</v>
       </c>
       <c r="O4" s="22" t="n">
@@ -1425,11 +1517,11 @@
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G5" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>Параметры!$B$10+4</f>
         <v>46276</v>
       </c>
       <c r="H5" s="26" t="n"/>
@@ -1460,25 +1552,25 @@
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>Организовать site-to-site VPN между площадками</t>
+          <t>Организовать site-to-site VPN: ЦОД — города</t>
         </is>
       </c>
       <c r="C6" s="26" t="n"/>
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="26" t="n"/>
       <c r="F6" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G6" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H6" s="26" t="n"/>
       <c r="I6" s="26" t="n"/>
       <c r="J6" s="26" t="inlineStr">
         <is>
-          <t>Сеть между площадками работает</t>
+          <t>Сеть между ЦОД и всеми площадками работает</t>
         </is>
       </c>
       <c r="K6" s="28" t="n"/>
@@ -1503,18 +1595,18 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>Замерить RTT и потери между всеми парами площадок</t>
+          <t>Замерить RTT и потери: ЦОД — каждый город и между залами ЦОД</t>
         </is>
       </c>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
       <c r="E7" s="26" t="n"/>
       <c r="F7" s="27">
-        <f>Параметры!$B$9+7</f>
+        <f>Параметры!$B$10+7</f>
         <v>46279</v>
       </c>
       <c r="G7" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H7" s="26" t="n"/>
@@ -1552,11 +1644,11 @@
       <c r="D8" s="26" t="n"/>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G8" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>Параметры!$B$10+4</f>
         <v>46276</v>
       </c>
       <c r="H8" s="26" t="n"/>
@@ -1587,25 +1679,25 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Выделить ВМ под московский узел, проверить размещение узлов по хостам</t>
+          <t>Выделить в ЦОД две ВМ — в разных залах, на разных хостах и вводах питания</t>
         </is>
       </c>
       <c r="C9" s="26" t="n"/>
       <c r="D9" s="26" t="n"/>
       <c r="E9" s="26" t="n"/>
       <c r="F9" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G9" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>Параметры!$B$10+4</f>
         <v>46276</v>
       </c>
       <c r="H9" s="26" t="n"/>
       <c r="I9" s="26" t="n"/>
       <c r="J9" s="26" t="inlineStr">
         <is>
-          <t>ВМ выделена; узлы кластера стоят на разных физических хостах</t>
+          <t>ВМ выделены; подтверждено, что залы не делят хост, питание и аплинк</t>
         </is>
       </c>
       <c r="K9" s="28" t="n"/>
@@ -1615,7 +1707,7 @@
         </is>
       </c>
       <c r="M9" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" s="26" t="n"/>
       <c r="O9" s="26" t="n"/>
@@ -1636,11 +1728,11 @@
       <c r="D10" s="26" t="n"/>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G10" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H10" s="26" t="n"/>
@@ -1657,7 +1749,7 @@
         </is>
       </c>
       <c r="M10" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="26" t="n"/>
       <c r="O10" s="26" t="n"/>
@@ -1687,11 +1779,11 @@
       </c>
       <c r="E11" s="20" t="n"/>
       <c r="F11" s="21">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G11" s="21">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H11" s="21">
@@ -1718,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="22">
-        <f>Параметры!$B$18*M11</f>
+        <f>Параметры!$B$20*M11</f>
         <v>115150</v>
       </c>
       <c r="O11" s="22" t="n">
@@ -1742,11 +1834,11 @@
       <c r="D12" s="26" t="n"/>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G12" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>Параметры!$B$10+4</f>
         <v>46276</v>
       </c>
       <c r="H12" s="26" t="n"/>
@@ -1784,11 +1876,11 @@
       <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G13" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>Параметры!$B$10+4</f>
         <v>46276</v>
       </c>
       <c r="H13" s="26" t="n"/>
@@ -1826,11 +1918,11 @@
       <c r="D14" s="26" t="n"/>
       <c r="E14" s="26" t="n"/>
       <c r="F14" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>Параметры!$B$10+0</f>
         <v>46272</v>
       </c>
       <c r="G14" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H14" s="26" t="n"/>
@@ -1869,11 +1961,11 @@
       <c r="D15" s="26" t="n"/>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="27">
-        <f>Параметры!$B$9+7</f>
+        <f>Параметры!$B$10+7</f>
         <v>46279</v>
       </c>
       <c r="G15" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H15" s="26" t="n"/>
@@ -1911,11 +2003,11 @@
       <c r="D16" s="26" t="n"/>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="27">
-        <f>Параметры!$B$9+7</f>
+        <f>Параметры!$B$10+7</f>
         <v>46279</v>
       </c>
       <c r="G16" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H16" s="26" t="n"/>
@@ -1953,11 +2045,11 @@
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="26" t="n"/>
       <c r="F17" s="27">
-        <f>Параметры!$B$9+7</f>
+        <f>Параметры!$B$10+7</f>
         <v>46279</v>
       </c>
       <c r="G17" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>Параметры!$B$10+11</f>
         <v>46283</v>
       </c>
       <c r="H17" s="26" t="n"/>
@@ -2003,11 +2095,11 @@
       </c>
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="21">
-        <f>Параметры!$B$9+14</f>
+        <f>Параметры!$B$10+14</f>
         <v>46286</v>
       </c>
       <c r="G18" s="21">
-        <f>Параметры!$B$9+18</f>
+        <f>Параметры!$B$10+18</f>
         <v>46290</v>
       </c>
       <c r="H18" s="21">
@@ -2016,12 +2108,12 @@
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>Процедуры восстановления кластера ни разу не выполнялись; способ развёртывания выноса клонированием не проверен</t>
+          <t>Процедуры восстановления кластера и передачи роли мастера ни разу не выполнялись</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>Стенд из двух машин прошёл чек-лист приёмки; восстановление кворума и передача роли мастера выполнены руками</t>
+          <t>Стенд из трёх машин прошёл чек-лист приёмки: клонирование, восстановление кворума и передача роли мастера выполнены руками</t>
         </is>
       </c>
       <c r="K18" s="20" t="n"/>
@@ -2034,7 +2126,7 @@
         <v>6</v>
       </c>
       <c r="N18" s="22">
-        <f>Параметры!$B$18*M18</f>
+        <f>Параметры!$B$20*M18</f>
         <v>69090</v>
       </c>
       <c r="O18" s="22" t="n">
@@ -2050,25 +2142,25 @@
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>Развернуть тестовый центральный узел и клонировать его в вынос</t>
+          <t>Развернуть тестовый мастер и клонировать его в два узла</t>
         </is>
       </c>
       <c r="C19" s="26" t="n"/>
       <c r="D19" s="26" t="n"/>
       <c r="E19" s="26" t="n"/>
       <c r="F19" s="27">
-        <f>Параметры!$B$9+14</f>
+        <f>Параметры!$B$10+14</f>
         <v>46286</v>
       </c>
       <c r="G19" s="27">
-        <f>Параметры!$B$9+18</f>
+        <f>Параметры!$B$10+18</f>
         <v>46290</v>
       </c>
       <c r="H19" s="26" t="n"/>
       <c r="I19" s="26" t="n"/>
       <c r="J19" s="26" t="inlineStr">
         <is>
-          <t>Клон вступил в кластер, конфликтов имён узлов нет</t>
+          <t>Клоны вступили в кластер, конфликтов имён узлов нет</t>
         </is>
       </c>
       <c r="K19" s="28" t="n"/>
@@ -2092,25 +2184,25 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Прогнать чек-лист приёмки</t>
+          <t>Отработать передачу роли мастера между двумя узлами</t>
         </is>
       </c>
       <c r="C20" s="26" t="n"/>
       <c r="D20" s="26" t="n"/>
       <c r="E20" s="26" t="n"/>
       <c r="F20" s="27">
-        <f>Параметры!$B$9+14</f>
+        <f>Параметры!$B$10+14</f>
         <v>46286</v>
       </c>
       <c r="G20" s="27">
-        <f>Параметры!$B$9+18</f>
+        <f>Параметры!$B$10+18</f>
         <v>46290</v>
       </c>
       <c r="H20" s="26" t="n"/>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="26" t="inlineStr">
         <is>
-          <t>Чек-лист пройден</t>
+          <t>Процедура выполнена в обе стороны и задокументирована</t>
         </is>
       </c>
       <c r="K20" s="28" t="n"/>
@@ -2120,7 +2212,7 @@
         </is>
       </c>
       <c r="M20" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" s="26" t="n"/>
       <c r="O20" s="26" t="n"/>
@@ -2134,25 +2226,25 @@
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>Отработать восстановление кворума и передачу роли мастера</t>
+          <t>Отработать восстановление кворума</t>
         </is>
       </c>
       <c r="C21" s="26" t="n"/>
       <c r="D21" s="26" t="n"/>
       <c r="E21" s="26" t="n"/>
       <c r="F21" s="27">
-        <f>Параметры!$B$9+14</f>
+        <f>Параметры!$B$10+14</f>
         <v>46286</v>
       </c>
       <c r="G21" s="27">
-        <f>Параметры!$B$9+18</f>
+        <f>Параметры!$B$10+18</f>
         <v>46290</v>
       </c>
       <c r="H21" s="26" t="n"/>
       <c r="I21" s="26" t="n"/>
       <c r="J21" s="26" t="inlineStr">
         <is>
-          <t>Процедуры выполнены и задокументированы</t>
+          <t>Кворум восстановлен вручную</t>
         </is>
       </c>
       <c r="K21" s="28" t="n"/>
@@ -2162,7 +2254,7 @@
         </is>
       </c>
       <c r="M21" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" s="26" t="n"/>
       <c r="O21" s="26" t="n"/>
@@ -2176,7 +2268,7 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Ростов — центральный узел кластера</t>
+          <t>Ростовская АТС — первый узел кластера</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
@@ -2191,11 +2283,11 @@
       </c>
       <c r="E22" s="20" t="n"/>
       <c r="F22" s="21">
-        <f>Параметры!$B$9+21</f>
+        <f>Параметры!$B$10+21</f>
         <v>46293</v>
       </c>
       <c r="G22" s="21">
-        <f>Параметры!$B$9+25</f>
+        <f>Параметры!$B$10+25</f>
         <v>46297</v>
       </c>
       <c r="H22" s="21">
@@ -2204,12 +2296,12 @@
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>Существующая ростовская АТС работает как отдельная станция и не может обслуживать выносы</t>
+          <t>Вся боевая база живёт на ростовской АТС; перенести её в ЦОД без простоя можно только через кластер</t>
         </is>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>Ростовская АТС работает центральным узлом без переустановки; номера доступны выносам через общую базу</t>
+          <t>Ростовская АТС работает узлом кластера без переустановки; база готова к репликации в ЦОД</t>
         </is>
       </c>
       <c r="K22" s="20" t="n"/>
@@ -2222,7 +2314,7 @@
         <v>4</v>
       </c>
       <c r="N22" s="22">
-        <f>Параметры!$B$18*M22</f>
+        <f>Параметры!$B$20*M22</f>
         <v>46060</v>
       </c>
       <c r="O22" s="22" t="n">
@@ -2245,11 +2337,11 @@
       <c r="D23" s="26" t="n"/>
       <c r="E23" s="26" t="n"/>
       <c r="F23" s="27">
-        <f>Параметры!$B$9+21</f>
+        <f>Параметры!$B$10+21</f>
         <v>46293</v>
       </c>
       <c r="G23" s="27">
-        <f>Параметры!$B$9+25</f>
+        <f>Параметры!$B$10+25</f>
         <v>46297</v>
       </c>
       <c r="H23" s="26" t="n"/>
@@ -2287,11 +2379,11 @@
       <c r="D24" s="26" t="n"/>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="27">
-        <f>Параметры!$B$9+21</f>
+        <f>Параметры!$B$10+21</f>
         <v>46293</v>
       </c>
       <c r="G24" s="27">
-        <f>Параметры!$B$9+25</f>
+        <f>Параметры!$B$10+25</f>
         <v>46297</v>
       </c>
       <c r="H24" s="26" t="n"/>
@@ -2322,18 +2414,18 @@
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Наблюдение до ввода первого выноса</t>
+          <t>Наблюдение до переноса центра</t>
         </is>
       </c>
       <c r="C25" s="26" t="n"/>
       <c r="D25" s="26" t="n"/>
       <c r="E25" s="26" t="n"/>
       <c r="F25" s="27">
-        <f>Параметры!$B$9+21</f>
+        <f>Параметры!$B$10+21</f>
         <v>46293</v>
       </c>
       <c r="G25" s="27">
-        <f>Параметры!$B$9+25</f>
+        <f>Параметры!$B$10+25</f>
         <v>46297</v>
       </c>
       <c r="H25" s="26" t="n"/>
@@ -2364,7 +2456,7 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>Пилотный вынос — Нижний Новгород</t>
+          <t>Центр в московском ЦОД: два живых узла в разных залах</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
@@ -2379,11 +2471,11 @@
       </c>
       <c r="E26" s="20" t="n"/>
       <c r="F26" s="21">
-        <f>Параметры!$B$9+28</f>
+        <f>Параметры!$B$10+28</f>
         <v>46300</v>
       </c>
       <c r="G26" s="21">
-        <f>Параметры!$B$9+39</f>
+        <f>Параметры!$B$10+39</f>
         <v>46311</v>
       </c>
       <c r="H26" s="21">
@@ -2392,12 +2484,12 @@
       </c>
       <c r="I26" s="19" t="inlineStr">
         <is>
-          <t>Схема не проверена на реальной нагрузке и реальном канале; Воронеж по решению совещания перенесён во второй этап и пилотом быть не может</t>
+          <t>Управление и база сосредоточены на ростовской АТС — площадке без резервирования; по решению совещания центр переносится в ЦОД с копией во втором зале</t>
         </is>
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>Нижний Новгород работает выносом кластера: локальная регистрация телефонов, свой выход в город, переключение на Ростов при отказе площадки</t>
+          <t>Два живых узла в разных залах ЦОД обслуживают вызовы, управление на ЦОД-1; Ростов понижен до выноса, 80 московских абонентов поделены между залами</t>
         </is>
       </c>
       <c r="K26" s="20" t="n"/>
@@ -2410,7 +2502,7 @@
         <v>10</v>
       </c>
       <c r="N26" s="22">
-        <f>Параметры!$B$18*M26</f>
+        <f>Параметры!$B$20*M26</f>
         <v>115150</v>
       </c>
       <c r="O26" s="22" t="n">
@@ -2427,25 +2519,25 @@
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>Клонировать машину центрального узла и расшить клон в вынос</t>
+          <t>Клонировать ростовскую АТС в ЦОД-1, расшить клон в узел</t>
         </is>
       </c>
       <c r="C27" s="26" t="n"/>
       <c r="D27" s="26" t="n"/>
       <c r="E27" s="26" t="n"/>
       <c r="F27" s="27">
-        <f>Параметры!$B$9+28</f>
+        <f>Параметры!$B$10+28</f>
         <v>46300</v>
       </c>
       <c r="G27" s="27">
-        <f>Параметры!$B$9+32</f>
+        <f>Параметры!$B$10+32</f>
         <v>46304</v>
       </c>
       <c r="H27" s="26" t="n"/>
       <c r="I27" s="26" t="n"/>
       <c r="J27" s="26" t="inlineStr">
         <is>
-          <t>Вынос в кластере</t>
+          <t>ЦОД-1 в кластере, синхронизирован</t>
         </is>
       </c>
       <c r="K27" s="28" t="n"/>
@@ -2469,25 +2561,25 @@
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Настроить межузловые транки и перенести диалплан</t>
+          <t>Передать роль мастера с Ростова на ЦОД-1</t>
         </is>
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="26" t="n"/>
       <c r="E28" s="26" t="n"/>
       <c r="F28" s="27">
-        <f>Параметры!$B$9+28</f>
+        <f>Параметры!$B$10+28</f>
         <v>46300</v>
       </c>
       <c r="G28" s="27">
-        <f>Параметры!$B$9+32</f>
+        <f>Параметры!$B$10+32</f>
         <v>46304</v>
       </c>
       <c r="H28" s="26" t="n"/>
       <c r="I28" s="26" t="n"/>
       <c r="J28" s="26" t="inlineStr">
         <is>
-          <t>Вызовы между Ростовом и Нижним Новгородом проходят</t>
+          <t>FreePBX и управление работают из ЦОД-1</t>
         </is>
       </c>
       <c r="K28" s="28" t="n"/>
@@ -2511,25 +2603,25 @@
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>Подключить локальный транк оператора</t>
+          <t>Клонировать ЦОД-1 в ЦОД-2 (второй зал), расшить клон в узел</t>
         </is>
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="26" t="n"/>
       <c r="E29" s="26" t="n"/>
       <c r="F29" s="27">
-        <f>Параметры!$B$9+28</f>
-        <v>46300</v>
+        <f>Параметры!$B$10+35</f>
+        <v>46307</v>
       </c>
       <c r="G29" s="27">
-        <f>Параметры!$B$9+32</f>
-        <v>46304</v>
+        <f>Параметры!$B$10+39</f>
+        <v>46311</v>
       </c>
       <c r="H29" s="26" t="n"/>
       <c r="I29" s="26" t="n"/>
       <c r="J29" s="26" t="inlineStr">
         <is>
-          <t>Свой выход в город работает</t>
+          <t>ЦОД-2 в кластере, узлов три — кворум нечётный</t>
         </is>
       </c>
       <c r="K29" s="28" t="n"/>
@@ -2539,11 +2631,11 @@
         </is>
       </c>
       <c r="M29" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N29" s="26" t="n"/>
       <c r="O29" s="26" t="n"/>
-      <c r="T29" s="23" t="n"/>
+      <c r="U29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
@@ -2553,25 +2645,25 @@
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Перевести телефоны на вынос через провижининг</t>
+          <t>Сделать ЦОД-2 живым узлом: транк оператора, FreePBX оставить выключенным</t>
         </is>
       </c>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="26" t="n"/>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="27">
-        <f>Параметры!$B$9+28</f>
-        <v>46300</v>
+        <f>Параметры!$B$10+35</f>
+        <v>46307</v>
       </c>
       <c r="G30" s="27">
-        <f>Параметры!$B$9+32</f>
-        <v>46304</v>
+        <f>Параметры!$B$10+39</f>
+        <v>46311</v>
       </c>
       <c r="H30" s="26" t="n"/>
       <c r="I30" s="26" t="n"/>
       <c r="J30" s="26" t="inlineStr">
         <is>
-          <t>Телефоны регистрируются на площадке, резервный сервер — Ростов</t>
+          <t>ЦОД-2 несёт вызовы наравне с ЦОД-1; панель управления включена ровно на одном узле</t>
         </is>
       </c>
       <c r="K30" s="28" t="n"/>
@@ -2585,7 +2677,7 @@
       </c>
       <c r="N30" s="26" t="n"/>
       <c r="O30" s="26" t="n"/>
-      <c r="T30" s="23" t="n"/>
+      <c r="U30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
@@ -2595,25 +2687,25 @@
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Неделя наблюдения под реальной нагрузкой</t>
+          <t>Понизить Ростов до выноса, поделить 80 московских абонентов между залами</t>
         </is>
       </c>
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="27">
-        <f>Параметры!$B$9+35</f>
+        <f>Параметры!$B$10+35</f>
         <v>46307</v>
       </c>
       <c r="G31" s="27">
-        <f>Параметры!$B$9+39</f>
+        <f>Параметры!$B$10+39</f>
         <v>46311</v>
       </c>
       <c r="H31" s="26" t="n"/>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="26" t="inlineStr">
         <is>
-          <t>Отказ площадки и возврат отработаны, решение о тиражировании принято</t>
+          <t>По 40 абонентов на зал, каждый зал прописан другому резервным</t>
         </is>
       </c>
       <c r="K31" s="28" t="n"/>
@@ -2623,7 +2715,7 @@
         </is>
       </c>
       <c r="M31" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31" s="26" t="n"/>
       <c r="O31" s="26" t="n"/>
@@ -2637,7 +2729,7 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>Тиражирование на остальные выносы этапа 1</t>
+          <t>Пилотный вынос — Нижний Новгород</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
@@ -2652,11 +2744,11 @@
       </c>
       <c r="E32" s="20" t="n"/>
       <c r="F32" s="21">
-        <f>Параметры!$B$9+42</f>
+        <f>Параметры!$B$10+42</f>
         <v>46314</v>
       </c>
       <c r="G32" s="21">
-        <f>Параметры!$B$9+53</f>
+        <f>Параметры!$B$10+53</f>
         <v>46325</v>
       </c>
       <c r="H32" s="21">
@@ -2665,12 +2757,12 @@
       </c>
       <c r="I32" s="19" t="inlineStr">
         <is>
-          <t>Славянск-на-Кубани обслуживается отдельной станцией, московские абоненты — удалённо из Ростова</t>
+          <t>Схема «центр в ЦОД — вынос в городе» не проверена на реальной нагрузке и канале</t>
         </is>
       </c>
       <c r="J32" s="19" t="inlineStr">
         <is>
-          <t>Все выносы этапа 1 работают узлами одного кластера</t>
+          <t>Нижний Новгород работает выносом: локальная регистрация телефонов, свой выход в город, переключение на ЦОД при отказе площадки</t>
         </is>
       </c>
       <c r="K32" s="20" t="n"/>
@@ -2683,7 +2775,7 @@
         <v>10</v>
       </c>
       <c r="N32" s="22">
-        <f>Параметры!$B$18*M32</f>
+        <f>Параметры!$B$20*M32</f>
         <v>115150</v>
       </c>
       <c r="O32" s="22" t="n">
@@ -2700,25 +2792,25 @@
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Славянск-на-Кубани (Краснодар) — 140 абонентов</t>
+          <t>Клонировать мастер и расшить клон в вынос</t>
         </is>
       </c>
       <c r="C33" s="26" t="n"/>
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="26" t="n"/>
       <c r="F33" s="27">
-        <f>Параметры!$B$9+42</f>
+        <f>Параметры!$B$10+42</f>
         <v>46314</v>
       </c>
       <c r="G33" s="27">
-        <f>Параметры!$B$9+46</f>
+        <f>Параметры!$B$10+46</f>
         <v>46318</v>
       </c>
       <c r="H33" s="26" t="n"/>
       <c r="I33" s="26" t="n"/>
       <c r="J33" s="26" t="inlineStr">
         <is>
-          <t>Вынос работает</t>
+          <t>Вынос в кластере</t>
         </is>
       </c>
       <c r="K33" s="28" t="n"/>
@@ -2728,7 +2820,7 @@
         </is>
       </c>
       <c r="M33" s="26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N33" s="26" t="n"/>
       <c r="O33" s="26" t="n"/>
@@ -2742,25 +2834,25 @@
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Москва — 80 абонентов, новый вынос вместо обслуживания из Ростова</t>
+          <t>Настроить межузловые транки и перенести диалплан</t>
         </is>
       </c>
       <c r="C34" s="26" t="n"/>
       <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="27">
-        <f>Параметры!$B$9+49</f>
-        <v>46321</v>
+        <f>Параметры!$B$10+42</f>
+        <v>46314</v>
       </c>
       <c r="G34" s="27">
-        <f>Параметры!$B$9+53</f>
-        <v>46325</v>
+        <f>Параметры!$B$10+46</f>
+        <v>46318</v>
       </c>
       <c r="H34" s="26" t="n"/>
       <c r="I34" s="26" t="n"/>
       <c r="J34" s="26" t="inlineStr">
         <is>
-          <t>Вынос работает, абоненты переведены с Ростова</t>
+          <t>Вызовы между ЦОД, Ростовом и Нижним Новгородом проходят</t>
         </is>
       </c>
       <c r="K34" s="28" t="n"/>
@@ -2770,101 +2862,81 @@
         </is>
       </c>
       <c r="M34" s="26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N34" s="26" t="n"/>
       <c r="O34" s="26" t="n"/>
-      <c r="W34" s="23" t="n"/>
+      <c r="V34" s="23" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Учебная передача роли центрального узла</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="21">
-        <f>Параметры!$B$9+56</f>
-        <v>46328</v>
-      </c>
-      <c r="G35" s="21">
-        <f>Параметры!$B$9+60</f>
-        <v>46332</v>
-      </c>
-      <c r="H35" s="21">
-        <f>G35</f>
-        <v>46332</v>
-      </c>
-      <c r="I35" s="19" t="inlineStr">
-        <is>
-          <t>Управление кластером сосредоточено на одном сервере, процедура замены не опробована</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="inlineStr">
-        <is>
-          <t>Роль центрального узла передана на другой узел и возвращена обратно в согласованное окно</t>
-        </is>
-      </c>
-      <c r="K35" s="20" t="n"/>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M35" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" s="22">
-        <f>Параметры!$B$18*M35</f>
-        <v>34545</v>
-      </c>
-      <c r="O35" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" s="23" t="n"/>
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Подключить локальный транк оператора</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="27">
+        <f>Параметры!$B$10+42</f>
+        <v>46314</v>
+      </c>
+      <c r="G35" s="27">
+        <f>Параметры!$B$10+46</f>
+        <v>46318</v>
+      </c>
+      <c r="H35" s="26" t="n"/>
+      <c r="I35" s="26" t="n"/>
+      <c r="J35" s="26" t="inlineStr">
+        <is>
+          <t>Свой выход в город работает</t>
+        </is>
+      </c>
+      <c r="K35" s="28" t="n"/>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="26" t="n"/>
+      <c r="O35" s="26" t="n"/>
+      <c r="V35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>Передать роль центрального узла на другой узел</t>
+          <t>Перевести телефоны на вынос через провижининг</t>
         </is>
       </c>
       <c r="C36" s="26" t="n"/>
       <c r="D36" s="26" t="n"/>
       <c r="E36" s="26" t="n"/>
       <c r="F36" s="27">
-        <f>Параметры!$B$9+56</f>
-        <v>46328</v>
+        <f>Параметры!$B$10+42</f>
+        <v>46314</v>
       </c>
       <c r="G36" s="27">
-        <f>Параметры!$B$9+60</f>
-        <v>46332</v>
+        <f>Параметры!$B$10+46</f>
+        <v>46318</v>
       </c>
       <c r="H36" s="26" t="n"/>
       <c r="I36" s="26" t="n"/>
       <c r="J36" s="26" t="inlineStr">
         <is>
-          <t>Управление и звонки работают с нового мастера</t>
+          <t>Телефоны регистрируются на площадке, резервный сервер — ЦОД-1</t>
         </is>
       </c>
       <c r="K36" s="28" t="n"/>
@@ -2878,35 +2950,35 @@
       </c>
       <c r="N36" s="26" t="n"/>
       <c r="O36" s="26" t="n"/>
-      <c r="X36" s="23" t="n"/>
+      <c r="V36" s="23" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>Вернуть роль обратно на Ростов</t>
+          <t>Неделя наблюдения под реальной нагрузкой</t>
         </is>
       </c>
       <c r="C37" s="26" t="n"/>
       <c r="D37" s="26" t="n"/>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="27">
-        <f>Параметры!$B$9+56</f>
-        <v>46328</v>
+        <f>Параметры!$B$10+49</f>
+        <v>46321</v>
       </c>
       <c r="G37" s="27">
-        <f>Параметры!$B$9+60</f>
-        <v>46332</v>
+        <f>Параметры!$B$10+53</f>
+        <v>46325</v>
       </c>
       <c r="H37" s="26" t="n"/>
       <c r="I37" s="26" t="n"/>
       <c r="J37" s="26" t="inlineStr">
         <is>
-          <t>Схема возвращена в штатное состояние</t>
+          <t>Отказ площадки и возврат отработаны, решение о тиражировании принято</t>
         </is>
       </c>
       <c r="K37" s="28" t="n"/>
@@ -2916,21 +2988,21 @@
         </is>
       </c>
       <c r="M37" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N37" s="26" t="n"/>
       <c r="O37" s="26" t="n"/>
-      <c r="X37" s="23" t="n"/>
+      <c r="W37" s="23" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>Консолидация мелких АТС этапа 1</t>
+          <t>Вынос Славянск-на-Кубани</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
@@ -2945,25 +3017,25 @@
       </c>
       <c r="E38" s="20" t="n"/>
       <c r="F38" s="21">
-        <f>Параметры!$B$9+42</f>
-        <v>46314</v>
+        <f>Параметры!$B$10+56</f>
+        <v>46328</v>
       </c>
       <c r="G38" s="21">
-        <f>Параметры!$B$9+67</f>
-        <v>46339</v>
+        <f>Параметры!$B$10+60</f>
+        <v>46332</v>
       </c>
       <c r="H38" s="21">
         <f>G38</f>
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="I38" s="19" t="inlineStr">
         <is>
-          <t>Шесть станций на 127 абонентов дорого поддерживать и невыгодно включать в кластер отдельными узлами</t>
+          <t>Славянск-на-Кубани обслуживается отдельной станцией вне кластера</t>
         </is>
       </c>
       <c r="J38" s="19" t="inlineStr">
         <is>
-          <t>Абоненты мелких станций переведены на выносы, станции выведены из эксплуатации</t>
+          <t>Все выносы этапа 1 работают узлами одного кластера, узлов пять — кворум нечётный</t>
         </is>
       </c>
       <c r="K38" s="20" t="n"/>
@@ -2973,47 +3045,44 @@
         </is>
       </c>
       <c r="M38" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38" s="22">
-        <f>Параметры!$B$18*M38</f>
-        <v>69090</v>
+        <f>Параметры!$B$20*M38</f>
+        <v>57575</v>
       </c>
       <c r="O38" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="23" t="n"/>
-      <c r="W38" s="23" t="n"/>
       <c r="X38" s="23" t="n"/>
-      <c r="Y38" s="23" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>ССЗ — 39 абонентов — в Нижний Новгород</t>
+          <t>Развернуть вынос по отработанной процедуре — 140 абонентов</t>
         </is>
       </c>
       <c r="C39" s="26" t="n"/>
       <c r="D39" s="26" t="n"/>
       <c r="E39" s="26" t="n"/>
       <c r="F39" s="27">
-        <f>Параметры!$B$9+42</f>
-        <v>46314</v>
+        <f>Параметры!$B$10+56</f>
+        <v>46328</v>
       </c>
       <c r="G39" s="27">
-        <f>Параметры!$B$9+46</f>
-        <v>46318</v>
+        <f>Параметры!$B$10+60</f>
+        <v>46332</v>
       </c>
       <c r="H39" s="26" t="n"/>
       <c r="I39" s="26" t="n"/>
       <c r="J39" s="26" t="inlineStr">
         <is>
-          <t>Станция выведена</t>
+          <t>Вынос работает, старая станция погашена</t>
         </is>
       </c>
       <c r="K39" s="28" t="n"/>
@@ -3023,39 +3092,39 @@
         </is>
       </c>
       <c r="M39" s="26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N39" s="26" t="n"/>
       <c r="O39" s="26" t="n"/>
-      <c r="V39" s="23" t="n"/>
+      <c r="X39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Манитек, Семикаракорский, Цимлянский, Приманыческий — 73 абонента — в Ростов</t>
+          <t>Проверить кворум и отказоустойчивость на пяти узлах</t>
         </is>
       </c>
       <c r="C40" s="26" t="n"/>
       <c r="D40" s="26" t="n"/>
       <c r="E40" s="26" t="n"/>
       <c r="F40" s="27">
-        <f>Параметры!$B$9+49</f>
-        <v>46321</v>
+        <f>Параметры!$B$10+56</f>
+        <v>46328</v>
       </c>
       <c r="G40" s="27">
-        <f>Параметры!$B$9+60</f>
+        <f>Параметры!$B$10+60</f>
         <v>46332</v>
       </c>
       <c r="H40" s="26" t="n"/>
       <c r="I40" s="26" t="n"/>
       <c r="J40" s="26" t="inlineStr">
         <is>
-          <t>Станции выведены</t>
+          <t>Кластер переживает потерю двух узлов из пяти</t>
         </is>
       </c>
       <c r="K40" s="28" t="n"/>
@@ -3065,150 +3134,143 @@
         </is>
       </c>
       <c r="M40" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N40" s="26" t="n"/>
       <c r="O40" s="26" t="n"/>
-      <c r="W40" s="23" t="n"/>
       <c r="X40" s="23" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>Локальный PBX — 15 абонентов — в Москву</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="n"/>
-      <c r="D41" s="26" t="n"/>
-      <c r="E41" s="26" t="n"/>
-      <c r="F41" s="27">
-        <f>Параметры!$B$9+63</f>
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Учебное переключение управления между залами ЦОД</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="21">
+        <f>Параметры!$B$10+63</f>
         <v>46335</v>
       </c>
-      <c r="G41" s="27">
-        <f>Параметры!$B$9+67</f>
+      <c r="G41" s="21">
+        <f>Параметры!$B$10+67</f>
         <v>46339</v>
       </c>
-      <c r="H41" s="26" t="n"/>
-      <c r="I41" s="26" t="n"/>
-      <c r="J41" s="26" t="inlineStr">
-        <is>
-          <t>Станция выведена</t>
-        </is>
-      </c>
-      <c r="K41" s="28" t="n"/>
-      <c r="L41" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M41" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="26" t="n"/>
-      <c r="O41" s="26" t="n"/>
+      <c r="H41" s="21">
+        <f>G41</f>
+        <v>46339</v>
+      </c>
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>Вызовы оба зала несут постоянно, но панель управления живёт на одном узле; её переключение не опробовано</t>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>Управление переведено в зал 2 и возвращено в зал 1 в согласованное окно; время переключения измерено и внесено в регламент</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="n"/>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M41" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" s="22">
+        <f>Параметры!$B$20*M41</f>
+        <v>34545</v>
+      </c>
+      <c r="O41" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="Y41" s="23" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>Перевод абонентов этапа 1 на единый план нумерации</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="21">
-        <f>Параметры!$B$9+28</f>
-        <v>46300</v>
-      </c>
-      <c r="G42" s="21">
-        <f>Параметры!$B$9+74</f>
-        <v>46346</v>
-      </c>
-      <c r="H42" s="21">
-        <f>G42</f>
-        <v>46346</v>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>Станции используют пересекающиеся номера, единый план невозможен без разведения конфликтов</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>810 абонентов этапа 1 переведены на пятизначную нумерацию, переадресации сняты</t>
-        </is>
-      </c>
-      <c r="K42" s="20" t="n"/>
-      <c r="L42" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="N42" s="22">
-        <f>Параметры!$B$18*M42</f>
-        <v>138180</v>
-      </c>
-      <c r="O42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="23" t="n"/>
-      <c r="U42" s="23" t="n"/>
-      <c r="V42" s="23" t="n"/>
-      <c r="W42" s="23" t="n"/>
-      <c r="X42" s="23" t="n"/>
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>Включить FreePBX на ЦОД-2, проверить управление и звонки</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="26" t="n"/>
+      <c r="F42" s="27">
+        <f>Параметры!$B$10+63</f>
+        <v>46335</v>
+      </c>
+      <c r="G42" s="27">
+        <f>Параметры!$B$10+67</f>
+        <v>46339</v>
+      </c>
+      <c r="H42" s="26" t="n"/>
+      <c r="I42" s="26" t="n"/>
+      <c r="J42" s="26" t="inlineStr">
+        <is>
+          <t>Управление работает из зала 2, вызовы не прерывались</t>
+        </is>
+      </c>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M42" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" s="26" t="n"/>
+      <c r="O42" s="26" t="n"/>
       <c r="Y42" s="23" t="n"/>
-      <c r="Z42" s="23" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>Нижний Новгород и ССЗ — 161 абонент</t>
+          <t>Вернуть управление в ЦОД-1, зафиксировать время переключения</t>
         </is>
       </c>
       <c r="C43" s="26" t="n"/>
       <c r="D43" s="26" t="n"/>
       <c r="E43" s="26" t="n"/>
       <c r="F43" s="27">
-        <f>Параметры!$B$9+28</f>
-        <v>46300</v>
+        <f>Параметры!$B$10+63</f>
+        <v>46335</v>
       </c>
       <c r="G43" s="27">
-        <f>Параметры!$B$9+46</f>
-        <v>46318</v>
+        <f>Параметры!$B$10+67</f>
+        <v>46339</v>
       </c>
       <c r="H43" s="26" t="n"/>
       <c r="I43" s="26" t="n"/>
       <c r="J43" s="26" t="inlineStr">
         <is>
-          <t>Площадки переведены</t>
+          <t>Схема в штатном состоянии, норматив записан в регламент</t>
         </is>
       </c>
       <c r="K43" s="28" t="n"/>
@@ -3218,85 +3280,104 @@
         </is>
       </c>
       <c r="M43" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N43" s="26" t="n"/>
       <c r="O43" s="26" t="n"/>
-      <c r="T43" s="23" t="n"/>
-      <c r="U43" s="23" t="n"/>
-      <c r="V43" s="23" t="n"/>
+      <c r="Y43" s="23" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="inlineStr">
-        <is>
-          <t>Славянск-на-Кубани — 136 абонентов</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="27">
-        <f>Параметры!$B$9+42</f>
-        <v>46314</v>
-      </c>
-      <c r="G44" s="27">
-        <f>Параметры!$B$9+60</f>
-        <v>46332</v>
-      </c>
-      <c r="H44" s="26" t="n"/>
-      <c r="I44" s="26" t="n"/>
-      <c r="J44" s="26" t="inlineStr">
-        <is>
-          <t>Площадка переведена</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="n"/>
-      <c r="L44" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M44" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N44" s="26" t="n"/>
-      <c r="O44" s="26" t="n"/>
-      <c r="V44" s="23" t="n"/>
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>Консолидация мелких АТС этапа 1</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="21">
+        <f>Параметры!$B$10+49</f>
+        <v>46321</v>
+      </c>
+      <c r="G44" s="21">
+        <f>Параметры!$B$10+74</f>
+        <v>46346</v>
+      </c>
+      <c r="H44" s="21">
+        <f>G44</f>
+        <v>46346</v>
+      </c>
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>Шесть станций на 127 абонентов дорого поддерживать и невыгодно включать в кластер отдельными узлами</t>
+        </is>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>Абоненты мелких станций переведены на выносы и в ЦОД, станции выведены из эксплуатации</t>
+        </is>
+      </c>
+      <c r="K44" s="20" t="n"/>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" s="22">
+        <f>Параметры!$B$20*M44</f>
+        <v>69090</v>
+      </c>
+      <c r="O44" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="W44" s="23" t="n"/>
       <c r="X44" s="23" t="n"/>
+      <c r="Y44" s="23" t="n"/>
+      <c r="Z44" s="23" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>Ростов, его мелкие площадки и Ставрополь — 426 абонентов</t>
+          <t>ССЗ — 39 абонентов — в Нижний Новгород</t>
         </is>
       </c>
       <c r="C45" s="26" t="n"/>
       <c r="D45" s="26" t="n"/>
       <c r="E45" s="26" t="n"/>
       <c r="F45" s="27">
-        <f>Параметры!$B$9+49</f>
+        <f>Параметры!$B$10+49</f>
         <v>46321</v>
       </c>
       <c r="G45" s="27">
-        <f>Параметры!$B$9+74</f>
-        <v>46346</v>
+        <f>Параметры!$B$10+53</f>
+        <v>46325</v>
       </c>
       <c r="H45" s="26" t="n"/>
       <c r="I45" s="26" t="n"/>
       <c r="J45" s="26" t="inlineStr">
         <is>
-          <t>Площадки переведены</t>
+          <t>Станция выведена</t>
         </is>
       </c>
       <c r="K45" s="28" t="n"/>
@@ -3306,42 +3387,39 @@
         </is>
       </c>
       <c r="M45" s="26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N45" s="26" t="n"/>
       <c r="O45" s="26" t="n"/>
       <c r="W45" s="23" t="n"/>
-      <c r="X45" s="23" t="n"/>
-      <c r="Y45" s="23" t="n"/>
-      <c r="Z45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>Москва — 80 абонентов, снятие переадресаций</t>
+          <t>Манитек, Семикаракорский, Цимлянский, Приманыческий — 73 абонента — в Ростов</t>
         </is>
       </c>
       <c r="C46" s="26" t="n"/>
       <c r="D46" s="26" t="n"/>
       <c r="E46" s="26" t="n"/>
       <c r="F46" s="27">
-        <f>Параметры!$B$9+56</f>
+        <f>Параметры!$B$10+56</f>
         <v>46328</v>
       </c>
       <c r="G46" s="27">
-        <f>Параметры!$B$9+74</f>
-        <v>46346</v>
+        <f>Параметры!$B$10+67</f>
+        <v>46339</v>
       </c>
       <c r="H46" s="26" t="n"/>
       <c r="I46" s="26" t="n"/>
       <c r="J46" s="26" t="inlineStr">
         <is>
-          <t>Площадка переведена</t>
+          <t>Станции выведены</t>
         </is>
       </c>
       <c r="K46" s="28" t="n"/>
@@ -3351,49 +3429,54 @@
         </is>
       </c>
       <c r="M46" s="26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N46" s="26" t="n"/>
       <c r="O46" s="26" t="n"/>
       <c r="X46" s="23" t="n"/>
       <c r="Y46" s="23" t="n"/>
-      <c r="Z46" s="23" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>ЭТАП 2 — Воронеж (недели 12–15, 445 абонентов)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="F47" s="17" t="n"/>
-      <c r="G47" s="17" t="n"/>
-      <c r="H47" s="17" t="n"/>
-      <c r="I47" s="17" t="n"/>
-      <c r="J47" s="17" t="n"/>
-      <c r="K47" s="17" t="n"/>
-      <c r="L47" s="17" t="n"/>
-      <c r="M47" s="17" t="n"/>
-      <c r="N47" s="17" t="n"/>
-      <c r="O47" s="17" t="n"/>
-      <c r="P47" s="17" t="n"/>
-      <c r="Q47" s="17" t="n"/>
-      <c r="R47" s="17" t="n"/>
-      <c r="S47" s="17" t="n"/>
-      <c r="T47" s="17" t="n"/>
-      <c r="U47" s="17" t="n"/>
-      <c r="V47" s="17" t="n"/>
-      <c r="W47" s="17" t="n"/>
-      <c r="X47" s="17" t="n"/>
-      <c r="Y47" s="17" t="n"/>
-      <c r="Z47" s="17" t="n"/>
-      <c r="AA47" s="17" t="n"/>
-      <c r="AB47" s="17" t="n"/>
-      <c r="AC47" s="17" t="n"/>
-      <c r="AD47" s="17" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>Локальный PBX — 15 абонентов — в ЦОД-1</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="n"/>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="27">
+        <f>Параметры!$B$10+70</f>
+        <v>46342</v>
+      </c>
+      <c r="G47" s="27">
+        <f>Параметры!$B$10+74</f>
+        <v>46346</v>
+      </c>
+      <c r="H47" s="26" t="n"/>
+      <c r="I47" s="26" t="n"/>
+      <c r="J47" s="26" t="inlineStr">
+        <is>
+          <t>Станция выведена</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="n"/>
+      <c r="L47" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="26" t="n"/>
+      <c r="O47" s="26" t="n"/>
+      <c r="Z47" s="23" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
@@ -3403,7 +3486,7 @@
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>Воронежский вынос</t>
+          <t>Перевод абонентов этапа 1 на единый план нумерации</t>
         </is>
       </c>
       <c r="C48" s="19" t="inlineStr">
@@ -3418,25 +3501,25 @@
       </c>
       <c r="E48" s="20" t="n"/>
       <c r="F48" s="21">
-        <f>Параметры!$B$9+77</f>
-        <v>46349</v>
+        <f>Параметры!$B$10+35</f>
+        <v>46307</v>
       </c>
       <c r="G48" s="21">
-        <f>Параметры!$B$9+88</f>
-        <v>46360</v>
+        <f>Параметры!$B$10+81</f>
+        <v>46353</v>
       </c>
       <c r="H48" s="21">
         <f>G48</f>
-        <v>46360</v>
+        <v>46353</v>
       </c>
       <c r="I48" s="19" t="inlineStr">
         <is>
-          <t>Воронеж — самая крупная площадка (445 абонентов) и по решению совещания вводится отдельным этапом после всех остальных</t>
+          <t>Станции используют пересекающиеся номера, единый план невозможен без разведения конфликтов</t>
         </is>
       </c>
       <c r="J48" s="19" t="inlineStr">
         <is>
-          <t>Воронеж работает выносом кластера: локальная регистрация, свой выход в город, переключение на Ростов при отказе площадки</t>
+          <t>810 абонентов этапа 1 переведены на пятизначную нумерацию, переадресации сняты</t>
         </is>
       </c>
       <c r="K48" s="20" t="n"/>
@@ -3446,17 +3529,22 @@
         </is>
       </c>
       <c r="M48" s="19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N48" s="22">
-        <f>Параметры!$B$18*M48</f>
-        <v>92120</v>
+        <f>Параметры!$B$20*M48</f>
+        <v>138180</v>
       </c>
       <c r="O48" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="U48" s="23" t="n"/>
+      <c r="V48" s="23" t="n"/>
+      <c r="W48" s="23" t="n"/>
+      <c r="X48" s="23" t="n"/>
+      <c r="Y48" s="23" t="n"/>
+      <c r="Z48" s="23" t="n"/>
       <c r="AA48" s="23" t="n"/>
-      <c r="AB48" s="23" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="24" t="inlineStr">
@@ -3466,25 +3554,25 @@
       </c>
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>Обновить список узлов на всех работающих выносах</t>
+          <t>Ростов, его мелкие площадки и Ставрополь — 426 абонентов</t>
         </is>
       </c>
       <c r="C49" s="26" t="n"/>
       <c r="D49" s="26" t="n"/>
       <c r="E49" s="26" t="n"/>
       <c r="F49" s="27">
-        <f>Параметры!$B$9+77</f>
-        <v>46349</v>
+        <f>Параметры!$B$10+35</f>
+        <v>46307</v>
       </c>
       <c r="G49" s="27">
-        <f>Параметры!$B$9+81</f>
-        <v>46353</v>
+        <f>Параметры!$B$10+60</f>
+        <v>46332</v>
       </c>
       <c r="H49" s="26" t="n"/>
       <c r="I49" s="26" t="n"/>
       <c r="J49" s="26" t="inlineStr">
         <is>
-          <t>Все узлы знают о новом участнике, кворум не терялся</t>
+          <t>Площадки переведены</t>
         </is>
       </c>
       <c r="K49" s="28" t="n"/>
@@ -3494,11 +3582,14 @@
         </is>
       </c>
       <c r="M49" s="26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N49" s="26" t="n"/>
       <c r="O49" s="26" t="n"/>
-      <c r="AA49" s="23" t="n"/>
+      <c r="U49" s="23" t="n"/>
+      <c r="V49" s="23" t="n"/>
+      <c r="W49" s="23" t="n"/>
+      <c r="X49" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="24" t="inlineStr">
@@ -3508,25 +3599,25 @@
       </c>
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>Клонировать центральный узел и расшить клон в вынос</t>
+          <t>Нижний Новгород и ССЗ — 161 абонент</t>
         </is>
       </c>
       <c r="C50" s="26" t="n"/>
       <c r="D50" s="26" t="n"/>
       <c r="E50" s="26" t="n"/>
       <c r="F50" s="27">
-        <f>Параметры!$B$9+77</f>
-        <v>46349</v>
+        <f>Параметры!$B$10+42</f>
+        <v>46314</v>
       </c>
       <c r="G50" s="27">
-        <f>Параметры!$B$9+81</f>
-        <v>46353</v>
+        <f>Параметры!$B$10+60</f>
+        <v>46332</v>
       </c>
       <c r="H50" s="26" t="n"/>
       <c r="I50" s="26" t="n"/>
       <c r="J50" s="26" t="inlineStr">
         <is>
-          <t>Вынос в кластере</t>
+          <t>Площадки переведены</t>
         </is>
       </c>
       <c r="K50" s="28" t="n"/>
@@ -3536,11 +3627,13 @@
         </is>
       </c>
       <c r="M50" s="26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50" s="26" t="n"/>
       <c r="O50" s="26" t="n"/>
-      <c r="AA50" s="23" t="n"/>
+      <c r="V50" s="23" t="n"/>
+      <c r="W50" s="23" t="n"/>
+      <c r="X50" s="23" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="24" t="inlineStr">
@@ -3550,25 +3643,25 @@
       </c>
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>Межузловые транки и диалплан</t>
+          <t>Славянск-на-Кубани — 136 абонентов</t>
         </is>
       </c>
       <c r="C51" s="26" t="n"/>
       <c r="D51" s="26" t="n"/>
       <c r="E51" s="26" t="n"/>
       <c r="F51" s="27">
-        <f>Параметры!$B$9+77</f>
-        <v>46349</v>
+        <f>Параметры!$B$10+56</f>
+        <v>46328</v>
       </c>
       <c r="G51" s="27">
-        <f>Параметры!$B$9+81</f>
-        <v>46353</v>
+        <f>Параметры!$B$10+74</f>
+        <v>46346</v>
       </c>
       <c r="H51" s="26" t="n"/>
       <c r="I51" s="26" t="n"/>
       <c r="J51" s="26" t="inlineStr">
         <is>
-          <t>Вызовы с другими площадками проходят</t>
+          <t>Площадка переведена</t>
         </is>
       </c>
       <c r="K51" s="28" t="n"/>
@@ -3582,7 +3675,9 @@
       </c>
       <c r="N51" s="26" t="n"/>
       <c r="O51" s="26" t="n"/>
-      <c r="AA51" s="23" t="n"/>
+      <c r="X51" s="23" t="n"/>
+      <c r="Y51" s="23" t="n"/>
+      <c r="Z51" s="23" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="24" t="inlineStr">
@@ -3592,25 +3687,25 @@
       </c>
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>Локальный транк оператора</t>
+          <t>Москва — 80 абонентов, снятие переадресаций</t>
         </is>
       </c>
       <c r="C52" s="26" t="n"/>
       <c r="D52" s="26" t="n"/>
       <c r="E52" s="26" t="n"/>
       <c r="F52" s="27">
-        <f>Параметры!$B$9+84</f>
-        <v>46356</v>
+        <f>Параметры!$B$10+63</f>
+        <v>46335</v>
       </c>
       <c r="G52" s="27">
-        <f>Параметры!$B$9+88</f>
-        <v>46360</v>
+        <f>Параметры!$B$10+81</f>
+        <v>46353</v>
       </c>
       <c r="H52" s="26" t="n"/>
       <c r="I52" s="26" t="n"/>
       <c r="J52" s="26" t="inlineStr">
         <is>
-          <t>Свой выход в город работает</t>
+          <t>Площадка переведена</t>
         </is>
       </c>
       <c r="K52" s="28" t="n"/>
@@ -3620,53 +3715,50 @@
         </is>
       </c>
       <c r="M52" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52" s="26" t="n"/>
       <c r="O52" s="26" t="n"/>
-      <c r="AB52" s="23" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="inlineStr">
-        <is>
-          <t>Перевести телефоны на вынос через провижининг</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="n"/>
-      <c r="D53" s="26" t="n"/>
-      <c r="E53" s="26" t="n"/>
-      <c r="F53" s="27">
-        <f>Параметры!$B$9+84</f>
-        <v>46356</v>
-      </c>
-      <c r="G53" s="27">
-        <f>Параметры!$B$9+88</f>
-        <v>46360</v>
-      </c>
-      <c r="H53" s="26" t="n"/>
-      <c r="I53" s="26" t="n"/>
-      <c r="J53" s="26" t="inlineStr">
-        <is>
-          <t>Телефоны регистрируются в Воронеже, резервный сервер — Ростов</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="n"/>
-      <c r="L53" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M53" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N53" s="26" t="n"/>
-      <c r="O53" s="26" t="n"/>
-      <c r="AB53" s="23" t="n"/>
+      <c r="Y52" s="23" t="n"/>
+      <c r="Z52" s="23" t="n"/>
+      <c r="AA52" s="23" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="17" t="n"/>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>ЭТАП 2 — Воронеж (недели 13–16, 445 абонентов)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="17" t="n"/>
+      <c r="G53" s="17" t="n"/>
+      <c r="H53" s="17" t="n"/>
+      <c r="I53" s="17" t="n"/>
+      <c r="J53" s="17" t="n"/>
+      <c r="K53" s="17" t="n"/>
+      <c r="L53" s="17" t="n"/>
+      <c r="M53" s="17" t="n"/>
+      <c r="N53" s="17" t="n"/>
+      <c r="O53" s="17" t="n"/>
+      <c r="P53" s="17" t="n"/>
+      <c r="Q53" s="17" t="n"/>
+      <c r="R53" s="17" t="n"/>
+      <c r="S53" s="17" t="n"/>
+      <c r="T53" s="17" t="n"/>
+      <c r="U53" s="17" t="n"/>
+      <c r="V53" s="17" t="n"/>
+      <c r="W53" s="17" t="n"/>
+      <c r="X53" s="17" t="n"/>
+      <c r="Y53" s="17" t="n"/>
+      <c r="Z53" s="17" t="n"/>
+      <c r="AA53" s="17" t="n"/>
+      <c r="AB53" s="17" t="n"/>
+      <c r="AC53" s="17" t="n"/>
+      <c r="AD53" s="17" t="n"/>
+      <c r="AE53" s="17" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
@@ -3676,7 +3768,7 @@
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>Консолидация воронежских АТС</t>
+          <t>Воронежский вынос и арбитр кворума</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
@@ -3691,11 +3783,11 @@
       </c>
       <c r="E54" s="20" t="n"/>
       <c r="F54" s="21">
-        <f>Параметры!$B$9+84</f>
+        <f>Параметры!$B$10+84</f>
         <v>46356</v>
       </c>
       <c r="G54" s="21">
-        <f>Параметры!$B$9+95</f>
+        <f>Параметры!$B$10+95</f>
         <v>46367</v>
       </c>
       <c r="H54" s="21">
@@ -3704,12 +3796,12 @@
       </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
-          <t>Мясокомбинат и Калуга — 216 абонентов на двух отдельных станциях</t>
+          <t>Воронеж — самая крупная площадка (445 абонентов); с его вводом узлов становится шесть, число чётное, и кластеру нужен арбитр</t>
         </is>
       </c>
       <c r="J54" s="19" t="inlineStr">
         <is>
-          <t>Абоненты переведены на воронежский вынос, станции выведены из эксплуатации</t>
+          <t>Воронеж работает выносом; установлен арбитр garbd, голосов семь — кворум нечётный</t>
         </is>
       </c>
       <c r="K54" s="20" t="n"/>
@@ -3719,11 +3811,11 @@
         </is>
       </c>
       <c r="M54" s="19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N54" s="22">
-        <f>Параметры!$B$18*M54</f>
-        <v>69090</v>
+        <f>Параметры!$B$20*M54</f>
+        <v>103635</v>
       </c>
       <c r="O54" s="22" t="n">
         <v>0</v>
@@ -3739,25 +3831,25 @@
       </c>
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>Мясокомбинат — 187 абонентов</t>
+          <t>Проверить, что все пять узлов Synced до начала работ</t>
         </is>
       </c>
       <c r="C55" s="26" t="n"/>
       <c r="D55" s="26" t="n"/>
       <c r="E55" s="26" t="n"/>
       <c r="F55" s="27">
-        <f>Параметры!$B$9+84</f>
+        <f>Параметры!$B$10+84</f>
         <v>46356</v>
       </c>
       <c r="G55" s="27">
-        <f>Параметры!$B$9+95</f>
-        <v>46367</v>
+        <f>Параметры!$B$10+88</f>
+        <v>46360</v>
       </c>
       <c r="H55" s="26" t="n"/>
       <c r="I55" s="26" t="n"/>
       <c r="J55" s="26" t="inlineStr">
         <is>
-          <t>Станция выведена</t>
+          <t>Кластер здоров, расхождений нет</t>
         </is>
       </c>
       <c r="K55" s="28" t="n"/>
@@ -3767,12 +3859,11 @@
         </is>
       </c>
       <c r="M55" s="26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N55" s="26" t="n"/>
       <c r="O55" s="26" t="n"/>
       <c r="AB55" s="23" t="n"/>
-      <c r="AC55" s="23" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="24" t="inlineStr">
@@ -3782,25 +3873,25 @@
       </c>
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>Калуга — 29 абонентов</t>
+          <t>Клонировать мастер и расшить клон в вынос</t>
         </is>
       </c>
       <c r="C56" s="26" t="n"/>
       <c r="D56" s="26" t="n"/>
       <c r="E56" s="26" t="n"/>
       <c r="F56" s="27">
-        <f>Параметры!$B$9+91</f>
-        <v>46363</v>
+        <f>Параметры!$B$10+84</f>
+        <v>46356</v>
       </c>
       <c r="G56" s="27">
-        <f>Параметры!$B$9+95</f>
-        <v>46367</v>
+        <f>Параметры!$B$10+88</f>
+        <v>46360</v>
       </c>
       <c r="H56" s="26" t="n"/>
       <c r="I56" s="26" t="n"/>
       <c r="J56" s="26" t="inlineStr">
         <is>
-          <t>Станция выведена</t>
+          <t>Вынос в кластере</t>
         </is>
       </c>
       <c r="K56" s="28" t="n"/>
@@ -3814,99 +3905,77 @@
       </c>
       <c r="N56" s="26" t="n"/>
       <c r="O56" s="26" t="n"/>
-      <c r="AC56" s="23" t="n"/>
+      <c r="AB56" s="23" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>Перевод воронежских абонентов на единый план нумерации</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E57" s="20" t="n"/>
-      <c r="F57" s="21">
-        <f>Параметры!$B$9+84</f>
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>Межузловые транки и диалплан</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="n"/>
+      <c r="D57" s="26" t="n"/>
+      <c r="E57" s="26" t="n"/>
+      <c r="F57" s="27">
+        <f>Параметры!$B$10+84</f>
         <v>46356</v>
       </c>
-      <c r="G57" s="21">
-        <f>Параметры!$B$9+102</f>
-        <v>46374</v>
-      </c>
-      <c r="H57" s="21">
-        <f>G57</f>
-        <v>46374</v>
-      </c>
-      <c r="I57" s="19" t="inlineStr">
-        <is>
-          <t>445 абонентов Воронежа и его станций используют старую нумерацию</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="inlineStr">
-        <is>
-          <t>Воронеж переведён на пятизначную нумерацию, переадресации со старых номеров сняты</t>
-        </is>
-      </c>
-      <c r="K57" s="20" t="n"/>
-      <c r="L57" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M57" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="N57" s="22">
-        <f>Параметры!$B$18*M57</f>
-        <v>69090</v>
-      </c>
-      <c r="O57" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G57" s="27">
+        <f>Параметры!$B$10+88</f>
+        <v>46360</v>
+      </c>
+      <c r="H57" s="26" t="n"/>
+      <c r="I57" s="26" t="n"/>
+      <c r="J57" s="26" t="inlineStr">
+        <is>
+          <t>Вызовы с другими площадками проходят</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="n"/>
+      <c r="L57" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M57" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N57" s="26" t="n"/>
+      <c r="O57" s="26" t="n"/>
       <c r="AB57" s="23" t="n"/>
-      <c r="AC57" s="23" t="n"/>
-      <c r="AD57" s="23" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>Воронеж и Мясокомбинат — 416 абонентов</t>
+          <t>Установить арбитр garbd на отдельной ВМ в Ростове</t>
         </is>
       </c>
       <c r="C58" s="26" t="n"/>
       <c r="D58" s="26" t="n"/>
       <c r="E58" s="26" t="n"/>
       <c r="F58" s="27">
-        <f>Параметры!$B$9+84</f>
+        <f>Параметры!$B$10+84</f>
         <v>46356</v>
       </c>
       <c r="G58" s="27">
-        <f>Параметры!$B$9+102</f>
-        <v>46374</v>
+        <f>Параметры!$B$10+88</f>
+        <v>46360</v>
       </c>
       <c r="H58" s="26" t="n"/>
       <c r="I58" s="26" t="n"/>
       <c r="J58" s="26" t="inlineStr">
         <is>
-          <t>Площадки переведены</t>
+          <t>Голосов семь; арбитр вне ЦОД, потеря ЦОД целиком не рушит кворум</t>
         </is>
       </c>
       <c r="K58" s="28" t="n"/>
@@ -3916,41 +3985,39 @@
         </is>
       </c>
       <c r="M58" s="26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N58" s="26" t="n"/>
       <c r="O58" s="26" t="n"/>
       <c r="AB58" s="23" t="n"/>
-      <c r="AC58" s="23" t="n"/>
-      <c r="AD58" s="23" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>Калуга — сверка: часть абонентов уже на пятизначных</t>
+          <t>Локальный транк оператора</t>
         </is>
       </c>
       <c r="C59" s="26" t="n"/>
       <c r="D59" s="26" t="n"/>
       <c r="E59" s="26" t="n"/>
       <c r="F59" s="27">
-        <f>Параметры!$B$9+98</f>
-        <v>46370</v>
+        <f>Параметры!$B$10+91</f>
+        <v>46363</v>
       </c>
       <c r="G59" s="27">
-        <f>Параметры!$B$9+102</f>
-        <v>46374</v>
+        <f>Параметры!$B$10+95</f>
+        <v>46367</v>
       </c>
       <c r="H59" s="26" t="n"/>
       <c r="I59" s="26" t="n"/>
       <c r="J59" s="26" t="inlineStr">
         <is>
-          <t>Расхождений нет, переадресации сняты</t>
+          <t>Свой выход в город работает</t>
         </is>
       </c>
       <c r="K59" s="28" t="n"/>
@@ -3964,42 +4031,382 @@
       </c>
       <c r="N59" s="26" t="n"/>
       <c r="O59" s="26" t="n"/>
-      <c r="AD59" s="23" t="n"/>
+      <c r="AC59" s="23" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="n"/>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>Перевести телефоны на вынос через провижининг</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="n"/>
+      <c r="D60" s="26" t="n"/>
+      <c r="E60" s="26" t="n"/>
+      <c r="F60" s="27">
+        <f>Параметры!$B$10+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G60" s="27">
+        <f>Параметры!$B$10+95</f>
+        <v>46367</v>
+      </c>
+      <c r="H60" s="26" t="n"/>
+      <c r="I60" s="26" t="n"/>
+      <c r="J60" s="26" t="inlineStr">
+        <is>
+          <t>Телефоны регистрируются в Воронеже, резервный сервер — ЦОД-1</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="n"/>
+      <c r="L60" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M60" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" s="26" t="n"/>
+      <c r="O60" s="26" t="n"/>
+      <c r="AC60" s="23" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>Консолидация воронежских АТС</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="21">
+        <f>Параметры!$B$10+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G61" s="21">
+        <f>Параметры!$B$10+102</f>
+        <v>46374</v>
+      </c>
+      <c r="H61" s="21">
+        <f>G61</f>
+        <v>46374</v>
+      </c>
+      <c r="I61" s="19" t="inlineStr">
+        <is>
+          <t>Мясокомбинат и Калуга — 216 абонентов на двух отдельных станциях</t>
+        </is>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>Абоненты переведены на воронежский вынос, станции выведены из эксплуатации</t>
+        </is>
+      </c>
+      <c r="K61" s="20" t="n"/>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M61" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N61" s="22">
+        <f>Параметры!$B$20*M61</f>
+        <v>69090</v>
+      </c>
+      <c r="O61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="23" t="n"/>
+      <c r="AD61" s="23" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>Мясокомбинат — 187 абонентов</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="n"/>
+      <c r="D62" s="26" t="n"/>
+      <c r="E62" s="26" t="n"/>
+      <c r="F62" s="27">
+        <f>Параметры!$B$10+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G62" s="27">
+        <f>Параметры!$B$10+102</f>
+        <v>46374</v>
+      </c>
+      <c r="H62" s="26" t="n"/>
+      <c r="I62" s="26" t="n"/>
+      <c r="J62" s="26" t="inlineStr">
+        <is>
+          <t>Станция выведена</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="n"/>
+      <c r="L62" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M62" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N62" s="26" t="n"/>
+      <c r="O62" s="26" t="n"/>
+      <c r="AC62" s="23" t="n"/>
+      <c r="AD62" s="23" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>Калуга — 29 абонентов</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="n"/>
+      <c r="D63" s="26" t="n"/>
+      <c r="E63" s="26" t="n"/>
+      <c r="F63" s="27">
+        <f>Параметры!$B$10+98</f>
+        <v>46370</v>
+      </c>
+      <c r="G63" s="27">
+        <f>Параметры!$B$10+102</f>
+        <v>46374</v>
+      </c>
+      <c r="H63" s="26" t="n"/>
+      <c r="I63" s="26" t="n"/>
+      <c r="J63" s="26" t="inlineStr">
+        <is>
+          <t>Станция выведена</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="n"/>
+      <c r="L63" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M63" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N63" s="26" t="n"/>
+      <c r="O63" s="26" t="n"/>
+      <c r="AD63" s="23" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>Перевод воронежских абонентов на единый план нумерации</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="n"/>
+      <c r="F64" s="21">
+        <f>Параметры!$B$10+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G64" s="21">
+        <f>Параметры!$B$10+109</f>
+        <v>46381</v>
+      </c>
+      <c r="H64" s="21">
+        <f>G64</f>
+        <v>46381</v>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>445 абонентов Воронежа и его станций используют старую нумерацию</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>Воронеж переведён на пятизначную нумерацию, переадресации со старых номеров сняты</t>
+        </is>
+      </c>
+      <c r="K64" s="20" t="n"/>
+      <c r="L64" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N64" s="22">
+        <f>Параметры!$B$20*M64</f>
+        <v>69090</v>
+      </c>
+      <c r="O64" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="23" t="n"/>
+      <c r="AD64" s="23" t="n"/>
+      <c r="AE64" s="23" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>Воронеж и Мясокомбинат — 416 абонентов</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="n"/>
+      <c r="D65" s="26" t="n"/>
+      <c r="E65" s="26" t="n"/>
+      <c r="F65" s="27">
+        <f>Параметры!$B$10+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G65" s="27">
+        <f>Параметры!$B$10+109</f>
+        <v>46381</v>
+      </c>
+      <c r="H65" s="26" t="n"/>
+      <c r="I65" s="26" t="n"/>
+      <c r="J65" s="26" t="inlineStr">
+        <is>
+          <t>Площадки переведены</t>
+        </is>
+      </c>
+      <c r="K65" s="28" t="n"/>
+      <c r="L65" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M65" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N65" s="26" t="n"/>
+      <c r="O65" s="26" t="n"/>
+      <c r="AC65" s="23" t="n"/>
+      <c r="AD65" s="23" t="n"/>
+      <c r="AE65" s="23" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>Калуга — сверка: часть абонентов уже на пятизначных</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="n"/>
+      <c r="D66" s="26" t="n"/>
+      <c r="E66" s="26" t="n"/>
+      <c r="F66" s="27">
+        <f>Параметры!$B$10+105</f>
+        <v>46377</v>
+      </c>
+      <c r="G66" s="27">
+        <f>Параметры!$B$10+109</f>
+        <v>46381</v>
+      </c>
+      <c r="H66" s="26" t="n"/>
+      <c r="I66" s="26" t="n"/>
+      <c r="J66" s="26" t="inlineStr">
+        <is>
+          <t>Расхождений нет, переадресации сняты</t>
+        </is>
+      </c>
+      <c r="K66" s="28" t="n"/>
+      <c r="L66" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="26" t="n"/>
+      <c r="O66" s="26" t="n"/>
+      <c r="AE66" s="23" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="n"/>
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>ИТОГО по проекту</t>
         </is>
       </c>
-      <c r="C60" s="29" t="n"/>
-      <c r="D60" s="29" t="n"/>
-      <c r="E60" s="29" t="n"/>
-      <c r="F60" s="29" t="n"/>
-      <c r="G60" s="29" t="n"/>
-      <c r="H60" s="29" t="n"/>
-      <c r="I60" s="29" t="n"/>
-      <c r="J60" s="29" t="n"/>
-      <c r="K60" s="29" t="n"/>
-      <c r="L60" s="29" t="n"/>
-      <c r="M60" s="29">
-        <f>M4+M11+M18+M22+M26+M32+M35+M38+M42+M48+M54+M57</f>
-        <v>89</v>
-      </c>
-      <c r="N60" s="30">
-        <f>N4+N11+N18+N22+N26+N32+N35+N38+N42+N48+N54+N57</f>
-        <v>1024835</v>
-      </c>
-      <c r="O60" s="30">
-        <f>O4+O11+O18+O22+O26+O32+O35+O38+O42+O48+O54+O57</f>
+      <c r="C67" s="29" t="n"/>
+      <c r="D67" s="29" t="n"/>
+      <c r="E67" s="29" t="n"/>
+      <c r="F67" s="29" t="n"/>
+      <c r="G67" s="29" t="n"/>
+      <c r="H67" s="29" t="n"/>
+      <c r="I67" s="29" t="n"/>
+      <c r="J67" s="29" t="n"/>
+      <c r="K67" s="29" t="n"/>
+      <c r="L67" s="29" t="n"/>
+      <c r="M67" s="29">
+        <f>M4+M11+M18+M22+M26+M32+M38+M41+M44+M48+M54+M61+M64</f>
+        <v>95</v>
+      </c>
+      <c r="N67" s="30">
+        <f>N4+N11+N18+N22+N26+N32+N38+N41+N44+N48+N54+N61+N64</f>
+        <v>1093925</v>
+      </c>
+      <c r="O67" s="30">
+        <f>O4+O11+O18+O22+O26+O32+O38+O41+O44+O48+O54+O61+O64</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="X1:AB1"/>
-    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="T1:W1"/>
   </mergeCells>

--- a/docs/plan/dit-annual-plan.xlsx
+++ b/docs/plan/dit-annual-plan.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -675,497 +675,548 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
+          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Два зала ЦОД — независимы?</t>
+          <t>Стойки в ЦОД — независимы</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ПРОВЕРИТЬ ДО СТАРТА</t>
+          <t>ПОДТВЕРЖДЕНО</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Копия во втором зале даёт резервирование только если залы не делят физический хост, ввод питания и аплинк. Две стойки одного зала за одним вводом — это не две площадки, и вся схема резервирования теряет смысл. Проверяется в задаче 1 до выделения ВМ.</t>
+          <t>Стойки свои, независимость подтверждена заказчиком. Это снимает главный риск схемы: два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Дата начала работ</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>46272</v>
+          <t>SIP-пользователи у операторов</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>заводим сами</t>
+        </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+          <t>Доступ к кабинету ВАТС есть, учётные записи на площадки создаются самостоятельно. Внешнего согласования и ожидания оператора нет.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Длительность, недель</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>16</v>
+          <t>Внешних зависимостей</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+          <t>Все площадки свои, адреса известны, стойки в ЦОД свои, SIP-пользователи заводятся самостоятельно, ПО бесплатное, машины на своей виртуализации. Сроки зависят только от собственных ресурсов — это редкая ситуация, и она означает, что сдвиг графика будет внутренней причиной, а не внешней.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>Дата начала работ</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Длительность, недель</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>Дата завершения работ</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B14" s="6" t="n">
         <v>46381</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Дата начала + 15 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>недели 1–12, 810 абонентов</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>ЦОД-1 (Москва) 80, ЦОД-2 копия, Ростов 426 (включая Ставрополь 74), Нижний Новгород 164, Славянск-на-Кубани 140.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ЭТАП 2 — Воронеж</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>недели 13–16, 445 абонентов</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Порядок переноса центра</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 426 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Пилотный вынос</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>95</v>
+          <t>Ставрополь получает свою АТС</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>да, задача 8.2</t>
+        </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>65</v>
+          <t>Порядок переноса центра</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
+        </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>30</v>
+          <t>Пилотный вынос</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Нижний Новгород</t>
+        </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
+          <t>Трудозатраты всего, ч-д</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>11515</v>
+        <v>98</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B21" s="7">
-        <f>B17*B20</f>
-        <v>1093925</v>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
+          <t>Внутренняя ставка, ₽/ч-д</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1255</v>
+        <v>11515</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>12</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>B20*B23</f>
+        <v>1128470</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>6</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40, ЦОД-2 40 (оба живые), Ростов 426, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Абонентов 1255 — сходится с аудитом.</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Абонентов в периметре</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>7</v>
+        <v>1255</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Шесть узлов — число ЧЁТНОЕ, поэтому нужен арбитр garbd: он даёт седьмой голос и не хранит данные. Кластер переживает потерю двух узлов и остаётся работоспособным при потере ЦОД целиком (четыре голоса из семи в городах).</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Где стоит арбитр</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Ростов, отдельная ВМ</t>
-        </is>
+          <t>Станций сейчас</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>НЕ в ЦОД. Если поставить арбитр в ЦОД, потеря дата-центра уносит три голоса из семи разом. В Ростове — самая крупная площадка после Воронежа и своя инфраструктура. Требования: 1 vCPU, 512 МБ.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Пять узлов — нечётное, арбитр на этапе 1 не нужен. Он ставится в задаче 11 вместе с вводом Воронежа, который делает число узлов чётным.</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и ВМ под арбитр в Ростове. Все — свои мощности, закупки нет. У четырёх городских площадок машины уже есть.</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
+          <t>Арбитр garbd</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>не нужен</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>нельзя</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Панель управления FreePBX</t>
+          <t>Размещение ВМ по хостам</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ровно на одном узле</t>
+          <t>проверить</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Оба узла ЦОД — живые</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Панель управления FreePBX</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>21–25 декабря</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Заказчик</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Исполнитель</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Номер приказа / внутреннего проекта</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Дата протокола совещания</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
+          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>IP-адреса Славянска-на-Кубани и локального PBX</t>
+          <t>Исполнитель</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>В исходных данных аудита отсутствуют, запрашиваются в первую неделю.</t>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Номер приказа / внутреннего проекта</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Дата протокола совещания</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Проставить дату документа, из которого взята этапность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Адресный план узлов</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1462,11 +1513,11 @@
       </c>
       <c r="E4" s="20" t="n"/>
       <c r="F4" s="21">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G4" s="21">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H4" s="21">
@@ -1475,12 +1526,12 @@
       </c>
       <c r="I4" s="19" t="inlineStr">
         <is>
-          <t>Площадки не связаны между собой сетью; в ЦОД не выделены машины под центральные узлы; у операторов нет отдельных учётных записей на каждую площадку</t>
+          <t>Площадки не связаны между собой сетью; в ЦОД не выделены машины под центральные узлы; у площадок нет отдельных учётных записей SIP для выхода в город</t>
         </is>
       </c>
       <c r="J4" s="19" t="inlineStr">
         <is>
-          <t>VPN между ЦОД и всеми городами поднят, RTT измерен, в ЦОД выделены две ВМ в разных залах, у каждой площадки свой SIP-пользователь ВАТС</t>
+          <t>VPN между ЦОД и всеми городами поднят, RTT измерен, в ЦОД выделены две ВМ в разных стойках, у каждой площадки заведён свой SIP-пользователь ВАТС</t>
         </is>
       </c>
       <c r="K4" s="20" t="n"/>
@@ -1493,7 +1544,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="22">
-        <f>Параметры!$B$20*M4</f>
+        <f>Параметры!$B$23*M4</f>
         <v>92120</v>
       </c>
       <c r="O4" s="22" t="n">
@@ -1517,11 +1568,11 @@
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="27">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G5" s="27">
-        <f>Параметры!$B$10+4</f>
+        <f>Параметры!$B$12+4</f>
         <v>46276</v>
       </c>
       <c r="H5" s="26" t="n"/>
@@ -1559,11 +1610,11 @@
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="26" t="n"/>
       <c r="F6" s="27">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G6" s="27">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H6" s="26" t="n"/>
@@ -1602,11 +1653,11 @@
       <c r="D7" s="26" t="n"/>
       <c r="E7" s="26" t="n"/>
       <c r="F7" s="27">
-        <f>Параметры!$B$10+7</f>
+        <f>Параметры!$B$12+7</f>
         <v>46279</v>
       </c>
       <c r="G7" s="27">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H7" s="26" t="n"/>
@@ -1637,25 +1688,25 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>Получить IP-адреса Славянска-на-Кубани и локального PBX</t>
+          <t>Собрать адресный план на семь узлов</t>
         </is>
       </c>
       <c r="C8" s="26" t="n"/>
       <c r="D8" s="26" t="n"/>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="27">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G8" s="27">
-        <f>Параметры!$B$10+4</f>
+        <f>Параметры!$B$12+4</f>
         <v>46276</v>
       </c>
       <c r="H8" s="26" t="n"/>
       <c r="I8" s="26" t="n"/>
       <c r="J8" s="26" t="inlineStr">
         <is>
-          <t>Адреса получены</t>
+          <t>Адреса всех площадок известны, план зафиксирован</t>
         </is>
       </c>
       <c r="K8" s="28" t="n"/>
@@ -1679,25 +1730,25 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Выделить в ЦОД две ВМ — в разных залах, на разных хостах и вводах питания</t>
+          <t>Выделить в ЦОД две ВМ в разных стойках</t>
         </is>
       </c>
       <c r="C9" s="26" t="n"/>
       <c r="D9" s="26" t="n"/>
       <c r="E9" s="26" t="n"/>
       <c r="F9" s="27">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G9" s="27">
-        <f>Параметры!$B$10+4</f>
+        <f>Параметры!$B$12+4</f>
         <v>46276</v>
       </c>
       <c r="H9" s="26" t="n"/>
       <c r="I9" s="26" t="n"/>
       <c r="J9" s="26" t="inlineStr">
         <is>
-          <t>ВМ выделены; подтверждено, что залы не делят хост, питание и аплинк</t>
+          <t>ВМ выделены; стойки свои и независимы — подтверждено</t>
         </is>
       </c>
       <c r="K9" s="28" t="n"/>
@@ -1707,7 +1758,7 @@
         </is>
       </c>
       <c r="M9" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" s="26" t="n"/>
       <c r="O9" s="26" t="n"/>
@@ -1721,25 +1772,25 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Получить у операторов SIP-пользователей ВАТС на каждую площадку</t>
+          <t>Завести SIP-пользователей ВАТС на каждую площадку самостоятельно</t>
         </is>
       </c>
       <c r="C10" s="26" t="n"/>
       <c r="D10" s="26" t="n"/>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="27">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G10" s="27">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H10" s="26" t="n"/>
       <c r="I10" s="26" t="n"/>
       <c r="J10" s="26" t="inlineStr">
         <is>
-          <t>Учётные записи получены на все площадки</t>
+          <t>Учётные записи созданы в кабинете ВАТС на все площадки, внешних согласований нет</t>
         </is>
       </c>
       <c r="K10" s="28" t="n"/>
@@ -1749,7 +1800,7 @@
         </is>
       </c>
       <c r="M10" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" s="26" t="n"/>
       <c r="O10" s="26" t="n"/>
@@ -1779,11 +1830,11 @@
       </c>
       <c r="E11" s="20" t="n"/>
       <c r="F11" s="21">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G11" s="21">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H11" s="21">
@@ -1810,7 +1861,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="22">
-        <f>Параметры!$B$20*M11</f>
+        <f>Параметры!$B$23*M11</f>
         <v>115150</v>
       </c>
       <c r="O11" s="22" t="n">
@@ -1834,11 +1885,11 @@
       <c r="D12" s="26" t="n"/>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="27">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G12" s="27">
-        <f>Параметры!$B$10+4</f>
+        <f>Параметры!$B$12+4</f>
         <v>46276</v>
       </c>
       <c r="H12" s="26" t="n"/>
@@ -1876,11 +1927,11 @@
       <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="27">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G13" s="27">
-        <f>Параметры!$B$10+4</f>
+        <f>Параметры!$B$12+4</f>
         <v>46276</v>
       </c>
       <c r="H13" s="26" t="n"/>
@@ -1918,11 +1969,11 @@
       <c r="D14" s="26" t="n"/>
       <c r="E14" s="26" t="n"/>
       <c r="F14" s="27">
-        <f>Параметры!$B$10+0</f>
+        <f>Параметры!$B$12+0</f>
         <v>46272</v>
       </c>
       <c r="G14" s="27">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H14" s="26" t="n"/>
@@ -1961,11 +2012,11 @@
       <c r="D15" s="26" t="n"/>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="27">
-        <f>Параметры!$B$10+7</f>
+        <f>Параметры!$B$12+7</f>
         <v>46279</v>
       </c>
       <c r="G15" s="27">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H15" s="26" t="n"/>
@@ -2003,11 +2054,11 @@
       <c r="D16" s="26" t="n"/>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="27">
-        <f>Параметры!$B$10+7</f>
+        <f>Параметры!$B$12+7</f>
         <v>46279</v>
       </c>
       <c r="G16" s="27">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H16" s="26" t="n"/>
@@ -2045,11 +2096,11 @@
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="26" t="n"/>
       <c r="F17" s="27">
-        <f>Параметры!$B$10+7</f>
+        <f>Параметры!$B$12+7</f>
         <v>46279</v>
       </c>
       <c r="G17" s="27">
-        <f>Параметры!$B$10+11</f>
+        <f>Параметры!$B$12+11</f>
         <v>46283</v>
       </c>
       <c r="H17" s="26" t="n"/>
@@ -2095,11 +2146,11 @@
       </c>
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="21">
-        <f>Параметры!$B$10+14</f>
+        <f>Параметры!$B$12+14</f>
         <v>46286</v>
       </c>
       <c r="G18" s="21">
-        <f>Параметры!$B$10+18</f>
+        <f>Параметры!$B$12+18</f>
         <v>46290</v>
       </c>
       <c r="H18" s="21">
@@ -2126,7 +2177,7 @@
         <v>6</v>
       </c>
       <c r="N18" s="22">
-        <f>Параметры!$B$20*M18</f>
+        <f>Параметры!$B$23*M18</f>
         <v>69090</v>
       </c>
       <c r="O18" s="22" t="n">
@@ -2149,11 +2200,11 @@
       <c r="D19" s="26" t="n"/>
       <c r="E19" s="26" t="n"/>
       <c r="F19" s="27">
-        <f>Параметры!$B$10+14</f>
+        <f>Параметры!$B$12+14</f>
         <v>46286</v>
       </c>
       <c r="G19" s="27">
-        <f>Параметры!$B$10+18</f>
+        <f>Параметры!$B$12+18</f>
         <v>46290</v>
       </c>
       <c r="H19" s="26" t="n"/>
@@ -2191,11 +2242,11 @@
       <c r="D20" s="26" t="n"/>
       <c r="E20" s="26" t="n"/>
       <c r="F20" s="27">
-        <f>Параметры!$B$10+14</f>
+        <f>Параметры!$B$12+14</f>
         <v>46286</v>
       </c>
       <c r="G20" s="27">
-        <f>Параметры!$B$10+18</f>
+        <f>Параметры!$B$12+18</f>
         <v>46290</v>
       </c>
       <c r="H20" s="26" t="n"/>
@@ -2233,11 +2284,11 @@
       <c r="D21" s="26" t="n"/>
       <c r="E21" s="26" t="n"/>
       <c r="F21" s="27">
-        <f>Параметры!$B$10+14</f>
+        <f>Параметры!$B$12+14</f>
         <v>46286</v>
       </c>
       <c r="G21" s="27">
-        <f>Параметры!$B$10+18</f>
+        <f>Параметры!$B$12+18</f>
         <v>46290</v>
       </c>
       <c r="H21" s="26" t="n"/>
@@ -2283,11 +2334,11 @@
       </c>
       <c r="E22" s="20" t="n"/>
       <c r="F22" s="21">
-        <f>Параметры!$B$10+21</f>
+        <f>Параметры!$B$12+21</f>
         <v>46293</v>
       </c>
       <c r="G22" s="21">
-        <f>Параметры!$B$10+25</f>
+        <f>Параметры!$B$12+25</f>
         <v>46297</v>
       </c>
       <c r="H22" s="21">
@@ -2314,7 +2365,7 @@
         <v>4</v>
       </c>
       <c r="N22" s="22">
-        <f>Параметры!$B$20*M22</f>
+        <f>Параметры!$B$23*M22</f>
         <v>46060</v>
       </c>
       <c r="O22" s="22" t="n">
@@ -2337,11 +2388,11 @@
       <c r="D23" s="26" t="n"/>
       <c r="E23" s="26" t="n"/>
       <c r="F23" s="27">
-        <f>Параметры!$B$10+21</f>
+        <f>Параметры!$B$12+21</f>
         <v>46293</v>
       </c>
       <c r="G23" s="27">
-        <f>Параметры!$B$10+25</f>
+        <f>Параметры!$B$12+25</f>
         <v>46297</v>
       </c>
       <c r="H23" s="26" t="n"/>
@@ -2379,11 +2430,11 @@
       <c r="D24" s="26" t="n"/>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="27">
-        <f>Параметры!$B$10+21</f>
+        <f>Параметры!$B$12+21</f>
         <v>46293</v>
       </c>
       <c r="G24" s="27">
-        <f>Параметры!$B$10+25</f>
+        <f>Параметры!$B$12+25</f>
         <v>46297</v>
       </c>
       <c r="H24" s="26" t="n"/>
@@ -2421,11 +2472,11 @@
       <c r="D25" s="26" t="n"/>
       <c r="E25" s="26" t="n"/>
       <c r="F25" s="27">
-        <f>Параметры!$B$10+21</f>
+        <f>Параметры!$B$12+21</f>
         <v>46293</v>
       </c>
       <c r="G25" s="27">
-        <f>Параметры!$B$10+25</f>
+        <f>Параметры!$B$12+25</f>
         <v>46297</v>
       </c>
       <c r="H25" s="26" t="n"/>
@@ -2471,11 +2522,11 @@
       </c>
       <c r="E26" s="20" t="n"/>
       <c r="F26" s="21">
-        <f>Параметры!$B$10+28</f>
+        <f>Параметры!$B$12+28</f>
         <v>46300</v>
       </c>
       <c r="G26" s="21">
-        <f>Параметры!$B$10+39</f>
+        <f>Параметры!$B$12+39</f>
         <v>46311</v>
       </c>
       <c r="H26" s="21">
@@ -2502,7 +2553,7 @@
         <v>10</v>
       </c>
       <c r="N26" s="22">
-        <f>Параметры!$B$20*M26</f>
+        <f>Параметры!$B$23*M26</f>
         <v>115150</v>
       </c>
       <c r="O26" s="22" t="n">
@@ -2526,11 +2577,11 @@
       <c r="D27" s="26" t="n"/>
       <c r="E27" s="26" t="n"/>
       <c r="F27" s="27">
-        <f>Параметры!$B$10+28</f>
+        <f>Параметры!$B$12+28</f>
         <v>46300</v>
       </c>
       <c r="G27" s="27">
-        <f>Параметры!$B$10+32</f>
+        <f>Параметры!$B$12+32</f>
         <v>46304</v>
       </c>
       <c r="H27" s="26" t="n"/>
@@ -2568,11 +2619,11 @@
       <c r="D28" s="26" t="n"/>
       <c r="E28" s="26" t="n"/>
       <c r="F28" s="27">
-        <f>Параметры!$B$10+28</f>
+        <f>Параметры!$B$12+28</f>
         <v>46300</v>
       </c>
       <c r="G28" s="27">
-        <f>Параметры!$B$10+32</f>
+        <f>Параметры!$B$12+32</f>
         <v>46304</v>
       </c>
       <c r="H28" s="26" t="n"/>
@@ -2610,11 +2661,11 @@
       <c r="D29" s="26" t="n"/>
       <c r="E29" s="26" t="n"/>
       <c r="F29" s="27">
-        <f>Параметры!$B$10+35</f>
+        <f>Параметры!$B$12+35</f>
         <v>46307</v>
       </c>
       <c r="G29" s="27">
-        <f>Параметры!$B$10+39</f>
+        <f>Параметры!$B$12+39</f>
         <v>46311</v>
       </c>
       <c r="H29" s="26" t="n"/>
@@ -2652,11 +2703,11 @@
       <c r="D30" s="26" t="n"/>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="27">
-        <f>Параметры!$B$10+35</f>
+        <f>Параметры!$B$12+35</f>
         <v>46307</v>
       </c>
       <c r="G30" s="27">
-        <f>Параметры!$B$10+39</f>
+        <f>Параметры!$B$12+39</f>
         <v>46311</v>
       </c>
       <c r="H30" s="26" t="n"/>
@@ -2694,11 +2745,11 @@
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="27">
-        <f>Параметры!$B$10+35</f>
+        <f>Параметры!$B$12+35</f>
         <v>46307</v>
       </c>
       <c r="G31" s="27">
-        <f>Параметры!$B$10+39</f>
+        <f>Параметры!$B$12+39</f>
         <v>46311</v>
       </c>
       <c r="H31" s="26" t="n"/>
@@ -2744,11 +2795,11 @@
       </c>
       <c r="E32" s="20" t="n"/>
       <c r="F32" s="21">
-        <f>Параметры!$B$10+42</f>
+        <f>Параметры!$B$12+42</f>
         <v>46314</v>
       </c>
       <c r="G32" s="21">
-        <f>Параметры!$B$10+53</f>
+        <f>Параметры!$B$12+53</f>
         <v>46325</v>
       </c>
       <c r="H32" s="21">
@@ -2775,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="N32" s="22">
-        <f>Параметры!$B$20*M32</f>
+        <f>Параметры!$B$23*M32</f>
         <v>115150</v>
       </c>
       <c r="O32" s="22" t="n">
@@ -2799,11 +2850,11 @@
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="26" t="n"/>
       <c r="F33" s="27">
-        <f>Параметры!$B$10+42</f>
+        <f>Параметры!$B$12+42</f>
         <v>46314</v>
       </c>
       <c r="G33" s="27">
-        <f>Параметры!$B$10+46</f>
+        <f>Параметры!$B$12+46</f>
         <v>46318</v>
       </c>
       <c r="H33" s="26" t="n"/>
@@ -2841,11 +2892,11 @@
       <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="27">
-        <f>Параметры!$B$10+42</f>
+        <f>Параметры!$B$12+42</f>
         <v>46314</v>
       </c>
       <c r="G34" s="27">
-        <f>Параметры!$B$10+46</f>
+        <f>Параметры!$B$12+46</f>
         <v>46318</v>
       </c>
       <c r="H34" s="26" t="n"/>
@@ -2883,11 +2934,11 @@
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="26" t="n"/>
       <c r="F35" s="27">
-        <f>Параметры!$B$10+42</f>
+        <f>Параметры!$B$12+42</f>
         <v>46314</v>
       </c>
       <c r="G35" s="27">
-        <f>Параметры!$B$10+46</f>
+        <f>Параметры!$B$12+46</f>
         <v>46318</v>
       </c>
       <c r="H35" s="26" t="n"/>
@@ -2925,11 +2976,11 @@
       <c r="D36" s="26" t="n"/>
       <c r="E36" s="26" t="n"/>
       <c r="F36" s="27">
-        <f>Параметры!$B$10+42</f>
+        <f>Параметры!$B$12+42</f>
         <v>46314</v>
       </c>
       <c r="G36" s="27">
-        <f>Параметры!$B$10+46</f>
+        <f>Параметры!$B$12+46</f>
         <v>46318</v>
       </c>
       <c r="H36" s="26" t="n"/>
@@ -2967,11 +3018,11 @@
       <c r="D37" s="26" t="n"/>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="27">
-        <f>Параметры!$B$10+49</f>
+        <f>Параметры!$B$12+49</f>
         <v>46321</v>
       </c>
       <c r="G37" s="27">
-        <f>Параметры!$B$10+53</f>
+        <f>Параметры!$B$12+53</f>
         <v>46325</v>
       </c>
       <c r="H37" s="26" t="n"/>
@@ -3002,7 +3053,7 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>Вынос Славянск-на-Кубани</t>
+          <t>Учебное переключение управления между залами ЦОД</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
@@ -3017,11 +3068,11 @@
       </c>
       <c r="E38" s="20" t="n"/>
       <c r="F38" s="21">
-        <f>Параметры!$B$10+56</f>
+        <f>Параметры!$B$12+56</f>
         <v>46328</v>
       </c>
       <c r="G38" s="21">
-        <f>Параметры!$B$10+60</f>
+        <f>Параметры!$B$12+60</f>
         <v>46332</v>
       </c>
       <c r="H38" s="21">
@@ -3030,12 +3081,12 @@
       </c>
       <c r="I38" s="19" t="inlineStr">
         <is>
-          <t>Славянск-на-Кубани обслуживается отдельной станцией вне кластера</t>
+          <t>Вызовы оба зала несут постоянно, но панель управления живёт на одном узле; её переключение не опробовано</t>
         </is>
       </c>
       <c r="J38" s="19" t="inlineStr">
         <is>
-          <t>Все выносы этапа 1 работают узлами одного кластера, узлов пять — кворум нечётный</t>
+          <t>Управление переведено в зал 2 и возвращено в зал 1 в согласованное окно; время переключения измерено и внесено в регламент</t>
         </is>
       </c>
       <c r="K38" s="20" t="n"/>
@@ -3045,11 +3096,11 @@
         </is>
       </c>
       <c r="M38" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N38" s="22">
-        <f>Параметры!$B$20*M38</f>
-        <v>57575</v>
+        <f>Параметры!$B$23*M38</f>
+        <v>34545</v>
       </c>
       <c r="O38" s="22" t="n">
         <v>0</v>
@@ -3064,25 +3115,25 @@
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>Развернуть вынос по отработанной процедуре — 140 абонентов</t>
+          <t>Включить FreePBX на ЦОД-2, проверить управление и звонки</t>
         </is>
       </c>
       <c r="C39" s="26" t="n"/>
       <c r="D39" s="26" t="n"/>
       <c r="E39" s="26" t="n"/>
       <c r="F39" s="27">
-        <f>Параметры!$B$10+56</f>
+        <f>Параметры!$B$12+56</f>
         <v>46328</v>
       </c>
       <c r="G39" s="27">
-        <f>Параметры!$B$10+60</f>
+        <f>Параметры!$B$12+60</f>
         <v>46332</v>
       </c>
       <c r="H39" s="26" t="n"/>
       <c r="I39" s="26" t="n"/>
       <c r="J39" s="26" t="inlineStr">
         <is>
-          <t>Вынос работает, старая станция погашена</t>
+          <t>Управление работает из зала 2, вызовы не прерывались</t>
         </is>
       </c>
       <c r="K39" s="28" t="n"/>
@@ -3092,7 +3143,7 @@
         </is>
       </c>
       <c r="M39" s="26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N39" s="26" t="n"/>
       <c r="O39" s="26" t="n"/>
@@ -3106,25 +3157,25 @@
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Проверить кворум и отказоустойчивость на пяти узлах</t>
+          <t>Вернуть управление в ЦОД-1, зафиксировать время переключения</t>
         </is>
       </c>
       <c r="C40" s="26" t="n"/>
       <c r="D40" s="26" t="n"/>
       <c r="E40" s="26" t="n"/>
       <c r="F40" s="27">
-        <f>Параметры!$B$10+56</f>
+        <f>Параметры!$B$12+56</f>
         <v>46328</v>
       </c>
       <c r="G40" s="27">
-        <f>Параметры!$B$10+60</f>
+        <f>Параметры!$B$12+60</f>
         <v>46332</v>
       </c>
       <c r="H40" s="26" t="n"/>
       <c r="I40" s="26" t="n"/>
       <c r="J40" s="26" t="inlineStr">
         <is>
-          <t>Кластер переживает потерю двух узлов из пяти</t>
+          <t>Схема в штатном состоянии, норматив записан в регламент</t>
         </is>
       </c>
       <c r="K40" s="28" t="n"/>
@@ -3148,7 +3199,7 @@
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>Учебное переключение управления между залами ЦОД</t>
+          <t>Выносы Славянск-на-Кубани и Ставрополь</t>
         </is>
       </c>
       <c r="C41" s="19" t="inlineStr">
@@ -3163,25 +3214,25 @@
       </c>
       <c r="E41" s="20" t="n"/>
       <c r="F41" s="21">
-        <f>Параметры!$B$10+63</f>
+        <f>Параметры!$B$12+63</f>
         <v>46335</v>
       </c>
       <c r="G41" s="21">
-        <f>Параметры!$B$10+67</f>
-        <v>46339</v>
+        <f>Параметры!$B$12+74</f>
+        <v>46346</v>
       </c>
       <c r="H41" s="21">
         <f>G41</f>
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="I41" s="19" t="inlineStr">
         <is>
-          <t>Вызовы оба зала несут постоянно, но панель управления живёт на одном узле; её переключение не опробовано</t>
+          <t>Славянск-на-Кубани обслуживается отдельной станцией вне кластера; у Ставрополя своей станции нет вообще — его 74 абонента висят на ростовском сервере</t>
         </is>
       </c>
       <c r="J41" s="19" t="inlineStr">
         <is>
-          <t>Управление переведено в зал 2 и возвращено в зал 1 в согласованное окно; время переключения измерено и внесено в регламент</t>
+          <t>Обе площадки работают выносами: локальная регистрация телефонов, свой выход в город, переключение в ЦОД при отказе площадки</t>
         </is>
       </c>
       <c r="K41" s="20" t="n"/>
@@ -3191,16 +3242,17 @@
         </is>
       </c>
       <c r="M41" s="19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N41" s="22">
-        <f>Параметры!$B$20*M41</f>
-        <v>34545</v>
+        <f>Параметры!$B$23*M41</f>
+        <v>103635</v>
       </c>
       <c r="O41" s="22" t="n">
         <v>0</v>
       </c>
       <c r="Y41" s="23" t="n"/>
+      <c r="Z41" s="23" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="24" t="inlineStr">
@@ -3210,25 +3262,25 @@
       </c>
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>Включить FreePBX на ЦОД-2, проверить управление и звонки</t>
+          <t>Славянск-на-Кубани — 140 абонентов, старая станция гасится</t>
         </is>
       </c>
       <c r="C42" s="26" t="n"/>
       <c r="D42" s="26" t="n"/>
       <c r="E42" s="26" t="n"/>
       <c r="F42" s="27">
-        <f>Параметры!$B$10+63</f>
+        <f>Параметры!$B$12+63</f>
         <v>46335</v>
       </c>
       <c r="G42" s="27">
-        <f>Параметры!$B$10+67</f>
+        <f>Параметры!$B$12+67</f>
         <v>46339</v>
       </c>
       <c r="H42" s="26" t="n"/>
       <c r="I42" s="26" t="n"/>
       <c r="J42" s="26" t="inlineStr">
         <is>
-          <t>Управление работает из зала 2, вызовы не прерывались</t>
+          <t>Вынос работает, станция выведена из эксплуатации</t>
         </is>
       </c>
       <c r="K42" s="28" t="n"/>
@@ -3238,7 +3290,7 @@
         </is>
       </c>
       <c r="M42" s="26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N42" s="26" t="n"/>
       <c r="O42" s="26" t="n"/>
@@ -3252,25 +3304,25 @@
       </c>
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>Вернуть управление в ЦОД-1, зафиксировать время переключения</t>
+          <t>Ставрополь — 74 абонента, новый вынос вместо обслуживания из Ростова</t>
         </is>
       </c>
       <c r="C43" s="26" t="n"/>
       <c r="D43" s="26" t="n"/>
       <c r="E43" s="26" t="n"/>
       <c r="F43" s="27">
-        <f>Параметры!$B$10+63</f>
-        <v>46335</v>
+        <f>Параметры!$B$12+70</f>
+        <v>46342</v>
       </c>
       <c r="G43" s="27">
-        <f>Параметры!$B$10+67</f>
-        <v>46339</v>
+        <f>Параметры!$B$12+74</f>
+        <v>46346</v>
       </c>
       <c r="H43" s="26" t="n"/>
       <c r="I43" s="26" t="n"/>
       <c r="J43" s="26" t="inlineStr">
         <is>
-          <t>Схема в штатном состоянии, норматив записан в регламент</t>
+          <t>Вынос работает, ставропольцы больше не зависят от канала до Ростова</t>
         </is>
       </c>
       <c r="K43" s="28" t="n"/>
@@ -3280,11 +3332,11 @@
         </is>
       </c>
       <c r="M43" s="26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N43" s="26" t="n"/>
       <c r="O43" s="26" t="n"/>
-      <c r="Y43" s="23" t="n"/>
+      <c r="Z43" s="23" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
@@ -3309,11 +3361,11 @@
       </c>
       <c r="E44" s="20" t="n"/>
       <c r="F44" s="21">
-        <f>Параметры!$B$10+49</f>
+        <f>Параметры!$B$12+49</f>
         <v>46321</v>
       </c>
       <c r="G44" s="21">
-        <f>Параметры!$B$10+74</f>
+        <f>Параметры!$B$12+74</f>
         <v>46346</v>
       </c>
       <c r="H44" s="21">
@@ -3340,7 +3392,7 @@
         <v>6</v>
       </c>
       <c r="N44" s="22">
-        <f>Параметры!$B$20*M44</f>
+        <f>Параметры!$B$23*M44</f>
         <v>69090</v>
       </c>
       <c r="O44" s="22" t="n">
@@ -3366,11 +3418,11 @@
       <c r="D45" s="26" t="n"/>
       <c r="E45" s="26" t="n"/>
       <c r="F45" s="27">
-        <f>Параметры!$B$10+49</f>
+        <f>Параметры!$B$12+49</f>
         <v>46321</v>
       </c>
       <c r="G45" s="27">
-        <f>Параметры!$B$10+53</f>
+        <f>Параметры!$B$12+53</f>
         <v>46325</v>
       </c>
       <c r="H45" s="26" t="n"/>
@@ -3408,11 +3460,11 @@
       <c r="D46" s="26" t="n"/>
       <c r="E46" s="26" t="n"/>
       <c r="F46" s="27">
-        <f>Параметры!$B$10+56</f>
+        <f>Параметры!$B$12+56</f>
         <v>46328</v>
       </c>
       <c r="G46" s="27">
-        <f>Параметры!$B$10+67</f>
+        <f>Параметры!$B$12+67</f>
         <v>46339</v>
       </c>
       <c r="H46" s="26" t="n"/>
@@ -3444,18 +3496,18 @@
       </c>
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>Локальный PBX — 15 абонентов — в ЦОД-1</t>
+          <t>Локальный PBX — 15 абонентов — в ЦОД</t>
         </is>
       </c>
       <c r="C47" s="26" t="n"/>
       <c r="D47" s="26" t="n"/>
       <c r="E47" s="26" t="n"/>
       <c r="F47" s="27">
-        <f>Параметры!$B$10+70</f>
+        <f>Параметры!$B$12+70</f>
         <v>46342</v>
       </c>
       <c r="G47" s="27">
-        <f>Параметры!$B$10+74</f>
+        <f>Параметры!$B$12+74</f>
         <v>46346</v>
       </c>
       <c r="H47" s="26" t="n"/>
@@ -3501,11 +3553,11 @@
       </c>
       <c r="E48" s="20" t="n"/>
       <c r="F48" s="21">
-        <f>Параметры!$B$10+35</f>
+        <f>Параметры!$B$12+35</f>
         <v>46307</v>
       </c>
       <c r="G48" s="21">
-        <f>Параметры!$B$10+81</f>
+        <f>Параметры!$B$12+81</f>
         <v>46353</v>
       </c>
       <c r="H48" s="21">
@@ -3532,7 +3584,7 @@
         <v>12</v>
       </c>
       <c r="N48" s="22">
-        <f>Параметры!$B$20*M48</f>
+        <f>Параметры!$B$23*M48</f>
         <v>138180</v>
       </c>
       <c r="O48" s="22" t="n">
@@ -3554,18 +3606,18 @@
       </c>
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>Ростов, его мелкие площадки и Ставрополь — 426 абонентов</t>
+          <t>Ростов и его мелкие площадки — 352 абонента</t>
         </is>
       </c>
       <c r="C49" s="26" t="n"/>
       <c r="D49" s="26" t="n"/>
       <c r="E49" s="26" t="n"/>
       <c r="F49" s="27">
-        <f>Параметры!$B$10+35</f>
+        <f>Параметры!$B$12+35</f>
         <v>46307</v>
       </c>
       <c r="G49" s="27">
-        <f>Параметры!$B$10+60</f>
+        <f>Параметры!$B$12+60</f>
         <v>46332</v>
       </c>
       <c r="H49" s="26" t="n"/>
@@ -3582,7 +3634,7 @@
         </is>
       </c>
       <c r="M49" s="26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N49" s="26" t="n"/>
       <c r="O49" s="26" t="n"/>
@@ -3599,18 +3651,18 @@
       </c>
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>Нижний Новгород и ССЗ — 161 абонент</t>
+          <t>Нижний Новгород и ССЗ — 164 абонента</t>
         </is>
       </c>
       <c r="C50" s="26" t="n"/>
       <c r="D50" s="26" t="n"/>
       <c r="E50" s="26" t="n"/>
       <c r="F50" s="27">
-        <f>Параметры!$B$10+42</f>
+        <f>Параметры!$B$12+42</f>
         <v>46314</v>
       </c>
       <c r="G50" s="27">
-        <f>Параметры!$B$10+60</f>
+        <f>Параметры!$B$12+60</f>
         <v>46332</v>
       </c>
       <c r="H50" s="26" t="n"/>
@@ -3643,18 +3695,18 @@
       </c>
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>Славянск-на-Кубани — 136 абонентов</t>
+          <t>Славянск-на-Кубани — 140 абонентов</t>
         </is>
       </c>
       <c r="C51" s="26" t="n"/>
       <c r="D51" s="26" t="n"/>
       <c r="E51" s="26" t="n"/>
       <c r="F51" s="27">
-        <f>Параметры!$B$10+56</f>
-        <v>46328</v>
+        <f>Параметры!$B$12+63</f>
+        <v>46335</v>
       </c>
       <c r="G51" s="27">
-        <f>Параметры!$B$10+74</f>
+        <f>Параметры!$B$12+74</f>
         <v>46346</v>
       </c>
       <c r="H51" s="26" t="n"/>
@@ -3675,7 +3727,6 @@
       </c>
       <c r="N51" s="26" t="n"/>
       <c r="O51" s="26" t="n"/>
-      <c r="X51" s="23" t="n"/>
       <c r="Y51" s="23" t="n"/>
       <c r="Z51" s="23" t="n"/>
     </row>
@@ -3687,18 +3738,18 @@
       </c>
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>Москва — 80 абонентов, снятие переадресаций</t>
+          <t>Ставрополь — 74 абонента</t>
         </is>
       </c>
       <c r="C52" s="26" t="n"/>
       <c r="D52" s="26" t="n"/>
       <c r="E52" s="26" t="n"/>
       <c r="F52" s="27">
-        <f>Параметры!$B$10+63</f>
-        <v>46335</v>
+        <f>Параметры!$B$12+70</f>
+        <v>46342</v>
       </c>
       <c r="G52" s="27">
-        <f>Параметры!$B$10+81</f>
+        <f>Параметры!$B$12+81</f>
         <v>46353</v>
       </c>
       <c r="H52" s="26" t="n"/>
@@ -3715,183 +3766,184 @@
         </is>
       </c>
       <c r="M52" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N52" s="26" t="n"/>
       <c r="O52" s="26" t="n"/>
-      <c r="Y52" s="23" t="n"/>
       <c r="Z52" s="23" t="n"/>
       <c r="AA52" s="23" t="n"/>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="18" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>Москва — 80 абонентов, снятие переадресаций</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="n"/>
+      <c r="D53" s="26" t="n"/>
+      <c r="E53" s="26" t="n"/>
+      <c r="F53" s="27">
+        <f>Параметры!$B$12+63</f>
+        <v>46335</v>
+      </c>
+      <c r="G53" s="27">
+        <f>Параметры!$B$12+81</f>
+        <v>46353</v>
+      </c>
+      <c r="H53" s="26" t="n"/>
+      <c r="I53" s="26" t="n"/>
+      <c r="J53" s="26" t="inlineStr">
+        <is>
+          <t>Площадка переведена</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="n"/>
+      <c r="L53" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M53" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" s="26" t="n"/>
+      <c r="O53" s="26" t="n"/>
+      <c r="Y53" s="23" t="n"/>
+      <c r="Z53" s="23" t="n"/>
+      <c r="AA53" s="23" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="17" t="n"/>
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>ЭТАП 2 — Воронеж (недели 13–16, 445 абонентов)</t>
         </is>
       </c>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="F53" s="17" t="n"/>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="17" t="n"/>
-      <c r="J53" s="17" t="n"/>
-      <c r="K53" s="17" t="n"/>
-      <c r="L53" s="17" t="n"/>
-      <c r="M53" s="17" t="n"/>
-      <c r="N53" s="17" t="n"/>
-      <c r="O53" s="17" t="n"/>
-      <c r="P53" s="17" t="n"/>
-      <c r="Q53" s="17" t="n"/>
-      <c r="R53" s="17" t="n"/>
-      <c r="S53" s="17" t="n"/>
-      <c r="T53" s="17" t="n"/>
-      <c r="U53" s="17" t="n"/>
-      <c r="V53" s="17" t="n"/>
-      <c r="W53" s="17" t="n"/>
-      <c r="X53" s="17" t="n"/>
-      <c r="Y53" s="17" t="n"/>
-      <c r="Z53" s="17" t="n"/>
-      <c r="AA53" s="17" t="n"/>
-      <c r="AB53" s="17" t="n"/>
-      <c r="AC53" s="17" t="n"/>
-      <c r="AD53" s="17" t="n"/>
-      <c r="AE53" s="17" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="inlineStr">
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="17" t="n"/>
+      <c r="G54" s="17" t="n"/>
+      <c r="H54" s="17" t="n"/>
+      <c r="I54" s="17" t="n"/>
+      <c r="J54" s="17" t="n"/>
+      <c r="K54" s="17" t="n"/>
+      <c r="L54" s="17" t="n"/>
+      <c r="M54" s="17" t="n"/>
+      <c r="N54" s="17" t="n"/>
+      <c r="O54" s="17" t="n"/>
+      <c r="P54" s="17" t="n"/>
+      <c r="Q54" s="17" t="n"/>
+      <c r="R54" s="17" t="n"/>
+      <c r="S54" s="17" t="n"/>
+      <c r="T54" s="17" t="n"/>
+      <c r="U54" s="17" t="n"/>
+      <c r="V54" s="17" t="n"/>
+      <c r="W54" s="17" t="n"/>
+      <c r="X54" s="17" t="n"/>
+      <c r="Y54" s="17" t="n"/>
+      <c r="Z54" s="17" t="n"/>
+      <c r="AA54" s="17" t="n"/>
+      <c r="AB54" s="17" t="n"/>
+      <c r="AC54" s="17" t="n"/>
+      <c r="AD54" s="17" t="n"/>
+      <c r="AE54" s="17" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>Воронежский вынос и арбитр кворума</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>Воронежский вынос</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D54" s="19" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E54" s="20" t="n"/>
-      <c r="F54" s="21">
-        <f>Параметры!$B$10+84</f>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="21">
+        <f>Параметры!$B$12+84</f>
         <v>46356</v>
       </c>
-      <c r="G54" s="21">
-        <f>Параметры!$B$10+95</f>
+      <c r="G55" s="21">
+        <f>Параметры!$B$12+95</f>
         <v>46367</v>
       </c>
-      <c r="H54" s="21">
-        <f>G54</f>
+      <c r="H55" s="21">
+        <f>G55</f>
         <v>46367</v>
       </c>
-      <c r="I54" s="19" t="inlineStr">
-        <is>
-          <t>Воронеж — самая крупная площадка (445 абонентов); с его вводом узлов становится шесть, число чётное, и кластеру нужен арбитр</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
-        <is>
-          <t>Воронеж работает выносом; установлен арбитр garbd, голосов семь — кворум нечётный</t>
-        </is>
-      </c>
-      <c r="K54" s="20" t="n"/>
-      <c r="L54" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M54" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="N54" s="22">
-        <f>Параметры!$B$20*M54</f>
-        <v>103635</v>
-      </c>
-      <c r="O54" s="22" t="n">
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>Воронеж — самая крупная площадка (445 абонентов) и по решению совещания вводится отдельным этапом после всех остальных</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>Воронеж работает выносом; узлов семь — число нечётное, кворум не требует арбитра</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="n"/>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M55" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="N55" s="22">
+        <f>Параметры!$B$23*M55</f>
+        <v>92120</v>
+      </c>
+      <c r="O55" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AB54" s="23" t="n"/>
-      <c r="AC54" s="23" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="24" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B55" s="25" t="inlineStr">
-        <is>
-          <t>Проверить, что все пять узлов Synced до начала работ</t>
-        </is>
-      </c>
-      <c r="C55" s="26" t="n"/>
-      <c r="D55" s="26" t="n"/>
-      <c r="E55" s="26" t="n"/>
-      <c r="F55" s="27">
-        <f>Параметры!$B$10+84</f>
-        <v>46356</v>
-      </c>
-      <c r="G55" s="27">
-        <f>Параметры!$B$10+88</f>
-        <v>46360</v>
-      </c>
-      <c r="H55" s="26" t="n"/>
-      <c r="I55" s="26" t="n"/>
-      <c r="J55" s="26" t="inlineStr">
-        <is>
-          <t>Кластер здоров, расхождений нет</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="n"/>
-      <c r="L55" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M55" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" s="26" t="n"/>
-      <c r="O55" s="26" t="n"/>
       <c r="AB55" s="23" t="n"/>
+      <c r="AC55" s="23" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>Клонировать мастер и расшить клон в вынос</t>
+          <t>Проверить, что все шесть узлов Synced до начала работ</t>
         </is>
       </c>
       <c r="C56" s="26" t="n"/>
       <c r="D56" s="26" t="n"/>
       <c r="E56" s="26" t="n"/>
       <c r="F56" s="27">
-        <f>Параметры!$B$10+84</f>
+        <f>Параметры!$B$12+84</f>
         <v>46356</v>
       </c>
       <c r="G56" s="27">
-        <f>Параметры!$B$10+88</f>
+        <f>Параметры!$B$12+88</f>
         <v>46360</v>
       </c>
       <c r="H56" s="26" t="n"/>
       <c r="I56" s="26" t="n"/>
       <c r="J56" s="26" t="inlineStr">
         <is>
-          <t>Вынос в кластере</t>
+          <t>Кластер здоров, расхождений нет</t>
         </is>
       </c>
       <c r="K56" s="28" t="n"/>
@@ -3901,7 +3953,7 @@
         </is>
       </c>
       <c r="M56" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N56" s="26" t="n"/>
       <c r="O56" s="26" t="n"/>
@@ -3910,30 +3962,30 @@
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>Межузловые транки и диалплан</t>
+          <t>Клонировать мастер и расшить клон в вынос</t>
         </is>
       </c>
       <c r="C57" s="26" t="n"/>
       <c r="D57" s="26" t="n"/>
       <c r="E57" s="26" t="n"/>
       <c r="F57" s="27">
-        <f>Параметры!$B$10+84</f>
+        <f>Параметры!$B$12+84</f>
         <v>46356</v>
       </c>
       <c r="G57" s="27">
-        <f>Параметры!$B$10+88</f>
+        <f>Параметры!$B$12+88</f>
         <v>46360</v>
       </c>
       <c r="H57" s="26" t="n"/>
       <c r="I57" s="26" t="n"/>
       <c r="J57" s="26" t="inlineStr">
         <is>
-          <t>Вызовы с другими площадками проходят</t>
+          <t>Вынос в кластере</t>
         </is>
       </c>
       <c r="K57" s="28" t="n"/>
@@ -3952,30 +4004,30 @@
     <row r="58">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>Установить арбитр garbd на отдельной ВМ в Ростове</t>
+          <t>Межузловые транки и диалплан</t>
         </is>
       </c>
       <c r="C58" s="26" t="n"/>
       <c r="D58" s="26" t="n"/>
       <c r="E58" s="26" t="n"/>
       <c r="F58" s="27">
-        <f>Параметры!$B$10+84</f>
+        <f>Параметры!$B$12+84</f>
         <v>46356</v>
       </c>
       <c r="G58" s="27">
-        <f>Параметры!$B$10+88</f>
+        <f>Параметры!$B$12+88</f>
         <v>46360</v>
       </c>
       <c r="H58" s="26" t="n"/>
       <c r="I58" s="26" t="n"/>
       <c r="J58" s="26" t="inlineStr">
         <is>
-          <t>Голосов семь; арбитр вне ЦОД, потеря ЦОД целиком не рушит кворум</t>
+          <t>Вызовы с другими площадками проходят</t>
         </is>
       </c>
       <c r="K58" s="28" t="n"/>
@@ -3985,7 +4037,7 @@
         </is>
       </c>
       <c r="M58" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58" s="26" t="n"/>
       <c r="O58" s="26" t="n"/>
@@ -3994,7 +4046,7 @@
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="B59" s="25" t="inlineStr">
@@ -4006,11 +4058,11 @@
       <c r="D59" s="26" t="n"/>
       <c r="E59" s="26" t="n"/>
       <c r="F59" s="27">
-        <f>Параметры!$B$10+91</f>
+        <f>Параметры!$B$12+91</f>
         <v>46363</v>
       </c>
       <c r="G59" s="27">
-        <f>Параметры!$B$10+95</f>
+        <f>Параметры!$B$12+95</f>
         <v>46367</v>
       </c>
       <c r="H59" s="26" t="n"/>
@@ -4036,7 +4088,7 @@
     <row r="60">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="B60" s="25" t="inlineStr">
@@ -4048,11 +4100,11 @@
       <c r="D60" s="26" t="n"/>
       <c r="E60" s="26" t="n"/>
       <c r="F60" s="27">
-        <f>Параметры!$B$10+91</f>
+        <f>Параметры!$B$12+91</f>
         <v>46363</v>
       </c>
       <c r="G60" s="27">
-        <f>Параметры!$B$10+95</f>
+        <f>Параметры!$B$12+95</f>
         <v>46367</v>
       </c>
       <c r="H60" s="26" t="n"/>
@@ -4098,11 +4150,11 @@
       </c>
       <c r="E61" s="20" t="n"/>
       <c r="F61" s="21">
-        <f>Параметры!$B$10+91</f>
+        <f>Параметры!$B$12+91</f>
         <v>46363</v>
       </c>
       <c r="G61" s="21">
-        <f>Параметры!$B$10+102</f>
+        <f>Параметры!$B$12+102</f>
         <v>46374</v>
       </c>
       <c r="H61" s="21">
@@ -4129,7 +4181,7 @@
         <v>6</v>
       </c>
       <c r="N61" s="22">
-        <f>Параметры!$B$20*M61</f>
+        <f>Параметры!$B$23*M61</f>
         <v>69090</v>
       </c>
       <c r="O61" s="22" t="n">
@@ -4153,11 +4205,11 @@
       <c r="D62" s="26" t="n"/>
       <c r="E62" s="26" t="n"/>
       <c r="F62" s="27">
-        <f>Параметры!$B$10+91</f>
+        <f>Параметры!$B$12+91</f>
         <v>46363</v>
       </c>
       <c r="G62" s="27">
-        <f>Параметры!$B$10+102</f>
+        <f>Параметры!$B$12+102</f>
         <v>46374</v>
       </c>
       <c r="H62" s="26" t="n"/>
@@ -4196,11 +4248,11 @@
       <c r="D63" s="26" t="n"/>
       <c r="E63" s="26" t="n"/>
       <c r="F63" s="27">
-        <f>Параметры!$B$10+98</f>
+        <f>Параметры!$B$12+98</f>
         <v>46370</v>
       </c>
       <c r="G63" s="27">
-        <f>Параметры!$B$10+102</f>
+        <f>Параметры!$B$12+102</f>
         <v>46374</v>
       </c>
       <c r="H63" s="26" t="n"/>
@@ -4246,11 +4298,11 @@
       </c>
       <c r="E64" s="20" t="n"/>
       <c r="F64" s="21">
-        <f>Параметры!$B$10+91</f>
+        <f>Параметры!$B$12+91</f>
         <v>46363</v>
       </c>
       <c r="G64" s="21">
-        <f>Параметры!$B$10+109</f>
+        <f>Параметры!$B$12+109</f>
         <v>46381</v>
       </c>
       <c r="H64" s="21">
@@ -4277,7 +4329,7 @@
         <v>6</v>
       </c>
       <c r="N64" s="22">
-        <f>Параметры!$B$20*M64</f>
+        <f>Параметры!$B$23*M64</f>
         <v>69090</v>
       </c>
       <c r="O64" s="22" t="n">
@@ -4302,11 +4354,11 @@
       <c r="D65" s="26" t="n"/>
       <c r="E65" s="26" t="n"/>
       <c r="F65" s="27">
-        <f>Параметры!$B$10+91</f>
+        <f>Параметры!$B$12+91</f>
         <v>46363</v>
       </c>
       <c r="G65" s="27">
-        <f>Параметры!$B$10+109</f>
+        <f>Параметры!$B$12+109</f>
         <v>46381</v>
       </c>
       <c r="H65" s="26" t="n"/>
@@ -4346,11 +4398,11 @@
       <c r="D66" s="26" t="n"/>
       <c r="E66" s="26" t="n"/>
       <c r="F66" s="27">
-        <f>Параметры!$B$10+105</f>
+        <f>Параметры!$B$12+105</f>
         <v>46377</v>
       </c>
       <c r="G66" s="27">
-        <f>Параметры!$B$10+109</f>
+        <f>Параметры!$B$12+109</f>
         <v>46381</v>
       </c>
       <c r="H66" s="26" t="n"/>
@@ -4391,15 +4443,15 @@
       <c r="K67" s="29" t="n"/>
       <c r="L67" s="29" t="n"/>
       <c r="M67" s="29">
-        <f>M4+M11+M18+M22+M26+M32+M38+M41+M44+M48+M54+M61+M64</f>
-        <v>95</v>
+        <f>M4+M11+M18+M22+M26+M32+M38+M41+M44+M48+M55+M61+M64</f>
+        <v>98</v>
       </c>
       <c r="N67" s="30">
-        <f>N4+N11+N18+N22+N26+N32+N38+N41+N44+N48+N54+N61+N64</f>
-        <v>1093925</v>
+        <f>N4+N11+N18+N22+N26+N32+N38+N41+N44+N48+N55+N61+N64</f>
+        <v>1128470</v>
       </c>
       <c r="O67" s="30">
-        <f>O4+O11+O18+O22+O26+O32+O38+O41+O44+O48+O54+O61+O64</f>
+        <f>O4+O11+O18+O22+O26+O32+O38+O41+O44+O48+O55+O61+O64</f>
         <v>0</v>
       </c>
     </row>

--- a/docs/plan/dit-annual-plan.xlsx
+++ b/docs/plan/dit-annual-plan.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -682,309 +682,307 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Стойки в ЦОД — независимы</t>
+          <t>Стойки в ЦОД</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ПОДТВЕРЖДЕНО</t>
+          <t>наши, залы независимы</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Стойки свои, независимость подтверждена заказчиком. Это снимает главный риск схемы: два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания.</t>
+          <t>Два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания. Это условие, без которого схема резервирования не имела бы смысла.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SIP-пользователи у операторов</t>
+          <t>Ждать никого не нужно</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>заводим сами</t>
+          <t>да</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Доступ к кабинету ВАТС есть, учётные записи на площадки создаются самостоятельно. Внешнего согласования и ожидания оператора нет.</t>
+          <t>Площадки наши, адреса известны, стойки в ЦОД наши, SIP-пользователей ВАТС заводим сами, ПО бесплатное, машины на своей виртуализации. Закупок и внешних согласований в плане нет. Практический вывод: если график поедет, причина будет внутренней — не хватило людей, не согласовали окно, не успели с перенумерацией.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Внешних зависимостей</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
+          <t>Дата начала работ</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Все площадки свои, адреса известны, стойки в ЦОД свои, SIP-пользователи заводятся самостоятельно, ПО бесплатное, машины на своей виртуализации. Сроки зависят только от собственных ресурсов — это редкая ситуация, и она означает, что сдвиг графика будет внутренней причиной, а не внешней.</t>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Дата начала работ</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>46272</v>
+          <t>Длительность, недель</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Длительность, недель</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>16</v>
+          <t>Дата завершения работ</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>46381</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+          <t>Дата начала + 15 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Дата завершения работ</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>46381</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Дата начала + 15 недель, последний рабочий день</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>недели 1–12, 810 абонентов</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
+          <t>ЭТАП 2 — Воронеж</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>недели 1–12, 810 абонентов</t>
+          <t>недели 13–16, 445 абонентов</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
+          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>ЭТАП 2 — Воронеж</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>недели 13–16, 445 абонентов</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Ставрополь получает свою АТС</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>да, задача 8.2</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Ставрополь получает свою АТС</t>
+          <t>Порядок переноса центра</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>да, задача 8.2</t>
+          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
+          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Порядок переноса центра</t>
+          <t>Пилотный вынос</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Пилотный вынос</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
+          <t>Трудозатраты всего, ч-д</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>98</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
+          <t>Внутренняя ставка, ₽/ч-д</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>30</v>
+        <v>11515</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>11515</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>B19*B22</f>
+        <v>1128470</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B24" s="7">
-        <f>B20*B23</f>
-        <v>1128470</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>0</v>
+          <t>Абонентов в периметре</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1255</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1255</v>
+        <v>12</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -992,231 +990,216 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>7</v>
+          <t>Арбитр garbd</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>не нужен</t>
+        </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Арбитр garbd</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>не нужен</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Виртуальных машин добавить</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>3</v>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
+          <t>Снимки ВМ как резервная копия</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>нельзя</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
+          <t>Оба узла ЦОД — живые</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>нельзя</t>
+          <t>да</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
+          <t>Панель управления FreePBX</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>ровно на одном узле</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Панель управления FreePBX</t>
+          <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>ровно на одном узле</t>
+          <t>21–25 декабря</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Неделя 16 — предновогодняя</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>21–25 декабря</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
           <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Что нужно заполнить вручную</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Что нужно заполнить вручную</t>
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Исполнитель</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Исполнитель</t>
+          <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
+          <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Номер приказа / внутреннего проекта</t>
+          <t>Дата протокола совещания</t>
         </is>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>Присваивается при открытии проекта.</t>
+          <t>Проставить дату документа, из которого взята этапность.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Дата протокола совещания</t>
+          <t>Адресный план узлов</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>Адресный план узлов</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
           <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1513,11 +1496,11 @@
       </c>
       <c r="E4" s="20" t="n"/>
       <c r="F4" s="21">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G4" s="21">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H4" s="21">
@@ -1544,7 +1527,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="22">
-        <f>Параметры!$B$23*M4</f>
+        <f>Параметры!$B$22*M4</f>
         <v>92120</v>
       </c>
       <c r="O4" s="22" t="n">
@@ -1568,11 +1551,11 @@
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="27">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G5" s="27">
-        <f>Параметры!$B$12+4</f>
+        <f>Параметры!$B$11+4</f>
         <v>46276</v>
       </c>
       <c r="H5" s="26" t="n"/>
@@ -1610,11 +1593,11 @@
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="26" t="n"/>
       <c r="F6" s="27">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G6" s="27">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H6" s="26" t="n"/>
@@ -1653,11 +1636,11 @@
       <c r="D7" s="26" t="n"/>
       <c r="E7" s="26" t="n"/>
       <c r="F7" s="27">
-        <f>Параметры!$B$12+7</f>
+        <f>Параметры!$B$11+7</f>
         <v>46279</v>
       </c>
       <c r="G7" s="27">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H7" s="26" t="n"/>
@@ -1695,11 +1678,11 @@
       <c r="D8" s="26" t="n"/>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="27">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G8" s="27">
-        <f>Параметры!$B$12+4</f>
+        <f>Параметры!$B$11+4</f>
         <v>46276</v>
       </c>
       <c r="H8" s="26" t="n"/>
@@ -1730,25 +1713,25 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Выделить в ЦОД две ВМ в разных стойках</t>
+          <t>Выделить три ВМ: две в ЦОД (разные стойки) и одну под Ставрополь</t>
         </is>
       </c>
       <c r="C9" s="26" t="n"/>
       <c r="D9" s="26" t="n"/>
       <c r="E9" s="26" t="n"/>
       <c r="F9" s="27">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G9" s="27">
-        <f>Параметры!$B$12+4</f>
+        <f>Параметры!$B$11+4</f>
         <v>46276</v>
       </c>
       <c r="H9" s="26" t="n"/>
       <c r="I9" s="26" t="n"/>
       <c r="J9" s="26" t="inlineStr">
         <is>
-          <t>ВМ выделены; стойки свои и независимы — подтверждено</t>
+          <t>ВМ выделены, узлы разнесены по физическим хостам</t>
         </is>
       </c>
       <c r="K9" s="28" t="n"/>
@@ -1772,25 +1755,25 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Завести SIP-пользователей ВАТС на каждую площадку самостоятельно</t>
+          <t>Завести SIP-пользователей ВАТС на каждую площадку</t>
         </is>
       </c>
       <c r="C10" s="26" t="n"/>
       <c r="D10" s="26" t="n"/>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="27">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G10" s="27">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H10" s="26" t="n"/>
       <c r="I10" s="26" t="n"/>
       <c r="J10" s="26" t="inlineStr">
         <is>
-          <t>Учётные записи созданы в кабинете ВАТС на все площадки, внешних согласований нет</t>
+          <t>Учётные записи созданы на все площадки, включая Воронеж</t>
         </is>
       </c>
       <c r="K10" s="28" t="n"/>
@@ -1830,11 +1813,11 @@
       </c>
       <c r="E11" s="20" t="n"/>
       <c r="F11" s="21">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G11" s="21">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H11" s="21">
@@ -1861,7 +1844,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="22">
-        <f>Параметры!$B$23*M11</f>
+        <f>Параметры!$B$22*M11</f>
         <v>115150</v>
       </c>
       <c r="O11" s="22" t="n">
@@ -1885,11 +1868,11 @@
       <c r="D12" s="26" t="n"/>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="27">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G12" s="27">
-        <f>Параметры!$B$12+4</f>
+        <f>Параметры!$B$11+4</f>
         <v>46276</v>
       </c>
       <c r="H12" s="26" t="n"/>
@@ -1927,11 +1910,11 @@
       <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="27">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G13" s="27">
-        <f>Параметры!$B$12+4</f>
+        <f>Параметры!$B$11+4</f>
         <v>46276</v>
       </c>
       <c r="H13" s="26" t="n"/>
@@ -1969,11 +1952,11 @@
       <c r="D14" s="26" t="n"/>
       <c r="E14" s="26" t="n"/>
       <c r="F14" s="27">
-        <f>Параметры!$B$12+0</f>
+        <f>Параметры!$B$11+0</f>
         <v>46272</v>
       </c>
       <c r="G14" s="27">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H14" s="26" t="n"/>
@@ -2012,11 +1995,11 @@
       <c r="D15" s="26" t="n"/>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="27">
-        <f>Параметры!$B$12+7</f>
+        <f>Параметры!$B$11+7</f>
         <v>46279</v>
       </c>
       <c r="G15" s="27">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H15" s="26" t="n"/>
@@ -2054,11 +2037,11 @@
       <c r="D16" s="26" t="n"/>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="27">
-        <f>Параметры!$B$12+7</f>
+        <f>Параметры!$B$11+7</f>
         <v>46279</v>
       </c>
       <c r="G16" s="27">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H16" s="26" t="n"/>
@@ -2096,11 +2079,11 @@
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="26" t="n"/>
       <c r="F17" s="27">
-        <f>Параметры!$B$12+7</f>
+        <f>Параметры!$B$11+7</f>
         <v>46279</v>
       </c>
       <c r="G17" s="27">
-        <f>Параметры!$B$12+11</f>
+        <f>Параметры!$B$11+11</f>
         <v>46283</v>
       </c>
       <c r="H17" s="26" t="n"/>
@@ -2146,11 +2129,11 @@
       </c>
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="21">
-        <f>Параметры!$B$12+14</f>
+        <f>Параметры!$B$11+14</f>
         <v>46286</v>
       </c>
       <c r="G18" s="21">
-        <f>Параметры!$B$12+18</f>
+        <f>Параметры!$B$11+18</f>
         <v>46290</v>
       </c>
       <c r="H18" s="21">
@@ -2177,7 +2160,7 @@
         <v>6</v>
       </c>
       <c r="N18" s="22">
-        <f>Параметры!$B$23*M18</f>
+        <f>Параметры!$B$22*M18</f>
         <v>69090</v>
       </c>
       <c r="O18" s="22" t="n">
@@ -2200,11 +2183,11 @@
       <c r="D19" s="26" t="n"/>
       <c r="E19" s="26" t="n"/>
       <c r="F19" s="27">
-        <f>Параметры!$B$12+14</f>
+        <f>Параметры!$B$11+14</f>
         <v>46286</v>
       </c>
       <c r="G19" s="27">
-        <f>Параметры!$B$12+18</f>
+        <f>Параметры!$B$11+18</f>
         <v>46290</v>
       </c>
       <c r="H19" s="26" t="n"/>
@@ -2242,11 +2225,11 @@
       <c r="D20" s="26" t="n"/>
       <c r="E20" s="26" t="n"/>
       <c r="F20" s="27">
-        <f>Параметры!$B$12+14</f>
+        <f>Параметры!$B$11+14</f>
         <v>46286</v>
       </c>
       <c r="G20" s="27">
-        <f>Параметры!$B$12+18</f>
+        <f>Параметры!$B$11+18</f>
         <v>46290</v>
       </c>
       <c r="H20" s="26" t="n"/>
@@ -2284,11 +2267,11 @@
       <c r="D21" s="26" t="n"/>
       <c r="E21" s="26" t="n"/>
       <c r="F21" s="27">
-        <f>Параметры!$B$12+14</f>
+        <f>Параметры!$B$11+14</f>
         <v>46286</v>
       </c>
       <c r="G21" s="27">
-        <f>Параметры!$B$12+18</f>
+        <f>Параметры!$B$11+18</f>
         <v>46290</v>
       </c>
       <c r="H21" s="26" t="n"/>
@@ -2334,11 +2317,11 @@
       </c>
       <c r="E22" s="20" t="n"/>
       <c r="F22" s="21">
-        <f>Параметры!$B$12+21</f>
+        <f>Параметры!$B$11+21</f>
         <v>46293</v>
       </c>
       <c r="G22" s="21">
-        <f>Параметры!$B$12+25</f>
+        <f>Параметры!$B$11+25</f>
         <v>46297</v>
       </c>
       <c r="H22" s="21">
@@ -2365,7 +2348,7 @@
         <v>4</v>
       </c>
       <c r="N22" s="22">
-        <f>Параметры!$B$23*M22</f>
+        <f>Параметры!$B$22*M22</f>
         <v>46060</v>
       </c>
       <c r="O22" s="22" t="n">
@@ -2388,11 +2371,11 @@
       <c r="D23" s="26" t="n"/>
       <c r="E23" s="26" t="n"/>
       <c r="F23" s="27">
-        <f>Параметры!$B$12+21</f>
+        <f>Параметры!$B$11+21</f>
         <v>46293</v>
       </c>
       <c r="G23" s="27">
-        <f>Параметры!$B$12+25</f>
+        <f>Параметры!$B$11+25</f>
         <v>46297</v>
       </c>
       <c r="H23" s="26" t="n"/>
@@ -2430,11 +2413,11 @@
       <c r="D24" s="26" t="n"/>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="27">
-        <f>Параметры!$B$12+21</f>
+        <f>Параметры!$B$11+21</f>
         <v>46293</v>
       </c>
       <c r="G24" s="27">
-        <f>Параметры!$B$12+25</f>
+        <f>Параметры!$B$11+25</f>
         <v>46297</v>
       </c>
       <c r="H24" s="26" t="n"/>
@@ -2472,11 +2455,11 @@
       <c r="D25" s="26" t="n"/>
       <c r="E25" s="26" t="n"/>
       <c r="F25" s="27">
-        <f>Параметры!$B$12+21</f>
+        <f>Параметры!$B$11+21</f>
         <v>46293</v>
       </c>
       <c r="G25" s="27">
-        <f>Параметры!$B$12+25</f>
+        <f>Параметры!$B$11+25</f>
         <v>46297</v>
       </c>
       <c r="H25" s="26" t="n"/>
@@ -2522,11 +2505,11 @@
       </c>
       <c r="E26" s="20" t="n"/>
       <c r="F26" s="21">
-        <f>Параметры!$B$12+28</f>
+        <f>Параметры!$B$11+28</f>
         <v>46300</v>
       </c>
       <c r="G26" s="21">
-        <f>Параметры!$B$12+39</f>
+        <f>Параметры!$B$11+39</f>
         <v>46311</v>
       </c>
       <c r="H26" s="21">
@@ -2553,7 +2536,7 @@
         <v>10</v>
       </c>
       <c r="N26" s="22">
-        <f>Параметры!$B$23*M26</f>
+        <f>Параметры!$B$22*M26</f>
         <v>115150</v>
       </c>
       <c r="O26" s="22" t="n">
@@ -2577,11 +2560,11 @@
       <c r="D27" s="26" t="n"/>
       <c r="E27" s="26" t="n"/>
       <c r="F27" s="27">
-        <f>Параметры!$B$12+28</f>
+        <f>Параметры!$B$11+28</f>
         <v>46300</v>
       </c>
       <c r="G27" s="27">
-        <f>Параметры!$B$12+32</f>
+        <f>Параметры!$B$11+32</f>
         <v>46304</v>
       </c>
       <c r="H27" s="26" t="n"/>
@@ -2619,11 +2602,11 @@
       <c r="D28" s="26" t="n"/>
       <c r="E28" s="26" t="n"/>
       <c r="F28" s="27">
-        <f>Параметры!$B$12+28</f>
+        <f>Параметры!$B$11+28</f>
         <v>46300</v>
       </c>
       <c r="G28" s="27">
-        <f>Параметры!$B$12+32</f>
+        <f>Параметры!$B$11+32</f>
         <v>46304</v>
       </c>
       <c r="H28" s="26" t="n"/>
@@ -2661,11 +2644,11 @@
       <c r="D29" s="26" t="n"/>
       <c r="E29" s="26" t="n"/>
       <c r="F29" s="27">
-        <f>Параметры!$B$12+35</f>
+        <f>Параметры!$B$11+35</f>
         <v>46307</v>
       </c>
       <c r="G29" s="27">
-        <f>Параметры!$B$12+39</f>
+        <f>Параметры!$B$11+39</f>
         <v>46311</v>
       </c>
       <c r="H29" s="26" t="n"/>
@@ -2703,11 +2686,11 @@
       <c r="D30" s="26" t="n"/>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="27">
-        <f>Параметры!$B$12+35</f>
+        <f>Параметры!$B$11+35</f>
         <v>46307</v>
       </c>
       <c r="G30" s="27">
-        <f>Параметры!$B$12+39</f>
+        <f>Параметры!$B$11+39</f>
         <v>46311</v>
       </c>
       <c r="H30" s="26" t="n"/>
@@ -2745,11 +2728,11 @@
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="27">
-        <f>Параметры!$B$12+35</f>
+        <f>Параметры!$B$11+35</f>
         <v>46307</v>
       </c>
       <c r="G31" s="27">
-        <f>Параметры!$B$12+39</f>
+        <f>Параметры!$B$11+39</f>
         <v>46311</v>
       </c>
       <c r="H31" s="26" t="n"/>
@@ -2795,11 +2778,11 @@
       </c>
       <c r="E32" s="20" t="n"/>
       <c r="F32" s="21">
-        <f>Параметры!$B$12+42</f>
+        <f>Параметры!$B$11+42</f>
         <v>46314</v>
       </c>
       <c r="G32" s="21">
-        <f>Параметры!$B$12+53</f>
+        <f>Параметры!$B$11+53</f>
         <v>46325</v>
       </c>
       <c r="H32" s="21">
@@ -2826,7 +2809,7 @@
         <v>10</v>
       </c>
       <c r="N32" s="22">
-        <f>Параметры!$B$23*M32</f>
+        <f>Параметры!$B$22*M32</f>
         <v>115150</v>
       </c>
       <c r="O32" s="22" t="n">
@@ -2850,11 +2833,11 @@
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="26" t="n"/>
       <c r="F33" s="27">
-        <f>Параметры!$B$12+42</f>
+        <f>Параметры!$B$11+42</f>
         <v>46314</v>
       </c>
       <c r="G33" s="27">
-        <f>Параметры!$B$12+46</f>
+        <f>Параметры!$B$11+46</f>
         <v>46318</v>
       </c>
       <c r="H33" s="26" t="n"/>
@@ -2892,11 +2875,11 @@
       <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="27">
-        <f>Параметры!$B$12+42</f>
+        <f>Параметры!$B$11+42</f>
         <v>46314</v>
       </c>
       <c r="G34" s="27">
-        <f>Параметры!$B$12+46</f>
+        <f>Параметры!$B$11+46</f>
         <v>46318</v>
       </c>
       <c r="H34" s="26" t="n"/>
@@ -2934,11 +2917,11 @@
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="26" t="n"/>
       <c r="F35" s="27">
-        <f>Параметры!$B$12+42</f>
+        <f>Параметры!$B$11+42</f>
         <v>46314</v>
       </c>
       <c r="G35" s="27">
-        <f>Параметры!$B$12+46</f>
+        <f>Параметры!$B$11+46</f>
         <v>46318</v>
       </c>
       <c r="H35" s="26" t="n"/>
@@ -2976,11 +2959,11 @@
       <c r="D36" s="26" t="n"/>
       <c r="E36" s="26" t="n"/>
       <c r="F36" s="27">
-        <f>Параметры!$B$12+42</f>
+        <f>Параметры!$B$11+42</f>
         <v>46314</v>
       </c>
       <c r="G36" s="27">
-        <f>Параметры!$B$12+46</f>
+        <f>Параметры!$B$11+46</f>
         <v>46318</v>
       </c>
       <c r="H36" s="26" t="n"/>
@@ -3018,11 +3001,11 @@
       <c r="D37" s="26" t="n"/>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="27">
-        <f>Параметры!$B$12+49</f>
+        <f>Параметры!$B$11+49</f>
         <v>46321</v>
       </c>
       <c r="G37" s="27">
-        <f>Параметры!$B$12+53</f>
+        <f>Параметры!$B$11+53</f>
         <v>46325</v>
       </c>
       <c r="H37" s="26" t="n"/>
@@ -3068,11 +3051,11 @@
       </c>
       <c r="E38" s="20" t="n"/>
       <c r="F38" s="21">
-        <f>Параметры!$B$12+56</f>
+        <f>Параметры!$B$11+56</f>
         <v>46328</v>
       </c>
       <c r="G38" s="21">
-        <f>Параметры!$B$12+60</f>
+        <f>Параметры!$B$11+60</f>
         <v>46332</v>
       </c>
       <c r="H38" s="21">
@@ -3099,7 +3082,7 @@
         <v>3</v>
       </c>
       <c r="N38" s="22">
-        <f>Параметры!$B$23*M38</f>
+        <f>Параметры!$B$22*M38</f>
         <v>34545</v>
       </c>
       <c r="O38" s="22" t="n">
@@ -3122,11 +3105,11 @@
       <c r="D39" s="26" t="n"/>
       <c r="E39" s="26" t="n"/>
       <c r="F39" s="27">
-        <f>Параметры!$B$12+56</f>
+        <f>Параметры!$B$11+56</f>
         <v>46328</v>
       </c>
       <c r="G39" s="27">
-        <f>Параметры!$B$12+60</f>
+        <f>Параметры!$B$11+60</f>
         <v>46332</v>
       </c>
       <c r="H39" s="26" t="n"/>
@@ -3164,11 +3147,11 @@
       <c r="D40" s="26" t="n"/>
       <c r="E40" s="26" t="n"/>
       <c r="F40" s="27">
-        <f>Параметры!$B$12+56</f>
+        <f>Параметры!$B$11+56</f>
         <v>46328</v>
       </c>
       <c r="G40" s="27">
-        <f>Параметры!$B$12+60</f>
+        <f>Параметры!$B$11+60</f>
         <v>46332</v>
       </c>
       <c r="H40" s="26" t="n"/>
@@ -3214,11 +3197,11 @@
       </c>
       <c r="E41" s="20" t="n"/>
       <c r="F41" s="21">
-        <f>Параметры!$B$12+63</f>
+        <f>Параметры!$B$11+63</f>
         <v>46335</v>
       </c>
       <c r="G41" s="21">
-        <f>Параметры!$B$12+74</f>
+        <f>Параметры!$B$11+74</f>
         <v>46346</v>
       </c>
       <c r="H41" s="21">
@@ -3245,7 +3228,7 @@
         <v>9</v>
       </c>
       <c r="N41" s="22">
-        <f>Параметры!$B$23*M41</f>
+        <f>Параметры!$B$22*M41</f>
         <v>103635</v>
       </c>
       <c r="O41" s="22" t="n">
@@ -3269,11 +3252,11 @@
       <c r="D42" s="26" t="n"/>
       <c r="E42" s="26" t="n"/>
       <c r="F42" s="27">
-        <f>Параметры!$B$12+63</f>
+        <f>Параметры!$B$11+63</f>
         <v>46335</v>
       </c>
       <c r="G42" s="27">
-        <f>Параметры!$B$12+67</f>
+        <f>Параметры!$B$11+67</f>
         <v>46339</v>
       </c>
       <c r="H42" s="26" t="n"/>
@@ -3311,11 +3294,11 @@
       <c r="D43" s="26" t="n"/>
       <c r="E43" s="26" t="n"/>
       <c r="F43" s="27">
-        <f>Параметры!$B$12+70</f>
+        <f>Параметры!$B$11+70</f>
         <v>46342</v>
       </c>
       <c r="G43" s="27">
-        <f>Параметры!$B$12+74</f>
+        <f>Параметры!$B$11+74</f>
         <v>46346</v>
       </c>
       <c r="H43" s="26" t="n"/>
@@ -3361,11 +3344,11 @@
       </c>
       <c r="E44" s="20" t="n"/>
       <c r="F44" s="21">
-        <f>Параметры!$B$12+49</f>
+        <f>Параметры!$B$11+49</f>
         <v>46321</v>
       </c>
       <c r="G44" s="21">
-        <f>Параметры!$B$12+74</f>
+        <f>Параметры!$B$11+74</f>
         <v>46346</v>
       </c>
       <c r="H44" s="21">
@@ -3392,7 +3375,7 @@
         <v>6</v>
       </c>
       <c r="N44" s="22">
-        <f>Параметры!$B$23*M44</f>
+        <f>Параметры!$B$22*M44</f>
         <v>69090</v>
       </c>
       <c r="O44" s="22" t="n">
@@ -3418,11 +3401,11 @@
       <c r="D45" s="26" t="n"/>
       <c r="E45" s="26" t="n"/>
       <c r="F45" s="27">
-        <f>Параметры!$B$12+49</f>
+        <f>Параметры!$B$11+49</f>
         <v>46321</v>
       </c>
       <c r="G45" s="27">
-        <f>Параметры!$B$12+53</f>
+        <f>Параметры!$B$11+53</f>
         <v>46325</v>
       </c>
       <c r="H45" s="26" t="n"/>
@@ -3460,11 +3443,11 @@
       <c r="D46" s="26" t="n"/>
       <c r="E46" s="26" t="n"/>
       <c r="F46" s="27">
-        <f>Параметры!$B$12+56</f>
+        <f>Параметры!$B$11+56</f>
         <v>46328</v>
       </c>
       <c r="G46" s="27">
-        <f>Параметры!$B$12+67</f>
+        <f>Параметры!$B$11+67</f>
         <v>46339</v>
       </c>
       <c r="H46" s="26" t="n"/>
@@ -3503,11 +3486,11 @@
       <c r="D47" s="26" t="n"/>
       <c r="E47" s="26" t="n"/>
       <c r="F47" s="27">
-        <f>Параметры!$B$12+70</f>
+        <f>Параметры!$B$11+70</f>
         <v>46342</v>
       </c>
       <c r="G47" s="27">
-        <f>Параметры!$B$12+74</f>
+        <f>Параметры!$B$11+74</f>
         <v>46346</v>
       </c>
       <c r="H47" s="26" t="n"/>
@@ -3553,11 +3536,11 @@
       </c>
       <c r="E48" s="20" t="n"/>
       <c r="F48" s="21">
-        <f>Параметры!$B$12+35</f>
+        <f>Параметры!$B$11+35</f>
         <v>46307</v>
       </c>
       <c r="G48" s="21">
-        <f>Параметры!$B$12+81</f>
+        <f>Параметры!$B$11+81</f>
         <v>46353</v>
       </c>
       <c r="H48" s="21">
@@ -3584,7 +3567,7 @@
         <v>12</v>
       </c>
       <c r="N48" s="22">
-        <f>Параметры!$B$23*M48</f>
+        <f>Параметры!$B$22*M48</f>
         <v>138180</v>
       </c>
       <c r="O48" s="22" t="n">
@@ -3613,11 +3596,11 @@
       <c r="D49" s="26" t="n"/>
       <c r="E49" s="26" t="n"/>
       <c r="F49" s="27">
-        <f>Параметры!$B$12+35</f>
+        <f>Параметры!$B$11+35</f>
         <v>46307</v>
       </c>
       <c r="G49" s="27">
-        <f>Параметры!$B$12+60</f>
+        <f>Параметры!$B$11+60</f>
         <v>46332</v>
       </c>
       <c r="H49" s="26" t="n"/>
@@ -3658,11 +3641,11 @@
       <c r="D50" s="26" t="n"/>
       <c r="E50" s="26" t="n"/>
       <c r="F50" s="27">
-        <f>Параметры!$B$12+42</f>
+        <f>Параметры!$B$11+42</f>
         <v>46314</v>
       </c>
       <c r="G50" s="27">
-        <f>Параметры!$B$12+60</f>
+        <f>Параметры!$B$11+60</f>
         <v>46332</v>
       </c>
       <c r="H50" s="26" t="n"/>
@@ -3702,11 +3685,11 @@
       <c r="D51" s="26" t="n"/>
       <c r="E51" s="26" t="n"/>
       <c r="F51" s="27">
-        <f>Параметры!$B$12+63</f>
+        <f>Параметры!$B$11+63</f>
         <v>46335</v>
       </c>
       <c r="G51" s="27">
-        <f>Параметры!$B$12+74</f>
+        <f>Параметры!$B$11+74</f>
         <v>46346</v>
       </c>
       <c r="H51" s="26" t="n"/>
@@ -3745,11 +3728,11 @@
       <c r="D52" s="26" t="n"/>
       <c r="E52" s="26" t="n"/>
       <c r="F52" s="27">
-        <f>Параметры!$B$12+70</f>
+        <f>Параметры!$B$11+70</f>
         <v>46342</v>
       </c>
       <c r="G52" s="27">
-        <f>Параметры!$B$12+81</f>
+        <f>Параметры!$B$11+81</f>
         <v>46353</v>
       </c>
       <c r="H52" s="26" t="n"/>
@@ -3788,11 +3771,11 @@
       <c r="D53" s="26" t="n"/>
       <c r="E53" s="26" t="n"/>
       <c r="F53" s="27">
-        <f>Параметры!$B$12+63</f>
+        <f>Параметры!$B$11+63</f>
         <v>46335</v>
       </c>
       <c r="G53" s="27">
-        <f>Параметры!$B$12+81</f>
+        <f>Параметры!$B$11+81</f>
         <v>46353</v>
       </c>
       <c r="H53" s="26" t="n"/>
@@ -3877,11 +3860,11 @@
       </c>
       <c r="E55" s="20" t="n"/>
       <c r="F55" s="21">
-        <f>Параметры!$B$12+84</f>
+        <f>Параметры!$B$11+84</f>
         <v>46356</v>
       </c>
       <c r="G55" s="21">
-        <f>Параметры!$B$12+95</f>
+        <f>Параметры!$B$11+95</f>
         <v>46367</v>
       </c>
       <c r="H55" s="21">
@@ -3908,7 +3891,7 @@
         <v>8</v>
       </c>
       <c r="N55" s="22">
-        <f>Параметры!$B$23*M55</f>
+        <f>Параметры!$B$22*M55</f>
         <v>92120</v>
       </c>
       <c r="O55" s="22" t="n">
@@ -3932,11 +3915,11 @@
       <c r="D56" s="26" t="n"/>
       <c r="E56" s="26" t="n"/>
       <c r="F56" s="27">
-        <f>Параметры!$B$12+84</f>
+        <f>Параметры!$B$11+84</f>
         <v>46356</v>
       </c>
       <c r="G56" s="27">
-        <f>Параметры!$B$12+88</f>
+        <f>Параметры!$B$11+88</f>
         <v>46360</v>
       </c>
       <c r="H56" s="26" t="n"/>
@@ -3974,11 +3957,11 @@
       <c r="D57" s="26" t="n"/>
       <c r="E57" s="26" t="n"/>
       <c r="F57" s="27">
-        <f>Параметры!$B$12+84</f>
+        <f>Параметры!$B$11+84</f>
         <v>46356</v>
       </c>
       <c r="G57" s="27">
-        <f>Параметры!$B$12+88</f>
+        <f>Параметры!$B$11+88</f>
         <v>46360</v>
       </c>
       <c r="H57" s="26" t="n"/>
@@ -4016,11 +3999,11 @@
       <c r="D58" s="26" t="n"/>
       <c r="E58" s="26" t="n"/>
       <c r="F58" s="27">
-        <f>Параметры!$B$12+84</f>
+        <f>Параметры!$B$11+84</f>
         <v>46356</v>
       </c>
       <c r="G58" s="27">
-        <f>Параметры!$B$12+88</f>
+        <f>Параметры!$B$11+88</f>
         <v>46360</v>
       </c>
       <c r="H58" s="26" t="n"/>
@@ -4058,11 +4041,11 @@
       <c r="D59" s="26" t="n"/>
       <c r="E59" s="26" t="n"/>
       <c r="F59" s="27">
-        <f>Параметры!$B$12+91</f>
+        <f>Параметры!$B$11+91</f>
         <v>46363</v>
       </c>
       <c r="G59" s="27">
-        <f>Параметры!$B$12+95</f>
+        <f>Параметры!$B$11+95</f>
         <v>46367</v>
       </c>
       <c r="H59" s="26" t="n"/>
@@ -4100,11 +4083,11 @@
       <c r="D60" s="26" t="n"/>
       <c r="E60" s="26" t="n"/>
       <c r="F60" s="27">
-        <f>Параметры!$B$12+91</f>
+        <f>Параметры!$B$11+91</f>
         <v>46363</v>
       </c>
       <c r="G60" s="27">
-        <f>Параметры!$B$12+95</f>
+        <f>Параметры!$B$11+95</f>
         <v>46367</v>
       </c>
       <c r="H60" s="26" t="n"/>
@@ -4150,11 +4133,11 @@
       </c>
       <c r="E61" s="20" t="n"/>
       <c r="F61" s="21">
-        <f>Параметры!$B$12+91</f>
+        <f>Параметры!$B$11+91</f>
         <v>46363</v>
       </c>
       <c r="G61" s="21">
-        <f>Параметры!$B$12+102</f>
+        <f>Параметры!$B$11+102</f>
         <v>46374</v>
       </c>
       <c r="H61" s="21">
@@ -4181,7 +4164,7 @@
         <v>6</v>
       </c>
       <c r="N61" s="22">
-        <f>Параметры!$B$23*M61</f>
+        <f>Параметры!$B$22*M61</f>
         <v>69090</v>
       </c>
       <c r="O61" s="22" t="n">
@@ -4205,11 +4188,11 @@
       <c r="D62" s="26" t="n"/>
       <c r="E62" s="26" t="n"/>
       <c r="F62" s="27">
-        <f>Параметры!$B$12+91</f>
+        <f>Параметры!$B$11+91</f>
         <v>46363</v>
       </c>
       <c r="G62" s="27">
-        <f>Параметры!$B$12+102</f>
+        <f>Параметры!$B$11+102</f>
         <v>46374</v>
       </c>
       <c r="H62" s="26" t="n"/>
@@ -4248,11 +4231,11 @@
       <c r="D63" s="26" t="n"/>
       <c r="E63" s="26" t="n"/>
       <c r="F63" s="27">
-        <f>Параметры!$B$12+98</f>
+        <f>Параметры!$B$11+98</f>
         <v>46370</v>
       </c>
       <c r="G63" s="27">
-        <f>Параметры!$B$12+102</f>
+        <f>Параметры!$B$11+102</f>
         <v>46374</v>
       </c>
       <c r="H63" s="26" t="n"/>
@@ -4298,11 +4281,11 @@
       </c>
       <c r="E64" s="20" t="n"/>
       <c r="F64" s="21">
-        <f>Параметры!$B$12+91</f>
+        <f>Параметры!$B$11+91</f>
         <v>46363</v>
       </c>
       <c r="G64" s="21">
-        <f>Параметры!$B$12+109</f>
+        <f>Параметры!$B$11+109</f>
         <v>46381</v>
       </c>
       <c r="H64" s="21">
@@ -4329,7 +4312,7 @@
         <v>6</v>
       </c>
       <c r="N64" s="22">
-        <f>Параметры!$B$23*M64</f>
+        <f>Параметры!$B$22*M64</f>
         <v>69090</v>
       </c>
       <c r="O64" s="22" t="n">
@@ -4354,11 +4337,11 @@
       <c r="D65" s="26" t="n"/>
       <c r="E65" s="26" t="n"/>
       <c r="F65" s="27">
-        <f>Параметры!$B$12+91</f>
+        <f>Параметры!$B$11+91</f>
         <v>46363</v>
       </c>
       <c r="G65" s="27">
-        <f>Параметры!$B$12+109</f>
+        <f>Параметры!$B$11+109</f>
         <v>46381</v>
       </c>
       <c r="H65" s="26" t="n"/>
@@ -4398,11 +4381,11 @@
       <c r="D66" s="26" t="n"/>
       <c r="E66" s="26" t="n"/>
       <c r="F66" s="27">
-        <f>Параметры!$B$12+105</f>
+        <f>Параметры!$B$11+105</f>
         <v>46377</v>
       </c>
       <c r="G66" s="27">
-        <f>Параметры!$B$12+109</f>
+        <f>Параметры!$B$11+109</f>
         <v>46381</v>
       </c>
       <c r="H66" s="26" t="n"/>

--- a/docs/plan/dit-annual-plan.xlsx
+++ b/docs/plan/dit-annual-plan.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -624,582 +624,548 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.» Уточнение: центр размещается в московском ЦОД — мастер на первой площадке, копия на второй; остальные узлы по городам.</t>
+          <t>«Обсудили верхнеуровневую архитектуру, решили строить централизованную на Asterisk с выносами в кластерах. По плану первый этап все за исключением Воронежа, далее Воронеж.» Уточнение: центр размещается в московском ЦОД, на обеих площадках живые узлы; остальные узлы по городам.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Скорректированная архитектура</t>
+          <t>Архитектура</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Савенко В. — до 05.08, выполнено</t>
+          <t>центр в ЦОД + выносы</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Из протокола, п. 3.</t>
+          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>План работ</t>
+          <t>Стойки в ЦОД</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Цеховской В. — срок 20.08</t>
+          <t>наши, залы независимы</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Из протокола, п. 3. Настоящий файл и есть этот план.</t>
+          <t>Два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания. Это условие, без которого схема резервирования не имела бы смысла.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Архитектура</t>
+          <t>Ждать никого не нужно</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>центр в ЦОД + выносы</t>
+          <t>да</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Центр — московский ЦОД: ДВА ЖИВЫХ УЗЛА в разных залах. Оба обслуживают вызовы, московские 80 абонентов поделены поровну и прописаны друг другу резервными. Панель управления FreePBX включена только на ЦОД-1. Выносы — Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж — работают узлами того же кластера: локальная регистрация телефонов и свой выход в город, при отказе площадки телефоны уходят в ЦОД.</t>
+          <t>Площадки наши, адреса известны, стойки в ЦОД наши, SIP-пользователей ВАТС заводим сами, ПО бесплатное, машины на своей виртуализации. Закупок и внешних согласований в плане нет. Практический вывод: если график поедет, причина будет внутренней — не хватило людей, не согласовали окно, не успели с перенумерацией.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Стойки в ЦОД</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>наши, залы независимы</t>
-        </is>
+          <t>Дата начала работ</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>46272</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Два узла в ЦОД действительно резервируют друг друга, а не стоят за одним вводом питания. Это условие, без которого схема резервирования не имела бы смысла.</t>
+          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Ждать никого не нужно</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+          <t>Длительность, недель</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Площадки наши, адреса известны, стойки в ЦОД наши, SIP-пользователей ВАТС заводим сами, ПО бесплатное, машины на своей виртуализации. Закупок и внешних согласований в плане нет. Практический вывод: если график поедет, причина будет внутренней — не хватило людей, не согласовали окно, не успели с перенумерацией.</t>
+          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Дата начала работ</t>
+          <t>Дата завершения работ</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>46272</v>
+        <v>46381</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Понедельник. Отсчёт идёт от старта работ, то есть от стадии «проект открыт». Стадии 0–4 воронки плана автоматизации (постановка задачи, оценка, согласование карточки, ВЕ, приказа) в эти 15 недель не входят и идут до них.</t>
+          <t>Дата начала + 15 недель, последний рабочий день</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Длительность, недель</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Два этапа подряд: 11 недель без Воронежа + 4 недели Воронеж. Этапы последовательны по решению совещания, совмещать нельзя.</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>недели 1–12, 810 абонентов</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Дата завершения работ</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>46381</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Дата начала + 15 недель, последний рабочий день</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ЭТАП 2 — Воронеж</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>недели 13–16, 445 абонентов</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>ЭТАП 1 — центр в ЦОД + все выносы, кроме Воронежа</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>недели 1–12, 810 абонентов</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>ЦОД-1 40 и ЦОД-2 40, Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140.</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Ставрополь получает свою АТС</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>да, задача 8.2</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>ЭТАП 2 — Воронеж</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>недели 13–16, 445 абонентов</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Воронеж 229, Мясокомбинат 187, Калуга 29.</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Порядок переноса центра</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ставрополь получает свою АТС</t>
+          <t>Пилотный вынос</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>да, задача 8.2</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Раньше его 74 абонента висели на ростовском сервере и зависели от канала до Ростова. Своя АТС даёт им локальную живучесть и попутно делает число узлов нечётным.</t>
+          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Порядок переноса центра</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Ростов → ЦОД-1 → +ЦОД-2</t>
-        </is>
+          <t>Трудозатраты всего, ч-д</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>98</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Вся боевая база сейчас на ростовской АТС. Сначала она вводится в кластер как первый узел (задача 4), затем клонируется в ЦОД-1 и роль мастера передаётся туда, затем ЦОД-1 клонируется в ЦОД-2 (задача 5). Ростов после этого — обычный вынос со своими 352 абонентами. Переустановки нет ни на одном шаге, откат — возврат роли на Ростов.</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Пилотный вынос</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Нижний Новгород</t>
-        </is>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
+          <t>Внутренняя ставка, ₽/ч-д</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>68</v>
+        <v>11515</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>30</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B21" s="7">
+        <f>B17*B20</f>
+        <v>1128470</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>11515</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B23" s="7">
-        <f>B19*B22</f>
-        <v>1128470</v>
+          <t>Абонентов в периметре</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1255</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>0</v>
+          <t>Станций сейчас</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1255</v>
+        <v>7</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>7</v>
+          <t>Арбитр garbd</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>не нужен</t>
+        </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Кворум в конце этапа 1</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Арбитр garbd</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>не нужен</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>6</v>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>3</v>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
+          <t>Оба узла ЦОД — живые</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>проверить</t>
+          <t>да</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
+          <t>Панель управления FreePBX</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>нельзя</t>
+          <t>ровно на одном узле</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
+          <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>21–25 декабря</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Панель управления FreePBX</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>ровно на одном узле</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+          <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Неделя 16 — предновогодняя</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>21–25 декабря</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Что нужно заполнить вручную</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Что нужно заполнить вручную</t>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Исполнитель</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
+          <t>Присваивается при открытии проекта.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Исполнитель</t>
+          <t>Дата протокола совещания</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
+          <t>Проставить дату документа, из которого взята этапность.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Номер приказа / внутреннего проекта</t>
+          <t>Адресный план узлов</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Присваивается при открытии проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>Дата протокола совещания</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
+          <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Адресный план узлов</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1496,11 +1462,11 @@
       </c>
       <c r="E4" s="20" t="n"/>
       <c r="F4" s="21">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G4" s="21">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H4" s="21">
@@ -1527,7 +1493,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="22">
-        <f>Параметры!$B$22*M4</f>
+        <f>Параметры!$B$20*M4</f>
         <v>92120</v>
       </c>
       <c r="O4" s="22" t="n">
@@ -1551,11 +1517,11 @@
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="27">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G5" s="27">
-        <f>Параметры!$B$11+4</f>
+        <f>Параметры!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H5" s="26" t="n"/>
@@ -1593,11 +1559,11 @@
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="26" t="n"/>
       <c r="F6" s="27">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G6" s="27">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H6" s="26" t="n"/>
@@ -1636,11 +1602,11 @@
       <c r="D7" s="26" t="n"/>
       <c r="E7" s="26" t="n"/>
       <c r="F7" s="27">
-        <f>Параметры!$B$11+7</f>
+        <f>Параметры!$B$9+7</f>
         <v>46279</v>
       </c>
       <c r="G7" s="27">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H7" s="26" t="n"/>
@@ -1678,11 +1644,11 @@
       <c r="D8" s="26" t="n"/>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="27">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G8" s="27">
-        <f>Параметры!$B$11+4</f>
+        <f>Параметры!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H8" s="26" t="n"/>
@@ -1720,11 +1686,11 @@
       <c r="D9" s="26" t="n"/>
       <c r="E9" s="26" t="n"/>
       <c r="F9" s="27">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G9" s="27">
-        <f>Параметры!$B$11+4</f>
+        <f>Параметры!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H9" s="26" t="n"/>
@@ -1762,11 +1728,11 @@
       <c r="D10" s="26" t="n"/>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="27">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G10" s="27">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H10" s="26" t="n"/>
@@ -1813,11 +1779,11 @@
       </c>
       <c r="E11" s="20" t="n"/>
       <c r="F11" s="21">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G11" s="21">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H11" s="21">
@@ -1844,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="22">
-        <f>Параметры!$B$22*M11</f>
+        <f>Параметры!$B$20*M11</f>
         <v>115150</v>
       </c>
       <c r="O11" s="22" t="n">
@@ -1868,11 +1834,11 @@
       <c r="D12" s="26" t="n"/>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="27">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G12" s="27">
-        <f>Параметры!$B$11+4</f>
+        <f>Параметры!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H12" s="26" t="n"/>
@@ -1910,11 +1876,11 @@
       <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="27">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G13" s="27">
-        <f>Параметры!$B$11+4</f>
+        <f>Параметры!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H13" s="26" t="n"/>
@@ -1952,11 +1918,11 @@
       <c r="D14" s="26" t="n"/>
       <c r="E14" s="26" t="n"/>
       <c r="F14" s="27">
-        <f>Параметры!$B$11+0</f>
+        <f>Параметры!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G14" s="27">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H14" s="26" t="n"/>
@@ -1995,11 +1961,11 @@
       <c r="D15" s="26" t="n"/>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="27">
-        <f>Параметры!$B$11+7</f>
+        <f>Параметры!$B$9+7</f>
         <v>46279</v>
       </c>
       <c r="G15" s="27">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H15" s="26" t="n"/>
@@ -2037,11 +2003,11 @@
       <c r="D16" s="26" t="n"/>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="27">
-        <f>Параметры!$B$11+7</f>
+        <f>Параметры!$B$9+7</f>
         <v>46279</v>
       </c>
       <c r="G16" s="27">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H16" s="26" t="n"/>
@@ -2079,11 +2045,11 @@
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="26" t="n"/>
       <c r="F17" s="27">
-        <f>Параметры!$B$11+7</f>
+        <f>Параметры!$B$9+7</f>
         <v>46279</v>
       </c>
       <c r="G17" s="27">
-        <f>Параметры!$B$11+11</f>
+        <f>Параметры!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H17" s="26" t="n"/>
@@ -2129,11 +2095,11 @@
       </c>
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="21">
-        <f>Параметры!$B$11+14</f>
+        <f>Параметры!$B$9+14</f>
         <v>46286</v>
       </c>
       <c r="G18" s="21">
-        <f>Параметры!$B$11+18</f>
+        <f>Параметры!$B$9+18</f>
         <v>46290</v>
       </c>
       <c r="H18" s="21">
@@ -2160,7 +2126,7 @@
         <v>6</v>
       </c>
       <c r="N18" s="22">
-        <f>Параметры!$B$22*M18</f>
+        <f>Параметры!$B$20*M18</f>
         <v>69090</v>
       </c>
       <c r="O18" s="22" t="n">
@@ -2183,11 +2149,11 @@
       <c r="D19" s="26" t="n"/>
       <c r="E19" s="26" t="n"/>
       <c r="F19" s="27">
-        <f>Параметры!$B$11+14</f>
+        <f>Параметры!$B$9+14</f>
         <v>46286</v>
       </c>
       <c r="G19" s="27">
-        <f>Параметры!$B$11+18</f>
+        <f>Параметры!$B$9+18</f>
         <v>46290</v>
       </c>
       <c r="H19" s="26" t="n"/>
@@ -2225,11 +2191,11 @@
       <c r="D20" s="26" t="n"/>
       <c r="E20" s="26" t="n"/>
       <c r="F20" s="27">
-        <f>Параметры!$B$11+14</f>
+        <f>Параметры!$B$9+14</f>
         <v>46286</v>
       </c>
       <c r="G20" s="27">
-        <f>Параметры!$B$11+18</f>
+        <f>Параметры!$B$9+18</f>
         <v>46290</v>
       </c>
       <c r="H20" s="26" t="n"/>
@@ -2267,11 +2233,11 @@
       <c r="D21" s="26" t="n"/>
       <c r="E21" s="26" t="n"/>
       <c r="F21" s="27">
-        <f>Параметры!$B$11+14</f>
+        <f>Параметры!$B$9+14</f>
         <v>46286</v>
       </c>
       <c r="G21" s="27">
-        <f>Параметры!$B$11+18</f>
+        <f>Параметры!$B$9+18</f>
         <v>46290</v>
       </c>
       <c r="H21" s="26" t="n"/>
@@ -2317,11 +2283,11 @@
       </c>
       <c r="E22" s="20" t="n"/>
       <c r="F22" s="21">
-        <f>Параметры!$B$11+21</f>
+        <f>Параметры!$B$9+21</f>
         <v>46293</v>
       </c>
       <c r="G22" s="21">
-        <f>Параметры!$B$11+25</f>
+        <f>Параметры!$B$9+25</f>
         <v>46297</v>
       </c>
       <c r="H22" s="21">
@@ -2348,7 +2314,7 @@
         <v>4</v>
       </c>
       <c r="N22" s="22">
-        <f>Параметры!$B$22*M22</f>
+        <f>Параметры!$B$20*M22</f>
         <v>46060</v>
       </c>
       <c r="O22" s="22" t="n">
@@ -2371,11 +2337,11 @@
       <c r="D23" s="26" t="n"/>
       <c r="E23" s="26" t="n"/>
       <c r="F23" s="27">
-        <f>Параметры!$B$11+21</f>
+        <f>Параметры!$B$9+21</f>
         <v>46293</v>
       </c>
       <c r="G23" s="27">
-        <f>Параметры!$B$11+25</f>
+        <f>Параметры!$B$9+25</f>
         <v>46297</v>
       </c>
       <c r="H23" s="26" t="n"/>
@@ -2413,11 +2379,11 @@
       <c r="D24" s="26" t="n"/>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="27">
-        <f>Параметры!$B$11+21</f>
+        <f>Параметры!$B$9+21</f>
         <v>46293</v>
       </c>
       <c r="G24" s="27">
-        <f>Параметры!$B$11+25</f>
+        <f>Параметры!$B$9+25</f>
         <v>46297</v>
       </c>
       <c r="H24" s="26" t="n"/>
@@ -2455,11 +2421,11 @@
       <c r="D25" s="26" t="n"/>
       <c r="E25" s="26" t="n"/>
       <c r="F25" s="27">
-        <f>Параметры!$B$11+21</f>
+        <f>Параметры!$B$9+21</f>
         <v>46293</v>
       </c>
       <c r="G25" s="27">
-        <f>Параметры!$B$11+25</f>
+        <f>Параметры!$B$9+25</f>
         <v>46297</v>
       </c>
       <c r="H25" s="26" t="n"/>
@@ -2505,11 +2471,11 @@
       </c>
       <c r="E26" s="20" t="n"/>
       <c r="F26" s="21">
-        <f>Параметры!$B$11+28</f>
+        <f>Параметры!$B$9+28</f>
         <v>46300</v>
       </c>
       <c r="G26" s="21">
-        <f>Параметры!$B$11+39</f>
+        <f>Параметры!$B$9+39</f>
         <v>46311</v>
       </c>
       <c r="H26" s="21">
@@ -2536,7 +2502,7 @@
         <v>10</v>
       </c>
       <c r="N26" s="22">
-        <f>Параметры!$B$22*M26</f>
+        <f>Параметры!$B$20*M26</f>
         <v>115150</v>
       </c>
       <c r="O26" s="22" t="n">
@@ -2560,11 +2526,11 @@
       <c r="D27" s="26" t="n"/>
       <c r="E27" s="26" t="n"/>
       <c r="F27" s="27">
-        <f>Параметры!$B$11+28</f>
+        <f>Параметры!$B$9+28</f>
         <v>46300</v>
       </c>
       <c r="G27" s="27">
-        <f>Параметры!$B$11+32</f>
+        <f>Параметры!$B$9+32</f>
         <v>46304</v>
       </c>
       <c r="H27" s="26" t="n"/>
@@ -2602,11 +2568,11 @@
       <c r="D28" s="26" t="n"/>
       <c r="E28" s="26" t="n"/>
       <c r="F28" s="27">
-        <f>Параметры!$B$11+28</f>
+        <f>Параметры!$B$9+28</f>
         <v>46300</v>
       </c>
       <c r="G28" s="27">
-        <f>Параметры!$B$11+32</f>
+        <f>Параметры!$B$9+32</f>
         <v>46304</v>
       </c>
       <c r="H28" s="26" t="n"/>
@@ -2644,11 +2610,11 @@
       <c r="D29" s="26" t="n"/>
       <c r="E29" s="26" t="n"/>
       <c r="F29" s="27">
-        <f>Параметры!$B$11+35</f>
+        <f>Параметры!$B$9+35</f>
         <v>46307</v>
       </c>
       <c r="G29" s="27">
-        <f>Параметры!$B$11+39</f>
+        <f>Параметры!$B$9+39</f>
         <v>46311</v>
       </c>
       <c r="H29" s="26" t="n"/>
@@ -2686,11 +2652,11 @@
       <c r="D30" s="26" t="n"/>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="27">
-        <f>Параметры!$B$11+35</f>
+        <f>Параметры!$B$9+35</f>
         <v>46307</v>
       </c>
       <c r="G30" s="27">
-        <f>Параметры!$B$11+39</f>
+        <f>Параметры!$B$9+39</f>
         <v>46311</v>
       </c>
       <c r="H30" s="26" t="n"/>
@@ -2728,11 +2694,11 @@
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="27">
-        <f>Параметры!$B$11+35</f>
+        <f>Параметры!$B$9+35</f>
         <v>46307</v>
       </c>
       <c r="G31" s="27">
-        <f>Параметры!$B$11+39</f>
+        <f>Параметры!$B$9+39</f>
         <v>46311</v>
       </c>
       <c r="H31" s="26" t="n"/>
@@ -2778,11 +2744,11 @@
       </c>
       <c r="E32" s="20" t="n"/>
       <c r="F32" s="21">
-        <f>Параметры!$B$11+42</f>
+        <f>Параметры!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G32" s="21">
-        <f>Параметры!$B$11+53</f>
+        <f>Параметры!$B$9+53</f>
         <v>46325</v>
       </c>
       <c r="H32" s="21">
@@ -2809,7 +2775,7 @@
         <v>10</v>
       </c>
       <c r="N32" s="22">
-        <f>Параметры!$B$22*M32</f>
+        <f>Параметры!$B$20*M32</f>
         <v>115150</v>
       </c>
       <c r="O32" s="22" t="n">
@@ -2833,11 +2799,11 @@
       <c r="D33" s="26" t="n"/>
       <c r="E33" s="26" t="n"/>
       <c r="F33" s="27">
-        <f>Параметры!$B$11+42</f>
+        <f>Параметры!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G33" s="27">
-        <f>Параметры!$B$11+46</f>
+        <f>Параметры!$B$9+46</f>
         <v>46318</v>
       </c>
       <c r="H33" s="26" t="n"/>
@@ -2875,11 +2841,11 @@
       <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="27">
-        <f>Параметры!$B$11+42</f>
+        <f>Параметры!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G34" s="27">
-        <f>Параметры!$B$11+46</f>
+        <f>Параметры!$B$9+46</f>
         <v>46318</v>
       </c>
       <c r="H34" s="26" t="n"/>
@@ -2917,11 +2883,11 @@
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="26" t="n"/>
       <c r="F35" s="27">
-        <f>Параметры!$B$11+42</f>
+        <f>Параметры!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G35" s="27">
-        <f>Параметры!$B$11+46</f>
+        <f>Параметры!$B$9+46</f>
         <v>46318</v>
       </c>
       <c r="H35" s="26" t="n"/>
@@ -2959,11 +2925,11 @@
       <c r="D36" s="26" t="n"/>
       <c r="E36" s="26" t="n"/>
       <c r="F36" s="27">
-        <f>Параметры!$B$11+42</f>
+        <f>Параметры!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G36" s="27">
-        <f>Параметры!$B$11+46</f>
+        <f>Параметры!$B$9+46</f>
         <v>46318</v>
       </c>
       <c r="H36" s="26" t="n"/>
@@ -3001,11 +2967,11 @@
       <c r="D37" s="26" t="n"/>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="27">
-        <f>Параметры!$B$11+49</f>
+        <f>Параметры!$B$9+49</f>
         <v>46321</v>
       </c>
       <c r="G37" s="27">
-        <f>Параметры!$B$11+53</f>
+        <f>Параметры!$B$9+53</f>
         <v>46325</v>
       </c>
       <c r="H37" s="26" t="n"/>
@@ -3051,11 +3017,11 @@
       </c>
       <c r="E38" s="20" t="n"/>
       <c r="F38" s="21">
-        <f>Параметры!$B$11+56</f>
+        <f>Параметры!$B$9+56</f>
         <v>46328</v>
       </c>
       <c r="G38" s="21">
-        <f>Параметры!$B$11+60</f>
+        <f>Параметры!$B$9+60</f>
         <v>46332</v>
       </c>
       <c r="H38" s="21">
@@ -3082,7 +3048,7 @@
         <v>3</v>
       </c>
       <c r="N38" s="22">
-        <f>Параметры!$B$22*M38</f>
+        <f>Параметры!$B$20*M38</f>
         <v>34545</v>
       </c>
       <c r="O38" s="22" t="n">
@@ -3105,11 +3071,11 @@
       <c r="D39" s="26" t="n"/>
       <c r="E39" s="26" t="n"/>
       <c r="F39" s="27">
-        <f>Параметры!$B$11+56</f>
+        <f>Параметры!$B$9+56</f>
         <v>46328</v>
       </c>
       <c r="G39" s="27">
-        <f>Параметры!$B$11+60</f>
+        <f>Параметры!$B$9+60</f>
         <v>46332</v>
       </c>
       <c r="H39" s="26" t="n"/>
@@ -3147,11 +3113,11 @@
       <c r="D40" s="26" t="n"/>
       <c r="E40" s="26" t="n"/>
       <c r="F40" s="27">
-        <f>Параметры!$B$11+56</f>
+        <f>Параметры!$B$9+56</f>
         <v>46328</v>
       </c>
       <c r="G40" s="27">
-        <f>Параметры!$B$11+60</f>
+        <f>Параметры!$B$9+60</f>
         <v>46332</v>
       </c>
       <c r="H40" s="26" t="n"/>
@@ -3197,11 +3163,11 @@
       </c>
       <c r="E41" s="20" t="n"/>
       <c r="F41" s="21">
-        <f>Параметры!$B$11+63</f>
+        <f>Параметры!$B$9+63</f>
         <v>46335</v>
       </c>
       <c r="G41" s="21">
-        <f>Параметры!$B$11+74</f>
+        <f>Параметры!$B$9+74</f>
         <v>46346</v>
       </c>
       <c r="H41" s="21">
@@ -3228,7 +3194,7 @@
         <v>9</v>
       </c>
       <c r="N41" s="22">
-        <f>Параметры!$B$22*M41</f>
+        <f>Параметры!$B$20*M41</f>
         <v>103635</v>
       </c>
       <c r="O41" s="22" t="n">
@@ -3252,11 +3218,11 @@
       <c r="D42" s="26" t="n"/>
       <c r="E42" s="26" t="n"/>
       <c r="F42" s="27">
-        <f>Параметры!$B$11+63</f>
+        <f>Параметры!$B$9+63</f>
         <v>46335</v>
       </c>
       <c r="G42" s="27">
-        <f>Параметры!$B$11+67</f>
+        <f>Параметры!$B$9+67</f>
         <v>46339</v>
       </c>
       <c r="H42" s="26" t="n"/>
@@ -3294,11 +3260,11 @@
       <c r="D43" s="26" t="n"/>
       <c r="E43" s="26" t="n"/>
       <c r="F43" s="27">
-        <f>Параметры!$B$11+70</f>
+        <f>Параметры!$B$9+70</f>
         <v>46342</v>
       </c>
       <c r="G43" s="27">
-        <f>Параметры!$B$11+74</f>
+        <f>Параметры!$B$9+74</f>
         <v>46346</v>
       </c>
       <c r="H43" s="26" t="n"/>
@@ -3344,11 +3310,11 @@
       </c>
       <c r="E44" s="20" t="n"/>
       <c r="F44" s="21">
-        <f>Параметры!$B$11+49</f>
+        <f>Параметры!$B$9+49</f>
         <v>46321</v>
       </c>
       <c r="G44" s="21">
-        <f>Параметры!$B$11+74</f>
+        <f>Параметры!$B$9+74</f>
         <v>46346</v>
       </c>
       <c r="H44" s="21">
@@ -3375,7 +3341,7 @@
         <v>6</v>
       </c>
       <c r="N44" s="22">
-        <f>Параметры!$B$22*M44</f>
+        <f>Параметры!$B$20*M44</f>
         <v>69090</v>
       </c>
       <c r="O44" s="22" t="n">
@@ -3401,11 +3367,11 @@
       <c r="D45" s="26" t="n"/>
       <c r="E45" s="26" t="n"/>
       <c r="F45" s="27">
-        <f>Параметры!$B$11+49</f>
+        <f>Параметры!$B$9+49</f>
         <v>46321</v>
       </c>
       <c r="G45" s="27">
-        <f>Параметры!$B$11+53</f>
+        <f>Параметры!$B$9+53</f>
         <v>46325</v>
       </c>
       <c r="H45" s="26" t="n"/>
@@ -3443,11 +3409,11 @@
       <c r="D46" s="26" t="n"/>
       <c r="E46" s="26" t="n"/>
       <c r="F46" s="27">
-        <f>Параметры!$B$11+56</f>
+        <f>Параметры!$B$9+56</f>
         <v>46328</v>
       </c>
       <c r="G46" s="27">
-        <f>Параметры!$B$11+67</f>
+        <f>Параметры!$B$9+67</f>
         <v>46339</v>
       </c>
       <c r="H46" s="26" t="n"/>
@@ -3486,11 +3452,11 @@
       <c r="D47" s="26" t="n"/>
       <c r="E47" s="26" t="n"/>
       <c r="F47" s="27">
-        <f>Параметры!$B$11+70</f>
+        <f>Параметры!$B$9+70</f>
         <v>46342</v>
       </c>
       <c r="G47" s="27">
-        <f>Параметры!$B$11+74</f>
+        <f>Параметры!$B$9+74</f>
         <v>46346</v>
       </c>
       <c r="H47" s="26" t="n"/>
@@ -3536,11 +3502,11 @@
       </c>
       <c r="E48" s="20" t="n"/>
       <c r="F48" s="21">
-        <f>Параметры!$B$11+35</f>
+        <f>Параметры!$B$9+35</f>
         <v>46307</v>
       </c>
       <c r="G48" s="21">
-        <f>Параметры!$B$11+81</f>
+        <f>Параметры!$B$9+81</f>
         <v>46353</v>
       </c>
       <c r="H48" s="21">
@@ -3567,7 +3533,7 @@
         <v>12</v>
       </c>
       <c r="N48" s="22">
-        <f>Параметры!$B$22*M48</f>
+        <f>Параметры!$B$20*M48</f>
         <v>138180</v>
       </c>
       <c r="O48" s="22" t="n">
@@ -3596,11 +3562,11 @@
       <c r="D49" s="26" t="n"/>
       <c r="E49" s="26" t="n"/>
       <c r="F49" s="27">
-        <f>Параметры!$B$11+35</f>
+        <f>Параметры!$B$9+35</f>
         <v>46307</v>
       </c>
       <c r="G49" s="27">
-        <f>Параметры!$B$11+60</f>
+        <f>Параметры!$B$9+60</f>
         <v>46332</v>
       </c>
       <c r="H49" s="26" t="n"/>
@@ -3641,11 +3607,11 @@
       <c r="D50" s="26" t="n"/>
       <c r="E50" s="26" t="n"/>
       <c r="F50" s="27">
-        <f>Параметры!$B$11+42</f>
+        <f>Параметры!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G50" s="27">
-        <f>Параметры!$B$11+60</f>
+        <f>Параметры!$B$9+60</f>
         <v>46332</v>
       </c>
       <c r="H50" s="26" t="n"/>
@@ -3685,11 +3651,11 @@
       <c r="D51" s="26" t="n"/>
       <c r="E51" s="26" t="n"/>
       <c r="F51" s="27">
-        <f>Параметры!$B$11+63</f>
+        <f>Параметры!$B$9+63</f>
         <v>46335</v>
       </c>
       <c r="G51" s="27">
-        <f>Параметры!$B$11+74</f>
+        <f>Параметры!$B$9+74</f>
         <v>46346</v>
       </c>
       <c r="H51" s="26" t="n"/>
@@ -3728,11 +3694,11 @@
       <c r="D52" s="26" t="n"/>
       <c r="E52" s="26" t="n"/>
       <c r="F52" s="27">
-        <f>Параметры!$B$11+70</f>
+        <f>Параметры!$B$9+70</f>
         <v>46342</v>
       </c>
       <c r="G52" s="27">
-        <f>Параметры!$B$11+81</f>
+        <f>Параметры!$B$9+81</f>
         <v>46353</v>
       </c>
       <c r="H52" s="26" t="n"/>
@@ -3771,11 +3737,11 @@
       <c r="D53" s="26" t="n"/>
       <c r="E53" s="26" t="n"/>
       <c r="F53" s="27">
-        <f>Параметры!$B$11+63</f>
+        <f>Параметры!$B$9+63</f>
         <v>46335</v>
       </c>
       <c r="G53" s="27">
-        <f>Параметры!$B$11+81</f>
+        <f>Параметры!$B$9+81</f>
         <v>46353</v>
       </c>
       <c r="H53" s="26" t="n"/>
@@ -3860,11 +3826,11 @@
       </c>
       <c r="E55" s="20" t="n"/>
       <c r="F55" s="21">
-        <f>Параметры!$B$11+84</f>
+        <f>Параметры!$B$9+84</f>
         <v>46356</v>
       </c>
       <c r="G55" s="21">
-        <f>Параметры!$B$11+95</f>
+        <f>Параметры!$B$9+95</f>
         <v>46367</v>
       </c>
       <c r="H55" s="21">
@@ -3891,7 +3857,7 @@
         <v>8</v>
       </c>
       <c r="N55" s="22">
-        <f>Параметры!$B$22*M55</f>
+        <f>Параметры!$B$20*M55</f>
         <v>92120</v>
       </c>
       <c r="O55" s="22" t="n">
@@ -3915,11 +3881,11 @@
       <c r="D56" s="26" t="n"/>
       <c r="E56" s="26" t="n"/>
       <c r="F56" s="27">
-        <f>Параметры!$B$11+84</f>
+        <f>Параметры!$B$9+84</f>
         <v>46356</v>
       </c>
       <c r="G56" s="27">
-        <f>Параметры!$B$11+88</f>
+        <f>Параметры!$B$9+88</f>
         <v>46360</v>
       </c>
       <c r="H56" s="26" t="n"/>
@@ -3957,11 +3923,11 @@
       <c r="D57" s="26" t="n"/>
       <c r="E57" s="26" t="n"/>
       <c r="F57" s="27">
-        <f>Параметры!$B$11+84</f>
+        <f>Параметры!$B$9+84</f>
         <v>46356</v>
       </c>
       <c r="G57" s="27">
-        <f>Параметры!$B$11+88</f>
+        <f>Параметры!$B$9+88</f>
         <v>46360</v>
       </c>
       <c r="H57" s="26" t="n"/>
@@ -3999,11 +3965,11 @@
       <c r="D58" s="26" t="n"/>
       <c r="E58" s="26" t="n"/>
       <c r="F58" s="27">
-        <f>Параметры!$B$11+84</f>
+        <f>Параметры!$B$9+84</f>
         <v>46356</v>
       </c>
       <c r="G58" s="27">
-        <f>Параметры!$B$11+88</f>
+        <f>Параметры!$B$9+88</f>
         <v>46360</v>
       </c>
       <c r="H58" s="26" t="n"/>
@@ -4041,11 +4007,11 @@
       <c r="D59" s="26" t="n"/>
       <c r="E59" s="26" t="n"/>
       <c r="F59" s="27">
-        <f>Параметры!$B$11+91</f>
+        <f>Параметры!$B$9+91</f>
         <v>46363</v>
       </c>
       <c r="G59" s="27">
-        <f>Параметры!$B$11+95</f>
+        <f>Параметры!$B$9+95</f>
         <v>46367</v>
       </c>
       <c r="H59" s="26" t="n"/>
@@ -4083,11 +4049,11 @@
       <c r="D60" s="26" t="n"/>
       <c r="E60" s="26" t="n"/>
       <c r="F60" s="27">
-        <f>Параметры!$B$11+91</f>
+        <f>Параметры!$B$9+91</f>
         <v>46363</v>
       </c>
       <c r="G60" s="27">
-        <f>Параметры!$B$11+95</f>
+        <f>Параметры!$B$9+95</f>
         <v>46367</v>
       </c>
       <c r="H60" s="26" t="n"/>
@@ -4133,11 +4099,11 @@
       </c>
       <c r="E61" s="20" t="n"/>
       <c r="F61" s="21">
-        <f>Параметры!$B$11+91</f>
+        <f>Параметры!$B$9+91</f>
         <v>46363</v>
       </c>
       <c r="G61" s="21">
-        <f>Параметры!$B$11+102</f>
+        <f>Параметры!$B$9+102</f>
         <v>46374</v>
       </c>
       <c r="H61" s="21">
@@ -4164,7 +4130,7 @@
         <v>6</v>
       </c>
       <c r="N61" s="22">
-        <f>Параметры!$B$22*M61</f>
+        <f>Параметры!$B$20*M61</f>
         <v>69090</v>
       </c>
       <c r="O61" s="22" t="n">
@@ -4188,11 +4154,11 @@
       <c r="D62" s="26" t="n"/>
       <c r="E62" s="26" t="n"/>
       <c r="F62" s="27">
-        <f>Параметры!$B$11+91</f>
+        <f>Параметры!$B$9+91</f>
         <v>46363</v>
       </c>
       <c r="G62" s="27">
-        <f>Параметры!$B$11+102</f>
+        <f>Параметры!$B$9+102</f>
         <v>46374</v>
       </c>
       <c r="H62" s="26" t="n"/>
@@ -4231,11 +4197,11 @@
       <c r="D63" s="26" t="n"/>
       <c r="E63" s="26" t="n"/>
       <c r="F63" s="27">
-        <f>Параметры!$B$11+98</f>
+        <f>Параметры!$B$9+98</f>
         <v>46370</v>
       </c>
       <c r="G63" s="27">
-        <f>Параметры!$B$11+102</f>
+        <f>Параметры!$B$9+102</f>
         <v>46374</v>
       </c>
       <c r="H63" s="26" t="n"/>
@@ -4281,11 +4247,11 @@
       </c>
       <c r="E64" s="20" t="n"/>
       <c r="F64" s="21">
-        <f>Параметры!$B$11+91</f>
+        <f>Параметры!$B$9+91</f>
         <v>46363</v>
       </c>
       <c r="G64" s="21">
-        <f>Параметры!$B$11+109</f>
+        <f>Параметры!$B$9+109</f>
         <v>46381</v>
       </c>
       <c r="H64" s="21">
@@ -4312,7 +4278,7 @@
         <v>6</v>
       </c>
       <c r="N64" s="22">
-        <f>Параметры!$B$22*M64</f>
+        <f>Параметры!$B$20*M64</f>
         <v>69090</v>
       </c>
       <c r="O64" s="22" t="n">
@@ -4337,11 +4303,11 @@
       <c r="D65" s="26" t="n"/>
       <c r="E65" s="26" t="n"/>
       <c r="F65" s="27">
-        <f>Параметры!$B$11+91</f>
+        <f>Параметры!$B$9+91</f>
         <v>46363</v>
       </c>
       <c r="G65" s="27">
-        <f>Параметры!$B$11+109</f>
+        <f>Параметры!$B$9+109</f>
         <v>46381</v>
       </c>
       <c r="H65" s="26" t="n"/>
@@ -4381,11 +4347,11 @@
       <c r="D66" s="26" t="n"/>
       <c r="E66" s="26" t="n"/>
       <c r="F66" s="27">
-        <f>Параметры!$B$11+105</f>
+        <f>Параметры!$B$9+105</f>
         <v>46377</v>
       </c>
       <c r="G66" s="27">
-        <f>Параметры!$B$11+109</f>
+        <f>Параметры!$B$9+109</f>
         <v>46381</v>
       </c>
       <c r="H66" s="26" t="n"/>

--- a/docs/plan/dit-annual-plan.xlsx
+++ b/docs/plan/dit-annual-plan.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -800,372 +800,406 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
+          <t>Ставрополь</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ДОПУЩЕНИЕ. Воронеж выведен во второй этап и пилотом быть не может. Ростов к этому моменту уже узел — он вошёл в кластер при переносе центра. Из оставшихся Нижний Новгород крупнее (164) и единственный со станцией на консолидацию (ССЗ), то есть отрабатывает процедуру целиком.</t>
+          <t>Порядок ввода выносов: Ставрополь (пилот), затем Нижний Новгород, затем Славянск-на-Кубани. ВАЖНО ПОНИМАТЬ: у Ставрополя нет своей станции — его 74 абонента уже в общей базе, поэтому пилот проверяет кластер, каналы и провижининг, но НЕ проверяет перенос действующей АТС с её гашением. Эта часть процедуры впервые отрабатывается на Нижнем Новгороде (задача 8.1) — её стоит пройти с тем же вниманием, что и пилот.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>98</v>
+          <t>Оповещение техподдержки</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>задача 1.7</t>
+        </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>До начала работ согласован порядок: кто и по какому каналу поднимается по тревоге, за какое время и что считается инцидентом. Порядок роздан всем участникам работ — иначе в первую же нештатную ситуацию искать будет некого.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>68</v>
+          <t>Исполнитель организационных задач</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Задачи 9, 10, 12, 13 — консолидация мелких АТС и перенумерация. Инженер кластера на задачи 1–8 и 11 в файле не проставлен: ячейки оставлены жёлтыми под заполнение.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
+          <t>Трудозатраты всего, ч-д</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>11515</v>
+        <v>68</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B21" s="7">
-        <f>B17*B20</f>
-        <v>1128470</v>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>0</v>
+          <t>Внутренняя ставка, ₽/ч-д</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>11515</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>1255</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B23" s="7">
+        <f>B19*B22</f>
+        <v>1128470</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>12</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
+          <t>Абонентов в периметре</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>7</v>
+        <v>1255</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Арбитр garbd</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>не нужен</t>
-        </is>
+          <t>Узлов кластера после внедрения</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Голосов в кворуме</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>3</v>
+          <t>Арбитр garbd</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>не нужен</t>
+        </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>нельзя</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
+          <t>Размещение ВМ по хостам</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>проверить</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Панель управления FreePBX</t>
+          <t>Снимки ВМ как резервная копия</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ровно на одном узле</t>
+          <t>нельзя</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>Оба узла ЦОД — живые</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Панель управления FreePBX</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>21–25 декабря</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Заказчик</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Исполнитель</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Номер приказа / внутреннего проекта</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Присваивается при открытии проекта.</t>
+          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Дата протокола совещания</t>
+          <t>Исполнитель</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
+          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Адресный план узлов</t>
+          <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
+          <t>Присваивается при открытии проекта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Дата протокола совещания</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Проставить дату документа, из которого взята этапность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Адресный план узлов</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
           <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1182,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE67"/>
+  <dimension ref="A1:AE68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7" customWidth="1" min="1" max="1"/>
@@ -1221,7 +1255,7 @@
     <row r="1">
       <c r="B1" s="13" t="inlineStr">
         <is>
-          <t>Централизованная телефония на Asterisk с выносами в кластерах: Ростов (центр), Нижний Новгород, Славянск-на-Кубани, Москва, Воронеж</t>
+          <t>Централизованная телефония на Asterisk: центр в московском ЦОД (два зала), выносы — Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж</t>
         </is>
       </c>
       <c r="P1" s="14" t="inlineStr">
@@ -1462,11 +1496,11 @@
       </c>
       <c r="E4" s="20" t="n"/>
       <c r="F4" s="21">
-        <f>Параметры!$B$9+0</f>
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G4" s="21">
-        <f>Параметры!$B$9+11</f>
+        <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H4" s="21">
@@ -1493,7 +1527,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="22">
-        <f>Параметры!$B$20*M4</f>
+        <f>'Параметры и допущения'!$B$22*M4</f>
         <v>92120</v>
       </c>
       <c r="O4" s="22" t="n">
@@ -1517,11 +1551,11 @@
       <c r="D5" s="26" t="n"/>
       <c r="E5" s="26" t="n"/>
       <c r="F5" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G5" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>'Параметры и допущения'!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H5" s="26" t="n"/>
@@ -1559,11 +1593,11 @@
       <c r="D6" s="26" t="n"/>
       <c r="E6" s="26" t="n"/>
       <c r="F6" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G6" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H6" s="26" t="n"/>
@@ -1602,11 +1636,11 @@
       <c r="D7" s="26" t="n"/>
       <c r="E7" s="26" t="n"/>
       <c r="F7" s="27">
-        <f>Параметры!$B$9+7</f>
+        <f>'Параметры и допущения'!$B$9+7</f>
         <v>46279</v>
       </c>
       <c r="G7" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H7" s="26" t="n"/>
@@ -1644,11 +1678,11 @@
       <c r="D8" s="26" t="n"/>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G8" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>'Параметры и допущения'!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H8" s="26" t="n"/>
@@ -1686,11 +1720,11 @@
       <c r="D9" s="26" t="n"/>
       <c r="E9" s="26" t="n"/>
       <c r="F9" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G9" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>'Параметры и допущения'!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H9" s="26" t="n"/>
@@ -1728,11 +1762,11 @@
       <c r="D10" s="26" t="n"/>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G10" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H10" s="26" t="n"/>
@@ -1749,7 +1783,7 @@
         </is>
       </c>
       <c r="M10" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="26" t="n"/>
       <c r="O10" s="26" t="n"/>
@@ -1757,137 +1791,137 @@
       <c r="Q10" s="23" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Согласовать порядок оповещения техподдержки при отклонениях</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="27">
+        <f>'Параметры и допущения'!$B$9+7</f>
+        <v>46279</v>
+      </c>
+      <c r="G11" s="27">
+        <f>'Параметры и допущения'!$B$9+11</f>
+        <v>46283</v>
+      </c>
+      <c r="H11" s="26" t="n"/>
+      <c r="I11" s="26" t="n"/>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>Известно, кто и по какому каналу поднимается по тревоге, за какое время и что считается инцидентом; порядок роздан всем участникам работ</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="26" t="n"/>
+      <c r="O11" s="26" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Смена учётных данных и защита периметра</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="21">
-        <f>Параметры!$B$9+0</f>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="21">
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
-      <c r="G11" s="21">
-        <f>Параметры!$B$9+11</f>
+      <c r="G12" s="21">
+        <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
-      <c r="H11" s="21">
-        <f>G11</f>
+      <c r="H12" s="21">
+        <f>G12</f>
         <v>46283</v>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>Учётные данные телефонии не менялись; журнал безопасности Asterisk не ведётся, подбор паролей не отслеживается</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>Пароли 444 абонентов, транков, AMI и базы данных сменены; включён журнал безопасности и блокировка подбора; восстановление из резервной копии проверено</t>
         </is>
       </c>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M11" s="19" t="n">
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="N11" s="22">
-        <f>Параметры!$B$20*M11</f>
+      <c r="N12" s="22">
+        <f>'Параметры и допущения'!$B$22*M12</f>
         <v>115150</v>
       </c>
-      <c r="O11" s="22" t="n">
+      <c r="O12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="23" t="n"/>
-      <c r="Q11" s="23" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>Включить журнал безопасности, fail2ban, ограничить доступ к AMI</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="27">
-        <f>Параметры!$B$9+0</f>
-        <v>46272</v>
-      </c>
-      <c r="G12" s="27">
-        <f>Параметры!$B$9+4</f>
-        <v>46276</v>
-      </c>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="inlineStr">
-        <is>
-          <t>Попытки подбора фиксируются и блокируются</t>
-        </is>
-      </c>
-      <c r="K12" s="28" t="n"/>
-      <c r="L12" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M12" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" s="26" t="n"/>
-      <c r="O12" s="26" t="n"/>
       <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="23" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Задать порядок идентификации абонентов и перечень кодеков</t>
+          <t>Включить журнал безопасности, fail2ban, ограничить доступ к AMI</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
       <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G13" s="27">
-        <f>Параметры!$B$9+4</f>
+        <f>'Параметры и допущения'!$B$9+4</f>
         <v>46276</v>
       </c>
       <c r="H13" s="26" t="n"/>
       <c r="I13" s="26" t="n"/>
       <c r="J13" s="26" t="inlineStr">
         <is>
-          <t>Идентификация по учётной записи, alaw первым кодеком</t>
+          <t>Попытки подбора фиксируются и блокируются</t>
         </is>
       </c>
       <c r="K13" s="28" t="n"/>
@@ -1897,7 +1931,7 @@
         </is>
       </c>
       <c r="M13" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="26" t="n"/>
       <c r="O13" s="26" t="n"/>
@@ -1906,30 +1940,30 @@
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Сменить пароли 444 абонентов</t>
+          <t>Задать порядок идентификации абонентов и перечень кодеков</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
       <c r="D14" s="26" t="n"/>
       <c r="E14" s="26" t="n"/>
       <c r="F14" s="27">
-        <f>Параметры!$B$9+0</f>
+        <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
       <c r="G14" s="27">
-        <f>Параметры!$B$9+11</f>
-        <v>46283</v>
+        <f>'Параметры и допущения'!$B$9+4</f>
+        <v>46276</v>
       </c>
       <c r="H14" s="26" t="n"/>
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="26" t="inlineStr">
         <is>
-          <t>Пароли сменены</t>
+          <t>Идентификация по учётной записи, alaw первым кодеком</t>
         </is>
       </c>
       <c r="K14" s="28" t="n"/>
@@ -1939,40 +1973,39 @@
         </is>
       </c>
       <c r="M14" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N14" s="26" t="n"/>
       <c r="O14" s="26" t="n"/>
       <c r="P14" s="23" t="n"/>
-      <c r="Q14" s="23" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>Сменить учётные данные транков, AMI и базы данных</t>
+          <t>Сменить пароли 444 абонентов</t>
         </is>
       </c>
       <c r="C15" s="26" t="n"/>
       <c r="D15" s="26" t="n"/>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="27">
-        <f>Параметры!$B$9+7</f>
-        <v>46279</v>
+        <f>'Параметры и допущения'!$B$9+0</f>
+        <v>46272</v>
       </c>
       <c r="G15" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H15" s="26" t="n"/>
       <c r="I15" s="26" t="n"/>
       <c r="J15" s="26" t="inlineStr">
         <is>
-          <t>Учётные данные сменены</t>
+          <t>Пароли сменены</t>
         </is>
       </c>
       <c r="K15" s="28" t="n"/>
@@ -1982,39 +2015,40 @@
         </is>
       </c>
       <c r="M15" s="26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" s="26" t="n"/>
       <c r="O15" s="26" t="n"/>
+      <c r="P15" s="23" t="n"/>
       <c r="Q15" s="23" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Пересобрать конфигурации телефонов</t>
+          <t>Сменить учётные данные транков, AMI и базы данных</t>
         </is>
       </c>
       <c r="C16" s="26" t="n"/>
       <c r="D16" s="26" t="n"/>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="27">
-        <f>Параметры!$B$9+7</f>
+        <f>'Параметры и допущения'!$B$9+7</f>
         <v>46279</v>
       </c>
       <c r="G16" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H16" s="26" t="n"/>
       <c r="I16" s="26" t="n"/>
       <c r="J16" s="26" t="inlineStr">
         <is>
-          <t>Телефоны работают с новыми паролями</t>
+          <t>Учётные данные сменены</t>
         </is>
       </c>
       <c r="K16" s="28" t="n"/>
@@ -2024,7 +2058,7 @@
         </is>
       </c>
       <c r="M16" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" s="26" t="n"/>
       <c r="O16" s="26" t="n"/>
@@ -2033,30 +2067,30 @@
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>Проверить восстановление из резервной копии на тестовой машине</t>
+          <t>Пересобрать конфигурации телефонов</t>
         </is>
       </c>
       <c r="C17" s="26" t="n"/>
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="26" t="n"/>
       <c r="F17" s="27">
-        <f>Параметры!$B$9+7</f>
+        <f>'Параметры и допущения'!$B$9+7</f>
         <v>46279</v>
       </c>
       <c r="G17" s="27">
-        <f>Параметры!$B$9+11</f>
+        <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
       <c r="H17" s="26" t="n"/>
       <c r="I17" s="26" t="n"/>
       <c r="J17" s="26" t="inlineStr">
         <is>
-          <t>Копия развёрнута и проверена</t>
+          <t>Телефоны работают с новыми паролями</t>
         </is>
       </c>
       <c r="K17" s="28" t="n"/>
@@ -2073,136 +2107,136 @@
       <c r="Q17" s="23" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Проверить восстановление из резервной копии на тестовой машине</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="27">
+        <f>'Параметры и допущения'!$B$9+7</f>
+        <v>46279</v>
+      </c>
+      <c r="G18" s="27">
+        <f>'Параметры и допущения'!$B$9+11</f>
+        <v>46283</v>
+      </c>
+      <c r="H18" s="26" t="n"/>
+      <c r="I18" s="26" t="n"/>
+      <c r="J18" s="26" t="inlineStr">
+        <is>
+          <t>Копия развёрнута и проверена</t>
+        </is>
+      </c>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="26" t="n"/>
+      <c r="O18" s="26" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Испытательный стенд</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="21">
-        <f>Параметры!$B$9+14</f>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="21">
+        <f>'Параметры и допущения'!$B$9+14</f>
         <v>46286</v>
       </c>
-      <c r="G18" s="21">
-        <f>Параметры!$B$9+18</f>
+      <c r="G19" s="21">
+        <f>'Параметры и допущения'!$B$9+18</f>
         <v>46290</v>
       </c>
-      <c r="H18" s="21">
-        <f>G18</f>
+      <c r="H19" s="21">
+        <f>G19</f>
         <v>46290</v>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>Процедуры восстановления кластера и передачи роли мастера ни разу не выполнялись</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="J19" s="19" t="inlineStr">
         <is>
           <t>Стенд из трёх машин прошёл чек-лист приёмки: клонирование, восстановление кворума и передача роли мастера выполнены руками</t>
         </is>
       </c>
-      <c r="K18" s="20" t="n"/>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M18" s="19" t="n">
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M19" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N18" s="22">
-        <f>Параметры!$B$20*M18</f>
+      <c r="N19" s="22">
+        <f>'Параметры и допущения'!$B$22*M19</f>
         <v>69090</v>
       </c>
-      <c r="O18" s="22" t="n">
+      <c r="O19" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R18" s="23" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>Развернуть тестовый мастер и клонировать его в два узла</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="27">
-        <f>Параметры!$B$9+14</f>
-        <v>46286</v>
-      </c>
-      <c r="G19" s="27">
-        <f>Параметры!$B$9+18</f>
-        <v>46290</v>
-      </c>
-      <c r="H19" s="26" t="n"/>
-      <c r="I19" s="26" t="n"/>
-      <c r="J19" s="26" t="inlineStr">
-        <is>
-          <t>Клоны вступили в кластер, конфликтов имён узлов нет</t>
-        </is>
-      </c>
-      <c r="K19" s="28" t="n"/>
-      <c r="L19" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M19" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" s="26" t="n"/>
-      <c r="O19" s="26" t="n"/>
       <c r="R19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Отработать передачу роли мастера между двумя узлами</t>
+          <t>Развернуть тестовый мастер и клонировать его в два узла</t>
         </is>
       </c>
       <c r="C20" s="26" t="n"/>
       <c r="D20" s="26" t="n"/>
       <c r="E20" s="26" t="n"/>
       <c r="F20" s="27">
-        <f>Параметры!$B$9+14</f>
+        <f>'Параметры и допущения'!$B$9+14</f>
         <v>46286</v>
       </c>
       <c r="G20" s="27">
-        <f>Параметры!$B$9+18</f>
+        <f>'Параметры и допущения'!$B$9+18</f>
         <v>46290</v>
       </c>
       <c r="H20" s="26" t="n"/>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="26" t="inlineStr">
         <is>
-          <t>Процедура выполнена в обе стороны и задокументирована</t>
+          <t>Клоны вступили в кластер, конфликтов имён узлов нет</t>
         </is>
       </c>
       <c r="K20" s="28" t="n"/>
@@ -2212,7 +2246,7 @@
         </is>
       </c>
       <c r="M20" s="26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" s="26" t="n"/>
       <c r="O20" s="26" t="n"/>
@@ -2221,30 +2255,30 @@
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>Отработать восстановление кворума</t>
+          <t>Отработать передачу роли мастера между двумя узлами</t>
         </is>
       </c>
       <c r="C21" s="26" t="n"/>
       <c r="D21" s="26" t="n"/>
       <c r="E21" s="26" t="n"/>
       <c r="F21" s="27">
-        <f>Параметры!$B$9+14</f>
+        <f>'Параметры и допущения'!$B$9+14</f>
         <v>46286</v>
       </c>
       <c r="G21" s="27">
-        <f>Параметры!$B$9+18</f>
+        <f>'Параметры и допущения'!$B$9+18</f>
         <v>46290</v>
       </c>
       <c r="H21" s="26" t="n"/>
       <c r="I21" s="26" t="n"/>
       <c r="J21" s="26" t="inlineStr">
         <is>
-          <t>Кворум восстановлен вручную</t>
+          <t>Процедура выполнена в обе стороны и задокументирована</t>
         </is>
       </c>
       <c r="K21" s="28" t="n"/>
@@ -2254,143 +2288,143 @@
         </is>
       </c>
       <c r="M21" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="26" t="n"/>
       <c r="O21" s="26" t="n"/>
       <c r="R21" s="23" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Отработать восстановление кворума</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="27">
+        <f>'Параметры и допущения'!$B$9+14</f>
+        <v>46286</v>
+      </c>
+      <c r="G22" s="27">
+        <f>'Параметры и допущения'!$B$9+18</f>
+        <v>46290</v>
+      </c>
+      <c r="H22" s="26" t="n"/>
+      <c r="I22" s="26" t="n"/>
+      <c r="J22" s="26" t="inlineStr">
+        <is>
+          <t>Кворум восстановлен вручную</t>
+        </is>
+      </c>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="26" t="n"/>
+      <c r="O22" s="26" t="n"/>
+      <c r="R22" s="23" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Ростовская АТС — первый узел кластера</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="21">
-        <f>Параметры!$B$9+21</f>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="21">
+        <f>'Параметры и допущения'!$B$9+21</f>
         <v>46293</v>
       </c>
-      <c r="G22" s="21">
-        <f>Параметры!$B$9+25</f>
+      <c r="G23" s="21">
+        <f>'Параметры и допущения'!$B$9+25</f>
         <v>46297</v>
       </c>
-      <c r="H22" s="21">
-        <f>G22</f>
+      <c r="H23" s="21">
+        <f>G23</f>
         <v>46297</v>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I23" s="19" t="inlineStr">
         <is>
           <t>Вся боевая база живёт на ростовской АТС; перенести её в ЦОД без простоя можно только через кластер</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J23" s="19" t="inlineStr">
         <is>
           <t>Ростовская АТС работает узлом кластера без переустановки; база готова к репликации в ЦОД</t>
         </is>
       </c>
-      <c r="K22" s="20" t="n"/>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M22" s="19" t="n">
+      <c r="K23" s="20" t="n"/>
+      <c r="L23" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M23" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N22" s="22">
-        <f>Параметры!$B$20*M22</f>
+      <c r="N23" s="22">
+        <f>'Параметры и допущения'!$B$22*M23</f>
         <v>46060</v>
       </c>
-      <c r="O22" s="22" t="n">
+      <c r="O23" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="23" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>Снять резервную копию, перевести таблицы и запустить репликацию</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="27">
-        <f>Параметры!$B$9+21</f>
-        <v>46293</v>
-      </c>
-      <c r="G23" s="27">
-        <f>Параметры!$B$9+25</f>
-        <v>46297</v>
-      </c>
-      <c r="H23" s="26" t="n"/>
-      <c r="I23" s="26" t="n"/>
-      <c r="J23" s="26" t="inlineStr">
-        <is>
-          <t>База работает в режиме кластера, число добавочных сошлось</t>
-        </is>
-      </c>
-      <c r="K23" s="28" t="n"/>
-      <c r="L23" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M23" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" s="26" t="n"/>
-      <c r="O23" s="26" t="n"/>
       <c r="S23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Выгрузить номера в общую базу и проверить</t>
+          <t>Снять резервную копию, перевести таблицы и запустить репликацию</t>
         </is>
       </c>
       <c r="C24" s="26" t="n"/>
       <c r="D24" s="26" t="n"/>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="27">
-        <f>Параметры!$B$9+21</f>
+        <f>'Параметры и допущения'!$B$9+21</f>
         <v>46293</v>
       </c>
       <c r="G24" s="27">
-        <f>Параметры!$B$9+25</f>
+        <f>'Параметры и допущения'!$B$9+25</f>
         <v>46297</v>
       </c>
       <c r="H24" s="26" t="n"/>
       <c r="I24" s="26" t="n"/>
       <c r="J24" s="26" t="inlineStr">
         <is>
-          <t>Абоненты видны из общей базы</t>
+          <t>База работает в режиме кластера, число добавочных сошлось</t>
         </is>
       </c>
       <c r="K24" s="28" t="n"/>
@@ -2400,7 +2434,7 @@
         </is>
       </c>
       <c r="M24" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N24" s="26" t="n"/>
       <c r="O24" s="26" t="n"/>
@@ -2409,30 +2443,30 @@
     <row r="25">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Наблюдение до переноса центра</t>
+          <t>Выгрузить номера в общую базу и проверить</t>
         </is>
       </c>
       <c r="C25" s="26" t="n"/>
       <c r="D25" s="26" t="n"/>
       <c r="E25" s="26" t="n"/>
       <c r="F25" s="27">
-        <f>Параметры!$B$9+21</f>
+        <f>'Параметры и допущения'!$B$9+21</f>
         <v>46293</v>
       </c>
       <c r="G25" s="27">
-        <f>Параметры!$B$9+25</f>
+        <f>'Параметры и допущения'!$B$9+25</f>
         <v>46297</v>
       </c>
       <c r="H25" s="26" t="n"/>
       <c r="I25" s="26" t="n"/>
       <c r="J25" s="26" t="inlineStr">
         <is>
-          <t>Отклонений не выявлено</t>
+          <t>Абоненты видны из общей базы</t>
         </is>
       </c>
       <c r="K25" s="28" t="n"/>
@@ -2449,137 +2483,137 @@
       <c r="S25" s="23" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Наблюдение до переноса центра</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="27">
+        <f>'Параметры и допущения'!$B$9+21</f>
+        <v>46293</v>
+      </c>
+      <c r="G26" s="27">
+        <f>'Параметры и допущения'!$B$9+25</f>
+        <v>46297</v>
+      </c>
+      <c r="H26" s="26" t="n"/>
+      <c r="I26" s="26" t="n"/>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>Отклонений не выявлено</t>
+        </is>
+      </c>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="26" t="n"/>
+      <c r="O26" s="26" t="n"/>
+      <c r="S26" s="23" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Центр в московском ЦОД: два живых узла в разных залах</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="21">
-        <f>Параметры!$B$9+28</f>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="21">
+        <f>'Параметры и допущения'!$B$9+28</f>
         <v>46300</v>
       </c>
-      <c r="G26" s="21">
-        <f>Параметры!$B$9+39</f>
+      <c r="G27" s="21">
+        <f>'Параметры и допущения'!$B$9+39</f>
         <v>46311</v>
       </c>
-      <c r="H26" s="21">
-        <f>G26</f>
+      <c r="H27" s="21">
+        <f>G27</f>
         <v>46311</v>
       </c>
-      <c r="I26" s="19" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>Управление и база сосредоточены на ростовской АТС — площадке без резервирования; по решению совещания центр переносится в ЦОД с копией во втором зале</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="J27" s="19" t="inlineStr">
         <is>
           <t>Два живых узла в разных залах ЦОД обслуживают вызовы, управление на ЦОД-1; Ростов понижен до выноса, 80 московских абонентов поделены между залами</t>
         </is>
       </c>
-      <c r="K26" s="20" t="n"/>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M26" s="19" t="n">
+      <c r="K27" s="20" t="n"/>
+      <c r="L27" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M27" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="N26" s="22">
-        <f>Параметры!$B$20*M26</f>
+      <c r="N27" s="22">
+        <f>'Параметры и допущения'!$B$22*M27</f>
         <v>115150</v>
       </c>
-      <c r="O26" s="22" t="n">
+      <c r="O27" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="23" t="n"/>
-      <c r="U26" s="23" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>Клонировать ростовскую АТС в ЦОД-1, расшить клон в узел</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="27">
-        <f>Параметры!$B$9+28</f>
-        <v>46300</v>
-      </c>
-      <c r="G27" s="27">
-        <f>Параметры!$B$9+32</f>
-        <v>46304</v>
-      </c>
-      <c r="H27" s="26" t="n"/>
-      <c r="I27" s="26" t="n"/>
-      <c r="J27" s="26" t="inlineStr">
-        <is>
-          <t>ЦОД-1 в кластере, синхронизирован</t>
-        </is>
-      </c>
-      <c r="K27" s="28" t="n"/>
-      <c r="L27" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M27" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" s="26" t="n"/>
-      <c r="O27" s="26" t="n"/>
       <c r="T27" s="23" t="n"/>
+      <c r="U27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Передать роль мастера с Ростова на ЦОД-1</t>
+          <t>Клонировать ростовскую АТС в ЦОД-1, расшить клон в узел</t>
         </is>
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="26" t="n"/>
       <c r="E28" s="26" t="n"/>
       <c r="F28" s="27">
-        <f>Параметры!$B$9+28</f>
+        <f>'Параметры и допущения'!$B$9+28</f>
         <v>46300</v>
       </c>
       <c r="G28" s="27">
-        <f>Параметры!$B$9+32</f>
+        <f>'Параметры и допущения'!$B$9+32</f>
         <v>46304</v>
       </c>
       <c r="H28" s="26" t="n"/>
       <c r="I28" s="26" t="n"/>
       <c r="J28" s="26" t="inlineStr">
         <is>
-          <t>FreePBX и управление работают из ЦОД-1</t>
+          <t>ЦОД-1 в кластере, синхронизирован</t>
         </is>
       </c>
       <c r="K28" s="28" t="n"/>
@@ -2598,30 +2632,30 @@
     <row r="29">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>Клонировать ЦОД-1 в ЦОД-2 (второй зал), расшить клон в узел</t>
+          <t>Передать роль мастера с Ростова на ЦОД-1</t>
         </is>
       </c>
       <c r="C29" s="26" t="n"/>
       <c r="D29" s="26" t="n"/>
       <c r="E29" s="26" t="n"/>
       <c r="F29" s="27">
-        <f>Параметры!$B$9+35</f>
-        <v>46307</v>
+        <f>'Параметры и допущения'!$B$9+28</f>
+        <v>46300</v>
       </c>
       <c r="G29" s="27">
-        <f>Параметры!$B$9+39</f>
-        <v>46311</v>
+        <f>'Параметры и допущения'!$B$9+32</f>
+        <v>46304</v>
       </c>
       <c r="H29" s="26" t="n"/>
       <c r="I29" s="26" t="n"/>
       <c r="J29" s="26" t="inlineStr">
         <is>
-          <t>ЦОД-2 в кластере, узлов три — кворум нечётный</t>
+          <t>FreePBX и управление работают из ЦОД-1</t>
         </is>
       </c>
       <c r="K29" s="28" t="n"/>
@@ -2635,35 +2669,35 @@
       </c>
       <c r="N29" s="26" t="n"/>
       <c r="O29" s="26" t="n"/>
-      <c r="U29" s="23" t="n"/>
+      <c r="T29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Сделать ЦОД-2 живым узлом: транк оператора, FreePBX оставить выключенным</t>
+          <t>Клонировать ЦОД-1 в ЦОД-2 (второй зал), расшить клон в узел</t>
         </is>
       </c>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="26" t="n"/>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="27">
-        <f>Параметры!$B$9+35</f>
+        <f>'Параметры и допущения'!$B$9+35</f>
         <v>46307</v>
       </c>
       <c r="G30" s="27">
-        <f>Параметры!$B$9+39</f>
+        <f>'Параметры и допущения'!$B$9+39</f>
         <v>46311</v>
       </c>
       <c r="H30" s="26" t="n"/>
       <c r="I30" s="26" t="n"/>
       <c r="J30" s="26" t="inlineStr">
         <is>
-          <t>ЦОД-2 несёт вызовы наравне с ЦОД-1; панель управления включена ровно на одном узле</t>
+          <t>ЦОД-2 в кластере, узлов три — кворум нечётный</t>
         </is>
       </c>
       <c r="K30" s="28" t="n"/>
@@ -2682,30 +2716,30 @@
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Понизить Ростов до выноса, поделить 80 московских абонентов между залами</t>
+          <t>Сделать ЦОД-2 живым узлом: транк оператора, FreePBX оставить выключенным</t>
         </is>
       </c>
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="27">
-        <f>Параметры!$B$9+35</f>
+        <f>'Параметры и допущения'!$B$9+35</f>
         <v>46307</v>
       </c>
       <c r="G31" s="27">
-        <f>Параметры!$B$9+39</f>
+        <f>'Параметры и допущения'!$B$9+39</f>
         <v>46311</v>
       </c>
       <c r="H31" s="26" t="n"/>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="26" t="inlineStr">
         <is>
-          <t>По 40 абонентов на зал, каждый зал прописан другому резервным</t>
+          <t>ЦОД-2 несёт вызовы наравне с ЦОД-1; панель управления включена ровно на одном узле</t>
         </is>
       </c>
       <c r="K31" s="28" t="n"/>
@@ -2722,137 +2756,137 @@
       <c r="U31" s="23" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>Понизить Ростов до выноса, поделить 80 московских абонентов между залами</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="27">
+        <f>'Параметры и допущения'!$B$9+35</f>
+        <v>46307</v>
+      </c>
+      <c r="G32" s="27">
+        <f>'Параметры и допущения'!$B$9+39</f>
+        <v>46311</v>
+      </c>
+      <c r="H32" s="26" t="n"/>
+      <c r="I32" s="26" t="n"/>
+      <c r="J32" s="26" t="inlineStr">
+        <is>
+          <t>По 40 абонентов на зал, каждый зал прописан другому резервным</t>
+        </is>
+      </c>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M32" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" s="26" t="n"/>
+      <c r="O32" s="26" t="n"/>
+      <c r="U32" s="23" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>Пилотный вынос — Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Пилотный вынос — Ставрополь</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="21">
-        <f>Параметры!$B$9+42</f>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="21">
+        <f>'Параметры и допущения'!$B$9+42</f>
         <v>46314</v>
       </c>
-      <c r="G32" s="21">
-        <f>Параметры!$B$9+53</f>
+      <c r="G33" s="21">
+        <f>'Параметры и допущения'!$B$9+53</f>
         <v>46325</v>
       </c>
-      <c r="H32" s="21">
-        <f>G32</f>
+      <c r="H33" s="21">
+        <f>G33</f>
         <v>46325</v>
       </c>
-      <c r="I32" s="19" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
         <is>
           <t>Схема «центр в ЦОД — вынос в городе» не проверена на реальной нагрузке и канале</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr">
-        <is>
-          <t>Нижний Новгород работает выносом: локальная регистрация телефонов, свой выход в город, переключение на ЦОД при отказе площадки</t>
-        </is>
-      </c>
-      <c r="K32" s="20" t="n"/>
-      <c r="L32" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M32" s="19" t="n">
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>Ставрополь работает выносом: локальная регистрация телефонов, свой выход в город, переключение в ЦОД при отказе площадки; его 74 абонента больше не зависят от канала до Ростова</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="n"/>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M33" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="N32" s="22">
-        <f>Параметры!$B$20*M32</f>
+      <c r="N33" s="22">
+        <f>'Параметры и допущения'!$B$22*M33</f>
         <v>115150</v>
       </c>
-      <c r="O32" s="22" t="n">
+      <c r="O33" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="23" t="n"/>
-      <c r="W32" s="23" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>Клонировать мастер и расшить клон в вынос</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="27">
-        <f>Параметры!$B$9+42</f>
-        <v>46314</v>
-      </c>
-      <c r="G33" s="27">
-        <f>Параметры!$B$9+46</f>
-        <v>46318</v>
-      </c>
-      <c r="H33" s="26" t="n"/>
-      <c r="I33" s="26" t="n"/>
-      <c r="J33" s="26" t="inlineStr">
-        <is>
-          <t>Вынос в кластере</t>
-        </is>
-      </c>
-      <c r="K33" s="28" t="n"/>
-      <c r="L33" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M33" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" s="26" t="n"/>
-      <c r="O33" s="26" t="n"/>
       <c r="V33" s="23" t="n"/>
+      <c r="W33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Настроить межузловые транки и перенести диалплан</t>
+          <t>Клонировать мастер и расшить клон в вынос</t>
         </is>
       </c>
       <c r="C34" s="26" t="n"/>
       <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="27">
-        <f>Параметры!$B$9+42</f>
+        <f>'Параметры и допущения'!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G34" s="27">
-        <f>Параметры!$B$9+46</f>
+        <f>'Параметры и допущения'!$B$9+46</f>
         <v>46318</v>
       </c>
       <c r="H34" s="26" t="n"/>
       <c r="I34" s="26" t="n"/>
       <c r="J34" s="26" t="inlineStr">
         <is>
-          <t>Вызовы между ЦОД, Ростовом и Нижним Новгородом проходят</t>
+          <t>Вынос в кластере</t>
         </is>
       </c>
       <c r="K34" s="28" t="n"/>
@@ -2871,30 +2905,30 @@
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>Подключить локальный транк оператора</t>
+          <t>Настроить межузловые транки и перенести диалплан</t>
         </is>
       </c>
       <c r="C35" s="26" t="n"/>
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="26" t="n"/>
       <c r="F35" s="27">
-        <f>Параметры!$B$9+42</f>
+        <f>'Параметры и допущения'!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G35" s="27">
-        <f>Параметры!$B$9+46</f>
+        <f>'Параметры и допущения'!$B$9+46</f>
         <v>46318</v>
       </c>
       <c r="H35" s="26" t="n"/>
       <c r="I35" s="26" t="n"/>
       <c r="J35" s="26" t="inlineStr">
         <is>
-          <t>Свой выход в город работает</t>
+          <t>Вызовы между ЦОД, Ростовом и Ставрополем проходят</t>
         </is>
       </c>
       <c r="K35" s="28" t="n"/>
@@ -2904,7 +2938,7 @@
         </is>
       </c>
       <c r="M35" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="26" t="n"/>
       <c r="O35" s="26" t="n"/>
@@ -2913,30 +2947,30 @@
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>Перевести телефоны на вынос через провижининг</t>
+          <t>Подключить локальный транк оператора</t>
         </is>
       </c>
       <c r="C36" s="26" t="n"/>
       <c r="D36" s="26" t="n"/>
       <c r="E36" s="26" t="n"/>
       <c r="F36" s="27">
-        <f>Параметры!$B$9+42</f>
+        <f>'Параметры и допущения'!$B$9+42</f>
         <v>46314</v>
       </c>
       <c r="G36" s="27">
-        <f>Параметры!$B$9+46</f>
+        <f>'Параметры и допущения'!$B$9+46</f>
         <v>46318</v>
       </c>
       <c r="H36" s="26" t="n"/>
       <c r="I36" s="26" t="n"/>
       <c r="J36" s="26" t="inlineStr">
         <is>
-          <t>Телефоны регистрируются на площадке, резервный сервер — ЦОД-1</t>
+          <t>Свой выход в город работает</t>
         </is>
       </c>
       <c r="K36" s="28" t="n"/>
@@ -2946,7 +2980,7 @@
         </is>
       </c>
       <c r="M36" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N36" s="26" t="n"/>
       <c r="O36" s="26" t="n"/>
@@ -2955,30 +2989,30 @@
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>Неделя наблюдения под реальной нагрузкой</t>
+          <t>Перевести телефоны на вынос через провижининг</t>
         </is>
       </c>
       <c r="C37" s="26" t="n"/>
       <c r="D37" s="26" t="n"/>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="27">
-        <f>Параметры!$B$9+49</f>
-        <v>46321</v>
+        <f>'Параметры и допущения'!$B$9+42</f>
+        <v>46314</v>
       </c>
       <c r="G37" s="27">
-        <f>Параметры!$B$9+53</f>
-        <v>46325</v>
+        <f>'Параметры и допущения'!$B$9+46</f>
+        <v>46318</v>
       </c>
       <c r="H37" s="26" t="n"/>
       <c r="I37" s="26" t="n"/>
       <c r="J37" s="26" t="inlineStr">
         <is>
-          <t>Отказ площадки и возврат отработаны, решение о тиражировании принято</t>
+          <t>Телефоны регистрируются в Ставрополе, резервный сервер — ЦОД-1</t>
         </is>
       </c>
       <c r="K37" s="28" t="n"/>
@@ -2988,143 +3022,143 @@
         </is>
       </c>
       <c r="M37" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" s="26" t="n"/>
       <c r="O37" s="26" t="n"/>
-      <c r="W37" s="23" t="n"/>
+      <c r="V37" s="23" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>Неделя наблюдения под реальной нагрузкой</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+      <c r="E38" s="26" t="n"/>
+      <c r="F38" s="27">
+        <f>'Параметры и допущения'!$B$9+49</f>
+        <v>46321</v>
+      </c>
+      <c r="G38" s="27">
+        <f>'Параметры и допущения'!$B$9+53</f>
+        <v>46325</v>
+      </c>
+      <c r="H38" s="26" t="n"/>
+      <c r="I38" s="26" t="n"/>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>Отказ площадки и возврат отработаны, решение о тиражировании принято</t>
+        </is>
+      </c>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" s="26" t="n"/>
+      <c r="O38" s="26" t="n"/>
+      <c r="W38" s="23" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>Учебное переключение управления между залами ЦОД</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="21">
-        <f>Параметры!$B$9+56</f>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="21">
+        <f>'Параметры и допущения'!$B$9+56</f>
         <v>46328</v>
       </c>
-      <c r="G38" s="21">
-        <f>Параметры!$B$9+60</f>
+      <c r="G39" s="21">
+        <f>'Параметры и допущения'!$B$9+60</f>
         <v>46332</v>
       </c>
-      <c r="H38" s="21">
-        <f>G38</f>
+      <c r="H39" s="21">
+        <f>G39</f>
         <v>46332</v>
       </c>
-      <c r="I38" s="19" t="inlineStr">
+      <c r="I39" s="19" t="inlineStr">
         <is>
           <t>Вызовы оба зала несут постоянно, но панель управления живёт на одном узле; её переключение не опробовано</t>
         </is>
       </c>
-      <c r="J38" s="19" t="inlineStr">
+      <c r="J39" s="19" t="inlineStr">
         <is>
           <t>Управление переведено в зал 2 и возвращено в зал 1 в согласованное окно; время переключения измерено и внесено в регламент</t>
         </is>
       </c>
-      <c r="K38" s="20" t="n"/>
-      <c r="L38" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M38" s="19" t="n">
+      <c r="K39" s="20" t="n"/>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M39" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="N38" s="22">
-        <f>Параметры!$B$20*M38</f>
+      <c r="N39" s="22">
+        <f>'Параметры и допущения'!$B$22*M39</f>
         <v>34545</v>
       </c>
-      <c r="O38" s="22" t="n">
+      <c r="O39" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="X38" s="23" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="inlineStr">
-        <is>
-          <t>Включить FreePBX на ЦОД-2, проверить управление и звонки</t>
-        </is>
-      </c>
-      <c r="C39" s="26" t="n"/>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="27">
-        <f>Параметры!$B$9+56</f>
-        <v>46328</v>
-      </c>
-      <c r="G39" s="27">
-        <f>Параметры!$B$9+60</f>
-        <v>46332</v>
-      </c>
-      <c r="H39" s="26" t="n"/>
-      <c r="I39" s="26" t="n"/>
-      <c r="J39" s="26" t="inlineStr">
-        <is>
-          <t>Управление работает из зала 2, вызовы не прерывались</t>
-        </is>
-      </c>
-      <c r="K39" s="28" t="n"/>
-      <c r="L39" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M39" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N39" s="26" t="n"/>
-      <c r="O39" s="26" t="n"/>
       <c r="X39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Вернуть управление в ЦОД-1, зафиксировать время переключения</t>
+          <t>Включить FreePBX на ЦОД-2, проверить управление и звонки</t>
         </is>
       </c>
       <c r="C40" s="26" t="n"/>
       <c r="D40" s="26" t="n"/>
       <c r="E40" s="26" t="n"/>
       <c r="F40" s="27">
-        <f>Параметры!$B$9+56</f>
+        <f>'Параметры и допущения'!$B$9+56</f>
         <v>46328</v>
       </c>
       <c r="G40" s="27">
-        <f>Параметры!$B$9+60</f>
+        <f>'Параметры и допущения'!$B$9+60</f>
         <v>46332</v>
       </c>
       <c r="H40" s="26" t="n"/>
       <c r="I40" s="26" t="n"/>
       <c r="J40" s="26" t="inlineStr">
         <is>
-          <t>Схема в штатном состоянии, норматив записан в регламент</t>
+          <t>Управление работает из зала 2, вызовы не прерывались</t>
         </is>
       </c>
       <c r="K40" s="28" t="n"/>
@@ -3134,144 +3168,144 @@
         </is>
       </c>
       <c r="M40" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N40" s="26" t="n"/>
       <c r="O40" s="26" t="n"/>
       <c r="X40" s="23" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Вернуть управление в ЦОД-1, зафиксировать время переключения</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="27">
+        <f>'Параметры и допущения'!$B$9+56</f>
+        <v>46328</v>
+      </c>
+      <c r="G41" s="27">
+        <f>'Параметры и допущения'!$B$9+60</f>
+        <v>46332</v>
+      </c>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="26" t="n"/>
+      <c r="J41" s="26" t="inlineStr">
+        <is>
+          <t>Схема в штатном состоянии, норматив записан в регламент</t>
+        </is>
+      </c>
+      <c r="K41" s="28" t="n"/>
+      <c r="L41" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="26" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="X41" s="23" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>Выносы Славянск-на-Кубани и Ставрополь</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Выносы Нижний Новгород и Славянск-на-Кубани</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="21">
-        <f>Параметры!$B$9+63</f>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="21">
+        <f>'Параметры и допущения'!$B$9+63</f>
         <v>46335</v>
       </c>
-      <c r="G41" s="21">
-        <f>Параметры!$B$9+74</f>
+      <c r="G42" s="21">
+        <f>'Параметры и допущения'!$B$9+74</f>
         <v>46346</v>
       </c>
-      <c r="H41" s="21">
-        <f>G41</f>
+      <c r="H42" s="21">
+        <f>G42</f>
         <v>46346</v>
       </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>Славянск-на-Кубани обслуживается отдельной станцией вне кластера; у Ставрополя своей станции нет вообще — его 74 абонента висят на ростовском сервере</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
-        <is>
-          <t>Обе площадки работают выносами: локальная регистрация телефонов, свой выход в город, переключение в ЦОД при отказе площадки</t>
-        </is>
-      </c>
-      <c r="K41" s="20" t="n"/>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M41" s="19" t="n">
+      <c r="I42" s="19" t="inlineStr">
+        <is>
+          <t>Обе площадки обслуживаются отдельными станциями вне кластера; на них впервые отрабатывается полный перенос с гашением старой АТС</t>
+        </is>
+      </c>
+      <c r="J42" s="19" t="inlineStr">
+        <is>
+          <t>Обе площадки работают выносами, старые станции выведены из эксплуатации</t>
+        </is>
+      </c>
+      <c r="K42" s="20" t="n"/>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M42" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="N41" s="22">
-        <f>Параметры!$B$20*M41</f>
+      <c r="N42" s="22">
+        <f>'Параметры и допущения'!$B$22*M42</f>
         <v>103635</v>
       </c>
-      <c r="O41" s="22" t="n">
+      <c r="O42" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Y41" s="23" t="n"/>
-      <c r="Z41" s="23" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>Славянск-на-Кубани — 140 абонентов, старая станция гасится</t>
-        </is>
-      </c>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="27">
-        <f>Параметры!$B$9+63</f>
-        <v>46335</v>
-      </c>
-      <c r="G42" s="27">
-        <f>Параметры!$B$9+67</f>
-        <v>46339</v>
-      </c>
-      <c r="H42" s="26" t="n"/>
-      <c r="I42" s="26" t="n"/>
-      <c r="J42" s="26" t="inlineStr">
-        <is>
-          <t>Вынос работает, станция выведена из эксплуатации</t>
-        </is>
-      </c>
-      <c r="K42" s="28" t="n"/>
-      <c r="L42" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M42" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="N42" s="26" t="n"/>
-      <c r="O42" s="26" t="n"/>
       <c r="Y42" s="23" t="n"/>
+      <c r="Z42" s="23" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>Ставрополь — 74 абонента, новый вынос вместо обслуживания из Ростова</t>
+          <t>Нижний Новгород — 164 абонента, старая станция гасится</t>
         </is>
       </c>
       <c r="C43" s="26" t="n"/>
       <c r="D43" s="26" t="n"/>
       <c r="E43" s="26" t="n"/>
       <c r="F43" s="27">
-        <f>Параметры!$B$9+70</f>
-        <v>46342</v>
+        <f>'Параметры и допущения'!$B$9+63</f>
+        <v>46335</v>
       </c>
       <c r="G43" s="27">
-        <f>Параметры!$B$9+74</f>
-        <v>46346</v>
+        <f>'Параметры и допущения'!$B$9+67</f>
+        <v>46339</v>
       </c>
       <c r="H43" s="26" t="n"/>
       <c r="I43" s="26" t="n"/>
       <c r="J43" s="26" t="inlineStr">
         <is>
-          <t>Вынос работает, ставропольцы больше не зависят от канала до Ростова</t>
+          <t>Вынос работает, станция выведена</t>
         </is>
       </c>
       <c r="K43" s="28" t="n"/>
@@ -3281,123 +3315,127 @@
         </is>
       </c>
       <c r="M43" s="26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N43" s="26" t="n"/>
       <c r="O43" s="26" t="n"/>
-      <c r="Z43" s="23" t="n"/>
+      <c r="Y43" s="23" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>Славянск-на-Кубани — 140 абонентов, старая станция гасится</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="26" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="27">
+        <f>'Параметры и допущения'!$B$9+70</f>
+        <v>46342</v>
+      </c>
+      <c r="G44" s="27">
+        <f>'Параметры и допущения'!$B$9+74</f>
+        <v>46346</v>
+      </c>
+      <c r="H44" s="26" t="n"/>
+      <c r="I44" s="26" t="n"/>
+      <c r="J44" s="26" t="inlineStr">
+        <is>
+          <t>Вынос работает, станция выведена; этап 1 закрыт</t>
+        </is>
+      </c>
+      <c r="K44" s="28" t="n"/>
+      <c r="L44" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M44" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N44" s="26" t="n"/>
+      <c r="O44" s="26" t="n"/>
+      <c r="Z44" s="23" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B44" s="19" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>Консолидация мелких АТС этапа 1</t>
         </is>
       </c>
-      <c r="C44" s="19" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D44" s="19" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="21">
-        <f>Параметры!$B$9+49</f>
+      <c r="E45" s="20" t="n"/>
+      <c r="F45" s="21">
+        <f>'Параметры и допущения'!$B$9+49</f>
         <v>46321</v>
       </c>
-      <c r="G44" s="21">
-        <f>Параметры!$B$9+74</f>
+      <c r="G45" s="21">
+        <f>'Параметры и допущения'!$B$9+74</f>
         <v>46346</v>
       </c>
-      <c r="H44" s="21">
-        <f>G44</f>
+      <c r="H45" s="21">
+        <f>G45</f>
         <v>46346</v>
       </c>
-      <c r="I44" s="19" t="inlineStr">
+      <c r="I45" s="19" t="inlineStr">
         <is>
           <t>Шесть станций на 127 абонентов дорого поддерживать и невыгодно включать в кластер отдельными узлами</t>
         </is>
       </c>
-      <c r="J44" s="19" t="inlineStr">
+      <c r="J45" s="19" t="inlineStr">
         <is>
           <t>Абоненты мелких станций переведены на выносы и в ЦОД, станции выведены из эксплуатации</t>
         </is>
       </c>
-      <c r="K44" s="20" t="n"/>
-      <c r="L44" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M44" s="19" t="n">
+      <c r="K45" s="19" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M45" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N44" s="22">
-        <f>Параметры!$B$20*M44</f>
+      <c r="N45" s="22">
+        <f>'Параметры и допущения'!$B$22*M45</f>
         <v>69090</v>
       </c>
-      <c r="O44" s="22" t="n">
+      <c r="O45" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="23" t="n"/>
-      <c r="X44" s="23" t="n"/>
-      <c r="Y44" s="23" t="n"/>
-      <c r="Z44" s="23" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="inlineStr">
-        <is>
-          <t>ССЗ — 39 абонентов — в Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C45" s="26" t="n"/>
-      <c r="D45" s="26" t="n"/>
-      <c r="E45" s="26" t="n"/>
-      <c r="F45" s="27">
-        <f>Параметры!$B$9+49</f>
-        <v>46321</v>
-      </c>
-      <c r="G45" s="27">
-        <f>Параметры!$B$9+53</f>
-        <v>46325</v>
-      </c>
-      <c r="H45" s="26" t="n"/>
-      <c r="I45" s="26" t="n"/>
-      <c r="J45" s="26" t="inlineStr">
-        <is>
-          <t>Станция выведена</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="n"/>
-      <c r="L45" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M45" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="26" t="n"/>
-      <c r="O45" s="26" t="n"/>
       <c r="W45" s="23" t="n"/>
+      <c r="X45" s="23" t="n"/>
+      <c r="Y45" s="23" t="n"/>
+      <c r="Z45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B46" s="25" t="inlineStr">
@@ -3409,12 +3447,12 @@
       <c r="D46" s="26" t="n"/>
       <c r="E46" s="26" t="n"/>
       <c r="F46" s="27">
-        <f>Параметры!$B$9+56</f>
-        <v>46328</v>
+        <f>'Параметры и допущения'!$B$9+49</f>
+        <v>46321</v>
       </c>
       <c r="G46" s="27">
-        <f>Параметры!$B$9+67</f>
-        <v>46339</v>
+        <f>'Параметры и допущения'!$B$9+60</f>
+        <v>46332</v>
       </c>
       <c r="H46" s="26" t="n"/>
       <c r="I46" s="26" t="n"/>
@@ -3423,7 +3461,11 @@
           <t>Станции выведены</t>
         </is>
       </c>
-      <c r="K46" s="28" t="n"/>
+      <c r="K46" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
       <c r="L46" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -3434,29 +3476,29 @@
       </c>
       <c r="N46" s="26" t="n"/>
       <c r="O46" s="26" t="n"/>
+      <c r="W46" s="23" t="n"/>
       <c r="X46" s="23" t="n"/>
-      <c r="Y46" s="23" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>Локальный PBX — 15 абонентов — в ЦОД</t>
+          <t>ССЗ — 39 абонентов — в Нижний Новгород</t>
         </is>
       </c>
       <c r="C47" s="26" t="n"/>
       <c r="D47" s="26" t="n"/>
       <c r="E47" s="26" t="n"/>
       <c r="F47" s="27">
-        <f>Параметры!$B$9+70</f>
+        <f>'Параметры и допущения'!$B$9+70</f>
         <v>46342</v>
       </c>
       <c r="G47" s="27">
-        <f>Параметры!$B$9+74</f>
+        <f>'Параметры и допущения'!$B$9+74</f>
         <v>46346</v>
       </c>
       <c r="H47" s="26" t="n"/>
@@ -3466,152 +3508,161 @@
           <t>Станция выведена</t>
         </is>
       </c>
-      <c r="K47" s="28" t="n"/>
+      <c r="K47" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
       <c r="L47" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M47" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N47" s="26" t="n"/>
       <c r="O47" s="26" t="n"/>
       <c r="Z47" s="23" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="inlineStr">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>Локальный PBX — 15 абонентов — в ЦОД</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="n"/>
+      <c r="D48" s="26" t="n"/>
+      <c r="E48" s="26" t="n"/>
+      <c r="F48" s="27">
+        <f>'Параметры и допущения'!$B$9+77</f>
+        <v>46349</v>
+      </c>
+      <c r="G48" s="27">
+        <f>'Параметры и допущения'!$B$9+81</f>
+        <v>46353</v>
+      </c>
+      <c r="H48" s="26" t="n"/>
+      <c r="I48" s="26" t="n"/>
+      <c r="J48" s="26" t="inlineStr">
+        <is>
+          <t>Станция выведена</t>
+        </is>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="26" t="n"/>
+      <c r="O48" s="26" t="n"/>
+      <c r="AA48" s="23" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Перевод абонентов этапа 1 на единый план нумерации</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D48" s="19" t="inlineStr">
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E48" s="20" t="n"/>
-      <c r="F48" s="21">
-        <f>Параметры!$B$9+35</f>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="21">
+        <f>'Параметры и допущения'!$B$9+35</f>
         <v>46307</v>
       </c>
-      <c r="G48" s="21">
-        <f>Параметры!$B$9+81</f>
+      <c r="G49" s="21">
+        <f>'Параметры и допущения'!$B$9+81</f>
         <v>46353</v>
       </c>
-      <c r="H48" s="21">
-        <f>G48</f>
+      <c r="H49" s="21">
+        <f>G49</f>
         <v>46353</v>
       </c>
-      <c r="I48" s="19" t="inlineStr">
+      <c r="I49" s="19" t="inlineStr">
         <is>
           <t>Станции используют пересекающиеся номера, единый план невозможен без разведения конфликтов</t>
         </is>
       </c>
-      <c r="J48" s="19" t="inlineStr">
+      <c r="J49" s="19" t="inlineStr">
         <is>
           <t>810 абонентов этапа 1 переведены на пятизначную нумерацию, переадресации сняты</t>
         </is>
       </c>
-      <c r="K48" s="20" t="n"/>
-      <c r="L48" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M48" s="19" t="n">
+      <c r="K49" s="19" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M49" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="N48" s="22">
-        <f>Параметры!$B$20*M48</f>
+      <c r="N49" s="22">
+        <f>'Параметры и допущения'!$B$22*M49</f>
         <v>138180</v>
       </c>
-      <c r="O48" s="22" t="n">
+      <c r="O49" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="23" t="n"/>
-      <c r="V48" s="23" t="n"/>
-      <c r="W48" s="23" t="n"/>
-      <c r="X48" s="23" t="n"/>
-      <c r="Y48" s="23" t="n"/>
-      <c r="Z48" s="23" t="n"/>
-      <c r="AA48" s="23" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="inlineStr">
-        <is>
-          <t>Ростов и его мелкие площадки — 352 абонента</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="n"/>
-      <c r="D49" s="26" t="n"/>
-      <c r="E49" s="26" t="n"/>
-      <c r="F49" s="27">
-        <f>Параметры!$B$9+35</f>
-        <v>46307</v>
-      </c>
-      <c r="G49" s="27">
-        <f>Параметры!$B$9+60</f>
-        <v>46332</v>
-      </c>
-      <c r="H49" s="26" t="n"/>
-      <c r="I49" s="26" t="n"/>
-      <c r="J49" s="26" t="inlineStr">
-        <is>
-          <t>Площадки переведены</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="n"/>
-      <c r="L49" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M49" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N49" s="26" t="n"/>
-      <c r="O49" s="26" t="n"/>
       <c r="U49" s="23" t="n"/>
       <c r="V49" s="23" t="n"/>
       <c r="W49" s="23" t="n"/>
       <c r="X49" s="23" t="n"/>
+      <c r="Y49" s="23" t="n"/>
+      <c r="Z49" s="23" t="n"/>
+      <c r="AA49" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>Нижний Новгород и ССЗ — 164 абонента</t>
+          <t>Ростов и его мелкие площадки — 352 абонента</t>
         </is>
       </c>
       <c r="C50" s="26" t="n"/>
       <c r="D50" s="26" t="n"/>
       <c r="E50" s="26" t="n"/>
       <c r="F50" s="27">
-        <f>Параметры!$B$9+42</f>
-        <v>46314</v>
+        <f>'Параметры и допущения'!$B$9+35</f>
+        <v>46307</v>
       </c>
       <c r="G50" s="27">
-        <f>Параметры!$B$9+60</f>
+        <f>'Параметры и допущения'!$B$9+60</f>
         <v>46332</v>
       </c>
       <c r="H50" s="26" t="n"/>
@@ -3621,17 +3672,22 @@
           <t>Площадки переведены</t>
         </is>
       </c>
-      <c r="K50" s="28" t="n"/>
+      <c r="K50" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
       <c r="L50" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M50" s="26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N50" s="26" t="n"/>
       <c r="O50" s="26" t="n"/>
+      <c r="U50" s="23" t="n"/>
       <c r="V50" s="23" t="n"/>
       <c r="W50" s="23" t="n"/>
       <c r="X50" s="23" t="n"/>
@@ -3639,24 +3695,24 @@
     <row r="51">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>Славянск-на-Кубани — 140 абонентов</t>
+          <t>Ставрополь — 74 абонента</t>
         </is>
       </c>
       <c r="C51" s="26" t="n"/>
       <c r="D51" s="26" t="n"/>
       <c r="E51" s="26" t="n"/>
       <c r="F51" s="27">
-        <f>Параметры!$B$9+63</f>
-        <v>46335</v>
+        <f>'Параметры и допущения'!$B$9+49</f>
+        <v>46321</v>
       </c>
       <c r="G51" s="27">
-        <f>Параметры!$B$9+74</f>
-        <v>46346</v>
+        <f>'Параметры и допущения'!$B$9+60</f>
+        <v>46332</v>
       </c>
       <c r="H51" s="26" t="n"/>
       <c r="I51" s="26" t="n"/>
@@ -3665,83 +3721,92 @@
           <t>Площадка переведена</t>
         </is>
       </c>
-      <c r="K51" s="28" t="n"/>
+      <c r="K51" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
       <c r="L51" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M51" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N51" s="26" t="n"/>
       <c r="O51" s="26" t="n"/>
-      <c r="Y51" s="23" t="n"/>
-      <c r="Z51" s="23" t="n"/>
+      <c r="W51" s="23" t="n"/>
+      <c r="X51" s="23" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>Ставрополь — 74 абонента</t>
+          <t>Нижний Новгород и ССЗ — 164 абонента</t>
         </is>
       </c>
       <c r="C52" s="26" t="n"/>
       <c r="D52" s="26" t="n"/>
       <c r="E52" s="26" t="n"/>
       <c r="F52" s="27">
-        <f>Параметры!$B$9+70</f>
-        <v>46342</v>
+        <f>'Параметры и допущения'!$B$9+63</f>
+        <v>46335</v>
       </c>
       <c r="G52" s="27">
-        <f>Параметры!$B$9+81</f>
+        <f>'Параметры и допущения'!$B$9+81</f>
         <v>46353</v>
       </c>
       <c r="H52" s="26" t="n"/>
       <c r="I52" s="26" t="n"/>
       <c r="J52" s="26" t="inlineStr">
         <is>
-          <t>Площадка переведена</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="n"/>
+          <t>Площадки переведены</t>
+        </is>
+      </c>
+      <c r="K52" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
       <c r="L52" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M52" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N52" s="26" t="n"/>
       <c r="O52" s="26" t="n"/>
+      <c r="Y52" s="23" t="n"/>
       <c r="Z52" s="23" t="n"/>
       <c r="AA52" s="23" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>Москва — 80 абонентов, снятие переадресаций</t>
+          <t>Славянск-на-Кубани — 140 абонентов</t>
         </is>
       </c>
       <c r="C53" s="26" t="n"/>
       <c r="D53" s="26" t="n"/>
       <c r="E53" s="26" t="n"/>
       <c r="F53" s="27">
-        <f>Параметры!$B$9+63</f>
-        <v>46335</v>
+        <f>'Параметры и допущения'!$B$9+70</f>
+        <v>46342</v>
       </c>
       <c r="G53" s="27">
-        <f>Параметры!$B$9+81</f>
+        <f>'Параметры и допущения'!$B$9+81</f>
         <v>46353</v>
       </c>
       <c r="H53" s="26" t="n"/>
@@ -3751,7 +3816,11 @@
           <t>Площадка переведена</t>
         </is>
       </c>
-      <c r="K53" s="28" t="n"/>
+      <c r="K53" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
       <c r="L53" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -3762,179 +3831,184 @@
       </c>
       <c r="N53" s="26" t="n"/>
       <c r="O53" s="26" t="n"/>
-      <c r="Y53" s="23" t="n"/>
       <c r="Z53" s="23" t="n"/>
       <c r="AA53" s="23" t="n"/>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="17" t="n"/>
-      <c r="B54" s="18" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>Москва — 80 абонентов, снятие переадресаций</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="n"/>
+      <c r="D54" s="26" t="n"/>
+      <c r="E54" s="26" t="n"/>
+      <c r="F54" s="27">
+        <f>'Параметры и допущения'!$B$9+63</f>
+        <v>46335</v>
+      </c>
+      <c r="G54" s="27">
+        <f>'Параметры и допущения'!$B$9+81</f>
+        <v>46353</v>
+      </c>
+      <c r="H54" s="26" t="n"/>
+      <c r="I54" s="26" t="n"/>
+      <c r="J54" s="26" t="inlineStr">
+        <is>
+          <t>Площадка переведена</t>
+        </is>
+      </c>
+      <c r="K54" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="26" t="n"/>
+      <c r="O54" s="26" t="n"/>
+      <c r="Y54" s="23" t="n"/>
+      <c r="Z54" s="23" t="n"/>
+      <c r="AA54" s="23" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="17" t="n"/>
+      <c r="B55" s="18" t="inlineStr">
         <is>
           <t>ЭТАП 2 — Воронеж (недели 13–16, 445 абонентов)</t>
         </is>
       </c>
-      <c r="C54" s="17" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="17" t="n"/>
-      <c r="F54" s="17" t="n"/>
-      <c r="G54" s="17" t="n"/>
-      <c r="H54" s="17" t="n"/>
-      <c r="I54" s="17" t="n"/>
-      <c r="J54" s="17" t="n"/>
-      <c r="K54" s="17" t="n"/>
-      <c r="L54" s="17" t="n"/>
-      <c r="M54" s="17" t="n"/>
-      <c r="N54" s="17" t="n"/>
-      <c r="O54" s="17" t="n"/>
-      <c r="P54" s="17" t="n"/>
-      <c r="Q54" s="17" t="n"/>
-      <c r="R54" s="17" t="n"/>
-      <c r="S54" s="17" t="n"/>
-      <c r="T54" s="17" t="n"/>
-      <c r="U54" s="17" t="n"/>
-      <c r="V54" s="17" t="n"/>
-      <c r="W54" s="17" t="n"/>
-      <c r="X54" s="17" t="n"/>
-      <c r="Y54" s="17" t="n"/>
-      <c r="Z54" s="17" t="n"/>
-      <c r="AA54" s="17" t="n"/>
-      <c r="AB54" s="17" t="n"/>
-      <c r="AC54" s="17" t="n"/>
-      <c r="AD54" s="17" t="n"/>
-      <c r="AE54" s="17" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="19" t="inlineStr">
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="17" t="n"/>
+      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="17" t="n"/>
+      <c r="I55" s="17" t="n"/>
+      <c r="J55" s="17" t="n"/>
+      <c r="K55" s="17" t="n"/>
+      <c r="L55" s="17" t="n"/>
+      <c r="M55" s="17" t="n"/>
+      <c r="N55" s="17" t="n"/>
+      <c r="O55" s="17" t="n"/>
+      <c r="P55" s="17" t="n"/>
+      <c r="Q55" s="17" t="n"/>
+      <c r="R55" s="17" t="n"/>
+      <c r="S55" s="17" t="n"/>
+      <c r="T55" s="17" t="n"/>
+      <c r="U55" s="17" t="n"/>
+      <c r="V55" s="17" t="n"/>
+      <c r="W55" s="17" t="n"/>
+      <c r="X55" s="17" t="n"/>
+      <c r="Y55" s="17" t="n"/>
+      <c r="Z55" s="17" t="n"/>
+      <c r="AA55" s="17" t="n"/>
+      <c r="AB55" s="17" t="n"/>
+      <c r="AC55" s="17" t="n"/>
+      <c r="AD55" s="17" t="n"/>
+      <c r="AE55" s="17" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>Воронежский вынос</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D56" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="21">
-        <f>Параметры!$B$9+84</f>
+      <c r="E56" s="20" t="n"/>
+      <c r="F56" s="21">
+        <f>'Параметры и допущения'!$B$9+84</f>
         <v>46356</v>
       </c>
-      <c r="G55" s="21">
-        <f>Параметры!$B$9+95</f>
+      <c r="G56" s="21">
+        <f>'Параметры и допущения'!$B$9+95</f>
         <v>46367</v>
       </c>
-      <c r="H55" s="21">
-        <f>G55</f>
+      <c r="H56" s="21">
+        <f>G56</f>
         <v>46367</v>
       </c>
-      <c r="I55" s="19" t="inlineStr">
+      <c r="I56" s="19" t="inlineStr">
         <is>
           <t>Воронеж — самая крупная площадка (445 абонентов) и по решению совещания вводится отдельным этапом после всех остальных</t>
         </is>
       </c>
-      <c r="J55" s="19" t="inlineStr">
+      <c r="J56" s="19" t="inlineStr">
         <is>
           <t>Воронеж работает выносом; узлов семь — число нечётное, кворум не требует арбитра</t>
         </is>
       </c>
-      <c r="K55" s="20" t="n"/>
-      <c r="L55" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M55" s="19" t="n">
+      <c r="K56" s="20" t="n"/>
+      <c r="L56" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M56" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="N55" s="22">
-        <f>Параметры!$B$20*M55</f>
+      <c r="N56" s="22">
+        <f>'Параметры и допущения'!$B$22*M56</f>
         <v>92120</v>
       </c>
-      <c r="O55" s="22" t="n">
+      <c r="O56" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AB55" s="23" t="n"/>
-      <c r="AC55" s="23" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="24" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B56" s="25" t="inlineStr">
-        <is>
-          <t>Проверить, что все шесть узлов Synced до начала работ</t>
-        </is>
-      </c>
-      <c r="C56" s="26" t="n"/>
-      <c r="D56" s="26" t="n"/>
-      <c r="E56" s="26" t="n"/>
-      <c r="F56" s="27">
-        <f>Параметры!$B$9+84</f>
-        <v>46356</v>
-      </c>
-      <c r="G56" s="27">
-        <f>Параметры!$B$9+88</f>
-        <v>46360</v>
-      </c>
-      <c r="H56" s="26" t="n"/>
-      <c r="I56" s="26" t="n"/>
-      <c r="J56" s="26" t="inlineStr">
-        <is>
-          <t>Кластер здоров, расхождений нет</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="n"/>
-      <c r="L56" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M56" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" s="26" t="n"/>
-      <c r="O56" s="26" t="n"/>
       <c r="AB56" s="23" t="n"/>
+      <c r="AC56" s="23" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>Клонировать мастер и расшить клон в вынос</t>
+          <t>Проверить, что все шесть узлов Synced до начала работ</t>
         </is>
       </c>
       <c r="C57" s="26" t="n"/>
       <c r="D57" s="26" t="n"/>
       <c r="E57" s="26" t="n"/>
       <c r="F57" s="27">
-        <f>Параметры!$B$9+84</f>
+        <f>'Параметры и допущения'!$B$9+84</f>
         <v>46356</v>
       </c>
       <c r="G57" s="27">
-        <f>Параметры!$B$9+88</f>
+        <f>'Параметры и допущения'!$B$9+88</f>
         <v>46360</v>
       </c>
       <c r="H57" s="26" t="n"/>
       <c r="I57" s="26" t="n"/>
       <c r="J57" s="26" t="inlineStr">
         <is>
-          <t>Вынос в кластере</t>
+          <t>Кластер здоров, расхождений нет</t>
         </is>
       </c>
       <c r="K57" s="28" t="n"/>
@@ -3944,7 +4018,7 @@
         </is>
       </c>
       <c r="M57" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57" s="26" t="n"/>
       <c r="O57" s="26" t="n"/>
@@ -3953,30 +4027,30 @@
     <row r="58">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>Межузловые транки и диалплан</t>
+          <t>Клонировать мастер и расшить клон в вынос</t>
         </is>
       </c>
       <c r="C58" s="26" t="n"/>
       <c r="D58" s="26" t="n"/>
       <c r="E58" s="26" t="n"/>
       <c r="F58" s="27">
-        <f>Параметры!$B$9+84</f>
+        <f>'Параметры и допущения'!$B$9+84</f>
         <v>46356</v>
       </c>
       <c r="G58" s="27">
-        <f>Параметры!$B$9+88</f>
+        <f>'Параметры и допущения'!$B$9+88</f>
         <v>46360</v>
       </c>
       <c r="H58" s="26" t="n"/>
       <c r="I58" s="26" t="n"/>
       <c r="J58" s="26" t="inlineStr">
         <is>
-          <t>Вызовы с другими площадками проходят</t>
+          <t>Вынос в кластере</t>
         </is>
       </c>
       <c r="K58" s="28" t="n"/>
@@ -3995,30 +4069,30 @@
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>Локальный транк оператора</t>
+          <t>Межузловые транки и диалплан</t>
         </is>
       </c>
       <c r="C59" s="26" t="n"/>
       <c r="D59" s="26" t="n"/>
       <c r="E59" s="26" t="n"/>
       <c r="F59" s="27">
-        <f>Параметры!$B$9+91</f>
-        <v>46363</v>
+        <f>'Параметры и допущения'!$B$9+84</f>
+        <v>46356</v>
       </c>
       <c r="G59" s="27">
-        <f>Параметры!$B$9+95</f>
-        <v>46367</v>
+        <f>'Параметры и допущения'!$B$9+88</f>
+        <v>46360</v>
       </c>
       <c r="H59" s="26" t="n"/>
       <c r="I59" s="26" t="n"/>
       <c r="J59" s="26" t="inlineStr">
         <is>
-          <t>Свой выход в город работает</t>
+          <t>Вызовы с другими площадками проходят</t>
         </is>
       </c>
       <c r="K59" s="28" t="n"/>
@@ -4028,39 +4102,39 @@
         </is>
       </c>
       <c r="M59" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" s="26" t="n"/>
       <c r="O59" s="26" t="n"/>
-      <c r="AC59" s="23" t="n"/>
+      <c r="AB59" s="23" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>Перевести телефоны на вынос через провижининг</t>
+          <t>Локальный транк оператора</t>
         </is>
       </c>
       <c r="C60" s="26" t="n"/>
       <c r="D60" s="26" t="n"/>
       <c r="E60" s="26" t="n"/>
       <c r="F60" s="27">
-        <f>Параметры!$B$9+91</f>
+        <f>'Параметры и допущения'!$B$9+91</f>
         <v>46363</v>
       </c>
       <c r="G60" s="27">
-        <f>Параметры!$B$9+95</f>
+        <f>'Параметры и допущения'!$B$9+95</f>
         <v>46367</v>
       </c>
       <c r="H60" s="26" t="n"/>
       <c r="I60" s="26" t="n"/>
       <c r="J60" s="26" t="inlineStr">
         <is>
-          <t>Телефоны регистрируются в Воронеже, резервный сервер — ЦОД-1</t>
+          <t>Свой выход в город работает</t>
         </is>
       </c>
       <c r="K60" s="28" t="n"/>
@@ -4070,138 +4144,141 @@
         </is>
       </c>
       <c r="M60" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N60" s="26" t="n"/>
       <c r="O60" s="26" t="n"/>
       <c r="AC60" s="23" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="19" t="inlineStr">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>Перевести телефоны на вынос через провижининг</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="n"/>
+      <c r="D61" s="26" t="n"/>
+      <c r="E61" s="26" t="n"/>
+      <c r="F61" s="27">
+        <f>'Параметры и допущения'!$B$9+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G61" s="27">
+        <f>'Параметры и допущения'!$B$9+95</f>
+        <v>46367</v>
+      </c>
+      <c r="H61" s="26" t="n"/>
+      <c r="I61" s="26" t="n"/>
+      <c r="J61" s="26" t="inlineStr">
+        <is>
+          <t>Телефоны регистрируются в Воронеже, резервный сервер — ЦОД-1</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="n"/>
+      <c r="L61" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M61" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N61" s="26" t="n"/>
+      <c r="O61" s="26" t="n"/>
+      <c r="AC61" s="23" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B61" s="19" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>Консолидация воронежских АТС</t>
         </is>
       </c>
-      <c r="C61" s="19" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="D62" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="21">
-        <f>Параметры!$B$9+91</f>
+      <c r="E62" s="20" t="n"/>
+      <c r="F62" s="21">
+        <f>'Параметры и допущения'!$B$9+91</f>
         <v>46363</v>
       </c>
-      <c r="G61" s="21">
-        <f>Параметры!$B$9+102</f>
+      <c r="G62" s="21">
+        <f>'Параметры и допущения'!$B$9+102</f>
         <v>46374</v>
       </c>
-      <c r="H61" s="21">
-        <f>G61</f>
+      <c r="H62" s="21">
+        <f>G62</f>
         <v>46374</v>
       </c>
-      <c r="I61" s="19" t="inlineStr">
+      <c r="I62" s="19" t="inlineStr">
         <is>
           <t>Мясокомбинат и Калуга — 216 абонентов на двух отдельных станциях</t>
         </is>
       </c>
-      <c r="J61" s="19" t="inlineStr">
+      <c r="J62" s="19" t="inlineStr">
         <is>
           <t>Абоненты переведены на воронежский вынос, станции выведены из эксплуатации</t>
         </is>
       </c>
-      <c r="K61" s="20" t="n"/>
-      <c r="L61" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M61" s="19" t="n">
+      <c r="K62" s="19" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L62" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M62" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N61" s="22">
-        <f>Параметры!$B$20*M61</f>
+      <c r="N62" s="22">
+        <f>'Параметры и допущения'!$B$22*M62</f>
         <v>69090</v>
       </c>
-      <c r="O61" s="22" t="n">
+      <c r="O62" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AC61" s="23" t="n"/>
-      <c r="AD61" s="23" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="24" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B62" s="25" t="inlineStr">
-        <is>
-          <t>Мясокомбинат — 187 абонентов</t>
-        </is>
-      </c>
-      <c r="C62" s="26" t="n"/>
-      <c r="D62" s="26" t="n"/>
-      <c r="E62" s="26" t="n"/>
-      <c r="F62" s="27">
-        <f>Параметры!$B$9+91</f>
-        <v>46363</v>
-      </c>
-      <c r="G62" s="27">
-        <f>Параметры!$B$9+102</f>
-        <v>46374</v>
-      </c>
-      <c r="H62" s="26" t="n"/>
-      <c r="I62" s="26" t="n"/>
-      <c r="J62" s="26" t="inlineStr">
-        <is>
-          <t>Станция выведена</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="n"/>
-      <c r="L62" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M62" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N62" s="26" t="n"/>
-      <c r="O62" s="26" t="n"/>
       <c r="AC62" s="23" t="n"/>
       <c r="AD62" s="23" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>Калуга — 29 абонентов</t>
+          <t>Мясокомбинат — 187 абонентов</t>
         </is>
       </c>
       <c r="C63" s="26" t="n"/>
       <c r="D63" s="26" t="n"/>
       <c r="E63" s="26" t="n"/>
       <c r="F63" s="27">
-        <f>Параметры!$B$9+98</f>
-        <v>46370</v>
+        <f>'Параметры и допущения'!$B$9+91</f>
+        <v>46363</v>
       </c>
       <c r="G63" s="27">
-        <f>Параметры!$B$9+102</f>
+        <f>'Параметры и допущения'!$B$9+102</f>
         <v>46374</v>
       </c>
       <c r="H63" s="26" t="n"/>
@@ -4211,123 +4288,134 @@
           <t>Станция выведена</t>
         </is>
       </c>
-      <c r="K63" s="28" t="n"/>
+      <c r="K63" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
       <c r="L63" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M63" s="26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N63" s="26" t="n"/>
       <c r="O63" s="26" t="n"/>
+      <c r="AC63" s="23" t="n"/>
       <c r="AD63" s="23" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="19" t="inlineStr">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>Калуга — 29 абонентов</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n"/>
+      <c r="D64" s="26" t="n"/>
+      <c r="E64" s="26" t="n"/>
+      <c r="F64" s="27">
+        <f>'Параметры и допущения'!$B$9+98</f>
+        <v>46370</v>
+      </c>
+      <c r="G64" s="27">
+        <f>'Параметры и допущения'!$B$9+102</f>
+        <v>46374</v>
+      </c>
+      <c r="H64" s="26" t="n"/>
+      <c r="I64" s="26" t="n"/>
+      <c r="J64" s="26" t="inlineStr">
+        <is>
+          <t>Станция выведена</t>
+        </is>
+      </c>
+      <c r="K64" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L64" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M64" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N64" s="26" t="n"/>
+      <c r="O64" s="26" t="n"/>
+      <c r="AD64" s="23" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B64" s="19" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>Перевод воронежских абонентов на единый план нумерации</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E64" s="20" t="n"/>
-      <c r="F64" s="21">
-        <f>Параметры!$B$9+91</f>
+      <c r="E65" s="20" t="n"/>
+      <c r="F65" s="21">
+        <f>'Параметры и допущения'!$B$9+91</f>
         <v>46363</v>
       </c>
-      <c r="G64" s="21">
-        <f>Параметры!$B$9+109</f>
+      <c r="G65" s="21">
+        <f>'Параметры и допущения'!$B$9+109</f>
         <v>46381</v>
       </c>
-      <c r="H64" s="21">
-        <f>G64</f>
+      <c r="H65" s="21">
+        <f>G65</f>
         <v>46381</v>
       </c>
-      <c r="I64" s="19" t="inlineStr">
+      <c r="I65" s="19" t="inlineStr">
         <is>
           <t>445 абонентов Воронежа и его станций используют старую нумерацию</t>
         </is>
       </c>
-      <c r="J64" s="19" t="inlineStr">
+      <c r="J65" s="19" t="inlineStr">
         <is>
           <t>Воронеж переведён на пятизначную нумерацию, переадресации со старых номеров сняты</t>
         </is>
       </c>
-      <c r="K64" s="20" t="n"/>
-      <c r="L64" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M64" s="19" t="n">
+      <c r="K65" s="19" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L65" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M65" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N64" s="22">
-        <f>Параметры!$B$20*M64</f>
+      <c r="N65" s="22">
+        <f>'Параметры и допущения'!$B$22*M65</f>
         <v>69090</v>
       </c>
-      <c r="O64" s="22" t="n">
+      <c r="O65" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AC64" s="23" t="n"/>
-      <c r="AD64" s="23" t="n"/>
-      <c r="AE64" s="23" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="24" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="B65" s="25" t="inlineStr">
-        <is>
-          <t>Воронеж и Мясокомбинат — 416 абонентов</t>
-        </is>
-      </c>
-      <c r="C65" s="26" t="n"/>
-      <c r="D65" s="26" t="n"/>
-      <c r="E65" s="26" t="n"/>
-      <c r="F65" s="27">
-        <f>Параметры!$B$9+91</f>
-        <v>46363</v>
-      </c>
-      <c r="G65" s="27">
-        <f>Параметры!$B$9+109</f>
-        <v>46381</v>
-      </c>
-      <c r="H65" s="26" t="n"/>
-      <c r="I65" s="26" t="n"/>
-      <c r="J65" s="26" t="inlineStr">
-        <is>
-          <t>Площадки переведены</t>
-        </is>
-      </c>
-      <c r="K65" s="28" t="n"/>
-      <c r="L65" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M65" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="N65" s="26" t="n"/>
-      <c r="O65" s="26" t="n"/>
       <c r="AC65" s="23" t="n"/>
       <c r="AD65" s="23" t="n"/>
       <c r="AE65" s="23" t="n"/>
@@ -4335,72 +4423,124 @@
     <row r="66">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>Калуга — сверка: часть абонентов уже на пятизначных</t>
+          <t>Воронеж и Мясокомбинат — 416 абонентов</t>
         </is>
       </c>
       <c r="C66" s="26" t="n"/>
       <c r="D66" s="26" t="n"/>
       <c r="E66" s="26" t="n"/>
       <c r="F66" s="27">
-        <f>Параметры!$B$9+105</f>
-        <v>46377</v>
+        <f>'Параметры и допущения'!$B$9+91</f>
+        <v>46363</v>
       </c>
       <c r="G66" s="27">
-        <f>Параметры!$B$9+109</f>
+        <f>'Параметры и допущения'!$B$9+109</f>
         <v>46381</v>
       </c>
       <c r="H66" s="26" t="n"/>
       <c r="I66" s="26" t="n"/>
       <c r="J66" s="26" t="inlineStr">
         <is>
-          <t>Расхождений нет, переадресации сняты</t>
-        </is>
-      </c>
-      <c r="K66" s="28" t="n"/>
+          <t>Площадки переведены</t>
+        </is>
+      </c>
+      <c r="K66" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
       <c r="L66" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M66" s="26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N66" s="26" t="n"/>
       <c r="O66" s="26" t="n"/>
+      <c r="AC66" s="23" t="n"/>
+      <c r="AD66" s="23" t="n"/>
       <c r="AE66" s="23" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="n"/>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>Калуга — сверка: часть абонентов уже на пятизначных</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="n"/>
+      <c r="D67" s="26" t="n"/>
+      <c r="E67" s="26" t="n"/>
+      <c r="F67" s="27">
+        <f>'Параметры и допущения'!$B$9+105</f>
+        <v>46377</v>
+      </c>
+      <c r="G67" s="27">
+        <f>'Параметры и допущения'!$B$9+109</f>
+        <v>46381</v>
+      </c>
+      <c r="H67" s="26" t="n"/>
+      <c r="I67" s="26" t="n"/>
+      <c r="J67" s="26" t="inlineStr">
+        <is>
+          <t>Расхождений нет, переадресации сняты</t>
+        </is>
+      </c>
+      <c r="K67" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L67" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M67" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="26" t="n"/>
+      <c r="O67" s="26" t="n"/>
+      <c r="AE67" s="23" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="n"/>
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>ИТОГО по проекту</t>
         </is>
       </c>
-      <c r="C67" s="29" t="n"/>
-      <c r="D67" s="29" t="n"/>
-      <c r="E67" s="29" t="n"/>
-      <c r="F67" s="29" t="n"/>
-      <c r="G67" s="29" t="n"/>
-      <c r="H67" s="29" t="n"/>
-      <c r="I67" s="29" t="n"/>
-      <c r="J67" s="29" t="n"/>
-      <c r="K67" s="29" t="n"/>
-      <c r="L67" s="29" t="n"/>
-      <c r="M67" s="29">
-        <f>M4+M11+M18+M22+M26+M32+M38+M41+M44+M48+M55+M61+M64</f>
+      <c r="C68" s="29" t="n"/>
+      <c r="D68" s="29" t="n"/>
+      <c r="E68" s="29" t="n"/>
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="29" t="n"/>
+      <c r="H68" s="29" t="n"/>
+      <c r="I68" s="29" t="n"/>
+      <c r="J68" s="29" t="n"/>
+      <c r="K68" s="29" t="n"/>
+      <c r="L68" s="29" t="n"/>
+      <c r="M68" s="29">
+        <f>M4+M12+M19+M23+M27+M33+M39+M42+M45+M49+M56+M62+M65</f>
         <v>98</v>
       </c>
-      <c r="N67" s="30">
-        <f>N4+N11+N18+N22+N26+N32+N38+N41+N44+N48+N55+N61+N64</f>
+      <c r="N68" s="30">
+        <f>N4+N12+N19+N23+N27+N33+N39+N42+N45+N49+N56+N62+N65</f>
         <v>1128470</v>
       </c>
-      <c r="O67" s="30">
-        <f>O4+O11+O18+O22+O26+O32+O38+O41+O44+O48+O55+O61+O64</f>
+      <c r="O68" s="30">
+        <f>O4+O12+O19+O23+O27+O33+O39+O42+O45+O49+O56+O62+O65</f>
         <v>0</v>
       </c>
     </row>

--- a/docs/plan/dit-annual-plan.xlsx
+++ b/docs/plan/dit-annual-plan.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,9 +200,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -572,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -817,7 +814,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>задача 1.7</t>
+          <t>задача 3</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -827,379 +824,417 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Исполнитель организационных задач</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Кириевская Е.</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Задачи 9, 10, 12, 13 — консолидация мелких АТС и перенумерация. Инженер кластера на задачи 1–8 и 11 в файле не проставлен: ячейки оставлены жёлтыми под заполнение.</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>КОМАНДА ПРОЕКТА</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>четыре человека</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты всего, ч-д</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>98</v>
+          <t xml:space="preserve">  Руководитель</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Сумма по задачам, см. лист плана</t>
+          <t>Главный по проекту, указан заказчиком во всех строках плана.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе инженер кластера</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>68</v>
+          <t xml:space="preserve">  Основной исполнитель</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
+          <t>Инженер кластера. Задачи 1–9 и 12 — вся работа с кластером, переносом центра и вводом выносов.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  в том числе второй исполнитель</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>30</v>
+          <t xml:space="preserve">  Помощник</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
+          <t>Задачи 10, 11, 13, 14 — консолидация мелких АТС и перенумерация. Частичная занятость, идут параллельно основным работам.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя ставка, ₽/ч-д</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>11515</v>
+          <t xml:space="preserve">  Развёртывание и адресация</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
+          <t>Создание клонов, установка и присвоение IP-адресов на площадках. Проставлен исполнителем в соответствующих подзадачах.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B23" s="7">
-        <f>B19*B22</f>
-        <v>1128470</v>
+          <t>Трудозатраты всего, ч-д</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Трудозатраты × ставка, рассчитывается формулой</t>
+          <t>Сумма по задачам, см. лист плана</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  в том числе инженер кластера</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>70</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
+          <t>Задачи 1–7 и 10. Помещается в 15 недель × 5 дней = 75 ч-д одного человека.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Абонентов в периметре</t>
+          <t xml:space="preserve">  в том числе второй исполнитель</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1255</v>
+        <v>30</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
+          <t>Задачи 8, 9, 11, 12 — консолидация мелких АТС и перенумерация. Работа организационная, идёт параллельно силами второго человека с частичной занятостью. Одним инженером весь объём в срок не выполняется — это ограничение плана, а не оценка.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Станций сейчас</t>
+          <t>Внутренняя ставка, ₽/ч-д</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>12</v>
+        <v>11515</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Там же</t>
+          <t>Из формулы =11515*M4 в файле «План работ ДИТ 2023.xlsx», колонка «Плановая себестоимость внутренних затрат».</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Узлов кластера после внедрения</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>7</v>
+          <t>Плановая себестоимость внутренних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B27" s="7">
+        <f>B23*B26</f>
+        <v>1151500</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
+          <t>Трудозатраты × ставка, рассчитывается формулой</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Голосов в кворуме</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>7</v>
+          <t>Плановая себестоимость внешних затрат, ₽ без НДС</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
+          <t>Всё программное обеспечение бесплатное: MariaDB Galera, Asterisk, FreePBX, OSS PBX End Point Manager. Все узлы — свои виртуальные машины, закупки нет.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Арбитр garbd</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>не нужен</t>
-        </is>
+          <t>Абонентов в периметре</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1255</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
+          <t>Аудит 12 станций, docs/plan/numbering-plan.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Кворум в конце этапа 1</t>
+          <t>Станций сейчас</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
+          <t>Там же</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Виртуальных машин добавить</t>
+          <t>Узлов кластера после внедрения</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
+          <t>ЦОД-1 40 и ЦОД-2 40 (оба живые), Ростов 352, Ставрополь 74, Нижний Новгород 164, Славянск-на-Кубани 140, Воронеж 445. Итого 1255 — сходится с аудитом.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Размещение ВМ по хостам</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>проверить</t>
-        </is>
+          <t>Голосов в кворуме</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+          <t>Семь узлов — число НЕЧЁТНОЕ, поэтому арбитр не нужен вообще. Кластер переживает потерю трёх узлов и остаётся работоспособным при потере московского ЦОД целиком: у городов остаётся 5 голосов из 7.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Снимки ВМ как резервная копия</t>
+          <t>Арбитр garbd</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>нельзя</t>
+          <t>не нужен</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+          <t>В прежней версии плана Ставрополь оставался на ростовском сервере, узлов было шесть, и чётность приходилось добирать арбитром. Собственная АТС в Ставрополе делает число нечётным — та же виртуальная машина вместо бесполезного голоса несёт 74 абонента.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Оба узла ЦОД — живые</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
+          <t>Кворум в конце этапа 1</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+          <t>ВНИМАНИЕ. Без Воронежа узлов шесть — число чётное. Держится недели 11–12, закрывается вводом Воронежа. Если даже две недели такого состояния неприемлемы, на этот период ставится временный арбитр garbd.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Панель управления FreePBX</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>ровно на одном узле</t>
-        </is>
+          <t>Виртуальных машин добавить</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+          <t>ЦОД-1, ЦОД-2 и Ставрополь. Все — свои мощности, закупки нет. У четырёх остальных площадок машины уже есть.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>Размещение ВМ по хостам</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>проверить</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>КРИТИЧНО. Узлы обязаны стоять на разных физических хостах: пять ВМ на одном гипервизоре — это не отказоустойчивый кластер, а пять копий одной точки отказа. Проверяется на этапе 1 до ввода второго узла.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Снимки ВМ как резервная копия</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>нельзя</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Откат узла на снимок возвращает его с устаревшим seqno. Такой узел вводится обратно только через prepare-clone.sh --full-resync. Резервные копии снимаются на уровне базы (mysqldump), а не гипервизора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Оба узла ЦОД — живые</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>ЦОД-2 не пассивная копия: он несёт вызовы наравне с ЦОД-1. Резерв, который никогда не берёт нагрузку, не проверен — поэтому 80 московских абонентов делятся по 40 на зал, и каждый зал прописан другому резервным. Отказ зала проверяется реальным трафиком, а не инструкцией.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Панель управления FreePBX</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Живой Asterisk — не второй FreePBX. Две включённые панели пишут в общую базу наперегонки. На ЦОД-2 FreePBX установлен (он клон) и выключен — включается за минуты. Переключение отрабатывается учебно в задаче 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t>Неделя 16 — предновогодняя</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>21–25 декабря</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>ВНИМАНИЕ. На эту неделю приходится завершение перенумерации Воронежа. Люди в отпусках, проверять изменения некому. Либо старт сдвигается на неделю раньше, либо задача 13 переносится на январь.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Что нужно заполнить вручную</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Заказчик</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Руководитель, от которого идёт задача. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>Исполнитель</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Инженер проекта и ответственные за задачи. Формат «И. Фамилия».</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Номер приказа / внутреннего проекта</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>Присваивается при открытии проекта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>Дата протокола совещания</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>Проставить дату документа, из которого взята этапность.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Адресный план узлов</t>
+          <t>Номер приказа / внутреннего проекта</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="inlineStr">
         <is>
+          <t>Присваивается при открытии проекта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Дата протокола совещания</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Проставить дату документа, из которого взята этапность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Адресный план узлов</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
           <t>Проставить IP семи узлов: ЦОД-1, ЦОД-2, Ростов, Ставрополь, Нижний Новгород, Славянск-на-Кубани, Воронеж.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Жёлтой заливкой отмечены ячейки, которые заполняются вручную.</t>
         </is>
@@ -1216,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE68"/>
+  <dimension ref="A1:AE70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7" customWidth="1" min="1" max="1"/>
@@ -1494,7 +1529,11 @@
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E4" s="20" t="n"/>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
       <c r="F4" s="21">
         <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
@@ -1517,7 +1556,11 @@
           <t>VPN между ЦОД и всеми городами поднят, RTT измерен, в ЦОД выделены две ВМ в разных стойках, у каждой площадки заведён свой SIP-пользователь ВАТС</t>
         </is>
       </c>
-      <c r="K4" s="20" t="n"/>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L4" s="19" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -1527,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="N4" s="22">
-        <f>'Параметры и допущения'!$B$22*M4</f>
+        <f>'Параметры и допущения'!$B$26*M4</f>
         <v>92120</v>
       </c>
       <c r="O4" s="22" t="n">
@@ -1565,7 +1608,11 @@
           <t>План нумерации утверждён, уведомления разосланы</t>
         </is>
       </c>
-      <c r="K5" s="28" t="n"/>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L5" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -1607,7 +1654,11 @@
           <t>Сеть между ЦОД и всеми площадками работает</t>
         </is>
       </c>
-      <c r="K6" s="28" t="n"/>
+      <c r="K6" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L6" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -1650,7 +1701,11 @@
           <t>Замеры выполнены; площадки с RTT выше 50 мс исключены из синхронной репликации</t>
         </is>
       </c>
-      <c r="K7" s="28" t="n"/>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L7" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -1692,7 +1747,11 @@
           <t>Адреса всех площадок известны, план зафиксирован</t>
         </is>
       </c>
-      <c r="K8" s="28" t="n"/>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
+      </c>
       <c r="L8" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -1734,7 +1793,11 @@
           <t>ВМ выделены, узлы разнесены по физическим хостам</t>
         </is>
       </c>
-      <c r="K9" s="28" t="n"/>
+      <c r="K9" s="26" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
+      </c>
       <c r="L9" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -1776,14 +1839,18 @@
           <t>Учётные записи созданы на все площадки, включая Воронеж</t>
         </is>
       </c>
-      <c r="K10" s="28" t="n"/>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L10" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M10" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" s="26" t="n"/>
       <c r="O10" s="26" t="n"/>
@@ -1791,119 +1858,131 @@
       <c r="Q10" s="23" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>Согласовать порядок оповещения техподдержки при отклонениях</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="27">
-        <f>'Параметры и допущения'!$B$9+7</f>
-        <v>46279</v>
-      </c>
-      <c r="G11" s="27">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Смена учётных данных и защита периметра</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F11" s="21">
+        <f>'Параметры и допущения'!$B$9+0</f>
+        <v>46272</v>
+      </c>
+      <c r="G11" s="21">
         <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="26" t="n"/>
-      <c r="J11" s="26" t="inlineStr">
-        <is>
-          <t>Известно, кто и по какому каналу поднимается по тревоге, за какое время и что считается инцидентом; порядок роздан всем участникам работ</t>
-        </is>
-      </c>
-      <c r="K11" s="28" t="n"/>
-      <c r="L11" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M11" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="26" t="n"/>
-      <c r="O11" s="26" t="n"/>
+      <c r="H11" s="21">
+        <f>G11</f>
+        <v>46283</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>Учётные данные телефонии не менялись; журнал безопасности Asterisk не ведётся, подбор паролей не отслеживается</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>Пароли 444 абонентов, транков, AMI и базы данных сменены; включён журнал безопасности и блокировка подбора; восстановление из резервной копии проверено</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" s="22">
+        <f>'Параметры и допущения'!$B$26*M11</f>
+        <v>115150</v>
+      </c>
+      <c r="O11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="23" t="n"/>
       <c r="Q11" s="23" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Смена учётных данных и защита периметра</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="21">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Включить журнал безопасности, fail2ban, ограничить доступ к AMI</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="27">
         <f>'Параметры и допущения'!$B$9+0</f>
         <v>46272</v>
       </c>
-      <c r="G12" s="21">
-        <f>'Параметры и допущения'!$B$9+11</f>
-        <v>46283</v>
-      </c>
-      <c r="H12" s="21">
-        <f>G12</f>
-        <v>46283</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>Учётные данные телефонии не менялись; журнал безопасности Asterisk не ведётся, подбор паролей не отслеживается</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>Пароли 444 абонентов, транков, AMI и базы данных сменены; включён журнал безопасности и блокировка подбора; восстановление из резервной копии проверено</t>
-        </is>
-      </c>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="N12" s="22">
-        <f>'Параметры и допущения'!$B$22*M12</f>
-        <v>115150</v>
-      </c>
-      <c r="O12" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G12" s="27">
+        <f>'Параметры и допущения'!$B$9+4</f>
+        <v>46276</v>
+      </c>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="inlineStr">
+        <is>
+          <t>Попытки подбора фиксируются и блокируются</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="26" t="n"/>
+      <c r="O12" s="26" t="n"/>
       <c r="P12" s="23" t="n"/>
-      <c r="Q12" s="23" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Включить журнал безопасности, fail2ban, ограничить доступ к AMI</t>
+          <t>Задать порядок идентификации абонентов и перечень кодеков</t>
         </is>
       </c>
       <c r="C13" s="26" t="n"/>
@@ -1921,17 +2000,21 @@
       <c r="I13" s="26" t="n"/>
       <c r="J13" s="26" t="inlineStr">
         <is>
-          <t>Попытки подбора фиксируются и блокируются</t>
-        </is>
-      </c>
-      <c r="K13" s="28" t="n"/>
+          <t>Идентификация по учётной записи, alaw первым кодеком</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L13" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M13" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="26" t="n"/>
       <c r="O13" s="26" t="n"/>
@@ -1940,12 +2023,12 @@
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Задать порядок идентификации абонентов и перечень кодеков</t>
+          <t>Сменить пароли 444 абонентов</t>
         </is>
       </c>
       <c r="C14" s="26" t="n"/>
@@ -1956,46 +2039,51 @@
         <v>46272</v>
       </c>
       <c r="G14" s="27">
-        <f>'Параметры и допущения'!$B$9+4</f>
-        <v>46276</v>
+        <f>'Параметры и допущения'!$B$9+11</f>
+        <v>46283</v>
       </c>
       <c r="H14" s="26" t="n"/>
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="26" t="inlineStr">
         <is>
-          <t>Идентификация по учётной записи, alaw первым кодеком</t>
-        </is>
-      </c>
-      <c r="K14" s="28" t="n"/>
+          <t>Пароли сменены</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L14" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M14" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N14" s="26" t="n"/>
       <c r="O14" s="26" t="n"/>
       <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="23" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>Сменить пароли 444 абонентов</t>
+          <t>Сменить учётные данные транков, AMI и базы данных</t>
         </is>
       </c>
       <c r="C15" s="26" t="n"/>
       <c r="D15" s="26" t="n"/>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="27">
-        <f>'Параметры и допущения'!$B$9+0</f>
-        <v>46272</v>
+        <f>'Параметры и допущения'!$B$9+7</f>
+        <v>46279</v>
       </c>
       <c r="G15" s="27">
         <f>'Параметры и допущения'!$B$9+11</f>
@@ -2005,32 +2093,35 @@
       <c r="I15" s="26" t="n"/>
       <c r="J15" s="26" t="inlineStr">
         <is>
-          <t>Пароли сменены</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="n"/>
+          <t>Учётные данные сменены</t>
+        </is>
+      </c>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L15" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M15" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15" s="26" t="n"/>
       <c r="O15" s="26" t="n"/>
-      <c r="P15" s="23" t="n"/>
       <c r="Q15" s="23" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Сменить учётные данные транков, AMI и базы данных</t>
+          <t>Пересобрать конфигурации телефонов</t>
         </is>
       </c>
       <c r="C16" s="26" t="n"/>
@@ -2048,17 +2139,21 @@
       <c r="I16" s="26" t="n"/>
       <c r="J16" s="26" t="inlineStr">
         <is>
-          <t>Учётные данные сменены</t>
-        </is>
-      </c>
-      <c r="K16" s="28" t="n"/>
+          <t>Телефоны работают с новыми паролями</t>
+        </is>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L16" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M16" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" s="26" t="n"/>
       <c r="O16" s="26" t="n"/>
@@ -2067,12 +2162,12 @@
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>Пересобрать конфигурации телефонов</t>
+          <t>Проверить восстановление из резервной копии на тестовой машине</t>
         </is>
       </c>
       <c r="C17" s="26" t="n"/>
@@ -2090,10 +2185,14 @@
       <c r="I17" s="26" t="n"/>
       <c r="J17" s="26" t="inlineStr">
         <is>
-          <t>Телефоны работают с новыми паролями</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="n"/>
+          <t>Копия развёрнута и проверена</t>
+        </is>
+      </c>
+      <c r="K17" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L17" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -2107,202 +2206,246 @@
       <c r="Q17" s="23" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>Проверить восстановление из резервной копии на тестовой машине</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="27">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Порядок оповещения техподдержки при отклонениях</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F18" s="21">
         <f>'Параметры и допущения'!$B$9+7</f>
         <v>46279</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="21">
         <f>'Параметры и допущения'!$B$9+11</f>
         <v>46283</v>
       </c>
-      <c r="H18" s="26" t="n"/>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="26" t="inlineStr">
-        <is>
-          <t>Копия развёрнута и проверена</t>
-        </is>
-      </c>
-      <c r="K18" s="28" t="n"/>
-      <c r="L18" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M18" s="26" t="n">
+      <c r="H18" s="21">
+        <f>G18</f>
+        <v>46283</v>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>Работы идут на боевой телефонии, но не определено, кто поднимается по тревоге и что вообще считается отклонением — договариваться об этом после первой нештатной ситуации поздно</t>
+        </is>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
+        <is>
+          <t>Порядок согласован и роздан всем участникам работ: известны дежурный, канал связи, время реакции и перечень событий, по которым поднимают тревогу</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="22">
+        <f>'Параметры и допущения'!$B$26*M18</f>
+        <v>23030</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="23" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>Определить перечень событий, по которым поднимают тревогу</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="27">
+        <f>'Параметры и допущения'!$B$9+7</f>
+        <v>46279</v>
+      </c>
+      <c r="G19" s="27">
+        <f>'Параметры и допущения'!$B$9+11</f>
+        <v>46283</v>
+      </c>
+      <c r="H19" s="26" t="n"/>
+      <c r="I19" s="26" t="n"/>
+      <c r="J19" s="26" t="inlineStr">
+        <is>
+          <t>Зафиксированы: потеря регистраций на площадке, расхождение узлов кластера, недоступность панели управления, отказ транка в город</t>
+        </is>
+      </c>
+      <c r="K19" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M19" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="26" t="n"/>
-      <c r="O18" s="26" t="n"/>
-      <c r="Q18" s="23" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>Испытательный стенд</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="21">
-        <f>'Параметры и допущения'!$B$9+14</f>
-        <v>46286</v>
-      </c>
-      <c r="G19" s="21">
-        <f>'Параметры и допущения'!$B$9+18</f>
-        <v>46290</v>
-      </c>
-      <c r="H19" s="21">
-        <f>G19</f>
-        <v>46290</v>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>Процедуры восстановления кластера и передачи роли мастера ни разу не выполнялись</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="inlineStr">
-        <is>
-          <t>Стенд из трёх машин прошёл чек-лист приёмки: клонирование, восстановление кворума и передача роли мастера выполнены руками</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M19" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="N19" s="22">
-        <f>'Параметры и допущения'!$B$22*M19</f>
-        <v>69090</v>
-      </c>
-      <c r="O19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="23" t="n"/>
+      <c r="N19" s="26" t="n"/>
+      <c r="O19" s="26" t="n"/>
+      <c r="Q19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Развернуть тестовый мастер и клонировать его в два узла</t>
+          <t>Назначить дежурного, канал связи и время реакции; раздать порядок</t>
         </is>
       </c>
       <c r="C20" s="26" t="n"/>
       <c r="D20" s="26" t="n"/>
       <c r="E20" s="26" t="n"/>
       <c r="F20" s="27">
-        <f>'Параметры и допущения'!$B$9+14</f>
-        <v>46286</v>
+        <f>'Параметры и допущения'!$B$9+7</f>
+        <v>46279</v>
       </c>
       <c r="G20" s="27">
-        <f>'Параметры и допущения'!$B$9+18</f>
-        <v>46290</v>
+        <f>'Параметры и допущения'!$B$9+11</f>
+        <v>46283</v>
       </c>
       <c r="H20" s="26" t="n"/>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="26" t="inlineStr">
         <is>
-          <t>Клоны вступили в кластер, конфликтов имён узлов нет</t>
-        </is>
-      </c>
-      <c r="K20" s="28" t="n"/>
+          <t>У каждого участника работ есть памятка: кому, куда и за какое время сообщать</t>
+        </is>
+      </c>
+      <c r="K20" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L20" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M20" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N20" s="26" t="n"/>
       <c r="O20" s="26" t="n"/>
-      <c r="R20" s="23" t="n"/>
+      <c r="Q20" s="23" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>Отработать передачу роли мастера между двумя узлами</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="27">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Испытательный стенд</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F21" s="21">
         <f>'Параметры и допущения'!$B$9+14</f>
         <v>46286</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="21">
         <f>'Параметры и допущения'!$B$9+18</f>
         <v>46290</v>
       </c>
-      <c r="H21" s="26" t="n"/>
-      <c r="I21" s="26" t="n"/>
-      <c r="J21" s="26" t="inlineStr">
-        <is>
-          <t>Процедура выполнена в обе стороны и задокументирована</t>
-        </is>
-      </c>
-      <c r="K21" s="28" t="n"/>
-      <c r="L21" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M21" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" s="26" t="n"/>
-      <c r="O21" s="26" t="n"/>
+      <c r="H21" s="21">
+        <f>G21</f>
+        <v>46290</v>
+      </c>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>Процедуры восстановления кластера и передачи роли мастера ни разу не выполнялись</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>Стенд из трёх машин прошёл чек-лист приёмки: клонирование, восстановление кворума и передача роли мастера выполнены руками</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L21" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M21" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N21" s="22">
+        <f>'Параметры и допущения'!$B$26*M21</f>
+        <v>69090</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="R21" s="23" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>Отработать восстановление кворума</t>
+          <t>Развернуть тестовый мастер и клонировать его в два узла</t>
         </is>
       </c>
       <c r="C22" s="26" t="n"/>
@@ -2320,177 +2463,197 @@
       <c r="I22" s="26" t="n"/>
       <c r="J22" s="26" t="inlineStr">
         <is>
-          <t>Кворум восстановлен вручную</t>
-        </is>
-      </c>
-      <c r="K22" s="28" t="n"/>
+          <t>Клоны вступили в кластер, конфликтов имён узлов нет</t>
+        </is>
+      </c>
+      <c r="K22" s="26" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
+      </c>
       <c r="L22" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M22" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N22" s="26" t="n"/>
       <c r="O22" s="26" t="n"/>
       <c r="R22" s="23" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>Ростовская АТС — первый узел кластера</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="21">
-        <f>'Параметры и допущения'!$B$9+21</f>
-        <v>46293</v>
-      </c>
-      <c r="G23" s="21">
-        <f>'Параметры и допущения'!$B$9+25</f>
-        <v>46297</v>
-      </c>
-      <c r="H23" s="21">
-        <f>G23</f>
-        <v>46297</v>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>Вся боевая база живёт на ростовской АТС; перенести её в ЦОД без простоя можно только через кластер</t>
-        </is>
-      </c>
-      <c r="J23" s="19" t="inlineStr">
-        <is>
-          <t>Ростовская АТС работает узлом кластера без переустановки; база готова к репликации в ЦОД</t>
-        </is>
-      </c>
-      <c r="K23" s="20" t="n"/>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M23" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" s="22">
-        <f>'Параметры и допущения'!$B$22*M23</f>
-        <v>46060</v>
-      </c>
-      <c r="O23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="23" t="n"/>
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>Отработать передачу роли мастера между двумя узлами</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="27">
+        <f>'Параметры и допущения'!$B$9+14</f>
+        <v>46286</v>
+      </c>
+      <c r="G23" s="27">
+        <f>'Параметры и допущения'!$B$9+18</f>
+        <v>46290</v>
+      </c>
+      <c r="H23" s="26" t="n"/>
+      <c r="I23" s="26" t="n"/>
+      <c r="J23" s="26" t="inlineStr">
+        <is>
+          <t>Процедура выполнена в обе стороны и задокументирована</t>
+        </is>
+      </c>
+      <c r="K23" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="26" t="n"/>
+      <c r="O23" s="26" t="n"/>
+      <c r="R23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Снять резервную копию, перевести таблицы и запустить репликацию</t>
+          <t>Отработать восстановление кворума</t>
         </is>
       </c>
       <c r="C24" s="26" t="n"/>
       <c r="D24" s="26" t="n"/>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="27">
-        <f>'Параметры и допущения'!$B$9+21</f>
-        <v>46293</v>
+        <f>'Параметры и допущения'!$B$9+14</f>
+        <v>46286</v>
       </c>
       <c r="G24" s="27">
-        <f>'Параметры и допущения'!$B$9+25</f>
-        <v>46297</v>
+        <f>'Параметры и допущения'!$B$9+18</f>
+        <v>46290</v>
       </c>
       <c r="H24" s="26" t="n"/>
       <c r="I24" s="26" t="n"/>
       <c r="J24" s="26" t="inlineStr">
         <is>
-          <t>База работает в режиме кластера, число добавочных сошлось</t>
-        </is>
-      </c>
-      <c r="K24" s="28" t="n"/>
+          <t>Кворум восстановлен вручную</t>
+        </is>
+      </c>
+      <c r="K24" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L24" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M24" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24" s="26" t="n"/>
       <c r="O24" s="26" t="n"/>
-      <c r="S24" s="23" t="n"/>
+      <c r="R24" s="23" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>Выгрузить номера в общую базу и проверить</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="27">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Ростовская АТС — первый узел кластера</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F25" s="21">
         <f>'Параметры и допущения'!$B$9+21</f>
         <v>46293</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="21">
         <f>'Параметры и допущения'!$B$9+25</f>
         <v>46297</v>
       </c>
-      <c r="H25" s="26" t="n"/>
-      <c r="I25" s="26" t="n"/>
-      <c r="J25" s="26" t="inlineStr">
-        <is>
-          <t>Абоненты видны из общей базы</t>
-        </is>
-      </c>
-      <c r="K25" s="28" t="n"/>
-      <c r="L25" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M25" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="26" t="n"/>
-      <c r="O25" s="26" t="n"/>
+      <c r="H25" s="21">
+        <f>G25</f>
+        <v>46297</v>
+      </c>
+      <c r="I25" s="19" t="inlineStr">
+        <is>
+          <t>Вся боевая база живёт на ростовской АТС; перенести её в ЦОД без простоя можно только через кластер</t>
+        </is>
+      </c>
+      <c r="J25" s="19" t="inlineStr">
+        <is>
+          <t>Ростовская АТС работает узлом кластера без переустановки; база готова к репликации в ЦОД</t>
+        </is>
+      </c>
+      <c r="K25" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L25" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" s="22">
+        <f>'Параметры и допущения'!$B$26*M25</f>
+        <v>46060</v>
+      </c>
+      <c r="O25" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="S25" s="23" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>Наблюдение до переноса центра</t>
+          <t>Снять резервную копию, перевести таблицы и запустить репликацию</t>
         </is>
       </c>
       <c r="C26" s="26" t="n"/>
@@ -2508,199 +2671,223 @@
       <c r="I26" s="26" t="n"/>
       <c r="J26" s="26" t="inlineStr">
         <is>
-          <t>Отклонений не выявлено</t>
-        </is>
-      </c>
-      <c r="K26" s="28" t="n"/>
+          <t>База работает в режиме кластера, число добавочных сошлось</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L26" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M26" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="26" t="n"/>
       <c r="O26" s="26" t="n"/>
       <c r="S26" s="23" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Центр в московском ЦОД: два живых узла в разных залах</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="21">
-        <f>'Параметры и допущения'!$B$9+28</f>
-        <v>46300</v>
-      </c>
-      <c r="G27" s="21">
-        <f>'Параметры и допущения'!$B$9+39</f>
-        <v>46311</v>
-      </c>
-      <c r="H27" s="21">
-        <f>G27</f>
-        <v>46311</v>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>Управление и база сосредоточены на ростовской АТС — площадке без резервирования; по решению совещания центр переносится в ЦОД с копией во втором зале</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>Два живых узла в разных залах ЦОД обслуживают вызовы, управление на ЦОД-1; Ростов понижен до выноса, 80 московских абонентов поделены между залами</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="n"/>
-      <c r="L27" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M27" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="N27" s="22">
-        <f>'Параметры и допущения'!$B$22*M27</f>
-        <v>115150</v>
-      </c>
-      <c r="O27" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="23" t="n"/>
-      <c r="U27" s="23" t="n"/>
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Выгрузить номера в общую базу и проверить</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="26" t="n"/>
+      <c r="F27" s="27">
+        <f>'Параметры и допущения'!$B$9+21</f>
+        <v>46293</v>
+      </c>
+      <c r="G27" s="27">
+        <f>'Параметры и допущения'!$B$9+25</f>
+        <v>46297</v>
+      </c>
+      <c r="H27" s="26" t="n"/>
+      <c r="I27" s="26" t="n"/>
+      <c r="J27" s="26" t="inlineStr">
+        <is>
+          <t>Абоненты видны из общей базы</t>
+        </is>
+      </c>
+      <c r="K27" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="26" t="n"/>
+      <c r="O27" s="26" t="n"/>
+      <c r="S27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Клонировать ростовскую АТС в ЦОД-1, расшить клон в узел</t>
+          <t>Наблюдение до переноса центра</t>
         </is>
       </c>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="26" t="n"/>
       <c r="E28" s="26" t="n"/>
       <c r="F28" s="27">
-        <f>'Параметры и допущения'!$B$9+28</f>
-        <v>46300</v>
+        <f>'Параметры и допущения'!$B$9+21</f>
+        <v>46293</v>
       </c>
       <c r="G28" s="27">
-        <f>'Параметры и допущения'!$B$9+32</f>
-        <v>46304</v>
+        <f>'Параметры и допущения'!$B$9+25</f>
+        <v>46297</v>
       </c>
       <c r="H28" s="26" t="n"/>
       <c r="I28" s="26" t="n"/>
       <c r="J28" s="26" t="inlineStr">
         <is>
-          <t>ЦОД-1 в кластере, синхронизирован</t>
-        </is>
-      </c>
-      <c r="K28" s="28" t="n"/>
+          <t>Отклонений не выявлено</t>
+        </is>
+      </c>
+      <c r="K28" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L28" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M28" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" s="26" t="n"/>
       <c r="O28" s="26" t="n"/>
-      <c r="T28" s="23" t="n"/>
+      <c r="S28" s="23" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>Передать роль мастера с Ростова на ЦОД-1</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="27">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Центр в московском ЦОД: два живых узла в разных залах</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F29" s="21">
         <f>'Параметры и допущения'!$B$9+28</f>
         <v>46300</v>
       </c>
-      <c r="G29" s="27">
-        <f>'Параметры и допущения'!$B$9+32</f>
-        <v>46304</v>
-      </c>
-      <c r="H29" s="26" t="n"/>
-      <c r="I29" s="26" t="n"/>
-      <c r="J29" s="26" t="inlineStr">
-        <is>
-          <t>FreePBX и управление работают из ЦОД-1</t>
-        </is>
-      </c>
-      <c r="K29" s="28" t="n"/>
-      <c r="L29" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M29" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" s="26" t="n"/>
-      <c r="O29" s="26" t="n"/>
+      <c r="G29" s="21">
+        <f>'Параметры и допущения'!$B$9+39</f>
+        <v>46311</v>
+      </c>
+      <c r="H29" s="21">
+        <f>G29</f>
+        <v>46311</v>
+      </c>
+      <c r="I29" s="19" t="inlineStr">
+        <is>
+          <t>Управление и база сосредоточены на ростовской АТС — площадке без резервирования; по решению совещания центр переносится в ЦОД с копией во втором зале</t>
+        </is>
+      </c>
+      <c r="J29" s="19" t="inlineStr">
+        <is>
+          <t>Два живых узла в разных залах ЦОД обслуживают вызовы, управление на ЦОД-1; Ростов понижен до выноса, 80 московских абонентов поделены между залами</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M29" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" s="22">
+        <f>'Параметры и допущения'!$B$26*M29</f>
+        <v>115150</v>
+      </c>
+      <c r="O29" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="T29" s="23" t="n"/>
+      <c r="U29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Клонировать ЦОД-1 в ЦОД-2 (второй зал), расшить клон в узел</t>
+          <t>Клонировать ростовскую АТС в ЦОД-1, расшить клон в узел</t>
         </is>
       </c>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="26" t="n"/>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="27">
-        <f>'Параметры и допущения'!$B$9+35</f>
-        <v>46307</v>
+        <f>'Параметры и допущения'!$B$9+28</f>
+        <v>46300</v>
       </c>
       <c r="G30" s="27">
-        <f>'Параметры и допущения'!$B$9+39</f>
-        <v>46311</v>
+        <f>'Параметры и допущения'!$B$9+32</f>
+        <v>46304</v>
       </c>
       <c r="H30" s="26" t="n"/>
       <c r="I30" s="26" t="n"/>
       <c r="J30" s="26" t="inlineStr">
         <is>
-          <t>ЦОД-2 в кластере, узлов три — кворум нечётный</t>
-        </is>
-      </c>
-      <c r="K30" s="28" t="n"/>
+          <t>ЦОД-1 в кластере, синхронизирован</t>
+        </is>
+      </c>
+      <c r="K30" s="26" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
+      </c>
       <c r="L30" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -2711,38 +2898,42 @@
       </c>
       <c r="N30" s="26" t="n"/>
       <c r="O30" s="26" t="n"/>
-      <c r="U30" s="23" t="n"/>
+      <c r="T30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Сделать ЦОД-2 живым узлом: транк оператора, FreePBX оставить выключенным</t>
+          <t>Передать роль мастера с Ростова на ЦОД-1</t>
         </is>
       </c>
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="27">
-        <f>'Параметры и допущения'!$B$9+35</f>
-        <v>46307</v>
+        <f>'Параметры и допущения'!$B$9+28</f>
+        <v>46300</v>
       </c>
       <c r="G31" s="27">
-        <f>'Параметры и допущения'!$B$9+39</f>
-        <v>46311</v>
+        <f>'Параметры и допущения'!$B$9+32</f>
+        <v>46304</v>
       </c>
       <c r="H31" s="26" t="n"/>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="26" t="inlineStr">
         <is>
-          <t>ЦОД-2 несёт вызовы наравне с ЦОД-1; панель управления включена ровно на одном узле</t>
-        </is>
-      </c>
-      <c r="K31" s="28" t="n"/>
+          <t>FreePBX и управление работают из ЦОД-1</t>
+        </is>
+      </c>
+      <c r="K31" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L31" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -2753,17 +2944,17 @@
       </c>
       <c r="N31" s="26" t="n"/>
       <c r="O31" s="26" t="n"/>
-      <c r="U31" s="23" t="n"/>
+      <c r="T31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>Понизить Ростов до выноса, поделить 80 московских абонентов между залами</t>
+          <t>Клонировать ЦОД-1 в ЦОД-2 (второй зал), расшить клон в узел</t>
         </is>
       </c>
       <c r="C32" s="26" t="n"/>
@@ -2781,10 +2972,14 @@
       <c r="I32" s="26" t="n"/>
       <c r="J32" s="26" t="inlineStr">
         <is>
-          <t>По 40 абонентов на зал, каждый зал прописан другому резервным</t>
-        </is>
-      </c>
-      <c r="K32" s="28" t="n"/>
+          <t>ЦОД-2 в кластере, узлов три — кворум нечётный</t>
+        </is>
+      </c>
+      <c r="K32" s="26" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
+      </c>
       <c r="L32" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -2798,98 +2993,85 @@
       <c r="U32" s="23" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>Пилотный вынос — Ставрополь</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="21">
-        <f>'Параметры и допущения'!$B$9+42</f>
-        <v>46314</v>
-      </c>
-      <c r="G33" s="21">
-        <f>'Параметры и допущения'!$B$9+53</f>
-        <v>46325</v>
-      </c>
-      <c r="H33" s="21">
-        <f>G33</f>
-        <v>46325</v>
-      </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>Схема «центр в ЦОД — вынос в городе» не проверена на реальной нагрузке и канале</t>
-        </is>
-      </c>
-      <c r="J33" s="19" t="inlineStr">
-        <is>
-          <t>Ставрополь работает выносом: локальная регистрация телефонов, свой выход в город, переключение в ЦОД при отказе площадки; его 74 абонента больше не зависят от канала до Ростова</t>
-        </is>
-      </c>
-      <c r="K33" s="20" t="n"/>
-      <c r="L33" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M33" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="N33" s="22">
-        <f>'Параметры и допущения'!$B$22*M33</f>
-        <v>115150</v>
-      </c>
-      <c r="O33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="23" t="n"/>
-      <c r="W33" s="23" t="n"/>
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Сделать ЦОД-2 живым узлом: транк оператора, FreePBX оставить выключенным</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="27">
+        <f>'Параметры и допущения'!$B$9+35</f>
+        <v>46307</v>
+      </c>
+      <c r="G33" s="27">
+        <f>'Параметры и допущения'!$B$9+39</f>
+        <v>46311</v>
+      </c>
+      <c r="H33" s="26" t="n"/>
+      <c r="I33" s="26" t="n"/>
+      <c r="J33" s="26" t="inlineStr">
+        <is>
+          <t>ЦОД-2 несёт вызовы наравне с ЦОД-1; панель управления включена ровно на одном узле</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M33" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" s="26" t="n"/>
+      <c r="O33" s="26" t="n"/>
+      <c r="U33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Клонировать мастер и расшить клон в вынос</t>
+          <t>Понизить Ростов до выноса, поделить 80 московских абонентов между залами</t>
         </is>
       </c>
       <c r="C34" s="26" t="n"/>
       <c r="D34" s="26" t="n"/>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="27">
-        <f>'Параметры и допущения'!$B$9+42</f>
-        <v>46314</v>
+        <f>'Параметры и допущения'!$B$9+35</f>
+        <v>46307</v>
       </c>
       <c r="G34" s="27">
-        <f>'Параметры и допущения'!$B$9+46</f>
-        <v>46318</v>
+        <f>'Параметры и допущения'!$B$9+39</f>
+        <v>46311</v>
       </c>
       <c r="H34" s="26" t="n"/>
       <c r="I34" s="26" t="n"/>
       <c r="J34" s="26" t="inlineStr">
         <is>
-          <t>Вынос в кластере</t>
-        </is>
-      </c>
-      <c r="K34" s="28" t="n"/>
+          <t>По 40 абонентов на зал, каждый зал прописан другому резервным</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L34" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -2900,59 +3082,88 @@
       </c>
       <c r="N34" s="26" t="n"/>
       <c r="O34" s="26" t="n"/>
-      <c r="V34" s="23" t="n"/>
+      <c r="U34" s="23" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>Настроить межузловые транки и перенести диалплан</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="27">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Пилотный вынос — Ставрополь</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F35" s="21">
         <f>'Параметры и допущения'!$B$9+42</f>
         <v>46314</v>
       </c>
-      <c r="G35" s="27">
-        <f>'Параметры и допущения'!$B$9+46</f>
-        <v>46318</v>
-      </c>
-      <c r="H35" s="26" t="n"/>
-      <c r="I35" s="26" t="n"/>
-      <c r="J35" s="26" t="inlineStr">
-        <is>
-          <t>Вызовы между ЦОД, Ростовом и Ставрополем проходят</t>
-        </is>
-      </c>
-      <c r="K35" s="28" t="n"/>
-      <c r="L35" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M35" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" s="26" t="n"/>
-      <c r="O35" s="26" t="n"/>
+      <c r="G35" s="21">
+        <f>'Параметры и допущения'!$B$9+53</f>
+        <v>46325</v>
+      </c>
+      <c r="H35" s="21">
+        <f>G35</f>
+        <v>46325</v>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>Схема «центр в ЦОД — вынос в городе» не проверена на реальной нагрузке и канале</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>Ставрополь работает выносом: локальная регистрация телефонов, свой выход в город, переключение в ЦОД при отказе площадки; его 74 абонента больше не зависят от канала до Ростова</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N35" s="22">
+        <f>'Параметры и допущения'!$B$26*M35</f>
+        <v>115150</v>
+      </c>
+      <c r="O35" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="V35" s="23" t="n"/>
+      <c r="W35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>Подключить локальный транк оператора</t>
+          <t>Клонировать мастер и расшить клон в вынос</t>
         </is>
       </c>
       <c r="C36" s="26" t="n"/>
@@ -2970,17 +3181,21 @@
       <c r="I36" s="26" t="n"/>
       <c r="J36" s="26" t="inlineStr">
         <is>
-          <t>Свой выход в город работает</t>
-        </is>
-      </c>
-      <c r="K36" s="28" t="n"/>
+          <t>Вынос в кластере</t>
+        </is>
+      </c>
+      <c r="K36" s="26" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
+      </c>
       <c r="L36" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M36" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" s="26" t="n"/>
       <c r="O36" s="26" t="n"/>
@@ -2989,12 +3204,12 @@
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>Перевести телефоны на вынос через провижининг</t>
+          <t>Настроить межузловые транки и перенести диалплан</t>
         </is>
       </c>
       <c r="C37" s="26" t="n"/>
@@ -3012,10 +3227,14 @@
       <c r="I37" s="26" t="n"/>
       <c r="J37" s="26" t="inlineStr">
         <is>
-          <t>Телефоны регистрируются в Ставрополе, резервный сервер — ЦОД-1</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="n"/>
+          <t>Вызовы между ЦОД, Ростовом и Ставрополем проходят</t>
+        </is>
+      </c>
+      <c r="K37" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L37" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -3031,439 +3250,452 @@
     <row r="38">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>Неделя наблюдения под реальной нагрузкой</t>
+          <t>Подключить локальный транк оператора</t>
         </is>
       </c>
       <c r="C38" s="26" t="n"/>
       <c r="D38" s="26" t="n"/>
       <c r="E38" s="26" t="n"/>
       <c r="F38" s="27">
-        <f>'Параметры и допущения'!$B$9+49</f>
-        <v>46321</v>
+        <f>'Параметры и допущения'!$B$9+42</f>
+        <v>46314</v>
       </c>
       <c r="G38" s="27">
-        <f>'Параметры и допущения'!$B$9+53</f>
-        <v>46325</v>
+        <f>'Параметры и допущения'!$B$9+46</f>
+        <v>46318</v>
       </c>
       <c r="H38" s="26" t="n"/>
       <c r="I38" s="26" t="n"/>
       <c r="J38" s="26" t="inlineStr">
         <is>
-          <t>Отказ площадки и возврат отработаны, решение о тиражировании принято</t>
-        </is>
-      </c>
-      <c r="K38" s="28" t="n"/>
+          <t>Свой выход в город работает</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L38" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M38" s="26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N38" s="26" t="n"/>
       <c r="O38" s="26" t="n"/>
-      <c r="W38" s="23" t="n"/>
+      <c r="V38" s="23" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Учебное переключение управления между залами ЦОД</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="21">
-        <f>'Параметры и допущения'!$B$9+56</f>
-        <v>46328</v>
-      </c>
-      <c r="G39" s="21">
-        <f>'Параметры и допущения'!$B$9+60</f>
-        <v>46332</v>
-      </c>
-      <c r="H39" s="21">
-        <f>G39</f>
-        <v>46332</v>
-      </c>
-      <c r="I39" s="19" t="inlineStr">
-        <is>
-          <t>Вызовы оба зала несут постоянно, но панель управления живёт на одном узле; её переключение не опробовано</t>
-        </is>
-      </c>
-      <c r="J39" s="19" t="inlineStr">
-        <is>
-          <t>Управление переведено в зал 2 и возвращено в зал 1 в согласованное окно; время переключения измерено и внесено в регламент</t>
-        </is>
-      </c>
-      <c r="K39" s="20" t="n"/>
-      <c r="L39" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" s="22">
-        <f>'Параметры и допущения'!$B$22*M39</f>
-        <v>34545</v>
-      </c>
-      <c r="O39" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" s="23" t="n"/>
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>Перевести телефоны на вынос через провижининг</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="26" t="n"/>
+      <c r="F39" s="27">
+        <f>'Параметры и допущения'!$B$9+42</f>
+        <v>46314</v>
+      </c>
+      <c r="G39" s="27">
+        <f>'Параметры и допущения'!$B$9+46</f>
+        <v>46318</v>
+      </c>
+      <c r="H39" s="26" t="n"/>
+      <c r="I39" s="26" t="n"/>
+      <c r="J39" s="26" t="inlineStr">
+        <is>
+          <t>Телефоны регистрируются в Ставрополе, резервный сервер — ЦОД-1</t>
+        </is>
+      </c>
+      <c r="K39" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M39" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" s="26" t="n"/>
+      <c r="O39" s="26" t="n"/>
+      <c r="V39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Включить FreePBX на ЦОД-2, проверить управление и звонки</t>
+          <t>Неделя наблюдения под реальной нагрузкой</t>
         </is>
       </c>
       <c r="C40" s="26" t="n"/>
       <c r="D40" s="26" t="n"/>
       <c r="E40" s="26" t="n"/>
       <c r="F40" s="27">
-        <f>'Параметры и допущения'!$B$9+56</f>
-        <v>46328</v>
+        <f>'Параметры и допущения'!$B$9+49</f>
+        <v>46321</v>
       </c>
       <c r="G40" s="27">
-        <f>'Параметры и допущения'!$B$9+60</f>
-        <v>46332</v>
+        <f>'Параметры и допущения'!$B$9+53</f>
+        <v>46325</v>
       </c>
       <c r="H40" s="26" t="n"/>
       <c r="I40" s="26" t="n"/>
       <c r="J40" s="26" t="inlineStr">
         <is>
-          <t>Управление работает из зала 2, вызовы не прерывались</t>
-        </is>
-      </c>
-      <c r="K40" s="28" t="n"/>
+          <t>Отказ площадки и возврат отработаны, решение о тиражировании принято</t>
+        </is>
+      </c>
+      <c r="K40" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L40" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M40" s="26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" s="26" t="n"/>
       <c r="O40" s="26" t="n"/>
-      <c r="X40" s="23" t="n"/>
+      <c r="W40" s="23" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>Вернуть управление в ЦОД-1, зафиксировать время переключения</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="n"/>
-      <c r="D41" s="26" t="n"/>
-      <c r="E41" s="26" t="n"/>
-      <c r="F41" s="27">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Учебное переключение управления между залами ЦОД</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F41" s="21">
         <f>'Параметры и допущения'!$B$9+56</f>
         <v>46328</v>
       </c>
-      <c r="G41" s="27">
+      <c r="G41" s="21">
         <f>'Параметры и допущения'!$B$9+60</f>
         <v>46332</v>
       </c>
-      <c r="H41" s="26" t="n"/>
-      <c r="I41" s="26" t="n"/>
-      <c r="J41" s="26" t="inlineStr">
-        <is>
-          <t>Схема в штатном состоянии, норматив записан в регламент</t>
-        </is>
-      </c>
-      <c r="K41" s="28" t="n"/>
-      <c r="L41" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M41" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="26" t="n"/>
-      <c r="O41" s="26" t="n"/>
+      <c r="H41" s="21">
+        <f>G41</f>
+        <v>46332</v>
+      </c>
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>Вызовы оба зала несут постоянно, но панель управления живёт на одном узле; её переключение не опробовано</t>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>Управление переведено в зал 2 и возвращено в зал 1 в согласованное окно; время переключения измерено и внесено в регламент</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M41" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" s="22">
+        <f>'Параметры и допущения'!$B$26*M41</f>
+        <v>34545</v>
+      </c>
+      <c r="O41" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="X41" s="23" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>Выносы Нижний Новгород и Славянск-на-Кубани</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="21">
-        <f>'Параметры и допущения'!$B$9+63</f>
-        <v>46335</v>
-      </c>
-      <c r="G42" s="21">
-        <f>'Параметры и допущения'!$B$9+74</f>
-        <v>46346</v>
-      </c>
-      <c r="H42" s="21">
-        <f>G42</f>
-        <v>46346</v>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>Обе площадки обслуживаются отдельными станциями вне кластера; на них впервые отрабатывается полный перенос с гашением старой АТС</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>Обе площадки работают выносами, старые станции выведены из эксплуатации</t>
-        </is>
-      </c>
-      <c r="K42" s="20" t="n"/>
-      <c r="L42" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="N42" s="22">
-        <f>'Параметры и допущения'!$B$22*M42</f>
-        <v>103635</v>
-      </c>
-      <c r="O42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="23" t="n"/>
-      <c r="Z42" s="23" t="n"/>
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>Включить FreePBX на ЦОД-2, проверить управление и звонки</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="26" t="n"/>
+      <c r="F42" s="27">
+        <f>'Параметры и допущения'!$B$9+56</f>
+        <v>46328</v>
+      </c>
+      <c r="G42" s="27">
+        <f>'Параметры и допущения'!$B$9+60</f>
+        <v>46332</v>
+      </c>
+      <c r="H42" s="26" t="n"/>
+      <c r="I42" s="26" t="n"/>
+      <c r="J42" s="26" t="inlineStr">
+        <is>
+          <t>Управление работает из зала 2, вызовы не прерывались</t>
+        </is>
+      </c>
+      <c r="K42" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M42" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" s="26" t="n"/>
+      <c r="O42" s="26" t="n"/>
+      <c r="X42" s="23" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>Нижний Новгород — 164 абонента, старая станция гасится</t>
+          <t>Вернуть управление в ЦОД-1, зафиксировать время переключения</t>
         </is>
       </c>
       <c r="C43" s="26" t="n"/>
       <c r="D43" s="26" t="n"/>
       <c r="E43" s="26" t="n"/>
       <c r="F43" s="27">
-        <f>'Параметры и допущения'!$B$9+63</f>
-        <v>46335</v>
+        <f>'Параметры и допущения'!$B$9+56</f>
+        <v>46328</v>
       </c>
       <c r="G43" s="27">
-        <f>'Параметры и допущения'!$B$9+67</f>
-        <v>46339</v>
+        <f>'Параметры и допущения'!$B$9+60</f>
+        <v>46332</v>
       </c>
       <c r="H43" s="26" t="n"/>
       <c r="I43" s="26" t="n"/>
       <c r="J43" s="26" t="inlineStr">
         <is>
-          <t>Вынос работает, станция выведена</t>
-        </is>
-      </c>
-      <c r="K43" s="28" t="n"/>
+          <t>Схема в штатном состоянии, норматив записан в регламент</t>
+        </is>
+      </c>
+      <c r="K43" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L43" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M43" s="26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N43" s="26" t="n"/>
       <c r="O43" s="26" t="n"/>
-      <c r="Y43" s="23" t="n"/>
+      <c r="X43" s="23" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="inlineStr">
-        <is>
-          <t>Славянск-на-Кубани — 140 абонентов, старая станция гасится</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="27">
-        <f>'Параметры и допущения'!$B$9+70</f>
-        <v>46342</v>
-      </c>
-      <c r="G44" s="27">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>Выносы Нижний Новгород и Славянск-на-Кубани</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F44" s="21">
+        <f>'Параметры и допущения'!$B$9+63</f>
+        <v>46335</v>
+      </c>
+      <c r="G44" s="21">
         <f>'Параметры и допущения'!$B$9+74</f>
         <v>46346</v>
       </c>
-      <c r="H44" s="26" t="n"/>
-      <c r="I44" s="26" t="n"/>
-      <c r="J44" s="26" t="inlineStr">
-        <is>
-          <t>Вынос работает, станция выведена; этап 1 закрыт</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="n"/>
-      <c r="L44" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M44" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N44" s="26" t="n"/>
-      <c r="O44" s="26" t="n"/>
+      <c r="H44" s="21">
+        <f>G44</f>
+        <v>46346</v>
+      </c>
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>Обе площадки обслуживаются отдельными станциями вне кластера; на них впервые отрабатывается полный перенос с гашением старой АТС</t>
+        </is>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>Обе площадки работают выносами, старые станции выведены из эксплуатации</t>
+        </is>
+      </c>
+      <c r="K44" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="N44" s="22">
+        <f>'Параметры и допущения'!$B$26*M44</f>
+        <v>103635</v>
+      </c>
+      <c r="O44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="23" t="n"/>
       <c r="Z44" s="23" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>Консолидация мелких АТС этапа 1</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="21">
-        <f>'Параметры и допущения'!$B$9+49</f>
-        <v>46321</v>
-      </c>
-      <c r="G45" s="21">
-        <f>'Параметры и допущения'!$B$9+74</f>
-        <v>46346</v>
-      </c>
-      <c r="H45" s="21">
-        <f>G45</f>
-        <v>46346</v>
-      </c>
-      <c r="I45" s="19" t="inlineStr">
-        <is>
-          <t>Шесть станций на 127 абонентов дорого поддерживать и невыгодно включать в кластер отдельными узлами</t>
-        </is>
-      </c>
-      <c r="J45" s="19" t="inlineStr">
-        <is>
-          <t>Абоненты мелких станций переведены на выносы и в ЦОД, станции выведены из эксплуатации</t>
-        </is>
-      </c>
-      <c r="K45" s="19" t="inlineStr">
-        <is>
-          <t>Кириевская Е.</t>
-        </is>
-      </c>
-      <c r="L45" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M45" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="N45" s="22">
-        <f>'Параметры и допущения'!$B$22*M45</f>
-        <v>69090</v>
-      </c>
-      <c r="O45" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" s="23" t="n"/>
-      <c r="X45" s="23" t="n"/>
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>Нижний Новгород — 164 абонента, старая станция гасится</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="n"/>
+      <c r="D45" s="26" t="n"/>
+      <c r="E45" s="26" t="n"/>
+      <c r="F45" s="27">
+        <f>'Параметры и допущения'!$B$9+63</f>
+        <v>46335</v>
+      </c>
+      <c r="G45" s="27">
+        <f>'Параметры и допущения'!$B$9+67</f>
+        <v>46339</v>
+      </c>
+      <c r="H45" s="26" t="n"/>
+      <c r="I45" s="26" t="n"/>
+      <c r="J45" s="26" t="inlineStr">
+        <is>
+          <t>Вынос работает, станция выведена</t>
+        </is>
+      </c>
+      <c r="K45" s="26" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M45" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N45" s="26" t="n"/>
+      <c r="O45" s="26" t="n"/>
       <c r="Y45" s="23" t="n"/>
-      <c r="Z45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>Манитек, Семикаракорский, Цимлянский, Приманыческий — 73 абонента — в Ростов</t>
+          <t>Славянск-на-Кубани — 140 абонентов, старая станция гасится</t>
         </is>
       </c>
       <c r="C46" s="26" t="n"/>
       <c r="D46" s="26" t="n"/>
       <c r="E46" s="26" t="n"/>
       <c r="F46" s="27">
-        <f>'Параметры и допущения'!$B$9+49</f>
-        <v>46321</v>
+        <f>'Параметры и допущения'!$B$9+70</f>
+        <v>46342</v>
       </c>
       <c r="G46" s="27">
-        <f>'Параметры и допущения'!$B$9+60</f>
-        <v>46332</v>
+        <f>'Параметры и допущения'!$B$9+74</f>
+        <v>46346</v>
       </c>
       <c r="H46" s="26" t="n"/>
       <c r="I46" s="26" t="n"/>
       <c r="J46" s="26" t="inlineStr">
         <is>
-          <t>Станции выведены</t>
+          <t>Вынос работает, станция выведена; этап 1 закрыт</t>
         </is>
       </c>
       <c r="K46" s="26" t="inlineStr">
         <is>
-          <t>Кириевская Е.</t>
+          <t>Дулепов А.</t>
         </is>
       </c>
       <c r="L46" s="26" t="inlineStr">
@@ -3472,86 +3704,112 @@
         </is>
       </c>
       <c r="M46" s="26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N46" s="26" t="n"/>
       <c r="O46" s="26" t="n"/>
-      <c r="W46" s="23" t="n"/>
-      <c r="X46" s="23" t="n"/>
+      <c r="Z46" s="23" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="inlineStr">
-        <is>
-          <t>ССЗ — 39 абонентов — в Нижний Новгород</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="n"/>
-      <c r="D47" s="26" t="n"/>
-      <c r="E47" s="26" t="n"/>
-      <c r="F47" s="27">
-        <f>'Параметры и допущения'!$B$9+70</f>
-        <v>46342</v>
-      </c>
-      <c r="G47" s="27">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>Консолидация мелких АТС этапа 1</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F47" s="21">
+        <f>'Параметры и допущения'!$B$9+49</f>
+        <v>46321</v>
+      </c>
+      <c r="G47" s="21">
         <f>'Параметры и допущения'!$B$9+74</f>
         <v>46346</v>
       </c>
-      <c r="H47" s="26" t="n"/>
-      <c r="I47" s="26" t="n"/>
-      <c r="J47" s="26" t="inlineStr">
-        <is>
-          <t>Станция выведена</t>
-        </is>
-      </c>
-      <c r="K47" s="26" t="inlineStr">
+      <c r="H47" s="21">
+        <f>G47</f>
+        <v>46346</v>
+      </c>
+      <c r="I47" s="19" t="inlineStr">
+        <is>
+          <t>Шесть станций на 127 абонентов дорого поддерживать и невыгодно включать в кластер отдельными узлами</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>Абоненты мелких станций переведены на выносы и в ЦОД, станции выведены из эксплуатации</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="inlineStr">
         <is>
           <t>Кириевская Е.</t>
         </is>
       </c>
-      <c r="L47" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M47" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" s="26" t="n"/>
-      <c r="O47" s="26" t="n"/>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M47" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N47" s="22">
+        <f>'Параметры и допущения'!$B$26*M47</f>
+        <v>69090</v>
+      </c>
+      <c r="O47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="23" t="n"/>
+      <c r="X47" s="23" t="n"/>
+      <c r="Y47" s="23" t="n"/>
       <c r="Z47" s="23" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>Локальный PBX — 15 абонентов — в ЦОД</t>
+          <t>Манитек, Семикаракорский, Цимлянский, Приманыческий — 73 абонента — в Ростов</t>
         </is>
       </c>
       <c r="C48" s="26" t="n"/>
       <c r="D48" s="26" t="n"/>
       <c r="E48" s="26" t="n"/>
       <c r="F48" s="27">
-        <f>'Параметры и допущения'!$B$9+77</f>
-        <v>46349</v>
+        <f>'Параметры и допущения'!$B$9+49</f>
+        <v>46321</v>
       </c>
       <c r="G48" s="27">
-        <f>'Параметры и допущения'!$B$9+81</f>
-        <v>46353</v>
+        <f>'Параметры и допущения'!$B$9+60</f>
+        <v>46332</v>
       </c>
       <c r="H48" s="26" t="n"/>
       <c r="I48" s="26" t="n"/>
       <c r="J48" s="26" t="inlineStr">
         <is>
-          <t>Станция выведена</t>
+          <t>Станции выведены</t>
         </is>
       </c>
       <c r="K48" s="26" t="inlineStr">
@@ -3565,111 +3823,86 @@
         </is>
       </c>
       <c r="M48" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N48" s="26" t="n"/>
       <c r="O48" s="26" t="n"/>
-      <c r="AA48" s="23" t="n"/>
+      <c r="W48" s="23" t="n"/>
+      <c r="X48" s="23" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="inlineStr">
-        <is>
-          <t>Перевод абонентов этапа 1 на единый план нумерации</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="21">
-        <f>'Параметры и допущения'!$B$9+35</f>
-        <v>46307</v>
-      </c>
-      <c r="G49" s="21">
-        <f>'Параметры и допущения'!$B$9+81</f>
-        <v>46353</v>
-      </c>
-      <c r="H49" s="21">
-        <f>G49</f>
-        <v>46353</v>
-      </c>
-      <c r="I49" s="19" t="inlineStr">
-        <is>
-          <t>Станции используют пересекающиеся номера, единый план невозможен без разведения конфликтов</t>
-        </is>
-      </c>
-      <c r="J49" s="19" t="inlineStr">
-        <is>
-          <t>810 абонентов этапа 1 переведены на пятизначную нумерацию, переадресации сняты</t>
-        </is>
-      </c>
-      <c r="K49" s="19" t="inlineStr">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>ССЗ — 39 абонентов — в Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="26" t="n"/>
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="27">
+        <f>'Параметры и допущения'!$B$9+70</f>
+        <v>46342</v>
+      </c>
+      <c r="G49" s="27">
+        <f>'Параметры и допущения'!$B$9+74</f>
+        <v>46346</v>
+      </c>
+      <c r="H49" s="26" t="n"/>
+      <c r="I49" s="26" t="n"/>
+      <c r="J49" s="26" t="inlineStr">
+        <is>
+          <t>Станция выведена</t>
+        </is>
+      </c>
+      <c r="K49" s="26" t="inlineStr">
         <is>
           <t>Кириевская Е.</t>
         </is>
       </c>
-      <c r="L49" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M49" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="N49" s="22">
-        <f>'Параметры и допущения'!$B$22*M49</f>
-        <v>138180</v>
-      </c>
-      <c r="O49" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="23" t="n"/>
-      <c r="V49" s="23" t="n"/>
-      <c r="W49" s="23" t="n"/>
-      <c r="X49" s="23" t="n"/>
-      <c r="Y49" s="23" t="n"/>
+      <c r="L49" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M49" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="26" t="n"/>
+      <c r="O49" s="26" t="n"/>
       <c r="Z49" s="23" t="n"/>
-      <c r="AA49" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>Ростов и его мелкие площадки — 352 абонента</t>
+          <t>Локальный PBX — 15 абонентов — в ЦОД</t>
         </is>
       </c>
       <c r="C50" s="26" t="n"/>
       <c r="D50" s="26" t="n"/>
       <c r="E50" s="26" t="n"/>
       <c r="F50" s="27">
-        <f>'Параметры и допущения'!$B$9+35</f>
-        <v>46307</v>
+        <f>'Параметры и допущения'!$B$9+77</f>
+        <v>46349</v>
       </c>
       <c r="G50" s="27">
-        <f>'Параметры и допущения'!$B$9+60</f>
-        <v>46332</v>
+        <f>'Параметры и допущения'!$B$9+81</f>
+        <v>46353</v>
       </c>
       <c r="H50" s="26" t="n"/>
       <c r="I50" s="26" t="n"/>
       <c r="J50" s="26" t="inlineStr">
         <is>
-          <t>Площадки переведены</t>
+          <t>Станция выведена</t>
         </is>
       </c>
       <c r="K50" s="26" t="inlineStr">
@@ -3683,83 +3916,109 @@
         </is>
       </c>
       <c r="M50" s="26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N50" s="26" t="n"/>
       <c r="O50" s="26" t="n"/>
-      <c r="U50" s="23" t="n"/>
-      <c r="V50" s="23" t="n"/>
-      <c r="W50" s="23" t="n"/>
-      <c r="X50" s="23" t="n"/>
+      <c r="AA50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="inlineStr">
-        <is>
-          <t>Ставрополь — 74 абонента</t>
-        </is>
-      </c>
-      <c r="C51" s="26" t="n"/>
-      <c r="D51" s="26" t="n"/>
-      <c r="E51" s="26" t="n"/>
-      <c r="F51" s="27">
-        <f>'Параметры и допущения'!$B$9+49</f>
-        <v>46321</v>
-      </c>
-      <c r="G51" s="27">
-        <f>'Параметры и допущения'!$B$9+60</f>
-        <v>46332</v>
-      </c>
-      <c r="H51" s="26" t="n"/>
-      <c r="I51" s="26" t="n"/>
-      <c r="J51" s="26" t="inlineStr">
-        <is>
-          <t>Площадка переведена</t>
-        </is>
-      </c>
-      <c r="K51" s="26" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>Перевод абонентов этапа 1 на единый план нумерации</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F51" s="21">
+        <f>'Параметры и допущения'!$B$9+35</f>
+        <v>46307</v>
+      </c>
+      <c r="G51" s="21">
+        <f>'Параметры и допущения'!$B$9+81</f>
+        <v>46353</v>
+      </c>
+      <c r="H51" s="21">
+        <f>G51</f>
+        <v>46353</v>
+      </c>
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>Станции используют пересекающиеся номера, единый план невозможен без разведения конфликтов</t>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>810 абонентов этапа 1 переведены на пятизначную нумерацию, переадресации сняты</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="inlineStr">
         <is>
           <t>Кириевская Е.</t>
         </is>
       </c>
-      <c r="L51" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M51" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" s="26" t="n"/>
-      <c r="O51" s="26" t="n"/>
+      <c r="L51" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M51" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="N51" s="22">
+        <f>'Параметры и допущения'!$B$26*M51</f>
+        <v>138180</v>
+      </c>
+      <c r="O51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="23" t="n"/>
+      <c r="V51" s="23" t="n"/>
       <c r="W51" s="23" t="n"/>
       <c r="X51" s="23" t="n"/>
+      <c r="Y51" s="23" t="n"/>
+      <c r="Z51" s="23" t="n"/>
+      <c r="AA51" s="23" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>Нижний Новгород и ССЗ — 164 абонента</t>
+          <t>Ростов и его мелкие площадки — 352 абонента</t>
         </is>
       </c>
       <c r="C52" s="26" t="n"/>
       <c r="D52" s="26" t="n"/>
       <c r="E52" s="26" t="n"/>
       <c r="F52" s="27">
-        <f>'Параметры и допущения'!$B$9+63</f>
-        <v>46335</v>
+        <f>'Параметры и допущения'!$B$9+35</f>
+        <v>46307</v>
       </c>
       <c r="G52" s="27">
-        <f>'Параметры и допущения'!$B$9+81</f>
-        <v>46353</v>
+        <f>'Параметры и допущения'!$B$9+60</f>
+        <v>46332</v>
       </c>
       <c r="H52" s="26" t="n"/>
       <c r="I52" s="26" t="n"/>
@@ -3779,35 +4038,36 @@
         </is>
       </c>
       <c r="M52" s="26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N52" s="26" t="n"/>
       <c r="O52" s="26" t="n"/>
-      <c r="Y52" s="23" t="n"/>
-      <c r="Z52" s="23" t="n"/>
-      <c r="AA52" s="23" t="n"/>
+      <c r="U52" s="23" t="n"/>
+      <c r="V52" s="23" t="n"/>
+      <c r="W52" s="23" t="n"/>
+      <c r="X52" s="23" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>Славянск-на-Кубани — 140 абонентов</t>
+          <t>Ставрополь — 74 абонента</t>
         </is>
       </c>
       <c r="C53" s="26" t="n"/>
       <c r="D53" s="26" t="n"/>
       <c r="E53" s="26" t="n"/>
       <c r="F53" s="27">
-        <f>'Параметры и допущения'!$B$9+70</f>
-        <v>46342</v>
+        <f>'Параметры и допущения'!$B$9+49</f>
+        <v>46321</v>
       </c>
       <c r="G53" s="27">
-        <f>'Параметры и допущения'!$B$9+81</f>
-        <v>46353</v>
+        <f>'Параметры и допущения'!$B$9+60</f>
+        <v>46332</v>
       </c>
       <c r="H53" s="26" t="n"/>
       <c r="I53" s="26" t="n"/>
@@ -3827,22 +4087,22 @@
         </is>
       </c>
       <c r="M53" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53" s="26" t="n"/>
       <c r="O53" s="26" t="n"/>
-      <c r="Z53" s="23" t="n"/>
-      <c r="AA53" s="23" t="n"/>
+      <c r="W53" s="23" t="n"/>
+      <c r="X53" s="23" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>Москва — 80 абонентов, снятие переадресаций</t>
+          <t>Нижний Новгород и ССЗ — 164 абонента</t>
         </is>
       </c>
       <c r="C54" s="26" t="n"/>
@@ -3860,7 +4120,7 @@
       <c r="I54" s="26" t="n"/>
       <c r="J54" s="26" t="inlineStr">
         <is>
-          <t>Площадка переведена</t>
+          <t>Площадки переведены</t>
         </is>
       </c>
       <c r="K54" s="26" t="inlineStr">
@@ -3874,7 +4134,7 @@
         </is>
       </c>
       <c r="M54" s="26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N54" s="26" t="n"/>
       <c r="O54" s="26" t="n"/>
@@ -3882,199 +4142,218 @@
       <c r="Z54" s="23" t="n"/>
       <c r="AA54" s="23" t="n"/>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="17" t="n"/>
-      <c r="B55" s="18" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>Славянск-на-Кубани — 140 абонентов</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="n"/>
+      <c r="D55" s="26" t="n"/>
+      <c r="E55" s="26" t="n"/>
+      <c r="F55" s="27">
+        <f>'Параметры и допущения'!$B$9+70</f>
+        <v>46342</v>
+      </c>
+      <c r="G55" s="27">
+        <f>'Параметры и допущения'!$B$9+81</f>
+        <v>46353</v>
+      </c>
+      <c r="H55" s="26" t="n"/>
+      <c r="I55" s="26" t="n"/>
+      <c r="J55" s="26" t="inlineStr">
+        <is>
+          <t>Площадка переведена</t>
+        </is>
+      </c>
+      <c r="K55" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L55" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M55" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" s="26" t="n"/>
+      <c r="O55" s="26" t="n"/>
+      <c r="Z55" s="23" t="n"/>
+      <c r="AA55" s="23" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>Москва — 80 абонентов, снятие переадресаций</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="n"/>
+      <c r="D56" s="26" t="n"/>
+      <c r="E56" s="26" t="n"/>
+      <c r="F56" s="27">
+        <f>'Параметры и допущения'!$B$9+63</f>
+        <v>46335</v>
+      </c>
+      <c r="G56" s="27">
+        <f>'Параметры и допущения'!$B$9+81</f>
+        <v>46353</v>
+      </c>
+      <c r="H56" s="26" t="n"/>
+      <c r="I56" s="26" t="n"/>
+      <c r="J56" s="26" t="inlineStr">
+        <is>
+          <t>Площадка переведена</t>
+        </is>
+      </c>
+      <c r="K56" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L56" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M56" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N56" s="26" t="n"/>
+      <c r="O56" s="26" t="n"/>
+      <c r="Y56" s="23" t="n"/>
+      <c r="Z56" s="23" t="n"/>
+      <c r="AA56" s="23" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="17" t="n"/>
+      <c r="B57" s="18" t="inlineStr">
         <is>
           <t>ЭТАП 2 — Воронеж (недели 13–16, 445 абонентов)</t>
         </is>
       </c>
-      <c r="C55" s="17" t="n"/>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="17" t="n"/>
-      <c r="F55" s="17" t="n"/>
-      <c r="G55" s="17" t="n"/>
-      <c r="H55" s="17" t="n"/>
-      <c r="I55" s="17" t="n"/>
-      <c r="J55" s="17" t="n"/>
-      <c r="K55" s="17" t="n"/>
-      <c r="L55" s="17" t="n"/>
-      <c r="M55" s="17" t="n"/>
-      <c r="N55" s="17" t="n"/>
-      <c r="O55" s="17" t="n"/>
-      <c r="P55" s="17" t="n"/>
-      <c r="Q55" s="17" t="n"/>
-      <c r="R55" s="17" t="n"/>
-      <c r="S55" s="17" t="n"/>
-      <c r="T55" s="17" t="n"/>
-      <c r="U55" s="17" t="n"/>
-      <c r="V55" s="17" t="n"/>
-      <c r="W55" s="17" t="n"/>
-      <c r="X55" s="17" t="n"/>
-      <c r="Y55" s="17" t="n"/>
-      <c r="Z55" s="17" t="n"/>
-      <c r="AA55" s="17" t="n"/>
-      <c r="AB55" s="17" t="n"/>
-      <c r="AC55" s="17" t="n"/>
-      <c r="AD55" s="17" t="n"/>
-      <c r="AE55" s="17" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B56" s="19" t="inlineStr">
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="17" t="n"/>
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="17" t="n"/>
+      <c r="I57" s="17" t="n"/>
+      <c r="J57" s="17" t="n"/>
+      <c r="K57" s="17" t="n"/>
+      <c r="L57" s="17" t="n"/>
+      <c r="M57" s="17" t="n"/>
+      <c r="N57" s="17" t="n"/>
+      <c r="O57" s="17" t="n"/>
+      <c r="P57" s="17" t="n"/>
+      <c r="Q57" s="17" t="n"/>
+      <c r="R57" s="17" t="n"/>
+      <c r="S57" s="17" t="n"/>
+      <c r="T57" s="17" t="n"/>
+      <c r="U57" s="17" t="n"/>
+      <c r="V57" s="17" t="n"/>
+      <c r="W57" s="17" t="n"/>
+      <c r="X57" s="17" t="n"/>
+      <c r="Y57" s="17" t="n"/>
+      <c r="Z57" s="17" t="n"/>
+      <c r="AA57" s="17" t="n"/>
+      <c r="AB57" s="17" t="n"/>
+      <c r="AC57" s="17" t="n"/>
+      <c r="AD57" s="17" t="n"/>
+      <c r="AE57" s="17" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>Воронежский вынос</t>
         </is>
       </c>
-      <c r="C56" s="19" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>развитие</t>
         </is>
       </c>
-      <c r="D56" s="19" t="inlineStr">
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>Инфраструктура</t>
         </is>
       </c>
-      <c r="E56" s="20" t="n"/>
-      <c r="F56" s="21">
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F58" s="21">
         <f>'Параметры и допущения'!$B$9+84</f>
         <v>46356</v>
       </c>
-      <c r="G56" s="21">
+      <c r="G58" s="21">
         <f>'Параметры и допущения'!$B$9+95</f>
         <v>46367</v>
       </c>
-      <c r="H56" s="21">
-        <f>G56</f>
+      <c r="H58" s="21">
+        <f>G58</f>
         <v>46367</v>
       </c>
-      <c r="I56" s="19" t="inlineStr">
+      <c r="I58" s="19" t="inlineStr">
         <is>
           <t>Воронеж — самая крупная площадка (445 абонентов) и по решению совещания вводится отдельным этапом после всех остальных</t>
         </is>
       </c>
-      <c r="J56" s="19" t="inlineStr">
+      <c r="J58" s="19" t="inlineStr">
         <is>
           <t>Воронеж работает выносом; узлов семь — число нечётное, кворум не требует арбитра</t>
         </is>
       </c>
-      <c r="K56" s="20" t="n"/>
-      <c r="L56" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M56" s="19" t="n">
+      <c r="K58" s="19" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L58" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M58" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="N56" s="22">
-        <f>'Параметры и допущения'!$B$22*M56</f>
+      <c r="N58" s="22">
+        <f>'Параметры и допущения'!$B$26*M58</f>
         <v>92120</v>
       </c>
-      <c r="O56" s="22" t="n">
+      <c r="O58" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="AB56" s="23" t="n"/>
-      <c r="AC56" s="23" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="24" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B57" s="25" t="inlineStr">
-        <is>
-          <t>Проверить, что все шесть узлов Synced до начала работ</t>
-        </is>
-      </c>
-      <c r="C57" s="26" t="n"/>
-      <c r="D57" s="26" t="n"/>
-      <c r="E57" s="26" t="n"/>
-      <c r="F57" s="27">
-        <f>'Параметры и допущения'!$B$9+84</f>
-        <v>46356</v>
-      </c>
-      <c r="G57" s="27">
-        <f>'Параметры и допущения'!$B$9+88</f>
-        <v>46360</v>
-      </c>
-      <c r="H57" s="26" t="n"/>
-      <c r="I57" s="26" t="n"/>
-      <c r="J57" s="26" t="inlineStr">
-        <is>
-          <t>Кластер здоров, расхождений нет</t>
-        </is>
-      </c>
-      <c r="K57" s="28" t="n"/>
-      <c r="L57" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M57" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" s="26" t="n"/>
-      <c r="O57" s="26" t="n"/>
-      <c r="AB57" s="23" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="24" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="B58" s="25" t="inlineStr">
-        <is>
-          <t>Клонировать мастер и расшить клон в вынос</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="n"/>
-      <c r="D58" s="26" t="n"/>
-      <c r="E58" s="26" t="n"/>
-      <c r="F58" s="27">
-        <f>'Параметры и допущения'!$B$9+84</f>
-        <v>46356</v>
-      </c>
-      <c r="G58" s="27">
-        <f>'Параметры и допущения'!$B$9+88</f>
-        <v>46360</v>
-      </c>
-      <c r="H58" s="26" t="n"/>
-      <c r="I58" s="26" t="n"/>
-      <c r="J58" s="26" t="inlineStr">
-        <is>
-          <t>Вынос в кластере</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="n"/>
-      <c r="L58" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M58" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" s="26" t="n"/>
-      <c r="O58" s="26" t="n"/>
       <c r="AB58" s="23" t="n"/>
+      <c r="AC58" s="23" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>Межузловые транки и диалплан</t>
+          <t>Проверить, что все шесть узлов Synced до начала работ</t>
         </is>
       </c>
       <c r="C59" s="26" t="n"/>
@@ -4092,17 +4371,21 @@
       <c r="I59" s="26" t="n"/>
       <c r="J59" s="26" t="inlineStr">
         <is>
-          <t>Вызовы с другими площадками проходят</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="n"/>
+          <t>Кластер здоров, расхождений нет</t>
+        </is>
+      </c>
+      <c r="K59" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L59" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M59" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59" s="26" t="n"/>
       <c r="O59" s="26" t="n"/>
@@ -4111,75 +4394,83 @@
     <row r="60">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>Локальный транк оператора</t>
+          <t>Клонировать мастер и расшить клон в вынос</t>
         </is>
       </c>
       <c r="C60" s="26" t="n"/>
       <c r="D60" s="26" t="n"/>
       <c r="E60" s="26" t="n"/>
       <c r="F60" s="27">
-        <f>'Параметры и допущения'!$B$9+91</f>
-        <v>46363</v>
+        <f>'Параметры и допущения'!$B$9+84</f>
+        <v>46356</v>
       </c>
       <c r="G60" s="27">
-        <f>'Параметры и допущения'!$B$9+95</f>
-        <v>46367</v>
+        <f>'Параметры и допущения'!$B$9+88</f>
+        <v>46360</v>
       </c>
       <c r="H60" s="26" t="n"/>
       <c r="I60" s="26" t="n"/>
       <c r="J60" s="26" t="inlineStr">
         <is>
-          <t>Свой выход в город работает</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="n"/>
+          <t>Вынос в кластере</t>
+        </is>
+      </c>
+      <c r="K60" s="26" t="inlineStr">
+        <is>
+          <t>Дулепов А.</t>
+        </is>
+      </c>
       <c r="L60" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
         </is>
       </c>
       <c r="M60" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N60" s="26" t="n"/>
       <c r="O60" s="26" t="n"/>
-      <c r="AC60" s="23" t="n"/>
+      <c r="AB60" s="23" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>Перевести телефоны на вынос через провижининг</t>
+          <t>Межузловые транки и диалплан</t>
         </is>
       </c>
       <c r="C61" s="26" t="n"/>
       <c r="D61" s="26" t="n"/>
       <c r="E61" s="26" t="n"/>
       <c r="F61" s="27">
-        <f>'Параметры и допущения'!$B$9+91</f>
-        <v>46363</v>
+        <f>'Параметры и допущения'!$B$9+84</f>
+        <v>46356</v>
       </c>
       <c r="G61" s="27">
-        <f>'Параметры и допущения'!$B$9+95</f>
-        <v>46367</v>
+        <f>'Параметры и допущения'!$B$9+88</f>
+        <v>46360</v>
       </c>
       <c r="H61" s="26" t="n"/>
       <c r="I61" s="26" t="n"/>
       <c r="J61" s="26" t="inlineStr">
         <is>
-          <t>Телефоны регистрируются в Воронеже, резервный сервер — ЦОД-1</t>
-        </is>
-      </c>
-      <c r="K61" s="28" t="n"/>
+          <t>Вызовы с другими площадками проходят</t>
+        </is>
+      </c>
+      <c r="K61" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
       <c r="L61" s="26" t="inlineStr">
         <is>
           <t>планируется</t>
@@ -4190,84 +4481,63 @@
       </c>
       <c r="N61" s="26" t="n"/>
       <c r="O61" s="26" t="n"/>
-      <c r="AC61" s="23" t="n"/>
+      <c r="AB61" s="23" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B62" s="19" t="inlineStr">
-        <is>
-          <t>Консолидация воронежских АТС</t>
-        </is>
-      </c>
-      <c r="C62" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E62" s="20" t="n"/>
-      <c r="F62" s="21">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>Локальный транк оператора</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="n"/>
+      <c r="D62" s="26" t="n"/>
+      <c r="E62" s="26" t="n"/>
+      <c r="F62" s="27">
         <f>'Параметры и допущения'!$B$9+91</f>
         <v>46363</v>
       </c>
-      <c r="G62" s="21">
-        <f>'Параметры и допущения'!$B$9+102</f>
-        <v>46374</v>
-      </c>
-      <c r="H62" s="21">
-        <f>G62</f>
-        <v>46374</v>
-      </c>
-      <c r="I62" s="19" t="inlineStr">
-        <is>
-          <t>Мясокомбинат и Калуга — 216 абонентов на двух отдельных станциях</t>
-        </is>
-      </c>
-      <c r="J62" s="19" t="inlineStr">
-        <is>
-          <t>Абоненты переведены на воронежский вынос, станции выведены из эксплуатации</t>
-        </is>
-      </c>
-      <c r="K62" s="19" t="inlineStr">
-        <is>
-          <t>Кириевская Е.</t>
-        </is>
-      </c>
-      <c r="L62" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M62" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="N62" s="22">
-        <f>'Параметры и допущения'!$B$22*M62</f>
-        <v>69090</v>
-      </c>
-      <c r="O62" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="G62" s="27">
+        <f>'Параметры и допущения'!$B$9+95</f>
+        <v>46367</v>
+      </c>
+      <c r="H62" s="26" t="n"/>
+      <c r="I62" s="26" t="n"/>
+      <c r="J62" s="26" t="inlineStr">
+        <is>
+          <t>Свой выход в город работает</t>
+        </is>
+      </c>
+      <c r="K62" s="26" t="inlineStr">
+        <is>
+          <t>Цеховской В.</t>
+        </is>
+      </c>
+      <c r="L62" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M62" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="26" t="n"/>
+      <c r="O62" s="26" t="n"/>
       <c r="AC62" s="23" t="n"/>
-      <c r="AD62" s="23" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>Мясокомбинат — 187 абонентов</t>
+          <t>Перевести телефоны на вынос через провижининг</t>
         </is>
       </c>
       <c r="C63" s="26" t="n"/>
@@ -4278,19 +4548,19 @@
         <v>46363</v>
       </c>
       <c r="G63" s="27">
-        <f>'Параметры и допущения'!$B$9+102</f>
-        <v>46374</v>
+        <f>'Параметры и допущения'!$B$9+95</f>
+        <v>46367</v>
       </c>
       <c r="H63" s="26" t="n"/>
       <c r="I63" s="26" t="n"/>
       <c r="J63" s="26" t="inlineStr">
         <is>
-          <t>Станция выведена</t>
+          <t>Телефоны регистрируются в Воронеже, резервный сервер — ЦОД-1</t>
         </is>
       </c>
       <c r="K63" s="26" t="inlineStr">
         <is>
-          <t>Кириевская Е.</t>
+          <t>Цеховской В.</t>
         </is>
       </c>
       <c r="L63" s="26" t="inlineStr">
@@ -4299,154 +4569,157 @@
         </is>
       </c>
       <c r="M63" s="26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N63" s="26" t="n"/>
       <c r="O63" s="26" t="n"/>
       <c r="AC63" s="23" t="n"/>
-      <c r="AD63" s="23" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="inlineStr">
-        <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="B64" s="25" t="inlineStr">
-        <is>
-          <t>Калуга — 29 абонентов</t>
-        </is>
-      </c>
-      <c r="C64" s="26" t="n"/>
-      <c r="D64" s="26" t="n"/>
-      <c r="E64" s="26" t="n"/>
-      <c r="F64" s="27">
-        <f>'Параметры и допущения'!$B$9+98</f>
-        <v>46370</v>
-      </c>
-      <c r="G64" s="27">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>Консолидация воронежских АТС</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F64" s="21">
+        <f>'Параметры и допущения'!$B$9+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G64" s="21">
         <f>'Параметры и допущения'!$B$9+102</f>
         <v>46374</v>
       </c>
-      <c r="H64" s="26" t="n"/>
-      <c r="I64" s="26" t="n"/>
-      <c r="J64" s="26" t="inlineStr">
-        <is>
-          <t>Станция выведена</t>
-        </is>
-      </c>
-      <c r="K64" s="26" t="inlineStr">
+      <c r="H64" s="21">
+        <f>G64</f>
+        <v>46374</v>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>Мясокомбинат и Калуга — 216 абонентов на двух отдельных станциях</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>Абоненты переведены на воронежский вынос, станции выведены из эксплуатации</t>
+        </is>
+      </c>
+      <c r="K64" s="19" t="inlineStr">
         <is>
           <t>Кириевская Е.</t>
         </is>
       </c>
-      <c r="L64" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M64" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N64" s="26" t="n"/>
-      <c r="O64" s="26" t="n"/>
+      <c r="L64" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N64" s="22">
+        <f>'Параметры и допущения'!$B$26*M64</f>
+        <v>69090</v>
+      </c>
+      <c r="O64" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="23" t="n"/>
       <c r="AD64" s="23" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>Перевод воронежских абонентов на единый план нумерации</t>
-        </is>
-      </c>
-      <c r="C65" s="19" t="inlineStr">
-        <is>
-          <t>развитие</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>Инфраструктура</t>
-        </is>
-      </c>
-      <c r="E65" s="20" t="n"/>
-      <c r="F65" s="21">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>Мясокомбинат — 187 абонентов</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="n"/>
+      <c r="D65" s="26" t="n"/>
+      <c r="E65" s="26" t="n"/>
+      <c r="F65" s="27">
         <f>'Параметры и допущения'!$B$9+91</f>
         <v>46363</v>
       </c>
-      <c r="G65" s="21">
-        <f>'Параметры и допущения'!$B$9+109</f>
-        <v>46381</v>
-      </c>
-      <c r="H65" s="21">
-        <f>G65</f>
-        <v>46381</v>
-      </c>
-      <c r="I65" s="19" t="inlineStr">
-        <is>
-          <t>445 абонентов Воронежа и его станций используют старую нумерацию</t>
-        </is>
-      </c>
-      <c r="J65" s="19" t="inlineStr">
-        <is>
-          <t>Воронеж переведён на пятизначную нумерацию, переадресации со старых номеров сняты</t>
-        </is>
-      </c>
-      <c r="K65" s="19" t="inlineStr">
+      <c r="G65" s="27">
+        <f>'Параметры и допущения'!$B$9+102</f>
+        <v>46374</v>
+      </c>
+      <c r="H65" s="26" t="n"/>
+      <c r="I65" s="26" t="n"/>
+      <c r="J65" s="26" t="inlineStr">
+        <is>
+          <t>Станция выведена</t>
+        </is>
+      </c>
+      <c r="K65" s="26" t="inlineStr">
         <is>
           <t>Кириевская Е.</t>
         </is>
       </c>
-      <c r="L65" s="19" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M65" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="N65" s="22">
-        <f>'Параметры и допущения'!$B$22*M65</f>
-        <v>69090</v>
-      </c>
-      <c r="O65" s="22" t="n">
-        <v>0</v>
-      </c>
+      <c r="L65" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M65" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N65" s="26" t="n"/>
+      <c r="O65" s="26" t="n"/>
       <c r="AC65" s="23" t="n"/>
       <c r="AD65" s="23" t="n"/>
-      <c r="AE65" s="23" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>Воронеж и Мясокомбинат — 416 абонентов</t>
+          <t>Калуга — 29 абонентов</t>
         </is>
       </c>
       <c r="C66" s="26" t="n"/>
       <c r="D66" s="26" t="n"/>
       <c r="E66" s="26" t="n"/>
       <c r="F66" s="27">
-        <f>'Параметры и допущения'!$B$9+91</f>
-        <v>46363</v>
+        <f>'Параметры и допущения'!$B$9+98</f>
+        <v>46370</v>
       </c>
       <c r="G66" s="27">
-        <f>'Параметры и допущения'!$B$9+109</f>
-        <v>46381</v>
+        <f>'Параметры и допущения'!$B$9+102</f>
+        <v>46374</v>
       </c>
       <c r="H66" s="26" t="n"/>
       <c r="I66" s="26" t="n"/>
       <c r="J66" s="26" t="inlineStr">
         <is>
-          <t>Площадки переведены</t>
+          <t>Станция выведена</t>
         </is>
       </c>
       <c r="K66" s="26" t="inlineStr">
@@ -4460,87 +4733,205 @@
         </is>
       </c>
       <c r="M66" s="26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N66" s="26" t="n"/>
       <c r="O66" s="26" t="n"/>
-      <c r="AC66" s="23" t="n"/>
       <c r="AD66" s="23" t="n"/>
-      <c r="AE66" s="23" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="inlineStr">
-        <is>
-          <t>13.2</t>
-        </is>
-      </c>
-      <c r="B67" s="25" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>Перевод воронежских абонентов на единый план нумерации</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="inlineStr">
+        <is>
+          <t>развитие</t>
+        </is>
+      </c>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>Савенко В.</t>
+        </is>
+      </c>
+      <c r="F67" s="21">
+        <f>'Параметры и допущения'!$B$9+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G67" s="21">
+        <f>'Параметры и допущения'!$B$9+109</f>
+        <v>46381</v>
+      </c>
+      <c r="H67" s="21">
+        <f>G67</f>
+        <v>46381</v>
+      </c>
+      <c r="I67" s="19" t="inlineStr">
+        <is>
+          <t>445 абонентов Воронежа и его станций используют старую нумерацию</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>Воронеж переведён на пятизначную нумерацию, переадресации со старых номеров сняты</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L67" s="19" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M67" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N67" s="22">
+        <f>'Параметры и допущения'!$B$26*M67</f>
+        <v>69090</v>
+      </c>
+      <c r="O67" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="23" t="n"/>
+      <c r="AD67" s="23" t="n"/>
+      <c r="AE67" s="23" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>Воронеж и Мясокомбинат — 416 абонентов</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="n"/>
+      <c r="D68" s="26" t="n"/>
+      <c r="E68" s="26" t="n"/>
+      <c r="F68" s="27">
+        <f>'Параметры и допущения'!$B$9+91</f>
+        <v>46363</v>
+      </c>
+      <c r="G68" s="27">
+        <f>'Параметры и допущения'!$B$9+109</f>
+        <v>46381</v>
+      </c>
+      <c r="H68" s="26" t="n"/>
+      <c r="I68" s="26" t="n"/>
+      <c r="J68" s="26" t="inlineStr">
+        <is>
+          <t>Площадки переведены</t>
+        </is>
+      </c>
+      <c r="K68" s="26" t="inlineStr">
+        <is>
+          <t>Кириевская Е.</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M68" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" s="26" t="n"/>
+      <c r="O68" s="26" t="n"/>
+      <c r="AC68" s="23" t="n"/>
+      <c r="AD68" s="23" t="n"/>
+      <c r="AE68" s="23" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
         <is>
           <t>Калуга — сверка: часть абонентов уже на пятизначных</t>
         </is>
       </c>
-      <c r="C67" s="26" t="n"/>
-      <c r="D67" s="26" t="n"/>
-      <c r="E67" s="26" t="n"/>
-      <c r="F67" s="27">
+      <c r="C69" s="26" t="n"/>
+      <c r="D69" s="26" t="n"/>
+      <c r="E69" s="26" t="n"/>
+      <c r="F69" s="27">
         <f>'Параметры и допущения'!$B$9+105</f>
         <v>46377</v>
       </c>
-      <c r="G67" s="27">
+      <c r="G69" s="27">
         <f>'Параметры и допущения'!$B$9+109</f>
         <v>46381</v>
       </c>
-      <c r="H67" s="26" t="n"/>
-      <c r="I67" s="26" t="n"/>
-      <c r="J67" s="26" t="inlineStr">
+      <c r="H69" s="26" t="n"/>
+      <c r="I69" s="26" t="n"/>
+      <c r="J69" s="26" t="inlineStr">
         <is>
           <t>Расхождений нет, переадресации сняты</t>
         </is>
       </c>
-      <c r="K67" s="26" t="inlineStr">
+      <c r="K69" s="26" t="inlineStr">
         <is>
           <t>Кириевская Е.</t>
         </is>
       </c>
-      <c r="L67" s="26" t="inlineStr">
-        <is>
-          <t>планируется</t>
-        </is>
-      </c>
-      <c r="M67" s="26" t="n">
+      <c r="L69" s="26" t="inlineStr">
+        <is>
+          <t>планируется</t>
+        </is>
+      </c>
+      <c r="M69" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="N67" s="26" t="n"/>
-      <c r="O67" s="26" t="n"/>
-      <c r="AE67" s="23" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="29" t="n"/>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="N69" s="26" t="n"/>
+      <c r="O69" s="26" t="n"/>
+      <c r="AE69" s="23" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="n"/>
+      <c r="B70" s="28" t="inlineStr">
         <is>
           <t>ИТОГО по проекту</t>
         </is>
       </c>
-      <c r="C68" s="29" t="n"/>
-      <c r="D68" s="29" t="n"/>
-      <c r="E68" s="29" t="n"/>
-      <c r="F68" s="29" t="n"/>
-      <c r="G68" s="29" t="n"/>
-      <c r="H68" s="29" t="n"/>
-      <c r="I68" s="29" t="n"/>
-      <c r="J68" s="29" t="n"/>
-      <c r="K68" s="29" t="n"/>
-      <c r="L68" s="29" t="n"/>
-      <c r="M68" s="29">
-        <f>M4+M12+M19+M23+M27+M33+M39+M42+M45+M49+M56+M62+M65</f>
-        <v>98</v>
-      </c>
-      <c r="N68" s="30">
-        <f>N4+N12+N19+N23+N27+N33+N39+N42+N45+N49+N56+N62+N65</f>
-        <v>1128470</v>
-      </c>
-      <c r="O68" s="30">
-        <f>O4+O12+O19+O23+O27+O33+O39+O42+O45+O49+O56+O62+O65</f>
+      <c r="C70" s="28" t="n"/>
+      <c r="D70" s="28" t="n"/>
+      <c r="E70" s="28" t="n"/>
+      <c r="F70" s="28" t="n"/>
+      <c r="G70" s="28" t="n"/>
+      <c r="H70" s="28" t="n"/>
+      <c r="I70" s="28" t="n"/>
+      <c r="J70" s="28" t="n"/>
+      <c r="K70" s="28" t="n"/>
+      <c r="L70" s="28" t="n"/>
+      <c r="M70" s="28">
+        <f>M4+M11+M18+M21+M25+M29+M35+M41+M44+M47+M51+M58+M64+M67</f>
+        <v>100</v>
+      </c>
+      <c r="N70" s="29">
+        <f>N4+N11+N18+N21+N25+N29+N35+N41+N44+N47+N51+N58+N64+N67</f>
+        <v>1151500</v>
+      </c>
+      <c r="O70" s="29">
+        <f>O4+O11+O18+O21+O25+O29+O35+O41+O44+O47+O51+O58+O64+O67</f>
         <v>0</v>
       </c>
     </row>
